--- a/go/xlsx/nyusha-juryo-form.xlsx
+++ b/go/xlsx/nyusha-juryo-form.xlsx
@@ -1603,7 +1603,7 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>本ファイルはマイナンバー等の特定個人情報を含みます。メール添付で平文送付せず、①パスワード付きZIP（パスワードは別経路で連絡）、または ②当事務所のセキュア便 でご返送ください。</t>
+          <t>本ファイルはマイナンバー等の特定個人情報を含みます。メール添付で平文送付せず、①パスワード付きZIP（パスワードは別経路で連絡）、または ②当事務所の案件ページ（受任メールのリンク） でご返送ください。</t>
         </is>
       </c>
     </row>
@@ -2003,7 +2003,7 @@
     <row r="27" ht="53.5" customHeight="1">
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>【ご返送方法】　マイナンバー等の重要情報を含みます。メール平文への添付は避け、パスワード付きZIP（パスワードは別経路でご連絡）または当事務所のセキュア便でご返送ください。マイナンバーを別経路で回収する運用の場合は、このフォームには入力せず、会社所定の安全な経路で提出してください。</t>
+          <t>【ご返送方法】　マイナンバー等の重要情報を含みます。メール平文への添付は避け、パスワード付きZIP（パスワードは別経路でご連絡）または当事務所の案件ページ（受任メールのリンク）からお送りください。マイナンバーを別経路で回収する運用の場合は、このフォームには入力せず、会社所定の安全な経路で提出してください。</t>
         </is>
       </c>
     </row>

--- a/go/xlsx/nyusha-juryo-form.xlsx
+++ b/go/xlsx/nyusha-juryo-form.xlsx
@@ -726,12 +726,12 @@
     </comment>
     <comment ref="B7" authorId="0" shapeId="0">
       <text>
-        <t>用途：資格取得届の被保険者氏名。電子申請の本人特定。</t>
+        <t>用途：資格取得届の被保険者氏名。届出の本人特定。</t>
       </text>
     </comment>
     <comment ref="C7" authorId="0" shapeId="0">
       <text>
-        <t>用途：電子申請のフリガナ欄（全角カタカナ）。</t>
+        <t>用途：届出のフリガナ欄（全角カタカナ）。</t>
       </text>
     </comment>
     <comment ref="D7" authorId="0" shapeId="0">
@@ -1307,7 +1307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C44"/>
+  <dimension ref="B1:C44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1329,7 +1329,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="22" customHeight="1">
       <c r="B4" s="3" t="inlineStr">
         <is>
@@ -1373,7 +1372,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9" ht="22" customHeight="1">
       <c r="B9" s="3" t="inlineStr">
         <is>
@@ -1384,11 +1382,10 @@
     <row r="10" ht="49" customHeight="1">
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>新しく入社された方の『社会保険（健康保険・厚生年金）』『雇用保険』の資格取得手続き（電子申請）に必要な情報を、正確に・もれなく回収するためのフォームです。電子申請への取込を見据えた項目構成になっています。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
+          <t>新しく入社された方の『社会保険（健康保険・厚生年金）』『雇用保険』の資格取得の届出に必要な情報を、正確に・もれなく回収するためのフォームです。届出様式への転記を見据えた項目構成になっています。</t>
+        </is>
+      </c>
+    </row>
     <row r="12" ht="22" customHeight="1">
       <c r="B12" s="3" t="inlineStr">
         <is>
@@ -1444,7 +1441,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18" ht="22" customHeight="1">
       <c r="B18" s="3" t="inlineStr">
         <is>
@@ -1560,7 +1556,6 @@
         </is>
       </c>
     </row>
-    <row r="28"/>
     <row r="29" ht="22" customHeight="1">
       <c r="B29" s="3" t="inlineStr">
         <is>
@@ -1575,7 +1570,6 @@
         </is>
       </c>
     </row>
-    <row r="31"/>
     <row r="32" ht="22" customHeight="1">
       <c r="B32" s="3" t="inlineStr">
         <is>
@@ -1619,7 +1613,6 @@
         </is>
       </c>
     </row>
-    <row r="36"/>
     <row r="37" ht="22" customHeight="1">
       <c r="B37" s="3" t="inlineStr">
         <is>
@@ -1675,7 +1668,6 @@
         </is>
       </c>
     </row>
-    <row r="42"/>
     <row r="43" ht="22" customHeight="1">
       <c r="B43" s="3" t="inlineStr">
         <is>
@@ -1713,7 +1705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="B1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1736,7 +1728,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="24" customHeight="1">
       <c r="B4" s="3" t="inlineStr">
         <is>
@@ -1873,7 +1864,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15" ht="24" customHeight="1">
       <c r="B15" s="3" t="inlineStr">
         <is>
@@ -1983,7 +1973,6 @@
         </is>
       </c>
     </row>
-    <row r="24"/>
     <row r="25" ht="24" customHeight="1">
       <c r="B25" s="3" t="inlineStr">
         <is>
@@ -2041,7 +2030,6 @@
       <c r="C30" s="69" t="n"/>
       <c r="D30" s="70" t="n"/>
     </row>
-    <row r="31"/>
     <row r="32" ht="24" customHeight="1">
       <c r="B32" s="3" t="inlineStr">
         <is>
@@ -2170,7 +2158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="B1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2207,7 +2195,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6" ht="38" customHeight="1">
       <c r="B6" s="31" t="inlineStr">
         <is>
@@ -8845,7 +8832,7 @@
       <formula>AND(B8&lt;&gt;"",ISERROR(FIND("　",B8)),ISERROR(FIND(" ",B8)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="8">
+  <dataValidations count="9">
     <dataValidation sqref="A7:A67" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="入力エラー" error="整数で入力してください。" promptTitle="入力のヒント" prompt="シート①の『フォーム内No.』（左端の番号）を入力。どの従業員の被扶養者かを紐付けます。" type="whole" errorStyle="stop" operator="between">
       <formula1>1</formula1>
       <formula2>9999</formula2>
@@ -8873,6 +8860,9 @@
     </dataValidation>
     <dataValidation sqref="L7:L67" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="入力エラー" error="一覧から選択してください。" promptTitle="入力のヒント" prompt="配偶者で20歳以上60歳未満のときに該当の可能性。第3号被保険者の届出要否の確認に使用。" type="list" errorStyle="stop">
       <formula1>m_第3号</formula1>
+    </dataValidation>
+    <dataValidation sqref="G7:G67" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="入力のヒント" prompt="12桁の数字。ハイフン無し。会社所定の安全な経路で別提出する場合は、ドロップダウンから『別経路提出』を選んでください。入社時点で未回収なら『後日提出』を選択します。" type="list">
+      <formula1>m_番号提出状態</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="0"/>

--- a/go/xlsx/nyusha-juryo-form.xlsx
+++ b/go/xlsx/nyusha-juryo-form.xlsx
@@ -40,6 +40,7 @@
     <definedName name="正社員週所定">'⓪ 事業所設定'!$C$13</definedName>
     <definedName name="正社員月所定">'⓪ 事業所設定'!$C$14</definedName>
     <definedName name="判定基準日">'⓪ 事業所設定'!$C$17</definedName>
+    <definedName name="m_職種">'_マスタ（非表示）'!$S$2:$S$13</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'⓪ 事業所設定'!$1:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'① 従業員情報（本人）'!$1:$7</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'② 被扶養者情報'!$1:$6</definedName>
@@ -816,7 +817,7 @@
     </comment>
     <comment ref="T7" authorId="0" shapeId="0">
       <text>
-        <t>用途：固定手当（月額）。報酬月額・8.8万円要件に算入。</t>
+        <t>用途：固定手当（月額）。社保の報酬月額に算入します。うち家族手当・精皆勤手当は右の『うち家族手当・精皆勤手当』欄にも金額をご記入ください（8.8万円要件の判定から差し引きます）。</t>
       </text>
     </comment>
     <comment ref="U7" authorId="0" shapeId="0">
@@ -939,6 +940,21 @@
         <t>用途：連絡事項（外字・特記など）。自由記入。</t>
       </text>
     </comment>
+    <comment ref="AV7" authorId="0" shapeId="0">
+      <text>
+        <t>用途：雇用保険 資格取得届の職種欄。近いものを選んでください（分からないときは『分からない』で構いません）。〔区分名は提出前に現行様式で照合します〕</t>
+      </text>
+    </comment>
+    <comment ref="AW7" authorId="0" shapeId="0">
+      <text>
+        <t>用途：8.8万円（賃金要件）の判定から差し引く手当。左の『固定手当』に含めた金額のうち、家族手当・精皆勤手当の分をご記入ください。〔健保法3条9項4号・要確認〕</t>
+      </text>
+    </comment>
+    <comment ref="AX7" authorId="0" shapeId="0">
+      <text>
+        <t>用途：他社でも社会保険（健康保険・厚生年金）に加入しているか。『はい』のときは二以上事業所勤務届が別途必要です。</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -1012,6 +1028,11 @@
     <comment ref="M6" authorId="0" shapeId="0">
       <text>
         <t>用途：連絡事項。自由記入。</t>
+      </text>
+    </comment>
+    <comment ref="P6" authorId="0" shapeId="0">
+      <text>
+        <t>用途：別居している被扶養者の住所（生計維持・仕送りの確認）。同居の方は記入不要です。</t>
       </text>
     </comment>
   </commentList>
@@ -1368,7 +1389,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>1.0（更新日 2026-07-04）</t>
+          <t>1.0（更新日 2026-09-11）</t>
         </is>
       </c>
     </row>
@@ -1382,7 +1403,7 @@
     <row r="10" ht="49" customHeight="1">
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>新しく入社された方の『社会保険（健康保険・厚生年金）』『雇用保険』の資格取得の届出に必要な情報を、正確に・もれなく回収するためのフォームです。届出様式への転記を見据えた項目構成になっています。</t>
+          <t>健康保険・厚生年金保険と雇用保険の資格取得手続きに必要な情報をご記入いただくフォームです。</t>
         </is>
       </c>
     </row>
@@ -1468,7 +1489,7 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>ヘッダーが薄い灰色。該当する場合に入力してください。</t>
+          <t>ヘッダーが薄い灰色。該当する場合に入力してください。【条件必須】と書かれた欄は、その条件に当てはまる方は必ず入力してください。</t>
         </is>
       </c>
     </row>
@@ -1480,7 +1501,7 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>灰色で塗られ、編集できません。自動で計算・判定されます。</t>
+          <t>灰色。自動で計算・判定されます（上書きしないでください）。</t>
         </is>
       </c>
     </row>
@@ -1597,7 +1618,7 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>本ファイルはマイナンバー等の特定個人情報を含みます。メール添付で平文送付せず、①パスワード付きZIP（パスワードは別経路で連絡）、または ②当事務所の案件ページ（受任メールのリンク） でご返送ください。</t>
+          <t>受任メールのリンクから案件ページを開き、記入したこのファイルをそのままお送りください。ZIPにする必要はありません。この経路は暗号化されており、メール添付より安全です。メールに直接添付して送るのは避けてください（マイナンバー等の特定個人情報を含みます）。</t>
         </is>
       </c>
     </row>
@@ -1620,49 +1641,61 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="49" customHeight="1">
+    <row r="38" ht="34" customHeight="1">
       <c r="B38" s="4" t="inlineStr">
         <is>
+          <t>本人にご確認いただく欄</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>本人にご確認いただく欄は、当事務所の書式『入社時 本人情報記入シート』（https://minano-sr.com/shoshiki/D-52.html）を印刷してご本人に記入いただくと、そのままこのフォームに転記できます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="49" customHeight="1">
+      <c r="B39" s="4" t="inlineStr">
+        <is>
           <t>基本の考え方</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>入社時点でどうしても分からない欄は、空欄のまま備考に『○○は後日提出』とご記入ください。分かり次第ご連絡いただければ当方で補います。下記は特に間違えやすい番号類の扱いです。</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="64" customHeight="1">
-      <c r="B39" s="4" t="inlineStr">
+    <row r="40" ht="64" customHeight="1">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>基礎年金番号</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>マイナンバーをご記入いただければ、基礎年金番号は省略できます（資格取得届はマイナンバーで提出できます）。マイナンバーを別経路提出にする、または番号が不明なときは、セルのドロップダウンから『後日提出』を選んでください（未入力扱いになりません）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="34" customHeight="1">
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>雇用保険被保険者番号</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>初めて就職する方・前職が無い方は空欄で構いません（新しく番号を取得します）。前職はあるが番号が不明なときは『後日提出』を選択してください。</t>
         </is>
       </c>
     </row>
     <row r="41" ht="34" customHeight="1">
       <c r="B41" s="4" t="inlineStr">
         <is>
+          <t>雇用保険被保険者番号</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>初めて就職する方・前職が無い方は空欄で構いません（新しく番号を取得します）。前職はあるが番号が不明なときは『後日提出』を選択してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="34" customHeight="1">
+      <c r="B42" s="4" t="inlineStr">
+        <is>
           <t>2か月超／31日以上 見込み</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>この2列は自動表示です（入力不要）。雇用期間の定め・契約満了日・更新の見込みを入れると自動で判定されます。</t>
         </is>
@@ -1724,7 +1757,7 @@
     <row r="2" ht="37" customHeight="1">
       <c r="B2" s="15" t="inlineStr">
         <is>
-          <t>このシートは顧問先（ご担当者さま）が、入力 → 提出前の確認 → 当事務所への返送まで迷わず進めるための案内です。本体シートをご記入のうえ、最後にここをご確認ください。</t>
+          <t>このシートは貴社（ご担当者さま）が、入力 → 提出前の確認 → 当事務所への返送まで迷わず進めるための案内です。本体シートをご記入のうえ、最後にここをご確認ください。</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1771,7 @@
     <row r="5" ht="26" customHeight="1">
       <c r="B5" s="16" t="inlineStr">
         <is>
-          <t>顧問先名</t>
+          <t>貴社名</t>
         </is>
       </c>
       <c r="C5" s="17" t="n"/>
@@ -1842,23 +1875,39 @@
         </is>
       </c>
       <c r="C12" s="23">
-        <f>IF('① 従業員情報（本人）'!B4=0,"未入力（対象者なし）",IF('① 従業員情報（本人）'!F4=0,"提出可（必須の未入力なし）","未入力あり：本体シートの薄赤セル・行ステータスをご確認ください"))</f>
+        <f>IF('① 従業員情報（本人）'!B4=0,"未入力（対象者なし）",IF(AND('① 従業員情報（本人）'!F4=0,'① 従業員情報（本人）'!D4&lt;&gt;'① 従業員情報（本人）'!B4),"確認が必要：式の入っていない行があります（行を挿入せず9〜58行にご記入ください）",IF(COUNTBLANK('⓪ 事業所設定'!$C$6)+COUNTBLANK('⓪ 事業所設定'!$C$8)+COUNTBLANK('⓪ 事業所設定'!$C$9)+COUNTBLANK('⓪ 事業所設定'!$C$11)+COUNTBLANK('⓪ 事業所設定'!$C$13)+COUNTBLANK('⓪ 事業所設定'!$C$14)+COUNTBLANK('⓪ 事業所設定'!$C$17)&gt;0,"未入力あり：⓪事業所設定をご記入ください",IF('① 従業員情報（本人）'!F4&gt;0,"未入力あり：本体シートの薄赤セル・行ステータスをご確認ください",IF('② 被扶養者情報'!E4&gt;0,"未入力あり：②被扶養者情報をご確認ください",IF(ISNUMBER(SEARCH("未入力",$C$13)),"未入力あり：被扶養者ありの方の②をご記入ください","提出可（必須の未入力なし）"))))))</f>
         <v/>
       </c>
       <c r="D12" s="18" t="inlineStr">
         <is>
-          <t>必須の未入力が無ければ『提出可』。残っていれば本体をご確認ください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="26" customHeight="1">
-      <c r="B13" s="16" t="inlineStr">
+          <t>⓪事業所設定・①本体・②被扶養者のすべてに必須の未入力が無ければ『提出可』。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="37" customHeight="1">
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>被扶養者の突合（自動）</t>
+        </is>
+      </c>
+      <c r="C13" s="23">
+        <f>IF('① 従業員情報（本人）'!$B$4=0,"—",IF(COUNTIFS('① 従業員情報（本人）'!$B$9:$B$58,"&lt;&gt;",'① 従業員情報（本人）'!$AQ$9:$AQ$58,"あり")=SUMPRODUCT(('② 被扶養者情報'!$A$8:$A$67&lt;&gt;"")/COUNTIF('② 被扶養者情報'!$A$8:$A$67,'② 被扶養者情報'!$A$8:$A$67&amp;"")),"✓ 一致（被扶養者ありの方 "&amp;COUNTIFS('① 従業員情報（本人）'!$B$9:$B$58,"&lt;&gt;",'① 従業員情報（本人）'!$AQ$9:$AQ$58,"あり")&amp;" 名／②の対象者 "&amp;SUMPRODUCT(('② 被扶養者情報'!$A$8:$A$67&lt;&gt;"")/COUNTIF('② 被扶養者情報'!$A$8:$A$67,'② 被扶養者情報'!$A$8:$A$67&amp;""))&amp;" 名）","被扶養者ありの方の②が未入力です（①であり "&amp;COUNTIFS('① 従業員情報（本人）'!$B$9:$B$58,"&lt;&gt;",'① 従業員情報（本人）'!$AQ$9:$AQ$58,"あり")&amp;" 名／②の対象者 "&amp;SUMPRODUCT(('② 被扶養者情報'!$A$8:$A$67&lt;&gt;"")/COUNTIF('② 被扶養者情報'!$A$8:$A$67,'② 被扶養者情報'!$A$8:$A$67&amp;""))&amp;" 名）"))</f>
+        <v/>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>①で『被扶養者の有無＝あり』の人数と、②に入力された対象者の人数を突き合わせます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>事務所への連絡事項</t>
         </is>
       </c>
-      <c r="C13" s="17" t="n"/>
-      <c r="D13" s="18" t="inlineStr">
+      <c r="C14" s="17" t="n"/>
+      <c r="D14" s="18" t="inlineStr">
         <is>
           <t>不明点・特記事項があればご記入ください（任意）。</t>
         </is>
@@ -1867,31 +1916,28 @@
     <row r="15" ht="24" customHeight="1">
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>② 添付資料チェック（この手続きで必要なもの）</t>
+          <t>② 一緒に送っていただく書類</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20.5" customHeight="1">
       <c r="B16" s="24" t="inlineStr">
         <is>
-          <t>「状態」を選び、未入手は『後日提出』『事務所で確認』等の状態を残してください（空欄のままにしない）。</t>
+          <t>書類の一覧と、いま何が届いているかは案件ページが正です。このシートには書類の状態を書かないでください（二重管理になります）。
+案件ページは受任メールのリンクから開けます。届いた書類はその場で受領済みに変わります。</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>資料・項目</t>
-        </is>
-      </c>
-      <c r="C17" s="25" t="inlineStr">
-        <is>
-          <t>状態</t>
-        </is>
-      </c>
+          <t>この手続きで必要になるもの</t>
+        </is>
+      </c>
+      <c r="C17" s="25" t="n"/>
       <c r="D17" s="25" t="inlineStr">
         <is>
-          <t>補足（何のために使うか）</t>
+          <t>（案件ページの一覧が正です）</t>
         </is>
       </c>
     </row>
@@ -1983,50 +2029,25 @@
     <row r="26" ht="53.5" customHeight="1">
       <c r="B26" s="24" t="inlineStr">
         <is>
-          <t>【ファイル名のつけ方】　YYYYMMDD_顧問先名_対象者名_手続名_返送_v1.0.xlsx
-　例）20260710_ABC株式会社_山田太郎_入社時 従業員情報_返送_v1.0.xlsx
-　複数名分をまとめる場合：20260710_ABC株式会社_複数名_各種手続_返送_v1.0.xlsx</t>
+          <t>【ご返送方法】　記入したこのファイルを、案件ページからそのままお送りください。ZIPにする必要はありません。ファイル名も変えなくて構いません。
+　案件ページ＝受任メールのリンクから開けます。この経路は暗号化されており、メール添付より安全です。
+　メールに直接添付して送るのは避けてください（マイナンバー等の特定個人情報を含みます）。</t>
         </is>
       </c>
     </row>
     <row r="27" ht="53.5" customHeight="1">
-      <c r="B27" s="15" t="inlineStr">
-        <is>
-          <t>【ご返送方法】　マイナンバー等の重要情報を含みます。メール平文への添付は避け、パスワード付きZIP（パスワードは別経路でご連絡）または当事務所の案件ページ（受任メールのリンク）からお送りください。マイナンバーを別経路で回収する運用の場合は、このフォームには入力せず、会社所定の安全な経路で提出してください。</t>
-        </is>
-      </c>
+      <c r="B27" s="15" t="n"/>
     </row>
     <row r="28" ht="20.5" customHeight="1">
-      <c r="B28" s="24" t="inlineStr">
-        <is>
-          <t>【送付メール文（コピペ用）】　下の枠を選択してコピーし、件名・本文にお使いください。</t>
-        </is>
-      </c>
+      <c r="B28" s="24" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
-      <c r="B29" s="27" t="inlineStr">
-        <is>
-          <t>件名：【入社手続】入社連絡フォーム送付の件（〇〇株式会社）</t>
-        </is>
-      </c>
+      <c r="B29" s="27" t="n"/>
       <c r="C29" s="69" t="n"/>
       <c r="D29" s="70" t="n"/>
     </row>
     <row r="30" ht="218.5" customHeight="1">
-      <c r="B30" s="28" t="inlineStr">
-        <is>
-          <t>みなの社会保険労務士事務所
-ご担当者さま
-いつもお世話になっております。
-入社手続きに関する入力フォームを送付いたします。
-　対象者数：　　名
-　添付資料：
-　未提出・後日提出の資料：
-　ご連絡事項：
-何卒よろしくお願いいたします。
-（貴社名・ご担当者名）</t>
-        </is>
-      </c>
+      <c r="B30" s="28" t="n"/>
       <c r="C30" s="69" t="n"/>
       <c r="D30" s="70" t="n"/>
     </row>
@@ -2075,76 +2096,18 @@
       <formula>C10&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C18">
-    <cfRule type="expression" priority="4" dxfId="2" stopIfTrue="1">
-      <formula>C18=""</formula>
+  <conditionalFormatting sqref="C13">
+    <cfRule type="expression" priority="16" dxfId="0" stopIfTrue="1">
+      <formula>ISNUMBER(SEARCH("✓",C13))</formula>
     </cfRule>
-    <cfRule type="expression" priority="5" dxfId="1" stopIfTrue="1">
-      <formula>OR(C18="後日提出",C18="事務所で確認",C18="不明")</formula>
+    <cfRule type="expression" priority="17" dxfId="1" stopIfTrue="1">
+      <formula>ISNUMBER(SEARCH("未入力",C13))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C19">
-    <cfRule type="expression" priority="6" dxfId="2" stopIfTrue="1">
-      <formula>C19=""</formula>
-    </cfRule>
-    <cfRule type="expression" priority="7" dxfId="1" stopIfTrue="1">
-      <formula>OR(C19="後日提出",C19="事務所で確認",C19="不明")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C20">
-    <cfRule type="expression" priority="8" dxfId="2" stopIfTrue="1">
-      <formula>C20=""</formula>
-    </cfRule>
-    <cfRule type="expression" priority="9" dxfId="1" stopIfTrue="1">
-      <formula>OR(C20="後日提出",C20="事務所で確認",C20="不明")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C21">
-    <cfRule type="expression" priority="10" dxfId="2" stopIfTrue="1">
-      <formula>C21=""</formula>
-    </cfRule>
-    <cfRule type="expression" priority="11" dxfId="1" stopIfTrue="1">
-      <formula>OR(C21="後日提出",C21="事務所で確認",C21="不明")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C22">
-    <cfRule type="expression" priority="12" dxfId="2" stopIfTrue="1">
-      <formula>C22=""</formula>
-    </cfRule>
-    <cfRule type="expression" priority="13" dxfId="1" stopIfTrue="1">
-      <formula>OR(C22="後日提出",C22="事務所で確認",C22="不明")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C23">
-    <cfRule type="expression" priority="14" dxfId="2" stopIfTrue="1">
-      <formula>C23=""</formula>
-    </cfRule>
-    <cfRule type="expression" priority="15" dxfId="1" stopIfTrue="1">
-      <formula>OR(C23="後日提出",C23="事務所で確認",C23="不明")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="7">
+  <dataValidations count="1">
     <dataValidation sqref="C8" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="西暦 YYYY/MM/DD。" type="whole" errorStyle="warning" operator="between">
       <formula1>1</formula1>
       <formula2>99999999</formula2>
-    </dataValidation>
-    <dataValidation sqref="C18" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="添付済／不明／後日提出／該当なし／事務所で確認 から選択。" type="list" errorStyle="stop">
-      <formula1>"添付済,不明,後日提出,該当なし,事務所で確認"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C19" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="添付済／不明／後日提出／該当なし／事務所で確認 から選択。" type="list" errorStyle="stop">
-      <formula1>"添付済,不明,後日提出,該当なし,事務所で確認"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C20" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="添付済／不明／後日提出／該当なし／事務所で確認 から選択。" type="list" errorStyle="stop">
-      <formula1>"添付済,不明,後日提出,該当なし,事務所で確認"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C21" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="添付済／不明／後日提出／該当なし／事務所で確認 から選択。" type="list" errorStyle="stop">
-      <formula1>"添付済,不明,後日提出,該当なし,事務所で確認"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C22" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="添付済／不明／後日提出／該当なし／事務所で確認 から選択。" type="list" errorStyle="stop">
-      <formula1>"添付済,不明,後日提出,該当なし,事務所で確認"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C23" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="入力のヒント" prompt="添付済／不明／後日提出／該当なし／事務所で確認 から選択。" type="list" errorStyle="stop">
-      <formula1>"添付済,不明,後日提出,該当なし,事務所で確認"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2462,7 +2425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AU58"/>
+  <dimension ref="A1:AX58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2512,6 +2475,9 @@
     <col hidden="1" width="13" customWidth="1" min="45" max="45"/>
     <col hidden="1" width="13" customWidth="1" min="46" max="46"/>
     <col hidden="1" width="13" customWidth="1" min="47" max="47"/>
+    <col width="22" customWidth="1" min="48" max="48"/>
+    <col width="22" customWidth="1" min="49" max="49"/>
+    <col width="22" customWidth="1" min="50" max="50"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -2613,7 +2579,7 @@
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="40" t="n"/>
       <c r="B5" s="45">
-        <f>IF(B4=0,"（このシートにはまだ入力がありません）",IF(F4=0,"✓ 必須の未入力はありません","⚠ 必須の未入力が "&amp;F4&amp;" 件あります：本体の赤いセルをご確認ください"))</f>
+        <f>IF(B4=0,"（まだ入力がありません。水色の記入例の下の行からご記入ください）",IF(AND(F4=0,D4&lt;&gt;B4),"⚠ 式の入っていない行があります：行を挿入せず 9〜58 行にご記入ください",IF(F4=0,"✓ 必須の未入力はありません","⚠ 必須の未入力が "&amp;F4&amp;" 件あります：本体の赤いセルをご確認ください")))</f>
         <v/>
       </c>
       <c r="M5" s="40" t="n"/>
@@ -2698,6 +2664,13 @@
       </c>
       <c r="AQ6" s="76" t="n"/>
       <c r="AR6" s="74" t="n"/>
+      <c r="AV6" s="52" t="inlineStr">
+        <is>
+          <t>I追加項目（職種・賃金要件・二以上勤務）</t>
+        </is>
+      </c>
+      <c r="AW6" s="76" t="n"/>
+      <c r="AX6" s="74" t="n"/>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
@@ -2931,19 +2904,19 @@
       <c r="AM7" s="7" t="inlineStr">
         <is>
           <t>在留資格
-【任】</t>
+【条件必須】外国籍のとき</t>
         </is>
       </c>
       <c r="AN7" s="7" t="inlineStr">
         <is>
           <t>在留期間満了日
-【任】</t>
+【条件必須】外国籍のとき</t>
         </is>
       </c>
       <c r="AO7" s="7" t="inlineStr">
         <is>
           <t>ローマ字氏名
-【任】</t>
+【条件必須】外国籍のとき</t>
         </is>
       </c>
       <c r="AP7" s="6" t="inlineStr">
@@ -2961,6 +2934,25 @@
       <c r="AR7" s="7" t="inlineStr">
         <is>
           <t>備考
+【任】</t>
+        </is>
+      </c>
+      <c r="AV7" s="6" t="inlineStr">
+        <is>
+          <t>職種（雇用保険）
+【必】</t>
+        </is>
+      </c>
+      <c r="AW7" s="7" t="inlineStr">
+        <is>
+          <t>うち家族手当・精皆勤手当
+(月額・円)
+【任】</t>
+        </is>
+      </c>
+      <c r="AX7" s="7" t="inlineStr">
+        <is>
+          <t>他社でも社会保険に加入
 【任】</t>
         </is>
       </c>
@@ -3020,7 +3012,7 @@
         </is>
       </c>
       <c r="O8" s="54">
-        <f>IF($B8="","",IF($I8="なし","あり",IF($I8="あり",IF(OR($K8="更新の可能性あり",AND($J8&lt;&gt;"",$G8&lt;&gt;"",$J8-$G8+1&gt;62)),"あり","なし"),"")))</f>
+        <f>IF($B8="","",IF($I8="なし","あり",IF($I8&lt;&gt;"あり","",IF($K8="更新の可能性あり","あり",IF(OR($J8="",$G8=""),"なし",IF(OR(NOT(ISNUMBER($G8)),NOT(ISNUMBER($J8)),$G8&gt;80000,$J8&gt;80000),"要確認（日付）",IF($J8&gt;IF(DAY(EDATE($G8,2))&lt;DAY($G8),EOMONTH($G8,2),EDATE($G8,2)-1),"あり","なし"))))))</f>
         <v/>
       </c>
       <c r="P8" s="54">
@@ -3050,7 +3042,7 @@
         <v/>
       </c>
       <c r="X8" s="54">
-        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B8="","",IF(AND($L8&gt;='⓪ 事業所設定'!$C$13*0.75,$M8&gt;='⓪ 事業所設定'!$C$14*0.75,$O8="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L8&gt;=20,$O8="あり",$N8&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S8+$T8)&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
+        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B8="","",IF(AND($L8&gt;='⓪ 事業所設定'!$C$13*0.75,$M8&gt;='⓪ 事業所設定'!$C$14*0.75,$O8="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L8&gt;=20,$O8="あり",$N8&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S8+$T8-N($AW8))&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
         <v/>
       </c>
       <c r="Y8" s="54">
@@ -3058,7 +3050,7 @@
         <v/>
       </c>
       <c r="Z8" s="54">
-        <f>IF($B8="","",IF(AND($L8&gt;=20,$P8="あり",$N8&lt;&gt;"昼間部の学生"),"加入","加入対象外"))</f>
+        <f>IF($B8="","",IF($H8="役員","対象外（兼務役員なら要相談）",IF(AND($L8&gt;=20,$P8="あり",$N8&lt;&gt;"昼間部の学生"),"加入","加入対象外")))</f>
         <v/>
       </c>
       <c r="AA8" s="57" t="inlineStr">
@@ -3115,12 +3107,25 @@
       </c>
       <c r="AQ8" s="54" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="AR8" s="54" t="inlineStr">
         <is>
-          <t>← この行は記入例です（編集不可）</t>
+          <t>← この行は記入例です。9行目からご記入ください（消しても構いません）</t>
+        </is>
+      </c>
+      <c r="AV8" s="54" t="inlineStr">
+        <is>
+          <t>事務的職業</t>
+        </is>
+      </c>
+      <c r="AW8" s="78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" s="54" t="inlineStr">
+        <is>
+          <t>いいえ</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3151,7 @@
       <c r="M9" s="17" t="n"/>
       <c r="N9" s="17" t="n"/>
       <c r="O9" s="23">
-        <f>IF($B9="","",IF($I9="なし","あり",IF($I9="あり",IF(OR($K9="更新の可能性あり",AND($J9&lt;&gt;"",$G9&lt;&gt;"",$J9-$G9+1&gt;62)),"あり","なし"),"")))</f>
+        <f>IF($B9="","",IF($I9="なし","あり",IF($I9&lt;&gt;"あり","",IF($K9="更新の可能性あり","あり",IF(OR($J9="",$G9=""),"なし",IF(OR(NOT(ISNUMBER($G9)),NOT(ISNUMBER($J9)),$G9&gt;80000,$J9&gt;80000),"要確認（日付）",IF($J9&gt;IF(DAY(EDATE($G9,2))&lt;DAY($G9),EOMONTH($G9,2),EDATE($G9,2)-1),"あり","なし"))))))</f>
         <v/>
       </c>
       <c r="P9" s="23">
@@ -3164,7 +3169,7 @@
         <v/>
       </c>
       <c r="X9" s="23">
-        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B9="","",IF(AND($L9&gt;='⓪ 事業所設定'!$C$13*0.75,$M9&gt;='⓪ 事業所設定'!$C$14*0.75,$O9="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L9&gt;=20,$O9="あり",$N9&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S9+$T9)&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
+        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B9="","",IF(AND($L9&gt;='⓪ 事業所設定'!$C$13*0.75,$M9&gt;='⓪ 事業所設定'!$C$14*0.75,$O9="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L9&gt;=20,$O9="あり",$N9&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S9+$T9-N($AW9))&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
         <v/>
       </c>
       <c r="Y9" s="23">
@@ -3172,7 +3177,7 @@
         <v/>
       </c>
       <c r="Z9" s="23">
-        <f>IF($B9="","",IF(AND($L9&gt;=20,$P9="あり",$N9&lt;&gt;"昼間部の学生"),"加入","加入対象外"))</f>
+        <f>IF($B9="","",IF($H9="役員","対象外（兼務役員なら要相談）",IF(AND($L9&gt;=20,$P9="あり",$N9&lt;&gt;"昼間部の学生"),"加入","加入対象外")))</f>
         <v/>
       </c>
       <c r="AA9" s="61" t="n"/>
@@ -3194,13 +3199,16 @@
       <c r="AQ9" s="17" t="n"/>
       <c r="AR9" s="17" t="n"/>
       <c r="AT9">
-        <f>IF($B9="","",IF($B9="",1,0)+IF($C9="",1,0)+IF($D9="",1,0)+IF($E9="",1,0)+IF($G9="",1,0)+IF($H9="",1,0)+IF($I9="",1,0)+IF($L9="",1,0)+IF($M9="",1,0)+IF($N9="",1,0)+IF($Q9="",1,0)+IF($S9="",1,0)+IF($AA9="",1,0)+IF($AC9="",1,0)+IF($AG9="",1,0)+IF($AH9="",1,0)+IF($AI9="",1,0)+IF($AL9="",1,0)+IF($AP9="",1,0)+IF($AQ9="",1,0)+IF(AND($I9="あり",$J9=""),1,0)+IF(AND($I9="あり",$K9=""),1,0)+IF(AND($AA9="",$AB9=""),1,0)+IF(AND($AC9="あり",$AD9=""),1,0)+IF(AND($AC9="あり",OR($AD9="",$AD9="後日提出"),$AE9=""),1,0))</f>
+        <f>IF($B9="","",IF($B9="",1,0)+IF($C9="",1,0)+IF($D9="",1,0)+IF($E9="",1,0)+IF($G9="",1,0)+IF($H9="",1,0)+IF($I9="",1,0)+IF($L9="",1,0)+IF($M9="",1,0)+IF($N9="",1,0)+IF($Q9="",1,0)+IF($S9="",1,0)+IF($AA9="",1,0)+IF($AC9="",1,0)+IF($AG9="",1,0)+IF($AH9="",1,0)+IF($AI9="",1,0)+IF($AL9="",1,0)+IF($AP9="",1,0)+IF($AQ9="",1,0)+IF(AND($I9="あり",$J9=""),1,0)+IF(AND($I9="あり",$K9=""),1,0)+IF(AND($AA9="",$AB9=""),1,0)+IF(AND($AC9="あり",$AD9=""),1,0)+IF(AND($AC9="あり",OR($AD9="",$AD9="後日提出"),$AE9=""),1,0)+IF($AV9="",1,0)+IF(AND($AL9="外国",$AM9=""),1,0)+IF(AND($AL9="外国",$AN9=""),1,0)+IF(AND($AL9="外国",$AO9=""),1,0))</f>
         <v/>
       </c>
       <c r="AU9">
         <f>IF($B9="","",IF(AND($AA9&lt;&gt;"",$AA9&lt;&gt;"後日提出",$AA9&lt;&gt;"別経路提出",LEN($AA9)&lt;&gt;12),1,0)+IF(AND($AB9&lt;&gt;"",$AB9&lt;&gt;"後日提出",LEN($AB9)&lt;&gt;10),1,0)+IF(AND($AD9&lt;&gt;"",$AD9&lt;&gt;"後日提出",LEN($AD9)&lt;&gt;11),1,0)+IF(AND($AG9&lt;&gt;"",LEN(SUBSTITUTE($AG9,"-",""))&lt;&gt;7),1,0))</f>
         <v/>
       </c>
+      <c r="AV9" s="17" t="n"/>
+      <c r="AW9" s="59" t="n"/>
+      <c r="AX9" s="17" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="23">
@@ -3224,7 +3232,7 @@
       <c r="M10" s="17" t="n"/>
       <c r="N10" s="17" t="n"/>
       <c r="O10" s="23">
-        <f>IF($B10="","",IF($I10="なし","あり",IF($I10="あり",IF(OR($K10="更新の可能性あり",AND($J10&lt;&gt;"",$G10&lt;&gt;"",$J10-$G10+1&gt;62)),"あり","なし"),"")))</f>
+        <f>IF($B10="","",IF($I10="なし","あり",IF($I10&lt;&gt;"あり","",IF($K10="更新の可能性あり","あり",IF(OR($J10="",$G10=""),"なし",IF(OR(NOT(ISNUMBER($G10)),NOT(ISNUMBER($J10)),$G10&gt;80000,$J10&gt;80000),"要確認（日付）",IF($J10&gt;IF(DAY(EDATE($G10,2))&lt;DAY($G10),EOMONTH($G10,2),EDATE($G10,2)-1),"あり","なし"))))))</f>
         <v/>
       </c>
       <c r="P10" s="23">
@@ -3242,7 +3250,7 @@
         <v/>
       </c>
       <c r="X10" s="23">
-        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B10="","",IF(AND($L10&gt;='⓪ 事業所設定'!$C$13*0.75,$M10&gt;='⓪ 事業所設定'!$C$14*0.75,$O10="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L10&gt;=20,$O10="あり",$N10&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S10+$T10)&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
+        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B10="","",IF(AND($L10&gt;='⓪ 事業所設定'!$C$13*0.75,$M10&gt;='⓪ 事業所設定'!$C$14*0.75,$O10="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L10&gt;=20,$O10="あり",$N10&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S10+$T10-N($AW10))&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
         <v/>
       </c>
       <c r="Y10" s="23">
@@ -3250,7 +3258,7 @@
         <v/>
       </c>
       <c r="Z10" s="23">
-        <f>IF($B10="","",IF(AND($L10&gt;=20,$P10="あり",$N10&lt;&gt;"昼間部の学生"),"加入","加入対象外"))</f>
+        <f>IF($B10="","",IF($H10="役員","対象外（兼務役員なら要相談）",IF(AND($L10&gt;=20,$P10="あり",$N10&lt;&gt;"昼間部の学生"),"加入","加入対象外")))</f>
         <v/>
       </c>
       <c r="AA10" s="61" t="n"/>
@@ -3272,13 +3280,16 @@
       <c r="AQ10" s="17" t="n"/>
       <c r="AR10" s="17" t="n"/>
       <c r="AT10">
-        <f>IF($B10="","",IF($B10="",1,0)+IF($C10="",1,0)+IF($D10="",1,0)+IF($E10="",1,0)+IF($G10="",1,0)+IF($H10="",1,0)+IF($I10="",1,0)+IF($L10="",1,0)+IF($M10="",1,0)+IF($N10="",1,0)+IF($Q10="",1,0)+IF($S10="",1,0)+IF($AA10="",1,0)+IF($AC10="",1,0)+IF($AG10="",1,0)+IF($AH10="",1,0)+IF($AI10="",1,0)+IF($AL10="",1,0)+IF($AP10="",1,0)+IF($AQ10="",1,0)+IF(AND($I10="あり",$J10=""),1,0)+IF(AND($I10="あり",$K10=""),1,0)+IF(AND($AA10="",$AB10=""),1,0)+IF(AND($AC10="あり",$AD10=""),1,0)+IF(AND($AC10="あり",OR($AD10="",$AD10="後日提出"),$AE10=""),1,0))</f>
+        <f>IF($B10="","",IF($B10="",1,0)+IF($C10="",1,0)+IF($D10="",1,0)+IF($E10="",1,0)+IF($G10="",1,0)+IF($H10="",1,0)+IF($I10="",1,0)+IF($L10="",1,0)+IF($M10="",1,0)+IF($N10="",1,0)+IF($Q10="",1,0)+IF($S10="",1,0)+IF($AA10="",1,0)+IF($AC10="",1,0)+IF($AG10="",1,0)+IF($AH10="",1,0)+IF($AI10="",1,0)+IF($AL10="",1,0)+IF($AP10="",1,0)+IF($AQ10="",1,0)+IF(AND($I10="あり",$J10=""),1,0)+IF(AND($I10="あり",$K10=""),1,0)+IF(AND($AA10="",$AB10=""),1,0)+IF(AND($AC10="あり",$AD10=""),1,0)+IF(AND($AC10="あり",OR($AD10="",$AD10="後日提出"),$AE10=""),1,0)+IF($AV10="",1,0)+IF(AND($AL10="外国",$AM10=""),1,0)+IF(AND($AL10="外国",$AN10=""),1,0)+IF(AND($AL10="外国",$AO10=""),1,0))</f>
         <v/>
       </c>
       <c r="AU10">
         <f>IF($B10="","",IF(AND($AA10&lt;&gt;"",$AA10&lt;&gt;"後日提出",$AA10&lt;&gt;"別経路提出",LEN($AA10)&lt;&gt;12),1,0)+IF(AND($AB10&lt;&gt;"",$AB10&lt;&gt;"後日提出",LEN($AB10)&lt;&gt;10),1,0)+IF(AND($AD10&lt;&gt;"",$AD10&lt;&gt;"後日提出",LEN($AD10)&lt;&gt;11),1,0)+IF(AND($AG10&lt;&gt;"",LEN(SUBSTITUTE($AG10,"-",""))&lt;&gt;7),1,0))</f>
         <v/>
       </c>
+      <c r="AV10" s="17" t="n"/>
+      <c r="AW10" s="59" t="n"/>
+      <c r="AX10" s="17" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="23">
@@ -3302,7 +3313,7 @@
       <c r="M11" s="17" t="n"/>
       <c r="N11" s="17" t="n"/>
       <c r="O11" s="23">
-        <f>IF($B11="","",IF($I11="なし","あり",IF($I11="あり",IF(OR($K11="更新の可能性あり",AND($J11&lt;&gt;"",$G11&lt;&gt;"",$J11-$G11+1&gt;62)),"あり","なし"),"")))</f>
+        <f>IF($B11="","",IF($I11="なし","あり",IF($I11&lt;&gt;"あり","",IF($K11="更新の可能性あり","あり",IF(OR($J11="",$G11=""),"なし",IF(OR(NOT(ISNUMBER($G11)),NOT(ISNUMBER($J11)),$G11&gt;80000,$J11&gt;80000),"要確認（日付）",IF($J11&gt;IF(DAY(EDATE($G11,2))&lt;DAY($G11),EOMONTH($G11,2),EDATE($G11,2)-1),"あり","なし"))))))</f>
         <v/>
       </c>
       <c r="P11" s="23">
@@ -3320,7 +3331,7 @@
         <v/>
       </c>
       <c r="X11" s="23">
-        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B11="","",IF(AND($L11&gt;='⓪ 事業所設定'!$C$13*0.75,$M11&gt;='⓪ 事業所設定'!$C$14*0.75,$O11="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L11&gt;=20,$O11="あり",$N11&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S11+$T11)&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
+        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B11="","",IF(AND($L11&gt;='⓪ 事業所設定'!$C$13*0.75,$M11&gt;='⓪ 事業所設定'!$C$14*0.75,$O11="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L11&gt;=20,$O11="あり",$N11&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S11+$T11-N($AW11))&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
         <v/>
       </c>
       <c r="Y11" s="23">
@@ -3328,7 +3339,7 @@
         <v/>
       </c>
       <c r="Z11" s="23">
-        <f>IF($B11="","",IF(AND($L11&gt;=20,$P11="あり",$N11&lt;&gt;"昼間部の学生"),"加入","加入対象外"))</f>
+        <f>IF($B11="","",IF($H11="役員","対象外（兼務役員なら要相談）",IF(AND($L11&gt;=20,$P11="あり",$N11&lt;&gt;"昼間部の学生"),"加入","加入対象外")))</f>
         <v/>
       </c>
       <c r="AA11" s="61" t="n"/>
@@ -3350,13 +3361,16 @@
       <c r="AQ11" s="17" t="n"/>
       <c r="AR11" s="17" t="n"/>
       <c r="AT11">
-        <f>IF($B11="","",IF($B11="",1,0)+IF($C11="",1,0)+IF($D11="",1,0)+IF($E11="",1,0)+IF($G11="",1,0)+IF($H11="",1,0)+IF($I11="",1,0)+IF($L11="",1,0)+IF($M11="",1,0)+IF($N11="",1,0)+IF($Q11="",1,0)+IF($S11="",1,0)+IF($AA11="",1,0)+IF($AC11="",1,0)+IF($AG11="",1,0)+IF($AH11="",1,0)+IF($AI11="",1,0)+IF($AL11="",1,0)+IF($AP11="",1,0)+IF($AQ11="",1,0)+IF(AND($I11="あり",$J11=""),1,0)+IF(AND($I11="あり",$K11=""),1,0)+IF(AND($AA11="",$AB11=""),1,0)+IF(AND($AC11="あり",$AD11=""),1,0)+IF(AND($AC11="あり",OR($AD11="",$AD11="後日提出"),$AE11=""),1,0))</f>
+        <f>IF($B11="","",IF($B11="",1,0)+IF($C11="",1,0)+IF($D11="",1,0)+IF($E11="",1,0)+IF($G11="",1,0)+IF($H11="",1,0)+IF($I11="",1,0)+IF($L11="",1,0)+IF($M11="",1,0)+IF($N11="",1,0)+IF($Q11="",1,0)+IF($S11="",1,0)+IF($AA11="",1,0)+IF($AC11="",1,0)+IF($AG11="",1,0)+IF($AH11="",1,0)+IF($AI11="",1,0)+IF($AL11="",1,0)+IF($AP11="",1,0)+IF($AQ11="",1,0)+IF(AND($I11="あり",$J11=""),1,0)+IF(AND($I11="あり",$K11=""),1,0)+IF(AND($AA11="",$AB11=""),1,0)+IF(AND($AC11="あり",$AD11=""),1,0)+IF(AND($AC11="あり",OR($AD11="",$AD11="後日提出"),$AE11=""),1,0)+IF($AV11="",1,0)+IF(AND($AL11="外国",$AM11=""),1,0)+IF(AND($AL11="外国",$AN11=""),1,0)+IF(AND($AL11="外国",$AO11=""),1,0))</f>
         <v/>
       </c>
       <c r="AU11">
         <f>IF($B11="","",IF(AND($AA11&lt;&gt;"",$AA11&lt;&gt;"後日提出",$AA11&lt;&gt;"別経路提出",LEN($AA11)&lt;&gt;12),1,0)+IF(AND($AB11&lt;&gt;"",$AB11&lt;&gt;"後日提出",LEN($AB11)&lt;&gt;10),1,0)+IF(AND($AD11&lt;&gt;"",$AD11&lt;&gt;"後日提出",LEN($AD11)&lt;&gt;11),1,0)+IF(AND($AG11&lt;&gt;"",LEN(SUBSTITUTE($AG11,"-",""))&lt;&gt;7),1,0))</f>
         <v/>
       </c>
+      <c r="AV11" s="17" t="n"/>
+      <c r="AW11" s="59" t="n"/>
+      <c r="AX11" s="17" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="23">
@@ -3380,7 +3394,7 @@
       <c r="M12" s="17" t="n"/>
       <c r="N12" s="17" t="n"/>
       <c r="O12" s="23">
-        <f>IF($B12="","",IF($I12="なし","あり",IF($I12="あり",IF(OR($K12="更新の可能性あり",AND($J12&lt;&gt;"",$G12&lt;&gt;"",$J12-$G12+1&gt;62)),"あり","なし"),"")))</f>
+        <f>IF($B12="","",IF($I12="なし","あり",IF($I12&lt;&gt;"あり","",IF($K12="更新の可能性あり","あり",IF(OR($J12="",$G12=""),"なし",IF(OR(NOT(ISNUMBER($G12)),NOT(ISNUMBER($J12)),$G12&gt;80000,$J12&gt;80000),"要確認（日付）",IF($J12&gt;IF(DAY(EDATE($G12,2))&lt;DAY($G12),EOMONTH($G12,2),EDATE($G12,2)-1),"あり","なし"))))))</f>
         <v/>
       </c>
       <c r="P12" s="23">
@@ -3398,7 +3412,7 @@
         <v/>
       </c>
       <c r="X12" s="23">
-        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B12="","",IF(AND($L12&gt;='⓪ 事業所設定'!$C$13*0.75,$M12&gt;='⓪ 事業所設定'!$C$14*0.75,$O12="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L12&gt;=20,$O12="あり",$N12&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S12+$T12)&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
+        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B12="","",IF(AND($L12&gt;='⓪ 事業所設定'!$C$13*0.75,$M12&gt;='⓪ 事業所設定'!$C$14*0.75,$O12="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L12&gt;=20,$O12="あり",$N12&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S12+$T12-N($AW12))&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
         <v/>
       </c>
       <c r="Y12" s="23">
@@ -3406,7 +3420,7 @@
         <v/>
       </c>
       <c r="Z12" s="23">
-        <f>IF($B12="","",IF(AND($L12&gt;=20,$P12="あり",$N12&lt;&gt;"昼間部の学生"),"加入","加入対象外"))</f>
+        <f>IF($B12="","",IF($H12="役員","対象外（兼務役員なら要相談）",IF(AND($L12&gt;=20,$P12="あり",$N12&lt;&gt;"昼間部の学生"),"加入","加入対象外")))</f>
         <v/>
       </c>
       <c r="AA12" s="61" t="n"/>
@@ -3428,13 +3442,16 @@
       <c r="AQ12" s="17" t="n"/>
       <c r="AR12" s="17" t="n"/>
       <c r="AT12">
-        <f>IF($B12="","",IF($B12="",1,0)+IF($C12="",1,0)+IF($D12="",1,0)+IF($E12="",1,0)+IF($G12="",1,0)+IF($H12="",1,0)+IF($I12="",1,0)+IF($L12="",1,0)+IF($M12="",1,0)+IF($N12="",1,0)+IF($Q12="",1,0)+IF($S12="",1,0)+IF($AA12="",1,0)+IF($AC12="",1,0)+IF($AG12="",1,0)+IF($AH12="",1,0)+IF($AI12="",1,0)+IF($AL12="",1,0)+IF($AP12="",1,0)+IF($AQ12="",1,0)+IF(AND($I12="あり",$J12=""),1,0)+IF(AND($I12="あり",$K12=""),1,0)+IF(AND($AA12="",$AB12=""),1,0)+IF(AND($AC12="あり",$AD12=""),1,0)+IF(AND($AC12="あり",OR($AD12="",$AD12="後日提出"),$AE12=""),1,0))</f>
+        <f>IF($B12="","",IF($B12="",1,0)+IF($C12="",1,0)+IF($D12="",1,0)+IF($E12="",1,0)+IF($G12="",1,0)+IF($H12="",1,0)+IF($I12="",1,0)+IF($L12="",1,0)+IF($M12="",1,0)+IF($N12="",1,0)+IF($Q12="",1,0)+IF($S12="",1,0)+IF($AA12="",1,0)+IF($AC12="",1,0)+IF($AG12="",1,0)+IF($AH12="",1,0)+IF($AI12="",1,0)+IF($AL12="",1,0)+IF($AP12="",1,0)+IF($AQ12="",1,0)+IF(AND($I12="あり",$J12=""),1,0)+IF(AND($I12="あり",$K12=""),1,0)+IF(AND($AA12="",$AB12=""),1,0)+IF(AND($AC12="あり",$AD12=""),1,0)+IF(AND($AC12="あり",OR($AD12="",$AD12="後日提出"),$AE12=""),1,0)+IF($AV12="",1,0)+IF(AND($AL12="外国",$AM12=""),1,0)+IF(AND($AL12="外国",$AN12=""),1,0)+IF(AND($AL12="外国",$AO12=""),1,0))</f>
         <v/>
       </c>
       <c r="AU12">
         <f>IF($B12="","",IF(AND($AA12&lt;&gt;"",$AA12&lt;&gt;"後日提出",$AA12&lt;&gt;"別経路提出",LEN($AA12)&lt;&gt;12),1,0)+IF(AND($AB12&lt;&gt;"",$AB12&lt;&gt;"後日提出",LEN($AB12)&lt;&gt;10),1,0)+IF(AND($AD12&lt;&gt;"",$AD12&lt;&gt;"後日提出",LEN($AD12)&lt;&gt;11),1,0)+IF(AND($AG12&lt;&gt;"",LEN(SUBSTITUTE($AG12,"-",""))&lt;&gt;7),1,0))</f>
         <v/>
       </c>
+      <c r="AV12" s="17" t="n"/>
+      <c r="AW12" s="59" t="n"/>
+      <c r="AX12" s="17" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="23">
@@ -3458,7 +3475,7 @@
       <c r="M13" s="17" t="n"/>
       <c r="N13" s="17" t="n"/>
       <c r="O13" s="23">
-        <f>IF($B13="","",IF($I13="なし","あり",IF($I13="あり",IF(OR($K13="更新の可能性あり",AND($J13&lt;&gt;"",$G13&lt;&gt;"",$J13-$G13+1&gt;62)),"あり","なし"),"")))</f>
+        <f>IF($B13="","",IF($I13="なし","あり",IF($I13&lt;&gt;"あり","",IF($K13="更新の可能性あり","あり",IF(OR($J13="",$G13=""),"なし",IF(OR(NOT(ISNUMBER($G13)),NOT(ISNUMBER($J13)),$G13&gt;80000,$J13&gt;80000),"要確認（日付）",IF($J13&gt;IF(DAY(EDATE($G13,2))&lt;DAY($G13),EOMONTH($G13,2),EDATE($G13,2)-1),"あり","なし"))))))</f>
         <v/>
       </c>
       <c r="P13" s="23">
@@ -3476,7 +3493,7 @@
         <v/>
       </c>
       <c r="X13" s="23">
-        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B13="","",IF(AND($L13&gt;='⓪ 事業所設定'!$C$13*0.75,$M13&gt;='⓪ 事業所設定'!$C$14*0.75,$O13="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L13&gt;=20,$O13="あり",$N13&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S13+$T13)&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
+        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B13="","",IF(AND($L13&gt;='⓪ 事業所設定'!$C$13*0.75,$M13&gt;='⓪ 事業所設定'!$C$14*0.75,$O13="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L13&gt;=20,$O13="あり",$N13&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S13+$T13-N($AW13))&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
         <v/>
       </c>
       <c r="Y13" s="23">
@@ -3484,7 +3501,7 @@
         <v/>
       </c>
       <c r="Z13" s="23">
-        <f>IF($B13="","",IF(AND($L13&gt;=20,$P13="あり",$N13&lt;&gt;"昼間部の学生"),"加入","加入対象外"))</f>
+        <f>IF($B13="","",IF($H13="役員","対象外（兼務役員なら要相談）",IF(AND($L13&gt;=20,$P13="あり",$N13&lt;&gt;"昼間部の学生"),"加入","加入対象外")))</f>
         <v/>
       </c>
       <c r="AA13" s="61" t="n"/>
@@ -3506,13 +3523,16 @@
       <c r="AQ13" s="17" t="n"/>
       <c r="AR13" s="17" t="n"/>
       <c r="AT13">
-        <f>IF($B13="","",IF($B13="",1,0)+IF($C13="",1,0)+IF($D13="",1,0)+IF($E13="",1,0)+IF($G13="",1,0)+IF($H13="",1,0)+IF($I13="",1,0)+IF($L13="",1,0)+IF($M13="",1,0)+IF($N13="",1,0)+IF($Q13="",1,0)+IF($S13="",1,0)+IF($AA13="",1,0)+IF($AC13="",1,0)+IF($AG13="",1,0)+IF($AH13="",1,0)+IF($AI13="",1,0)+IF($AL13="",1,0)+IF($AP13="",1,0)+IF($AQ13="",1,0)+IF(AND($I13="あり",$J13=""),1,0)+IF(AND($I13="あり",$K13=""),1,0)+IF(AND($AA13="",$AB13=""),1,0)+IF(AND($AC13="あり",$AD13=""),1,0)+IF(AND($AC13="あり",OR($AD13="",$AD13="後日提出"),$AE13=""),1,0))</f>
+        <f>IF($B13="","",IF($B13="",1,0)+IF($C13="",1,0)+IF($D13="",1,0)+IF($E13="",1,0)+IF($G13="",1,0)+IF($H13="",1,0)+IF($I13="",1,0)+IF($L13="",1,0)+IF($M13="",1,0)+IF($N13="",1,0)+IF($Q13="",1,0)+IF($S13="",1,0)+IF($AA13="",1,0)+IF($AC13="",1,0)+IF($AG13="",1,0)+IF($AH13="",1,0)+IF($AI13="",1,0)+IF($AL13="",1,0)+IF($AP13="",1,0)+IF($AQ13="",1,0)+IF(AND($I13="あり",$J13=""),1,0)+IF(AND($I13="あり",$K13=""),1,0)+IF(AND($AA13="",$AB13=""),1,0)+IF(AND($AC13="あり",$AD13=""),1,0)+IF(AND($AC13="あり",OR($AD13="",$AD13="後日提出"),$AE13=""),1,0)+IF($AV13="",1,0)+IF(AND($AL13="外国",$AM13=""),1,0)+IF(AND($AL13="外国",$AN13=""),1,0)+IF(AND($AL13="外国",$AO13=""),1,0))</f>
         <v/>
       </c>
       <c r="AU13">
         <f>IF($B13="","",IF(AND($AA13&lt;&gt;"",$AA13&lt;&gt;"後日提出",$AA13&lt;&gt;"別経路提出",LEN($AA13)&lt;&gt;12),1,0)+IF(AND($AB13&lt;&gt;"",$AB13&lt;&gt;"後日提出",LEN($AB13)&lt;&gt;10),1,0)+IF(AND($AD13&lt;&gt;"",$AD13&lt;&gt;"後日提出",LEN($AD13)&lt;&gt;11),1,0)+IF(AND($AG13&lt;&gt;"",LEN(SUBSTITUTE($AG13,"-",""))&lt;&gt;7),1,0))</f>
         <v/>
       </c>
+      <c r="AV13" s="17" t="n"/>
+      <c r="AW13" s="59" t="n"/>
+      <c r="AX13" s="17" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="23">
@@ -3536,7 +3556,7 @@
       <c r="M14" s="17" t="n"/>
       <c r="N14" s="17" t="n"/>
       <c r="O14" s="23">
-        <f>IF($B14="","",IF($I14="なし","あり",IF($I14="あり",IF(OR($K14="更新の可能性あり",AND($J14&lt;&gt;"",$G14&lt;&gt;"",$J14-$G14+1&gt;62)),"あり","なし"),"")))</f>
+        <f>IF($B14="","",IF($I14="なし","あり",IF($I14&lt;&gt;"あり","",IF($K14="更新の可能性あり","あり",IF(OR($J14="",$G14=""),"なし",IF(OR(NOT(ISNUMBER($G14)),NOT(ISNUMBER($J14)),$G14&gt;80000,$J14&gt;80000),"要確認（日付）",IF($J14&gt;IF(DAY(EDATE($G14,2))&lt;DAY($G14),EOMONTH($G14,2),EDATE($G14,2)-1),"あり","なし"))))))</f>
         <v/>
       </c>
       <c r="P14" s="23">
@@ -3554,7 +3574,7 @@
         <v/>
       </c>
       <c r="X14" s="23">
-        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B14="","",IF(AND($L14&gt;='⓪ 事業所設定'!$C$13*0.75,$M14&gt;='⓪ 事業所設定'!$C$14*0.75,$O14="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L14&gt;=20,$O14="あり",$N14&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S14+$T14)&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
+        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B14="","",IF(AND($L14&gt;='⓪ 事業所設定'!$C$13*0.75,$M14&gt;='⓪ 事業所設定'!$C$14*0.75,$O14="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L14&gt;=20,$O14="あり",$N14&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S14+$T14-N($AW14))&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
         <v/>
       </c>
       <c r="Y14" s="23">
@@ -3562,7 +3582,7 @@
         <v/>
       </c>
       <c r="Z14" s="23">
-        <f>IF($B14="","",IF(AND($L14&gt;=20,$P14="あり",$N14&lt;&gt;"昼間部の学生"),"加入","加入対象外"))</f>
+        <f>IF($B14="","",IF($H14="役員","対象外（兼務役員なら要相談）",IF(AND($L14&gt;=20,$P14="あり",$N14&lt;&gt;"昼間部の学生"),"加入","加入対象外")))</f>
         <v/>
       </c>
       <c r="AA14" s="61" t="n"/>
@@ -3584,13 +3604,16 @@
       <c r="AQ14" s="17" t="n"/>
       <c r="AR14" s="17" t="n"/>
       <c r="AT14">
-        <f>IF($B14="","",IF($B14="",1,0)+IF($C14="",1,0)+IF($D14="",1,0)+IF($E14="",1,0)+IF($G14="",1,0)+IF($H14="",1,0)+IF($I14="",1,0)+IF($L14="",1,0)+IF($M14="",1,0)+IF($N14="",1,0)+IF($Q14="",1,0)+IF($S14="",1,0)+IF($AA14="",1,0)+IF($AC14="",1,0)+IF($AG14="",1,0)+IF($AH14="",1,0)+IF($AI14="",1,0)+IF($AL14="",1,0)+IF($AP14="",1,0)+IF($AQ14="",1,0)+IF(AND($I14="あり",$J14=""),1,0)+IF(AND($I14="あり",$K14=""),1,0)+IF(AND($AA14="",$AB14=""),1,0)+IF(AND($AC14="あり",$AD14=""),1,0)+IF(AND($AC14="あり",OR($AD14="",$AD14="後日提出"),$AE14=""),1,0))</f>
+        <f>IF($B14="","",IF($B14="",1,0)+IF($C14="",1,0)+IF($D14="",1,0)+IF($E14="",1,0)+IF($G14="",1,0)+IF($H14="",1,0)+IF($I14="",1,0)+IF($L14="",1,0)+IF($M14="",1,0)+IF($N14="",1,0)+IF($Q14="",1,0)+IF($S14="",1,0)+IF($AA14="",1,0)+IF($AC14="",1,0)+IF($AG14="",1,0)+IF($AH14="",1,0)+IF($AI14="",1,0)+IF($AL14="",1,0)+IF($AP14="",1,0)+IF($AQ14="",1,0)+IF(AND($I14="あり",$J14=""),1,0)+IF(AND($I14="あり",$K14=""),1,0)+IF(AND($AA14="",$AB14=""),1,0)+IF(AND($AC14="あり",$AD14=""),1,0)+IF(AND($AC14="あり",OR($AD14="",$AD14="後日提出"),$AE14=""),1,0)+IF($AV14="",1,0)+IF(AND($AL14="外国",$AM14=""),1,0)+IF(AND($AL14="外国",$AN14=""),1,0)+IF(AND($AL14="外国",$AO14=""),1,0))</f>
         <v/>
       </c>
       <c r="AU14">
         <f>IF($B14="","",IF(AND($AA14&lt;&gt;"",$AA14&lt;&gt;"後日提出",$AA14&lt;&gt;"別経路提出",LEN($AA14)&lt;&gt;12),1,0)+IF(AND($AB14&lt;&gt;"",$AB14&lt;&gt;"後日提出",LEN($AB14)&lt;&gt;10),1,0)+IF(AND($AD14&lt;&gt;"",$AD14&lt;&gt;"後日提出",LEN($AD14)&lt;&gt;11),1,0)+IF(AND($AG14&lt;&gt;"",LEN(SUBSTITUTE($AG14,"-",""))&lt;&gt;7),1,0))</f>
         <v/>
       </c>
+      <c r="AV14" s="17" t="n"/>
+      <c r="AW14" s="59" t="n"/>
+      <c r="AX14" s="17" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="23">
@@ -3614,7 +3637,7 @@
       <c r="M15" s="17" t="n"/>
       <c r="N15" s="17" t="n"/>
       <c r="O15" s="23">
-        <f>IF($B15="","",IF($I15="なし","あり",IF($I15="あり",IF(OR($K15="更新の可能性あり",AND($J15&lt;&gt;"",$G15&lt;&gt;"",$J15-$G15+1&gt;62)),"あり","なし"),"")))</f>
+        <f>IF($B15="","",IF($I15="なし","あり",IF($I15&lt;&gt;"あり","",IF($K15="更新の可能性あり","あり",IF(OR($J15="",$G15=""),"なし",IF(OR(NOT(ISNUMBER($G15)),NOT(ISNUMBER($J15)),$G15&gt;80000,$J15&gt;80000),"要確認（日付）",IF($J15&gt;IF(DAY(EDATE($G15,2))&lt;DAY($G15),EOMONTH($G15,2),EDATE($G15,2)-1),"あり","なし"))))))</f>
         <v/>
       </c>
       <c r="P15" s="23">
@@ -3632,7 +3655,7 @@
         <v/>
       </c>
       <c r="X15" s="23">
-        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B15="","",IF(AND($L15&gt;='⓪ 事業所設定'!$C$13*0.75,$M15&gt;='⓪ 事業所設定'!$C$14*0.75,$O15="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L15&gt;=20,$O15="あり",$N15&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S15+$T15)&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
+        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B15="","",IF(AND($L15&gt;='⓪ 事業所設定'!$C$13*0.75,$M15&gt;='⓪ 事業所設定'!$C$14*0.75,$O15="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L15&gt;=20,$O15="あり",$N15&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S15+$T15-N($AW15))&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
         <v/>
       </c>
       <c r="Y15" s="23">
@@ -3640,7 +3663,7 @@
         <v/>
       </c>
       <c r="Z15" s="23">
-        <f>IF($B15="","",IF(AND($L15&gt;=20,$P15="あり",$N15&lt;&gt;"昼間部の学生"),"加入","加入対象外"))</f>
+        <f>IF($B15="","",IF($H15="役員","対象外（兼務役員なら要相談）",IF(AND($L15&gt;=20,$P15="あり",$N15&lt;&gt;"昼間部の学生"),"加入","加入対象外")))</f>
         <v/>
       </c>
       <c r="AA15" s="61" t="n"/>
@@ -3662,13 +3685,16 @@
       <c r="AQ15" s="17" t="n"/>
       <c r="AR15" s="17" t="n"/>
       <c r="AT15">
-        <f>IF($B15="","",IF($B15="",1,0)+IF($C15="",1,0)+IF($D15="",1,0)+IF($E15="",1,0)+IF($G15="",1,0)+IF($H15="",1,0)+IF($I15="",1,0)+IF($L15="",1,0)+IF($M15="",1,0)+IF($N15="",1,0)+IF($Q15="",1,0)+IF($S15="",1,0)+IF($AA15="",1,0)+IF($AC15="",1,0)+IF($AG15="",1,0)+IF($AH15="",1,0)+IF($AI15="",1,0)+IF($AL15="",1,0)+IF($AP15="",1,0)+IF($AQ15="",1,0)+IF(AND($I15="あり",$J15=""),1,0)+IF(AND($I15="あり",$K15=""),1,0)+IF(AND($AA15="",$AB15=""),1,0)+IF(AND($AC15="あり",$AD15=""),1,0)+IF(AND($AC15="あり",OR($AD15="",$AD15="後日提出"),$AE15=""),1,0))</f>
+        <f>IF($B15="","",IF($B15="",1,0)+IF($C15="",1,0)+IF($D15="",1,0)+IF($E15="",1,0)+IF($G15="",1,0)+IF($H15="",1,0)+IF($I15="",1,0)+IF($L15="",1,0)+IF($M15="",1,0)+IF($N15="",1,0)+IF($Q15="",1,0)+IF($S15="",1,0)+IF($AA15="",1,0)+IF($AC15="",1,0)+IF($AG15="",1,0)+IF($AH15="",1,0)+IF($AI15="",1,0)+IF($AL15="",1,0)+IF($AP15="",1,0)+IF($AQ15="",1,0)+IF(AND($I15="あり",$J15=""),1,0)+IF(AND($I15="あり",$K15=""),1,0)+IF(AND($AA15="",$AB15=""),1,0)+IF(AND($AC15="あり",$AD15=""),1,0)+IF(AND($AC15="あり",OR($AD15="",$AD15="後日提出"),$AE15=""),1,0)+IF($AV15="",1,0)+IF(AND($AL15="外国",$AM15=""),1,0)+IF(AND($AL15="外国",$AN15=""),1,0)+IF(AND($AL15="外国",$AO15=""),1,0))</f>
         <v/>
       </c>
       <c r="AU15">
         <f>IF($B15="","",IF(AND($AA15&lt;&gt;"",$AA15&lt;&gt;"後日提出",$AA15&lt;&gt;"別経路提出",LEN($AA15)&lt;&gt;12),1,0)+IF(AND($AB15&lt;&gt;"",$AB15&lt;&gt;"後日提出",LEN($AB15)&lt;&gt;10),1,0)+IF(AND($AD15&lt;&gt;"",$AD15&lt;&gt;"後日提出",LEN($AD15)&lt;&gt;11),1,0)+IF(AND($AG15&lt;&gt;"",LEN(SUBSTITUTE($AG15,"-",""))&lt;&gt;7),1,0))</f>
         <v/>
       </c>
+      <c r="AV15" s="17" t="n"/>
+      <c r="AW15" s="59" t="n"/>
+      <c r="AX15" s="17" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="23">
@@ -3692,7 +3718,7 @@
       <c r="M16" s="17" t="n"/>
       <c r="N16" s="17" t="n"/>
       <c r="O16" s="23">
-        <f>IF($B16="","",IF($I16="なし","あり",IF($I16="あり",IF(OR($K16="更新の可能性あり",AND($J16&lt;&gt;"",$G16&lt;&gt;"",$J16-$G16+1&gt;62)),"あり","なし"),"")))</f>
+        <f>IF($B16="","",IF($I16="なし","あり",IF($I16&lt;&gt;"あり","",IF($K16="更新の可能性あり","あり",IF(OR($J16="",$G16=""),"なし",IF(OR(NOT(ISNUMBER($G16)),NOT(ISNUMBER($J16)),$G16&gt;80000,$J16&gt;80000),"要確認（日付）",IF($J16&gt;IF(DAY(EDATE($G16,2))&lt;DAY($G16),EOMONTH($G16,2),EDATE($G16,2)-1),"あり","なし"))))))</f>
         <v/>
       </c>
       <c r="P16" s="23">
@@ -3710,7 +3736,7 @@
         <v/>
       </c>
       <c r="X16" s="23">
-        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B16="","",IF(AND($L16&gt;='⓪ 事業所設定'!$C$13*0.75,$M16&gt;='⓪ 事業所設定'!$C$14*0.75,$O16="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L16&gt;=20,$O16="あり",$N16&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S16+$T16)&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
+        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B16="","",IF(AND($L16&gt;='⓪ 事業所設定'!$C$13*0.75,$M16&gt;='⓪ 事業所設定'!$C$14*0.75,$O16="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L16&gt;=20,$O16="あり",$N16&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S16+$T16-N($AW16))&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
         <v/>
       </c>
       <c r="Y16" s="23">
@@ -3718,7 +3744,7 @@
         <v/>
       </c>
       <c r="Z16" s="23">
-        <f>IF($B16="","",IF(AND($L16&gt;=20,$P16="あり",$N16&lt;&gt;"昼間部の学生"),"加入","加入対象外"))</f>
+        <f>IF($B16="","",IF($H16="役員","対象外（兼務役員なら要相談）",IF(AND($L16&gt;=20,$P16="あり",$N16&lt;&gt;"昼間部の学生"),"加入","加入対象外")))</f>
         <v/>
       </c>
       <c r="AA16" s="61" t="n"/>
@@ -3740,13 +3766,16 @@
       <c r="AQ16" s="17" t="n"/>
       <c r="AR16" s="17" t="n"/>
       <c r="AT16">
-        <f>IF($B16="","",IF($B16="",1,0)+IF($C16="",1,0)+IF($D16="",1,0)+IF($E16="",1,0)+IF($G16="",1,0)+IF($H16="",1,0)+IF($I16="",1,0)+IF($L16="",1,0)+IF($M16="",1,0)+IF($N16="",1,0)+IF($Q16="",1,0)+IF($S16="",1,0)+IF($AA16="",1,0)+IF($AC16="",1,0)+IF($AG16="",1,0)+IF($AH16="",1,0)+IF($AI16="",1,0)+IF($AL16="",1,0)+IF($AP16="",1,0)+IF($AQ16="",1,0)+IF(AND($I16="あり",$J16=""),1,0)+IF(AND($I16="あり",$K16=""),1,0)+IF(AND($AA16="",$AB16=""),1,0)+IF(AND($AC16="あり",$AD16=""),1,0)+IF(AND($AC16="あり",OR($AD16="",$AD16="後日提出"),$AE16=""),1,0))</f>
+        <f>IF($B16="","",IF($B16="",1,0)+IF($C16="",1,0)+IF($D16="",1,0)+IF($E16="",1,0)+IF($G16="",1,0)+IF($H16="",1,0)+IF($I16="",1,0)+IF($L16="",1,0)+IF($M16="",1,0)+IF($N16="",1,0)+IF($Q16="",1,0)+IF($S16="",1,0)+IF($AA16="",1,0)+IF($AC16="",1,0)+IF($AG16="",1,0)+IF($AH16="",1,0)+IF($AI16="",1,0)+IF($AL16="",1,0)+IF($AP16="",1,0)+IF($AQ16="",1,0)+IF(AND($I16="あり",$J16=""),1,0)+IF(AND($I16="あり",$K16=""),1,0)+IF(AND($AA16="",$AB16=""),1,0)+IF(AND($AC16="あり",$AD16=""),1,0)+IF(AND($AC16="あり",OR($AD16="",$AD16="後日提出"),$AE16=""),1,0)+IF($AV16="",1,0)+IF(AND($AL16="外国",$AM16=""),1,0)+IF(AND($AL16="外国",$AN16=""),1,0)+IF(AND($AL16="外国",$AO16=""),1,0))</f>
         <v/>
       </c>
       <c r="AU16">
         <f>IF($B16="","",IF(AND($AA16&lt;&gt;"",$AA16&lt;&gt;"後日提出",$AA16&lt;&gt;"別経路提出",LEN($AA16)&lt;&gt;12),1,0)+IF(AND($AB16&lt;&gt;"",$AB16&lt;&gt;"後日提出",LEN($AB16)&lt;&gt;10),1,0)+IF(AND($AD16&lt;&gt;"",$AD16&lt;&gt;"後日提出",LEN($AD16)&lt;&gt;11),1,0)+IF(AND($AG16&lt;&gt;"",LEN(SUBSTITUTE($AG16,"-",""))&lt;&gt;7),1,0))</f>
         <v/>
       </c>
+      <c r="AV16" s="17" t="n"/>
+      <c r="AW16" s="59" t="n"/>
+      <c r="AX16" s="17" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="23">
@@ -3770,7 +3799,7 @@
       <c r="M17" s="17" t="n"/>
       <c r="N17" s="17" t="n"/>
       <c r="O17" s="23">
-        <f>IF($B17="","",IF($I17="なし","あり",IF($I17="あり",IF(OR($K17="更新の可能性あり",AND($J17&lt;&gt;"",$G17&lt;&gt;"",$J17-$G17+1&gt;62)),"あり","なし"),"")))</f>
+        <f>IF($B17="","",IF($I17="なし","あり",IF($I17&lt;&gt;"あり","",IF($K17="更新の可能性あり","あり",IF(OR($J17="",$G17=""),"なし",IF(OR(NOT(ISNUMBER($G17)),NOT(ISNUMBER($J17)),$G17&gt;80000,$J17&gt;80000),"要確認（日付）",IF($J17&gt;IF(DAY(EDATE($G17,2))&lt;DAY($G17),EOMONTH($G17,2),EDATE($G17,2)-1),"あり","なし"))))))</f>
         <v/>
       </c>
       <c r="P17" s="23">
@@ -3788,7 +3817,7 @@
         <v/>
       </c>
       <c r="X17" s="23">
-        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B17="","",IF(AND($L17&gt;='⓪ 事業所設定'!$C$13*0.75,$M17&gt;='⓪ 事業所設定'!$C$14*0.75,$O17="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L17&gt;=20,$O17="あり",$N17&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S17+$T17)&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
+        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B17="","",IF(AND($L17&gt;='⓪ 事業所設定'!$C$13*0.75,$M17&gt;='⓪ 事業所設定'!$C$14*0.75,$O17="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L17&gt;=20,$O17="あり",$N17&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S17+$T17-N($AW17))&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
         <v/>
       </c>
       <c r="Y17" s="23">
@@ -3796,7 +3825,7 @@
         <v/>
       </c>
       <c r="Z17" s="23">
-        <f>IF($B17="","",IF(AND($L17&gt;=20,$P17="あり",$N17&lt;&gt;"昼間部の学生"),"加入","加入対象外"))</f>
+        <f>IF($B17="","",IF($H17="役員","対象外（兼務役員なら要相談）",IF(AND($L17&gt;=20,$P17="あり",$N17&lt;&gt;"昼間部の学生"),"加入","加入対象外")))</f>
         <v/>
       </c>
       <c r="AA17" s="61" t="n"/>
@@ -3818,13 +3847,16 @@
       <c r="AQ17" s="17" t="n"/>
       <c r="AR17" s="17" t="n"/>
       <c r="AT17">
-        <f>IF($B17="","",IF($B17="",1,0)+IF($C17="",1,0)+IF($D17="",1,0)+IF($E17="",1,0)+IF($G17="",1,0)+IF($H17="",1,0)+IF($I17="",1,0)+IF($L17="",1,0)+IF($M17="",1,0)+IF($N17="",1,0)+IF($Q17="",1,0)+IF($S17="",1,0)+IF($AA17="",1,0)+IF($AC17="",1,0)+IF($AG17="",1,0)+IF($AH17="",1,0)+IF($AI17="",1,0)+IF($AL17="",1,0)+IF($AP17="",1,0)+IF($AQ17="",1,0)+IF(AND($I17="あり",$J17=""),1,0)+IF(AND($I17="あり",$K17=""),1,0)+IF(AND($AA17="",$AB17=""),1,0)+IF(AND($AC17="あり",$AD17=""),1,0)+IF(AND($AC17="あり",OR($AD17="",$AD17="後日提出"),$AE17=""),1,0))</f>
+        <f>IF($B17="","",IF($B17="",1,0)+IF($C17="",1,0)+IF($D17="",1,0)+IF($E17="",1,0)+IF($G17="",1,0)+IF($H17="",1,0)+IF($I17="",1,0)+IF($L17="",1,0)+IF($M17="",1,0)+IF($N17="",1,0)+IF($Q17="",1,0)+IF($S17="",1,0)+IF($AA17="",1,0)+IF($AC17="",1,0)+IF($AG17="",1,0)+IF($AH17="",1,0)+IF($AI17="",1,0)+IF($AL17="",1,0)+IF($AP17="",1,0)+IF($AQ17="",1,0)+IF(AND($I17="あり",$J17=""),1,0)+IF(AND($I17="あり",$K17=""),1,0)+IF(AND($AA17="",$AB17=""),1,0)+IF(AND($AC17="あり",$AD17=""),1,0)+IF(AND($AC17="あり",OR($AD17="",$AD17="後日提出"),$AE17=""),1,0)+IF($AV17="",1,0)+IF(AND($AL17="外国",$AM17=""),1,0)+IF(AND($AL17="外国",$AN17=""),1,0)+IF(AND($AL17="外国",$AO17=""),1,0))</f>
         <v/>
       </c>
       <c r="AU17">
         <f>IF($B17="","",IF(AND($AA17&lt;&gt;"",$AA17&lt;&gt;"後日提出",$AA17&lt;&gt;"別経路提出",LEN($AA17)&lt;&gt;12),1,0)+IF(AND($AB17&lt;&gt;"",$AB17&lt;&gt;"後日提出",LEN($AB17)&lt;&gt;10),1,0)+IF(AND($AD17&lt;&gt;"",$AD17&lt;&gt;"後日提出",LEN($AD17)&lt;&gt;11),1,0)+IF(AND($AG17&lt;&gt;"",LEN(SUBSTITUTE($AG17,"-",""))&lt;&gt;7),1,0))</f>
         <v/>
       </c>
+      <c r="AV17" s="17" t="n"/>
+      <c r="AW17" s="59" t="n"/>
+      <c r="AX17" s="17" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="23">
@@ -3848,7 +3880,7 @@
       <c r="M18" s="17" t="n"/>
       <c r="N18" s="17" t="n"/>
       <c r="O18" s="23">
-        <f>IF($B18="","",IF($I18="なし","あり",IF($I18="あり",IF(OR($K18="更新の可能性あり",AND($J18&lt;&gt;"",$G18&lt;&gt;"",$J18-$G18+1&gt;62)),"あり","なし"),"")))</f>
+        <f>IF($B18="","",IF($I18="なし","あり",IF($I18&lt;&gt;"あり","",IF($K18="更新の可能性あり","あり",IF(OR($J18="",$G18=""),"なし",IF(OR(NOT(ISNUMBER($G18)),NOT(ISNUMBER($J18)),$G18&gt;80000,$J18&gt;80000),"要確認（日付）",IF($J18&gt;IF(DAY(EDATE($G18,2))&lt;DAY($G18),EOMONTH($G18,2),EDATE($G18,2)-1),"あり","なし"))))))</f>
         <v/>
       </c>
       <c r="P18" s="23">
@@ -3866,7 +3898,7 @@
         <v/>
       </c>
       <c r="X18" s="23">
-        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B18="","",IF(AND($L18&gt;='⓪ 事業所設定'!$C$13*0.75,$M18&gt;='⓪ 事業所設定'!$C$14*0.75,$O18="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L18&gt;=20,$O18="あり",$N18&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S18+$T18)&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
+        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B18="","",IF(AND($L18&gt;='⓪ 事業所設定'!$C$13*0.75,$M18&gt;='⓪ 事業所設定'!$C$14*0.75,$O18="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L18&gt;=20,$O18="あり",$N18&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S18+$T18-N($AW18))&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
         <v/>
       </c>
       <c r="Y18" s="23">
@@ -3874,7 +3906,7 @@
         <v/>
       </c>
       <c r="Z18" s="23">
-        <f>IF($B18="","",IF(AND($L18&gt;=20,$P18="あり",$N18&lt;&gt;"昼間部の学生"),"加入","加入対象外"))</f>
+        <f>IF($B18="","",IF($H18="役員","対象外（兼務役員なら要相談）",IF(AND($L18&gt;=20,$P18="あり",$N18&lt;&gt;"昼間部の学生"),"加入","加入対象外")))</f>
         <v/>
       </c>
       <c r="AA18" s="61" t="n"/>
@@ -3896,13 +3928,16 @@
       <c r="AQ18" s="17" t="n"/>
       <c r="AR18" s="17" t="n"/>
       <c r="AT18">
-        <f>IF($B18="","",IF($B18="",1,0)+IF($C18="",1,0)+IF($D18="",1,0)+IF($E18="",1,0)+IF($G18="",1,0)+IF($H18="",1,0)+IF($I18="",1,0)+IF($L18="",1,0)+IF($M18="",1,0)+IF($N18="",1,0)+IF($Q18="",1,0)+IF($S18="",1,0)+IF($AA18="",1,0)+IF($AC18="",1,0)+IF($AG18="",1,0)+IF($AH18="",1,0)+IF($AI18="",1,0)+IF($AL18="",1,0)+IF($AP18="",1,0)+IF($AQ18="",1,0)+IF(AND($I18="あり",$J18=""),1,0)+IF(AND($I18="あり",$K18=""),1,0)+IF(AND($AA18="",$AB18=""),1,0)+IF(AND($AC18="あり",$AD18=""),1,0)+IF(AND($AC18="あり",OR($AD18="",$AD18="後日提出"),$AE18=""),1,0))</f>
+        <f>IF($B18="","",IF($B18="",1,0)+IF($C18="",1,0)+IF($D18="",1,0)+IF($E18="",1,0)+IF($G18="",1,0)+IF($H18="",1,0)+IF($I18="",1,0)+IF($L18="",1,0)+IF($M18="",1,0)+IF($N18="",1,0)+IF($Q18="",1,0)+IF($S18="",1,0)+IF($AA18="",1,0)+IF($AC18="",1,0)+IF($AG18="",1,0)+IF($AH18="",1,0)+IF($AI18="",1,0)+IF($AL18="",1,0)+IF($AP18="",1,0)+IF($AQ18="",1,0)+IF(AND($I18="あり",$J18=""),1,0)+IF(AND($I18="あり",$K18=""),1,0)+IF(AND($AA18="",$AB18=""),1,0)+IF(AND($AC18="あり",$AD18=""),1,0)+IF(AND($AC18="あり",OR($AD18="",$AD18="後日提出"),$AE18=""),1,0)+IF($AV18="",1,0)+IF(AND($AL18="外国",$AM18=""),1,0)+IF(AND($AL18="外国",$AN18=""),1,0)+IF(AND($AL18="外国",$AO18=""),1,0))</f>
         <v/>
       </c>
       <c r="AU18">
         <f>IF($B18="","",IF(AND($AA18&lt;&gt;"",$AA18&lt;&gt;"後日提出",$AA18&lt;&gt;"別経路提出",LEN($AA18)&lt;&gt;12),1,0)+IF(AND($AB18&lt;&gt;"",$AB18&lt;&gt;"後日提出",LEN($AB18)&lt;&gt;10),1,0)+IF(AND($AD18&lt;&gt;"",$AD18&lt;&gt;"後日提出",LEN($AD18)&lt;&gt;11),1,0)+IF(AND($AG18&lt;&gt;"",LEN(SUBSTITUTE($AG18,"-",""))&lt;&gt;7),1,0))</f>
         <v/>
       </c>
+      <c r="AV18" s="17" t="n"/>
+      <c r="AW18" s="59" t="n"/>
+      <c r="AX18" s="17" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="23">
@@ -3926,7 +3961,7 @@
       <c r="M19" s="17" t="n"/>
       <c r="N19" s="17" t="n"/>
       <c r="O19" s="23">
-        <f>IF($B19="","",IF($I19="なし","あり",IF($I19="あり",IF(OR($K19="更新の可能性あり",AND($J19&lt;&gt;"",$G19&lt;&gt;"",$J19-$G19+1&gt;62)),"あり","なし"),"")))</f>
+        <f>IF($B19="","",IF($I19="なし","あり",IF($I19&lt;&gt;"あり","",IF($K19="更新の可能性あり","あり",IF(OR($J19="",$G19=""),"なし",IF(OR(NOT(ISNUMBER($G19)),NOT(ISNUMBER($J19)),$G19&gt;80000,$J19&gt;80000),"要確認（日付）",IF($J19&gt;IF(DAY(EDATE($G19,2))&lt;DAY($G19),EOMONTH($G19,2),EDATE($G19,2)-1),"あり","なし"))))))</f>
         <v/>
       </c>
       <c r="P19" s="23">
@@ -3944,7 +3979,7 @@
         <v/>
       </c>
       <c r="X19" s="23">
-        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B19="","",IF(AND($L19&gt;='⓪ 事業所設定'!$C$13*0.75,$M19&gt;='⓪ 事業所設定'!$C$14*0.75,$O19="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L19&gt;=20,$O19="あり",$N19&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S19+$T19)&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
+        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B19="","",IF(AND($L19&gt;='⓪ 事業所設定'!$C$13*0.75,$M19&gt;='⓪ 事業所設定'!$C$14*0.75,$O19="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L19&gt;=20,$O19="あり",$N19&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S19+$T19-N($AW19))&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
         <v/>
       </c>
       <c r="Y19" s="23">
@@ -3952,7 +3987,7 @@
         <v/>
       </c>
       <c r="Z19" s="23">
-        <f>IF($B19="","",IF(AND($L19&gt;=20,$P19="あり",$N19&lt;&gt;"昼間部の学生"),"加入","加入対象外"))</f>
+        <f>IF($B19="","",IF($H19="役員","対象外（兼務役員なら要相談）",IF(AND($L19&gt;=20,$P19="あり",$N19&lt;&gt;"昼間部の学生"),"加入","加入対象外")))</f>
         <v/>
       </c>
       <c r="AA19" s="61" t="n"/>
@@ -3974,13 +4009,16 @@
       <c r="AQ19" s="17" t="n"/>
       <c r="AR19" s="17" t="n"/>
       <c r="AT19">
-        <f>IF($B19="","",IF($B19="",1,0)+IF($C19="",1,0)+IF($D19="",1,0)+IF($E19="",1,0)+IF($G19="",1,0)+IF($H19="",1,0)+IF($I19="",1,0)+IF($L19="",1,0)+IF($M19="",1,0)+IF($N19="",1,0)+IF($Q19="",1,0)+IF($S19="",1,0)+IF($AA19="",1,0)+IF($AC19="",1,0)+IF($AG19="",1,0)+IF($AH19="",1,0)+IF($AI19="",1,0)+IF($AL19="",1,0)+IF($AP19="",1,0)+IF($AQ19="",1,0)+IF(AND($I19="あり",$J19=""),1,0)+IF(AND($I19="あり",$K19=""),1,0)+IF(AND($AA19="",$AB19=""),1,0)+IF(AND($AC19="あり",$AD19=""),1,0)+IF(AND($AC19="あり",OR($AD19="",$AD19="後日提出"),$AE19=""),1,0))</f>
+        <f>IF($B19="","",IF($B19="",1,0)+IF($C19="",1,0)+IF($D19="",1,0)+IF($E19="",1,0)+IF($G19="",1,0)+IF($H19="",1,0)+IF($I19="",1,0)+IF($L19="",1,0)+IF($M19="",1,0)+IF($N19="",1,0)+IF($Q19="",1,0)+IF($S19="",1,0)+IF($AA19="",1,0)+IF($AC19="",1,0)+IF($AG19="",1,0)+IF($AH19="",1,0)+IF($AI19="",1,0)+IF($AL19="",1,0)+IF($AP19="",1,0)+IF($AQ19="",1,0)+IF(AND($I19="あり",$J19=""),1,0)+IF(AND($I19="あり",$K19=""),1,0)+IF(AND($AA19="",$AB19=""),1,0)+IF(AND($AC19="あり",$AD19=""),1,0)+IF(AND($AC19="あり",OR($AD19="",$AD19="後日提出"),$AE19=""),1,0)+IF($AV19="",1,0)+IF(AND($AL19="外国",$AM19=""),1,0)+IF(AND($AL19="外国",$AN19=""),1,0)+IF(AND($AL19="外国",$AO19=""),1,0))</f>
         <v/>
       </c>
       <c r="AU19">
         <f>IF($B19="","",IF(AND($AA19&lt;&gt;"",$AA19&lt;&gt;"後日提出",$AA19&lt;&gt;"別経路提出",LEN($AA19)&lt;&gt;12),1,0)+IF(AND($AB19&lt;&gt;"",$AB19&lt;&gt;"後日提出",LEN($AB19)&lt;&gt;10),1,0)+IF(AND($AD19&lt;&gt;"",$AD19&lt;&gt;"後日提出",LEN($AD19)&lt;&gt;11),1,0)+IF(AND($AG19&lt;&gt;"",LEN(SUBSTITUTE($AG19,"-",""))&lt;&gt;7),1,0))</f>
         <v/>
       </c>
+      <c r="AV19" s="17" t="n"/>
+      <c r="AW19" s="59" t="n"/>
+      <c r="AX19" s="17" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="23">
@@ -4004,7 +4042,7 @@
       <c r="M20" s="17" t="n"/>
       <c r="N20" s="17" t="n"/>
       <c r="O20" s="23">
-        <f>IF($B20="","",IF($I20="なし","あり",IF($I20="あり",IF(OR($K20="更新の可能性あり",AND($J20&lt;&gt;"",$G20&lt;&gt;"",$J20-$G20+1&gt;62)),"あり","なし"),"")))</f>
+        <f>IF($B20="","",IF($I20="なし","あり",IF($I20&lt;&gt;"あり","",IF($K20="更新の可能性あり","あり",IF(OR($J20="",$G20=""),"なし",IF(OR(NOT(ISNUMBER($G20)),NOT(ISNUMBER($J20)),$G20&gt;80000,$J20&gt;80000),"要確認（日付）",IF($J20&gt;IF(DAY(EDATE($G20,2))&lt;DAY($G20),EOMONTH($G20,2),EDATE($G20,2)-1),"あり","なし"))))))</f>
         <v/>
       </c>
       <c r="P20" s="23">
@@ -4022,7 +4060,7 @@
         <v/>
       </c>
       <c r="X20" s="23">
-        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B20="","",IF(AND($L20&gt;='⓪ 事業所設定'!$C$13*0.75,$M20&gt;='⓪ 事業所設定'!$C$14*0.75,$O20="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L20&gt;=20,$O20="あり",$N20&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S20+$T20)&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
+        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B20="","",IF(AND($L20&gt;='⓪ 事業所設定'!$C$13*0.75,$M20&gt;='⓪ 事業所設定'!$C$14*0.75,$O20="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L20&gt;=20,$O20="あり",$N20&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S20+$T20-N($AW20))&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
         <v/>
       </c>
       <c r="Y20" s="23">
@@ -4030,7 +4068,7 @@
         <v/>
       </c>
       <c r="Z20" s="23">
-        <f>IF($B20="","",IF(AND($L20&gt;=20,$P20="あり",$N20&lt;&gt;"昼間部の学生"),"加入","加入対象外"))</f>
+        <f>IF($B20="","",IF($H20="役員","対象外（兼務役員なら要相談）",IF(AND($L20&gt;=20,$P20="あり",$N20&lt;&gt;"昼間部の学生"),"加入","加入対象外")))</f>
         <v/>
       </c>
       <c r="AA20" s="61" t="n"/>
@@ -4052,13 +4090,16 @@
       <c r="AQ20" s="17" t="n"/>
       <c r="AR20" s="17" t="n"/>
       <c r="AT20">
-        <f>IF($B20="","",IF($B20="",1,0)+IF($C20="",1,0)+IF($D20="",1,0)+IF($E20="",1,0)+IF($G20="",1,0)+IF($H20="",1,0)+IF($I20="",1,0)+IF($L20="",1,0)+IF($M20="",1,0)+IF($N20="",1,0)+IF($Q20="",1,0)+IF($S20="",1,0)+IF($AA20="",1,0)+IF($AC20="",1,0)+IF($AG20="",1,0)+IF($AH20="",1,0)+IF($AI20="",1,0)+IF($AL20="",1,0)+IF($AP20="",1,0)+IF($AQ20="",1,0)+IF(AND($I20="あり",$J20=""),1,0)+IF(AND($I20="あり",$K20=""),1,0)+IF(AND($AA20="",$AB20=""),1,0)+IF(AND($AC20="あり",$AD20=""),1,0)+IF(AND($AC20="あり",OR($AD20="",$AD20="後日提出"),$AE20=""),1,0))</f>
+        <f>IF($B20="","",IF($B20="",1,0)+IF($C20="",1,0)+IF($D20="",1,0)+IF($E20="",1,0)+IF($G20="",1,0)+IF($H20="",1,0)+IF($I20="",1,0)+IF($L20="",1,0)+IF($M20="",1,0)+IF($N20="",1,0)+IF($Q20="",1,0)+IF($S20="",1,0)+IF($AA20="",1,0)+IF($AC20="",1,0)+IF($AG20="",1,0)+IF($AH20="",1,0)+IF($AI20="",1,0)+IF($AL20="",1,0)+IF($AP20="",1,0)+IF($AQ20="",1,0)+IF(AND($I20="あり",$J20=""),1,0)+IF(AND($I20="あり",$K20=""),1,0)+IF(AND($AA20="",$AB20=""),1,0)+IF(AND($AC20="あり",$AD20=""),1,0)+IF(AND($AC20="あり",OR($AD20="",$AD20="後日提出"),$AE20=""),1,0)+IF($AV20="",1,0)+IF(AND($AL20="外国",$AM20=""),1,0)+IF(AND($AL20="外国",$AN20=""),1,0)+IF(AND($AL20="外国",$AO20=""),1,0))</f>
         <v/>
       </c>
       <c r="AU20">
         <f>IF($B20="","",IF(AND($AA20&lt;&gt;"",$AA20&lt;&gt;"後日提出",$AA20&lt;&gt;"別経路提出",LEN($AA20)&lt;&gt;12),1,0)+IF(AND($AB20&lt;&gt;"",$AB20&lt;&gt;"後日提出",LEN($AB20)&lt;&gt;10),1,0)+IF(AND($AD20&lt;&gt;"",$AD20&lt;&gt;"後日提出",LEN($AD20)&lt;&gt;11),1,0)+IF(AND($AG20&lt;&gt;"",LEN(SUBSTITUTE($AG20,"-",""))&lt;&gt;7),1,0))</f>
         <v/>
       </c>
+      <c r="AV20" s="17" t="n"/>
+      <c r="AW20" s="59" t="n"/>
+      <c r="AX20" s="17" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="23">
@@ -4082,7 +4123,7 @@
       <c r="M21" s="17" t="n"/>
       <c r="N21" s="17" t="n"/>
       <c r="O21" s="23">
-        <f>IF($B21="","",IF($I21="なし","あり",IF($I21="あり",IF(OR($K21="更新の可能性あり",AND($J21&lt;&gt;"",$G21&lt;&gt;"",$J21-$G21+1&gt;62)),"あり","なし"),"")))</f>
+        <f>IF($B21="","",IF($I21="なし","あり",IF($I21&lt;&gt;"あり","",IF($K21="更新の可能性あり","あり",IF(OR($J21="",$G21=""),"なし",IF(OR(NOT(ISNUMBER($G21)),NOT(ISNUMBER($J21)),$G21&gt;80000,$J21&gt;80000),"要確認（日付）",IF($J21&gt;IF(DAY(EDATE($G21,2))&lt;DAY($G21),EOMONTH($G21,2),EDATE($G21,2)-1),"あり","なし"))))))</f>
         <v/>
       </c>
       <c r="P21" s="23">
@@ -4100,7 +4141,7 @@
         <v/>
       </c>
       <c r="X21" s="23">
-        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B21="","",IF(AND($L21&gt;='⓪ 事業所設定'!$C$13*0.75,$M21&gt;='⓪ 事業所設定'!$C$14*0.75,$O21="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L21&gt;=20,$O21="あり",$N21&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S21+$T21)&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
+        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B21="","",IF(AND($L21&gt;='⓪ 事業所設定'!$C$13*0.75,$M21&gt;='⓪ 事業所設定'!$C$14*0.75,$O21="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L21&gt;=20,$O21="あり",$N21&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S21+$T21-N($AW21))&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
         <v/>
       </c>
       <c r="Y21" s="23">
@@ -4108,7 +4149,7 @@
         <v/>
       </c>
       <c r="Z21" s="23">
-        <f>IF($B21="","",IF(AND($L21&gt;=20,$P21="あり",$N21&lt;&gt;"昼間部の学生"),"加入","加入対象外"))</f>
+        <f>IF($B21="","",IF($H21="役員","対象外（兼務役員なら要相談）",IF(AND($L21&gt;=20,$P21="あり",$N21&lt;&gt;"昼間部の学生"),"加入","加入対象外")))</f>
         <v/>
       </c>
       <c r="AA21" s="61" t="n"/>
@@ -4130,13 +4171,16 @@
       <c r="AQ21" s="17" t="n"/>
       <c r="AR21" s="17" t="n"/>
       <c r="AT21">
-        <f>IF($B21="","",IF($B21="",1,0)+IF($C21="",1,0)+IF($D21="",1,0)+IF($E21="",1,0)+IF($G21="",1,0)+IF($H21="",1,0)+IF($I21="",1,0)+IF($L21="",1,0)+IF($M21="",1,0)+IF($N21="",1,0)+IF($Q21="",1,0)+IF($S21="",1,0)+IF($AA21="",1,0)+IF($AC21="",1,0)+IF($AG21="",1,0)+IF($AH21="",1,0)+IF($AI21="",1,0)+IF($AL21="",1,0)+IF($AP21="",1,0)+IF($AQ21="",1,0)+IF(AND($I21="あり",$J21=""),1,0)+IF(AND($I21="あり",$K21=""),1,0)+IF(AND($AA21="",$AB21=""),1,0)+IF(AND($AC21="あり",$AD21=""),1,0)+IF(AND($AC21="あり",OR($AD21="",$AD21="後日提出"),$AE21=""),1,0))</f>
+        <f>IF($B21="","",IF($B21="",1,0)+IF($C21="",1,0)+IF($D21="",1,0)+IF($E21="",1,0)+IF($G21="",1,0)+IF($H21="",1,0)+IF($I21="",1,0)+IF($L21="",1,0)+IF($M21="",1,0)+IF($N21="",1,0)+IF($Q21="",1,0)+IF($S21="",1,0)+IF($AA21="",1,0)+IF($AC21="",1,0)+IF($AG21="",1,0)+IF($AH21="",1,0)+IF($AI21="",1,0)+IF($AL21="",1,0)+IF($AP21="",1,0)+IF($AQ21="",1,0)+IF(AND($I21="あり",$J21=""),1,0)+IF(AND($I21="あり",$K21=""),1,0)+IF(AND($AA21="",$AB21=""),1,0)+IF(AND($AC21="あり",$AD21=""),1,0)+IF(AND($AC21="あり",OR($AD21="",$AD21="後日提出"),$AE21=""),1,0)+IF($AV21="",1,0)+IF(AND($AL21="外国",$AM21=""),1,0)+IF(AND($AL21="外国",$AN21=""),1,0)+IF(AND($AL21="外国",$AO21=""),1,0))</f>
         <v/>
       </c>
       <c r="AU21">
         <f>IF($B21="","",IF(AND($AA21&lt;&gt;"",$AA21&lt;&gt;"後日提出",$AA21&lt;&gt;"別経路提出",LEN($AA21)&lt;&gt;12),1,0)+IF(AND($AB21&lt;&gt;"",$AB21&lt;&gt;"後日提出",LEN($AB21)&lt;&gt;10),1,0)+IF(AND($AD21&lt;&gt;"",$AD21&lt;&gt;"後日提出",LEN($AD21)&lt;&gt;11),1,0)+IF(AND($AG21&lt;&gt;"",LEN(SUBSTITUTE($AG21,"-",""))&lt;&gt;7),1,0))</f>
         <v/>
       </c>
+      <c r="AV21" s="17" t="n"/>
+      <c r="AW21" s="59" t="n"/>
+      <c r="AX21" s="17" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="23">
@@ -4160,7 +4204,7 @@
       <c r="M22" s="17" t="n"/>
       <c r="N22" s="17" t="n"/>
       <c r="O22" s="23">
-        <f>IF($B22="","",IF($I22="なし","あり",IF($I22="あり",IF(OR($K22="更新の可能性あり",AND($J22&lt;&gt;"",$G22&lt;&gt;"",$J22-$G22+1&gt;62)),"あり","なし"),"")))</f>
+        <f>IF($B22="","",IF($I22="なし","あり",IF($I22&lt;&gt;"あり","",IF($K22="更新の可能性あり","あり",IF(OR($J22="",$G22=""),"なし",IF(OR(NOT(ISNUMBER($G22)),NOT(ISNUMBER($J22)),$G22&gt;80000,$J22&gt;80000),"要確認（日付）",IF($J22&gt;IF(DAY(EDATE($G22,2))&lt;DAY($G22),EOMONTH($G22,2),EDATE($G22,2)-1),"あり","なし"))))))</f>
         <v/>
       </c>
       <c r="P22" s="23">
@@ -4178,7 +4222,7 @@
         <v/>
       </c>
       <c r="X22" s="23">
-        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B22="","",IF(AND($L22&gt;='⓪ 事業所設定'!$C$13*0.75,$M22&gt;='⓪ 事業所設定'!$C$14*0.75,$O22="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L22&gt;=20,$O22="あり",$N22&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S22+$T22)&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
+        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B22="","",IF(AND($L22&gt;='⓪ 事業所設定'!$C$13*0.75,$M22&gt;='⓪ 事業所設定'!$C$14*0.75,$O22="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L22&gt;=20,$O22="あり",$N22&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S22+$T22-N($AW22))&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
         <v/>
       </c>
       <c r="Y22" s="23">
@@ -4186,7 +4230,7 @@
         <v/>
       </c>
       <c r="Z22" s="23">
-        <f>IF($B22="","",IF(AND($L22&gt;=20,$P22="あり",$N22&lt;&gt;"昼間部の学生"),"加入","加入対象外"))</f>
+        <f>IF($B22="","",IF($H22="役員","対象外（兼務役員なら要相談）",IF(AND($L22&gt;=20,$P22="あり",$N22&lt;&gt;"昼間部の学生"),"加入","加入対象外")))</f>
         <v/>
       </c>
       <c r="AA22" s="61" t="n"/>
@@ -4208,13 +4252,16 @@
       <c r="AQ22" s="17" t="n"/>
       <c r="AR22" s="17" t="n"/>
       <c r="AT22">
-        <f>IF($B22="","",IF($B22="",1,0)+IF($C22="",1,0)+IF($D22="",1,0)+IF($E22="",1,0)+IF($G22="",1,0)+IF($H22="",1,0)+IF($I22="",1,0)+IF($L22="",1,0)+IF($M22="",1,0)+IF($N22="",1,0)+IF($Q22="",1,0)+IF($S22="",1,0)+IF($AA22="",1,0)+IF($AC22="",1,0)+IF($AG22="",1,0)+IF($AH22="",1,0)+IF($AI22="",1,0)+IF($AL22="",1,0)+IF($AP22="",1,0)+IF($AQ22="",1,0)+IF(AND($I22="あり",$J22=""),1,0)+IF(AND($I22="あり",$K22=""),1,0)+IF(AND($AA22="",$AB22=""),1,0)+IF(AND($AC22="あり",$AD22=""),1,0)+IF(AND($AC22="あり",OR($AD22="",$AD22="後日提出"),$AE22=""),1,0))</f>
+        <f>IF($B22="","",IF($B22="",1,0)+IF($C22="",1,0)+IF($D22="",1,0)+IF($E22="",1,0)+IF($G22="",1,0)+IF($H22="",1,0)+IF($I22="",1,0)+IF($L22="",1,0)+IF($M22="",1,0)+IF($N22="",1,0)+IF($Q22="",1,0)+IF($S22="",1,0)+IF($AA22="",1,0)+IF($AC22="",1,0)+IF($AG22="",1,0)+IF($AH22="",1,0)+IF($AI22="",1,0)+IF($AL22="",1,0)+IF($AP22="",1,0)+IF($AQ22="",1,0)+IF(AND($I22="あり",$J22=""),1,0)+IF(AND($I22="あり",$K22=""),1,0)+IF(AND($AA22="",$AB22=""),1,0)+IF(AND($AC22="あり",$AD22=""),1,0)+IF(AND($AC22="あり",OR($AD22="",$AD22="後日提出"),$AE22=""),1,0)+IF($AV22="",1,0)+IF(AND($AL22="外国",$AM22=""),1,0)+IF(AND($AL22="外国",$AN22=""),1,0)+IF(AND($AL22="外国",$AO22=""),1,0))</f>
         <v/>
       </c>
       <c r="AU22">
         <f>IF($B22="","",IF(AND($AA22&lt;&gt;"",$AA22&lt;&gt;"後日提出",$AA22&lt;&gt;"別経路提出",LEN($AA22)&lt;&gt;12),1,0)+IF(AND($AB22&lt;&gt;"",$AB22&lt;&gt;"後日提出",LEN($AB22)&lt;&gt;10),1,0)+IF(AND($AD22&lt;&gt;"",$AD22&lt;&gt;"後日提出",LEN($AD22)&lt;&gt;11),1,0)+IF(AND($AG22&lt;&gt;"",LEN(SUBSTITUTE($AG22,"-",""))&lt;&gt;7),1,0))</f>
         <v/>
       </c>
+      <c r="AV22" s="17" t="n"/>
+      <c r="AW22" s="59" t="n"/>
+      <c r="AX22" s="17" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="23">
@@ -4238,7 +4285,7 @@
       <c r="M23" s="17" t="n"/>
       <c r="N23" s="17" t="n"/>
       <c r="O23" s="23">
-        <f>IF($B23="","",IF($I23="なし","あり",IF($I23="あり",IF(OR($K23="更新の可能性あり",AND($J23&lt;&gt;"",$G23&lt;&gt;"",$J23-$G23+1&gt;62)),"あり","なし"),"")))</f>
+        <f>IF($B23="","",IF($I23="なし","あり",IF($I23&lt;&gt;"あり","",IF($K23="更新の可能性あり","あり",IF(OR($J23="",$G23=""),"なし",IF(OR(NOT(ISNUMBER($G23)),NOT(ISNUMBER($J23)),$G23&gt;80000,$J23&gt;80000),"要確認（日付）",IF($J23&gt;IF(DAY(EDATE($G23,2))&lt;DAY($G23),EOMONTH($G23,2),EDATE($G23,2)-1),"あり","なし"))))))</f>
         <v/>
       </c>
       <c r="P23" s="23">
@@ -4256,7 +4303,7 @@
         <v/>
       </c>
       <c r="X23" s="23">
-        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B23="","",IF(AND($L23&gt;='⓪ 事業所設定'!$C$13*0.75,$M23&gt;='⓪ 事業所設定'!$C$14*0.75,$O23="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L23&gt;=20,$O23="あり",$N23&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S23+$T23)&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
+        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B23="","",IF(AND($L23&gt;='⓪ 事業所設定'!$C$13*0.75,$M23&gt;='⓪ 事業所設定'!$C$14*0.75,$O23="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L23&gt;=20,$O23="あり",$N23&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S23+$T23-N($AW23))&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
         <v/>
       </c>
       <c r="Y23" s="23">
@@ -4264,7 +4311,7 @@
         <v/>
       </c>
       <c r="Z23" s="23">
-        <f>IF($B23="","",IF(AND($L23&gt;=20,$P23="あり",$N23&lt;&gt;"昼間部の学生"),"加入","加入対象外"))</f>
+        <f>IF($B23="","",IF($H23="役員","対象外（兼務役員なら要相談）",IF(AND($L23&gt;=20,$P23="あり",$N23&lt;&gt;"昼間部の学生"),"加入","加入対象外")))</f>
         <v/>
       </c>
       <c r="AA23" s="61" t="n"/>
@@ -4286,13 +4333,16 @@
       <c r="AQ23" s="17" t="n"/>
       <c r="AR23" s="17" t="n"/>
       <c r="AT23">
-        <f>IF($B23="","",IF($B23="",1,0)+IF($C23="",1,0)+IF($D23="",1,0)+IF($E23="",1,0)+IF($G23="",1,0)+IF($H23="",1,0)+IF($I23="",1,0)+IF($L23="",1,0)+IF($M23="",1,0)+IF($N23="",1,0)+IF($Q23="",1,0)+IF($S23="",1,0)+IF($AA23="",1,0)+IF($AC23="",1,0)+IF($AG23="",1,0)+IF($AH23="",1,0)+IF($AI23="",1,0)+IF($AL23="",1,0)+IF($AP23="",1,0)+IF($AQ23="",1,0)+IF(AND($I23="あり",$J23=""),1,0)+IF(AND($I23="あり",$K23=""),1,0)+IF(AND($AA23="",$AB23=""),1,0)+IF(AND($AC23="あり",$AD23=""),1,0)+IF(AND($AC23="あり",OR($AD23="",$AD23="後日提出"),$AE23=""),1,0))</f>
+        <f>IF($B23="","",IF($B23="",1,0)+IF($C23="",1,0)+IF($D23="",1,0)+IF($E23="",1,0)+IF($G23="",1,0)+IF($H23="",1,0)+IF($I23="",1,0)+IF($L23="",1,0)+IF($M23="",1,0)+IF($N23="",1,0)+IF($Q23="",1,0)+IF($S23="",1,0)+IF($AA23="",1,0)+IF($AC23="",1,0)+IF($AG23="",1,0)+IF($AH23="",1,0)+IF($AI23="",1,0)+IF($AL23="",1,0)+IF($AP23="",1,0)+IF($AQ23="",1,0)+IF(AND($I23="あり",$J23=""),1,0)+IF(AND($I23="あり",$K23=""),1,0)+IF(AND($AA23="",$AB23=""),1,0)+IF(AND($AC23="あり",$AD23=""),1,0)+IF(AND($AC23="あり",OR($AD23="",$AD23="後日提出"),$AE23=""),1,0)+IF($AV23="",1,0)+IF(AND($AL23="外国",$AM23=""),1,0)+IF(AND($AL23="外国",$AN23=""),1,0)+IF(AND($AL23="外国",$AO23=""),1,0))</f>
         <v/>
       </c>
       <c r="AU23">
         <f>IF($B23="","",IF(AND($AA23&lt;&gt;"",$AA23&lt;&gt;"後日提出",$AA23&lt;&gt;"別経路提出",LEN($AA23)&lt;&gt;12),1,0)+IF(AND($AB23&lt;&gt;"",$AB23&lt;&gt;"後日提出",LEN($AB23)&lt;&gt;10),1,0)+IF(AND($AD23&lt;&gt;"",$AD23&lt;&gt;"後日提出",LEN($AD23)&lt;&gt;11),1,0)+IF(AND($AG23&lt;&gt;"",LEN(SUBSTITUTE($AG23,"-",""))&lt;&gt;7),1,0))</f>
         <v/>
       </c>
+      <c r="AV23" s="17" t="n"/>
+      <c r="AW23" s="59" t="n"/>
+      <c r="AX23" s="17" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="23">
@@ -4316,7 +4366,7 @@
       <c r="M24" s="17" t="n"/>
       <c r="N24" s="17" t="n"/>
       <c r="O24" s="23">
-        <f>IF($B24="","",IF($I24="なし","あり",IF($I24="あり",IF(OR($K24="更新の可能性あり",AND($J24&lt;&gt;"",$G24&lt;&gt;"",$J24-$G24+1&gt;62)),"あり","なし"),"")))</f>
+        <f>IF($B24="","",IF($I24="なし","あり",IF($I24&lt;&gt;"あり","",IF($K24="更新の可能性あり","あり",IF(OR($J24="",$G24=""),"なし",IF(OR(NOT(ISNUMBER($G24)),NOT(ISNUMBER($J24)),$G24&gt;80000,$J24&gt;80000),"要確認（日付）",IF($J24&gt;IF(DAY(EDATE($G24,2))&lt;DAY($G24),EOMONTH($G24,2),EDATE($G24,2)-1),"あり","なし"))))))</f>
         <v/>
       </c>
       <c r="P24" s="23">
@@ -4334,7 +4384,7 @@
         <v/>
       </c>
       <c r="X24" s="23">
-        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B24="","",IF(AND($L24&gt;='⓪ 事業所設定'!$C$13*0.75,$M24&gt;='⓪ 事業所設定'!$C$14*0.75,$O24="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L24&gt;=20,$O24="あり",$N24&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S24+$T24)&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
+        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B24="","",IF(AND($L24&gt;='⓪ 事業所設定'!$C$13*0.75,$M24&gt;='⓪ 事業所設定'!$C$14*0.75,$O24="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L24&gt;=20,$O24="あり",$N24&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S24+$T24-N($AW24))&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
         <v/>
       </c>
       <c r="Y24" s="23">
@@ -4342,7 +4392,7 @@
         <v/>
       </c>
       <c r="Z24" s="23">
-        <f>IF($B24="","",IF(AND($L24&gt;=20,$P24="あり",$N24&lt;&gt;"昼間部の学生"),"加入","加入対象外"))</f>
+        <f>IF($B24="","",IF($H24="役員","対象外（兼務役員なら要相談）",IF(AND($L24&gt;=20,$P24="あり",$N24&lt;&gt;"昼間部の学生"),"加入","加入対象外")))</f>
         <v/>
       </c>
       <c r="AA24" s="61" t="n"/>
@@ -4364,13 +4414,16 @@
       <c r="AQ24" s="17" t="n"/>
       <c r="AR24" s="17" t="n"/>
       <c r="AT24">
-        <f>IF($B24="","",IF($B24="",1,0)+IF($C24="",1,0)+IF($D24="",1,0)+IF($E24="",1,0)+IF($G24="",1,0)+IF($H24="",1,0)+IF($I24="",1,0)+IF($L24="",1,0)+IF($M24="",1,0)+IF($N24="",1,0)+IF($Q24="",1,0)+IF($S24="",1,0)+IF($AA24="",1,0)+IF($AC24="",1,0)+IF($AG24="",1,0)+IF($AH24="",1,0)+IF($AI24="",1,0)+IF($AL24="",1,0)+IF($AP24="",1,0)+IF($AQ24="",1,0)+IF(AND($I24="あり",$J24=""),1,0)+IF(AND($I24="あり",$K24=""),1,0)+IF(AND($AA24="",$AB24=""),1,0)+IF(AND($AC24="あり",$AD24=""),1,0)+IF(AND($AC24="あり",OR($AD24="",$AD24="後日提出"),$AE24=""),1,0))</f>
+        <f>IF($B24="","",IF($B24="",1,0)+IF($C24="",1,0)+IF($D24="",1,0)+IF($E24="",1,0)+IF($G24="",1,0)+IF($H24="",1,0)+IF($I24="",1,0)+IF($L24="",1,0)+IF($M24="",1,0)+IF($N24="",1,0)+IF($Q24="",1,0)+IF($S24="",1,0)+IF($AA24="",1,0)+IF($AC24="",1,0)+IF($AG24="",1,0)+IF($AH24="",1,0)+IF($AI24="",1,0)+IF($AL24="",1,0)+IF($AP24="",1,0)+IF($AQ24="",1,0)+IF(AND($I24="あり",$J24=""),1,0)+IF(AND($I24="あり",$K24=""),1,0)+IF(AND($AA24="",$AB24=""),1,0)+IF(AND($AC24="あり",$AD24=""),1,0)+IF(AND($AC24="あり",OR($AD24="",$AD24="後日提出"),$AE24=""),1,0)+IF($AV24="",1,0)+IF(AND($AL24="外国",$AM24=""),1,0)+IF(AND($AL24="外国",$AN24=""),1,0)+IF(AND($AL24="外国",$AO24=""),1,0))</f>
         <v/>
       </c>
       <c r="AU24">
         <f>IF($B24="","",IF(AND($AA24&lt;&gt;"",$AA24&lt;&gt;"後日提出",$AA24&lt;&gt;"別経路提出",LEN($AA24)&lt;&gt;12),1,0)+IF(AND($AB24&lt;&gt;"",$AB24&lt;&gt;"後日提出",LEN($AB24)&lt;&gt;10),1,0)+IF(AND($AD24&lt;&gt;"",$AD24&lt;&gt;"後日提出",LEN($AD24)&lt;&gt;11),1,0)+IF(AND($AG24&lt;&gt;"",LEN(SUBSTITUTE($AG24,"-",""))&lt;&gt;7),1,0))</f>
         <v/>
       </c>
+      <c r="AV24" s="17" t="n"/>
+      <c r="AW24" s="59" t="n"/>
+      <c r="AX24" s="17" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="23">
@@ -4394,7 +4447,7 @@
       <c r="M25" s="17" t="n"/>
       <c r="N25" s="17" t="n"/>
       <c r="O25" s="23">
-        <f>IF($B25="","",IF($I25="なし","あり",IF($I25="あり",IF(OR($K25="更新の可能性あり",AND($J25&lt;&gt;"",$G25&lt;&gt;"",$J25-$G25+1&gt;62)),"あり","なし"),"")))</f>
+        <f>IF($B25="","",IF($I25="なし","あり",IF($I25&lt;&gt;"あり","",IF($K25="更新の可能性あり","あり",IF(OR($J25="",$G25=""),"なし",IF(OR(NOT(ISNUMBER($G25)),NOT(ISNUMBER($J25)),$G25&gt;80000,$J25&gt;80000),"要確認（日付）",IF($J25&gt;IF(DAY(EDATE($G25,2))&lt;DAY($G25),EOMONTH($G25,2),EDATE($G25,2)-1),"あり","なし"))))))</f>
         <v/>
       </c>
       <c r="P25" s="23">
@@ -4412,7 +4465,7 @@
         <v/>
       </c>
       <c r="X25" s="23">
-        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B25="","",IF(AND($L25&gt;='⓪ 事業所設定'!$C$13*0.75,$M25&gt;='⓪ 事業所設定'!$C$14*0.75,$O25="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L25&gt;=20,$O25="あり",$N25&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S25+$T25)&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
+        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B25="","",IF(AND($L25&gt;='⓪ 事業所設定'!$C$13*0.75,$M25&gt;='⓪ 事業所設定'!$C$14*0.75,$O25="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L25&gt;=20,$O25="あり",$N25&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S25+$T25-N($AW25))&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
         <v/>
       </c>
       <c r="Y25" s="23">
@@ -4420,7 +4473,7 @@
         <v/>
       </c>
       <c r="Z25" s="23">
-        <f>IF($B25="","",IF(AND($L25&gt;=20,$P25="あり",$N25&lt;&gt;"昼間部の学生"),"加入","加入対象外"))</f>
+        <f>IF($B25="","",IF($H25="役員","対象外（兼務役員なら要相談）",IF(AND($L25&gt;=20,$P25="あり",$N25&lt;&gt;"昼間部の学生"),"加入","加入対象外")))</f>
         <v/>
       </c>
       <c r="AA25" s="61" t="n"/>
@@ -4442,13 +4495,16 @@
       <c r="AQ25" s="17" t="n"/>
       <c r="AR25" s="17" t="n"/>
       <c r="AT25">
-        <f>IF($B25="","",IF($B25="",1,0)+IF($C25="",1,0)+IF($D25="",1,0)+IF($E25="",1,0)+IF($G25="",1,0)+IF($H25="",1,0)+IF($I25="",1,0)+IF($L25="",1,0)+IF($M25="",1,0)+IF($N25="",1,0)+IF($Q25="",1,0)+IF($S25="",1,0)+IF($AA25="",1,0)+IF($AC25="",1,0)+IF($AG25="",1,0)+IF($AH25="",1,0)+IF($AI25="",1,0)+IF($AL25="",1,0)+IF($AP25="",1,0)+IF($AQ25="",1,0)+IF(AND($I25="あり",$J25=""),1,0)+IF(AND($I25="あり",$K25=""),1,0)+IF(AND($AA25="",$AB25=""),1,0)+IF(AND($AC25="あり",$AD25=""),1,0)+IF(AND($AC25="あり",OR($AD25="",$AD25="後日提出"),$AE25=""),1,0))</f>
+        <f>IF($B25="","",IF($B25="",1,0)+IF($C25="",1,0)+IF($D25="",1,0)+IF($E25="",1,0)+IF($G25="",1,0)+IF($H25="",1,0)+IF($I25="",1,0)+IF($L25="",1,0)+IF($M25="",1,0)+IF($N25="",1,0)+IF($Q25="",1,0)+IF($S25="",1,0)+IF($AA25="",1,0)+IF($AC25="",1,0)+IF($AG25="",1,0)+IF($AH25="",1,0)+IF($AI25="",1,0)+IF($AL25="",1,0)+IF($AP25="",1,0)+IF($AQ25="",1,0)+IF(AND($I25="あり",$J25=""),1,0)+IF(AND($I25="あり",$K25=""),1,0)+IF(AND($AA25="",$AB25=""),1,0)+IF(AND($AC25="あり",$AD25=""),1,0)+IF(AND($AC25="あり",OR($AD25="",$AD25="後日提出"),$AE25=""),1,0)+IF($AV25="",1,0)+IF(AND($AL25="外国",$AM25=""),1,0)+IF(AND($AL25="外国",$AN25=""),1,0)+IF(AND($AL25="外国",$AO25=""),1,0))</f>
         <v/>
       </c>
       <c r="AU25">
         <f>IF($B25="","",IF(AND($AA25&lt;&gt;"",$AA25&lt;&gt;"後日提出",$AA25&lt;&gt;"別経路提出",LEN($AA25)&lt;&gt;12),1,0)+IF(AND($AB25&lt;&gt;"",$AB25&lt;&gt;"後日提出",LEN($AB25)&lt;&gt;10),1,0)+IF(AND($AD25&lt;&gt;"",$AD25&lt;&gt;"後日提出",LEN($AD25)&lt;&gt;11),1,0)+IF(AND($AG25&lt;&gt;"",LEN(SUBSTITUTE($AG25,"-",""))&lt;&gt;7),1,0))</f>
         <v/>
       </c>
+      <c r="AV25" s="17" t="n"/>
+      <c r="AW25" s="59" t="n"/>
+      <c r="AX25" s="17" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="23">
@@ -4472,7 +4528,7 @@
       <c r="M26" s="17" t="n"/>
       <c r="N26" s="17" t="n"/>
       <c r="O26" s="23">
-        <f>IF($B26="","",IF($I26="なし","あり",IF($I26="あり",IF(OR($K26="更新の可能性あり",AND($J26&lt;&gt;"",$G26&lt;&gt;"",$J26-$G26+1&gt;62)),"あり","なし"),"")))</f>
+        <f>IF($B26="","",IF($I26="なし","あり",IF($I26&lt;&gt;"あり","",IF($K26="更新の可能性あり","あり",IF(OR($J26="",$G26=""),"なし",IF(OR(NOT(ISNUMBER($G26)),NOT(ISNUMBER($J26)),$G26&gt;80000,$J26&gt;80000),"要確認（日付）",IF($J26&gt;IF(DAY(EDATE($G26,2))&lt;DAY($G26),EOMONTH($G26,2),EDATE($G26,2)-1),"あり","なし"))))))</f>
         <v/>
       </c>
       <c r="P26" s="23">
@@ -4490,7 +4546,7 @@
         <v/>
       </c>
       <c r="X26" s="23">
-        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B26="","",IF(AND($L26&gt;='⓪ 事業所設定'!$C$13*0.75,$M26&gt;='⓪ 事業所設定'!$C$14*0.75,$O26="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L26&gt;=20,$O26="あり",$N26&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S26+$T26)&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
+        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B26="","",IF(AND($L26&gt;='⓪ 事業所設定'!$C$13*0.75,$M26&gt;='⓪ 事業所設定'!$C$14*0.75,$O26="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L26&gt;=20,$O26="あり",$N26&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S26+$T26-N($AW26))&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
         <v/>
       </c>
       <c r="Y26" s="23">
@@ -4498,7 +4554,7 @@
         <v/>
       </c>
       <c r="Z26" s="23">
-        <f>IF($B26="","",IF(AND($L26&gt;=20,$P26="あり",$N26&lt;&gt;"昼間部の学生"),"加入","加入対象外"))</f>
+        <f>IF($B26="","",IF($H26="役員","対象外（兼務役員なら要相談）",IF(AND($L26&gt;=20,$P26="あり",$N26&lt;&gt;"昼間部の学生"),"加入","加入対象外")))</f>
         <v/>
       </c>
       <c r="AA26" s="61" t="n"/>
@@ -4520,13 +4576,16 @@
       <c r="AQ26" s="17" t="n"/>
       <c r="AR26" s="17" t="n"/>
       <c r="AT26">
-        <f>IF($B26="","",IF($B26="",1,0)+IF($C26="",1,0)+IF($D26="",1,0)+IF($E26="",1,0)+IF($G26="",1,0)+IF($H26="",1,0)+IF($I26="",1,0)+IF($L26="",1,0)+IF($M26="",1,0)+IF($N26="",1,0)+IF($Q26="",1,0)+IF($S26="",1,0)+IF($AA26="",1,0)+IF($AC26="",1,0)+IF($AG26="",1,0)+IF($AH26="",1,0)+IF($AI26="",1,0)+IF($AL26="",1,0)+IF($AP26="",1,0)+IF($AQ26="",1,0)+IF(AND($I26="あり",$J26=""),1,0)+IF(AND($I26="あり",$K26=""),1,0)+IF(AND($AA26="",$AB26=""),1,0)+IF(AND($AC26="あり",$AD26=""),1,0)+IF(AND($AC26="あり",OR($AD26="",$AD26="後日提出"),$AE26=""),1,0))</f>
+        <f>IF($B26="","",IF($B26="",1,0)+IF($C26="",1,0)+IF($D26="",1,0)+IF($E26="",1,0)+IF($G26="",1,0)+IF($H26="",1,0)+IF($I26="",1,0)+IF($L26="",1,0)+IF($M26="",1,0)+IF($N26="",1,0)+IF($Q26="",1,0)+IF($S26="",1,0)+IF($AA26="",1,0)+IF($AC26="",1,0)+IF($AG26="",1,0)+IF($AH26="",1,0)+IF($AI26="",1,0)+IF($AL26="",1,0)+IF($AP26="",1,0)+IF($AQ26="",1,0)+IF(AND($I26="あり",$J26=""),1,0)+IF(AND($I26="あり",$K26=""),1,0)+IF(AND($AA26="",$AB26=""),1,0)+IF(AND($AC26="あり",$AD26=""),1,0)+IF(AND($AC26="あり",OR($AD26="",$AD26="後日提出"),$AE26=""),1,0)+IF($AV26="",1,0)+IF(AND($AL26="外国",$AM26=""),1,0)+IF(AND($AL26="外国",$AN26=""),1,0)+IF(AND($AL26="外国",$AO26=""),1,0))</f>
         <v/>
       </c>
       <c r="AU26">
         <f>IF($B26="","",IF(AND($AA26&lt;&gt;"",$AA26&lt;&gt;"後日提出",$AA26&lt;&gt;"別経路提出",LEN($AA26)&lt;&gt;12),1,0)+IF(AND($AB26&lt;&gt;"",$AB26&lt;&gt;"後日提出",LEN($AB26)&lt;&gt;10),1,0)+IF(AND($AD26&lt;&gt;"",$AD26&lt;&gt;"後日提出",LEN($AD26)&lt;&gt;11),1,0)+IF(AND($AG26&lt;&gt;"",LEN(SUBSTITUTE($AG26,"-",""))&lt;&gt;7),1,0))</f>
         <v/>
       </c>
+      <c r="AV26" s="17" t="n"/>
+      <c r="AW26" s="59" t="n"/>
+      <c r="AX26" s="17" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="23">
@@ -4550,7 +4609,7 @@
       <c r="M27" s="17" t="n"/>
       <c r="N27" s="17" t="n"/>
       <c r="O27" s="23">
-        <f>IF($B27="","",IF($I27="なし","あり",IF($I27="あり",IF(OR($K27="更新の可能性あり",AND($J27&lt;&gt;"",$G27&lt;&gt;"",$J27-$G27+1&gt;62)),"あり","なし"),"")))</f>
+        <f>IF($B27="","",IF($I27="なし","あり",IF($I27&lt;&gt;"あり","",IF($K27="更新の可能性あり","あり",IF(OR($J27="",$G27=""),"なし",IF(OR(NOT(ISNUMBER($G27)),NOT(ISNUMBER($J27)),$G27&gt;80000,$J27&gt;80000),"要確認（日付）",IF($J27&gt;IF(DAY(EDATE($G27,2))&lt;DAY($G27),EOMONTH($G27,2),EDATE($G27,2)-1),"あり","なし"))))))</f>
         <v/>
       </c>
       <c r="P27" s="23">
@@ -4568,7 +4627,7 @@
         <v/>
       </c>
       <c r="X27" s="23">
-        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B27="","",IF(AND($L27&gt;='⓪ 事業所設定'!$C$13*0.75,$M27&gt;='⓪ 事業所設定'!$C$14*0.75,$O27="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L27&gt;=20,$O27="あり",$N27&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S27+$T27)&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
+        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B27="","",IF(AND($L27&gt;='⓪ 事業所設定'!$C$13*0.75,$M27&gt;='⓪ 事業所設定'!$C$14*0.75,$O27="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L27&gt;=20,$O27="あり",$N27&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S27+$T27-N($AW27))&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
         <v/>
       </c>
       <c r="Y27" s="23">
@@ -4576,7 +4635,7 @@
         <v/>
       </c>
       <c r="Z27" s="23">
-        <f>IF($B27="","",IF(AND($L27&gt;=20,$P27="あり",$N27&lt;&gt;"昼間部の学生"),"加入","加入対象外"))</f>
+        <f>IF($B27="","",IF($H27="役員","対象外（兼務役員なら要相談）",IF(AND($L27&gt;=20,$P27="あり",$N27&lt;&gt;"昼間部の学生"),"加入","加入対象外")))</f>
         <v/>
       </c>
       <c r="AA27" s="61" t="n"/>
@@ -4598,13 +4657,16 @@
       <c r="AQ27" s="17" t="n"/>
       <c r="AR27" s="17" t="n"/>
       <c r="AT27">
-        <f>IF($B27="","",IF($B27="",1,0)+IF($C27="",1,0)+IF($D27="",1,0)+IF($E27="",1,0)+IF($G27="",1,0)+IF($H27="",1,0)+IF($I27="",1,0)+IF($L27="",1,0)+IF($M27="",1,0)+IF($N27="",1,0)+IF($Q27="",1,0)+IF($S27="",1,0)+IF($AA27="",1,0)+IF($AC27="",1,0)+IF($AG27="",1,0)+IF($AH27="",1,0)+IF($AI27="",1,0)+IF($AL27="",1,0)+IF($AP27="",1,0)+IF($AQ27="",1,0)+IF(AND($I27="あり",$J27=""),1,0)+IF(AND($I27="あり",$K27=""),1,0)+IF(AND($AA27="",$AB27=""),1,0)+IF(AND($AC27="あり",$AD27=""),1,0)+IF(AND($AC27="あり",OR($AD27="",$AD27="後日提出"),$AE27=""),1,0))</f>
+        <f>IF($B27="","",IF($B27="",1,0)+IF($C27="",1,0)+IF($D27="",1,0)+IF($E27="",1,0)+IF($G27="",1,0)+IF($H27="",1,0)+IF($I27="",1,0)+IF($L27="",1,0)+IF($M27="",1,0)+IF($N27="",1,0)+IF($Q27="",1,0)+IF($S27="",1,0)+IF($AA27="",1,0)+IF($AC27="",1,0)+IF($AG27="",1,0)+IF($AH27="",1,0)+IF($AI27="",1,0)+IF($AL27="",1,0)+IF($AP27="",1,0)+IF($AQ27="",1,0)+IF(AND($I27="あり",$J27=""),1,0)+IF(AND($I27="あり",$K27=""),1,0)+IF(AND($AA27="",$AB27=""),1,0)+IF(AND($AC27="あり",$AD27=""),1,0)+IF(AND($AC27="あり",OR($AD27="",$AD27="後日提出"),$AE27=""),1,0)+IF($AV27="",1,0)+IF(AND($AL27="外国",$AM27=""),1,0)+IF(AND($AL27="外国",$AN27=""),1,0)+IF(AND($AL27="外国",$AO27=""),1,0))</f>
         <v/>
       </c>
       <c r="AU27">
         <f>IF($B27="","",IF(AND($AA27&lt;&gt;"",$AA27&lt;&gt;"後日提出",$AA27&lt;&gt;"別経路提出",LEN($AA27)&lt;&gt;12),1,0)+IF(AND($AB27&lt;&gt;"",$AB27&lt;&gt;"後日提出",LEN($AB27)&lt;&gt;10),1,0)+IF(AND($AD27&lt;&gt;"",$AD27&lt;&gt;"後日提出",LEN($AD27)&lt;&gt;11),1,0)+IF(AND($AG27&lt;&gt;"",LEN(SUBSTITUTE($AG27,"-",""))&lt;&gt;7),1,0))</f>
         <v/>
       </c>
+      <c r="AV27" s="17" t="n"/>
+      <c r="AW27" s="59" t="n"/>
+      <c r="AX27" s="17" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="23">
@@ -4628,7 +4690,7 @@
       <c r="M28" s="17" t="n"/>
       <c r="N28" s="17" t="n"/>
       <c r="O28" s="23">
-        <f>IF($B28="","",IF($I28="なし","あり",IF($I28="あり",IF(OR($K28="更新の可能性あり",AND($J28&lt;&gt;"",$G28&lt;&gt;"",$J28-$G28+1&gt;62)),"あり","なし"),"")))</f>
+        <f>IF($B28="","",IF($I28="なし","あり",IF($I28&lt;&gt;"あり","",IF($K28="更新の可能性あり","あり",IF(OR($J28="",$G28=""),"なし",IF(OR(NOT(ISNUMBER($G28)),NOT(ISNUMBER($J28)),$G28&gt;80000,$J28&gt;80000),"要確認（日付）",IF($J28&gt;IF(DAY(EDATE($G28,2))&lt;DAY($G28),EOMONTH($G28,2),EDATE($G28,2)-1),"あり","なし"))))))</f>
         <v/>
       </c>
       <c r="P28" s="23">
@@ -4646,7 +4708,7 @@
         <v/>
       </c>
       <c r="X28" s="23">
-        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B28="","",IF(AND($L28&gt;='⓪ 事業所設定'!$C$13*0.75,$M28&gt;='⓪ 事業所設定'!$C$14*0.75,$O28="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L28&gt;=20,$O28="あり",$N28&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S28+$T28)&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
+        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B28="","",IF(AND($L28&gt;='⓪ 事業所設定'!$C$13*0.75,$M28&gt;='⓪ 事業所設定'!$C$14*0.75,$O28="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L28&gt;=20,$O28="あり",$N28&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S28+$T28-N($AW28))&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
         <v/>
       </c>
       <c r="Y28" s="23">
@@ -4654,7 +4716,7 @@
         <v/>
       </c>
       <c r="Z28" s="23">
-        <f>IF($B28="","",IF(AND($L28&gt;=20,$P28="あり",$N28&lt;&gt;"昼間部の学生"),"加入","加入対象外"))</f>
+        <f>IF($B28="","",IF($H28="役員","対象外（兼務役員なら要相談）",IF(AND($L28&gt;=20,$P28="あり",$N28&lt;&gt;"昼間部の学生"),"加入","加入対象外")))</f>
         <v/>
       </c>
       <c r="AA28" s="61" t="n"/>
@@ -4676,13 +4738,16 @@
       <c r="AQ28" s="17" t="n"/>
       <c r="AR28" s="17" t="n"/>
       <c r="AT28">
-        <f>IF($B28="","",IF($B28="",1,0)+IF($C28="",1,0)+IF($D28="",1,0)+IF($E28="",1,0)+IF($G28="",1,0)+IF($H28="",1,0)+IF($I28="",1,0)+IF($L28="",1,0)+IF($M28="",1,0)+IF($N28="",1,0)+IF($Q28="",1,0)+IF($S28="",1,0)+IF($AA28="",1,0)+IF($AC28="",1,0)+IF($AG28="",1,0)+IF($AH28="",1,0)+IF($AI28="",1,0)+IF($AL28="",1,0)+IF($AP28="",1,0)+IF($AQ28="",1,0)+IF(AND($I28="あり",$J28=""),1,0)+IF(AND($I28="あり",$K28=""),1,0)+IF(AND($AA28="",$AB28=""),1,0)+IF(AND($AC28="あり",$AD28=""),1,0)+IF(AND($AC28="あり",OR($AD28="",$AD28="後日提出"),$AE28=""),1,0))</f>
+        <f>IF($B28="","",IF($B28="",1,0)+IF($C28="",1,0)+IF($D28="",1,0)+IF($E28="",1,0)+IF($G28="",1,0)+IF($H28="",1,0)+IF($I28="",1,0)+IF($L28="",1,0)+IF($M28="",1,0)+IF($N28="",1,0)+IF($Q28="",1,0)+IF($S28="",1,0)+IF($AA28="",1,0)+IF($AC28="",1,0)+IF($AG28="",1,0)+IF($AH28="",1,0)+IF($AI28="",1,0)+IF($AL28="",1,0)+IF($AP28="",1,0)+IF($AQ28="",1,0)+IF(AND($I28="あり",$J28=""),1,0)+IF(AND($I28="あり",$K28=""),1,0)+IF(AND($AA28="",$AB28=""),1,0)+IF(AND($AC28="あり",$AD28=""),1,0)+IF(AND($AC28="あり",OR($AD28="",$AD28="後日提出"),$AE28=""),1,0)+IF($AV28="",1,0)+IF(AND($AL28="外国",$AM28=""),1,0)+IF(AND($AL28="外国",$AN28=""),1,0)+IF(AND($AL28="外国",$AO28=""),1,0))</f>
         <v/>
       </c>
       <c r="AU28">
         <f>IF($B28="","",IF(AND($AA28&lt;&gt;"",$AA28&lt;&gt;"後日提出",$AA28&lt;&gt;"別経路提出",LEN($AA28)&lt;&gt;12),1,0)+IF(AND($AB28&lt;&gt;"",$AB28&lt;&gt;"後日提出",LEN($AB28)&lt;&gt;10),1,0)+IF(AND($AD28&lt;&gt;"",$AD28&lt;&gt;"後日提出",LEN($AD28)&lt;&gt;11),1,0)+IF(AND($AG28&lt;&gt;"",LEN(SUBSTITUTE($AG28,"-",""))&lt;&gt;7),1,0))</f>
         <v/>
       </c>
+      <c r="AV28" s="17" t="n"/>
+      <c r="AW28" s="59" t="n"/>
+      <c r="AX28" s="17" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="23">
@@ -4706,7 +4771,7 @@
       <c r="M29" s="17" t="n"/>
       <c r="N29" s="17" t="n"/>
       <c r="O29" s="23">
-        <f>IF($B29="","",IF($I29="なし","あり",IF($I29="あり",IF(OR($K29="更新の可能性あり",AND($J29&lt;&gt;"",$G29&lt;&gt;"",$J29-$G29+1&gt;62)),"あり","なし"),"")))</f>
+        <f>IF($B29="","",IF($I29="なし","あり",IF($I29&lt;&gt;"あり","",IF($K29="更新の可能性あり","あり",IF(OR($J29="",$G29=""),"なし",IF(OR(NOT(ISNUMBER($G29)),NOT(ISNUMBER($J29)),$G29&gt;80000,$J29&gt;80000),"要確認（日付）",IF($J29&gt;IF(DAY(EDATE($G29,2))&lt;DAY($G29),EOMONTH($G29,2),EDATE($G29,2)-1),"あり","なし"))))))</f>
         <v/>
       </c>
       <c r="P29" s="23">
@@ -4724,7 +4789,7 @@
         <v/>
       </c>
       <c r="X29" s="23">
-        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B29="","",IF(AND($L29&gt;='⓪ 事業所設定'!$C$13*0.75,$M29&gt;='⓪ 事業所設定'!$C$14*0.75,$O29="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L29&gt;=20,$O29="あり",$N29&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S29+$T29)&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
+        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B29="","",IF(AND($L29&gt;='⓪ 事業所設定'!$C$13*0.75,$M29&gt;='⓪ 事業所設定'!$C$14*0.75,$O29="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L29&gt;=20,$O29="あり",$N29&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S29+$T29-N($AW29))&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
         <v/>
       </c>
       <c r="Y29" s="23">
@@ -4732,7 +4797,7 @@
         <v/>
       </c>
       <c r="Z29" s="23">
-        <f>IF($B29="","",IF(AND($L29&gt;=20,$P29="あり",$N29&lt;&gt;"昼間部の学生"),"加入","加入対象外"))</f>
+        <f>IF($B29="","",IF($H29="役員","対象外（兼務役員なら要相談）",IF(AND($L29&gt;=20,$P29="あり",$N29&lt;&gt;"昼間部の学生"),"加入","加入対象外")))</f>
         <v/>
       </c>
       <c r="AA29" s="61" t="n"/>
@@ -4754,13 +4819,16 @@
       <c r="AQ29" s="17" t="n"/>
       <c r="AR29" s="17" t="n"/>
       <c r="AT29">
-        <f>IF($B29="","",IF($B29="",1,0)+IF($C29="",1,0)+IF($D29="",1,0)+IF($E29="",1,0)+IF($G29="",1,0)+IF($H29="",1,0)+IF($I29="",1,0)+IF($L29="",1,0)+IF($M29="",1,0)+IF($N29="",1,0)+IF($Q29="",1,0)+IF($S29="",1,0)+IF($AA29="",1,0)+IF($AC29="",1,0)+IF($AG29="",1,0)+IF($AH29="",1,0)+IF($AI29="",1,0)+IF($AL29="",1,0)+IF($AP29="",1,0)+IF($AQ29="",1,0)+IF(AND($I29="あり",$J29=""),1,0)+IF(AND($I29="あり",$K29=""),1,0)+IF(AND($AA29="",$AB29=""),1,0)+IF(AND($AC29="あり",$AD29=""),1,0)+IF(AND($AC29="あり",OR($AD29="",$AD29="後日提出"),$AE29=""),1,0))</f>
+        <f>IF($B29="","",IF($B29="",1,0)+IF($C29="",1,0)+IF($D29="",1,0)+IF($E29="",1,0)+IF($G29="",1,0)+IF($H29="",1,0)+IF($I29="",1,0)+IF($L29="",1,0)+IF($M29="",1,0)+IF($N29="",1,0)+IF($Q29="",1,0)+IF($S29="",1,0)+IF($AA29="",1,0)+IF($AC29="",1,0)+IF($AG29="",1,0)+IF($AH29="",1,0)+IF($AI29="",1,0)+IF($AL29="",1,0)+IF($AP29="",1,0)+IF($AQ29="",1,0)+IF(AND($I29="あり",$J29=""),1,0)+IF(AND($I29="あり",$K29=""),1,0)+IF(AND($AA29="",$AB29=""),1,0)+IF(AND($AC29="あり",$AD29=""),1,0)+IF(AND($AC29="あり",OR($AD29="",$AD29="後日提出"),$AE29=""),1,0)+IF($AV29="",1,0)+IF(AND($AL29="外国",$AM29=""),1,0)+IF(AND($AL29="外国",$AN29=""),1,0)+IF(AND($AL29="外国",$AO29=""),1,0))</f>
         <v/>
       </c>
       <c r="AU29">
         <f>IF($B29="","",IF(AND($AA29&lt;&gt;"",$AA29&lt;&gt;"後日提出",$AA29&lt;&gt;"別経路提出",LEN($AA29)&lt;&gt;12),1,0)+IF(AND($AB29&lt;&gt;"",$AB29&lt;&gt;"後日提出",LEN($AB29)&lt;&gt;10),1,0)+IF(AND($AD29&lt;&gt;"",$AD29&lt;&gt;"後日提出",LEN($AD29)&lt;&gt;11),1,0)+IF(AND($AG29&lt;&gt;"",LEN(SUBSTITUTE($AG29,"-",""))&lt;&gt;7),1,0))</f>
         <v/>
       </c>
+      <c r="AV29" s="17" t="n"/>
+      <c r="AW29" s="59" t="n"/>
+      <c r="AX29" s="17" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="23">
@@ -4784,7 +4852,7 @@
       <c r="M30" s="17" t="n"/>
       <c r="N30" s="17" t="n"/>
       <c r="O30" s="23">
-        <f>IF($B30="","",IF($I30="なし","あり",IF($I30="あり",IF(OR($K30="更新の可能性あり",AND($J30&lt;&gt;"",$G30&lt;&gt;"",$J30-$G30+1&gt;62)),"あり","なし"),"")))</f>
+        <f>IF($B30="","",IF($I30="なし","あり",IF($I30&lt;&gt;"あり","",IF($K30="更新の可能性あり","あり",IF(OR($J30="",$G30=""),"なし",IF(OR(NOT(ISNUMBER($G30)),NOT(ISNUMBER($J30)),$G30&gt;80000,$J30&gt;80000),"要確認（日付）",IF($J30&gt;IF(DAY(EDATE($G30,2))&lt;DAY($G30),EOMONTH($G30,2),EDATE($G30,2)-1),"あり","なし"))))))</f>
         <v/>
       </c>
       <c r="P30" s="23">
@@ -4802,7 +4870,7 @@
         <v/>
       </c>
       <c r="X30" s="23">
-        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B30="","",IF(AND($L30&gt;='⓪ 事業所設定'!$C$13*0.75,$M30&gt;='⓪ 事業所設定'!$C$14*0.75,$O30="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L30&gt;=20,$O30="あり",$N30&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S30+$T30)&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
+        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B30="","",IF(AND($L30&gt;='⓪ 事業所設定'!$C$13*0.75,$M30&gt;='⓪ 事業所設定'!$C$14*0.75,$O30="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L30&gt;=20,$O30="あり",$N30&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S30+$T30-N($AW30))&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
         <v/>
       </c>
       <c r="Y30" s="23">
@@ -4810,7 +4878,7 @@
         <v/>
       </c>
       <c r="Z30" s="23">
-        <f>IF($B30="","",IF(AND($L30&gt;=20,$P30="あり",$N30&lt;&gt;"昼間部の学生"),"加入","加入対象外"))</f>
+        <f>IF($B30="","",IF($H30="役員","対象外（兼務役員なら要相談）",IF(AND($L30&gt;=20,$P30="あり",$N30&lt;&gt;"昼間部の学生"),"加入","加入対象外")))</f>
         <v/>
       </c>
       <c r="AA30" s="61" t="n"/>
@@ -4832,13 +4900,16 @@
       <c r="AQ30" s="17" t="n"/>
       <c r="AR30" s="17" t="n"/>
       <c r="AT30">
-        <f>IF($B30="","",IF($B30="",1,0)+IF($C30="",1,0)+IF($D30="",1,0)+IF($E30="",1,0)+IF($G30="",1,0)+IF($H30="",1,0)+IF($I30="",1,0)+IF($L30="",1,0)+IF($M30="",1,0)+IF($N30="",1,0)+IF($Q30="",1,0)+IF($S30="",1,0)+IF($AA30="",1,0)+IF($AC30="",1,0)+IF($AG30="",1,0)+IF($AH30="",1,0)+IF($AI30="",1,0)+IF($AL30="",1,0)+IF($AP30="",1,0)+IF($AQ30="",1,0)+IF(AND($I30="あり",$J30=""),1,0)+IF(AND($I30="あり",$K30=""),1,0)+IF(AND($AA30="",$AB30=""),1,0)+IF(AND($AC30="あり",$AD30=""),1,0)+IF(AND($AC30="あり",OR($AD30="",$AD30="後日提出"),$AE30=""),1,0))</f>
+        <f>IF($B30="","",IF($B30="",1,0)+IF($C30="",1,0)+IF($D30="",1,0)+IF($E30="",1,0)+IF($G30="",1,0)+IF($H30="",1,0)+IF($I30="",1,0)+IF($L30="",1,0)+IF($M30="",1,0)+IF($N30="",1,0)+IF($Q30="",1,0)+IF($S30="",1,0)+IF($AA30="",1,0)+IF($AC30="",1,0)+IF($AG30="",1,0)+IF($AH30="",1,0)+IF($AI30="",1,0)+IF($AL30="",1,0)+IF($AP30="",1,0)+IF($AQ30="",1,0)+IF(AND($I30="あり",$J30=""),1,0)+IF(AND($I30="あり",$K30=""),1,0)+IF(AND($AA30="",$AB30=""),1,0)+IF(AND($AC30="あり",$AD30=""),1,0)+IF(AND($AC30="あり",OR($AD30="",$AD30="後日提出"),$AE30=""),1,0)+IF($AV30="",1,0)+IF(AND($AL30="外国",$AM30=""),1,0)+IF(AND($AL30="外国",$AN30=""),1,0)+IF(AND($AL30="外国",$AO30=""),1,0))</f>
         <v/>
       </c>
       <c r="AU30">
         <f>IF($B30="","",IF(AND($AA30&lt;&gt;"",$AA30&lt;&gt;"後日提出",$AA30&lt;&gt;"別経路提出",LEN($AA30)&lt;&gt;12),1,0)+IF(AND($AB30&lt;&gt;"",$AB30&lt;&gt;"後日提出",LEN($AB30)&lt;&gt;10),1,0)+IF(AND($AD30&lt;&gt;"",$AD30&lt;&gt;"後日提出",LEN($AD30)&lt;&gt;11),1,0)+IF(AND($AG30&lt;&gt;"",LEN(SUBSTITUTE($AG30,"-",""))&lt;&gt;7),1,0))</f>
         <v/>
       </c>
+      <c r="AV30" s="17" t="n"/>
+      <c r="AW30" s="59" t="n"/>
+      <c r="AX30" s="17" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="23">
@@ -4862,7 +4933,7 @@
       <c r="M31" s="17" t="n"/>
       <c r="N31" s="17" t="n"/>
       <c r="O31" s="23">
-        <f>IF($B31="","",IF($I31="なし","あり",IF($I31="あり",IF(OR($K31="更新の可能性あり",AND($J31&lt;&gt;"",$G31&lt;&gt;"",$J31-$G31+1&gt;62)),"あり","なし"),"")))</f>
+        <f>IF($B31="","",IF($I31="なし","あり",IF($I31&lt;&gt;"あり","",IF($K31="更新の可能性あり","あり",IF(OR($J31="",$G31=""),"なし",IF(OR(NOT(ISNUMBER($G31)),NOT(ISNUMBER($J31)),$G31&gt;80000,$J31&gt;80000),"要確認（日付）",IF($J31&gt;IF(DAY(EDATE($G31,2))&lt;DAY($G31),EOMONTH($G31,2),EDATE($G31,2)-1),"あり","なし"))))))</f>
         <v/>
       </c>
       <c r="P31" s="23">
@@ -4880,7 +4951,7 @@
         <v/>
       </c>
       <c r="X31" s="23">
-        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B31="","",IF(AND($L31&gt;='⓪ 事業所設定'!$C$13*0.75,$M31&gt;='⓪ 事業所設定'!$C$14*0.75,$O31="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L31&gt;=20,$O31="あり",$N31&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S31+$T31)&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
+        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B31="","",IF(AND($L31&gt;='⓪ 事業所設定'!$C$13*0.75,$M31&gt;='⓪ 事業所設定'!$C$14*0.75,$O31="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L31&gt;=20,$O31="あり",$N31&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S31+$T31-N($AW31))&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
         <v/>
       </c>
       <c r="Y31" s="23">
@@ -4888,7 +4959,7 @@
         <v/>
       </c>
       <c r="Z31" s="23">
-        <f>IF($B31="","",IF(AND($L31&gt;=20,$P31="あり",$N31&lt;&gt;"昼間部の学生"),"加入","加入対象外"))</f>
+        <f>IF($B31="","",IF($H31="役員","対象外（兼務役員なら要相談）",IF(AND($L31&gt;=20,$P31="あり",$N31&lt;&gt;"昼間部の学生"),"加入","加入対象外")))</f>
         <v/>
       </c>
       <c r="AA31" s="61" t="n"/>
@@ -4910,13 +4981,16 @@
       <c r="AQ31" s="17" t="n"/>
       <c r="AR31" s="17" t="n"/>
       <c r="AT31">
-        <f>IF($B31="","",IF($B31="",1,0)+IF($C31="",1,0)+IF($D31="",1,0)+IF($E31="",1,0)+IF($G31="",1,0)+IF($H31="",1,0)+IF($I31="",1,0)+IF($L31="",1,0)+IF($M31="",1,0)+IF($N31="",1,0)+IF($Q31="",1,0)+IF($S31="",1,0)+IF($AA31="",1,0)+IF($AC31="",1,0)+IF($AG31="",1,0)+IF($AH31="",1,0)+IF($AI31="",1,0)+IF($AL31="",1,0)+IF($AP31="",1,0)+IF($AQ31="",1,0)+IF(AND($I31="あり",$J31=""),1,0)+IF(AND($I31="あり",$K31=""),1,0)+IF(AND($AA31="",$AB31=""),1,0)+IF(AND($AC31="あり",$AD31=""),1,0)+IF(AND($AC31="あり",OR($AD31="",$AD31="後日提出"),$AE31=""),1,0))</f>
+        <f>IF($B31="","",IF($B31="",1,0)+IF($C31="",1,0)+IF($D31="",1,0)+IF($E31="",1,0)+IF($G31="",1,0)+IF($H31="",1,0)+IF($I31="",1,0)+IF($L31="",1,0)+IF($M31="",1,0)+IF($N31="",1,0)+IF($Q31="",1,0)+IF($S31="",1,0)+IF($AA31="",1,0)+IF($AC31="",1,0)+IF($AG31="",1,0)+IF($AH31="",1,0)+IF($AI31="",1,0)+IF($AL31="",1,0)+IF($AP31="",1,0)+IF($AQ31="",1,0)+IF(AND($I31="あり",$J31=""),1,0)+IF(AND($I31="あり",$K31=""),1,0)+IF(AND($AA31="",$AB31=""),1,0)+IF(AND($AC31="あり",$AD31=""),1,0)+IF(AND($AC31="あり",OR($AD31="",$AD31="後日提出"),$AE31=""),1,0)+IF($AV31="",1,0)+IF(AND($AL31="外国",$AM31=""),1,0)+IF(AND($AL31="外国",$AN31=""),1,0)+IF(AND($AL31="外国",$AO31=""),1,0))</f>
         <v/>
       </c>
       <c r="AU31">
         <f>IF($B31="","",IF(AND($AA31&lt;&gt;"",$AA31&lt;&gt;"後日提出",$AA31&lt;&gt;"別経路提出",LEN($AA31)&lt;&gt;12),1,0)+IF(AND($AB31&lt;&gt;"",$AB31&lt;&gt;"後日提出",LEN($AB31)&lt;&gt;10),1,0)+IF(AND($AD31&lt;&gt;"",$AD31&lt;&gt;"後日提出",LEN($AD31)&lt;&gt;11),1,0)+IF(AND($AG31&lt;&gt;"",LEN(SUBSTITUTE($AG31,"-",""))&lt;&gt;7),1,0))</f>
         <v/>
       </c>
+      <c r="AV31" s="17" t="n"/>
+      <c r="AW31" s="59" t="n"/>
+      <c r="AX31" s="17" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="23">
@@ -4940,7 +5014,7 @@
       <c r="M32" s="17" t="n"/>
       <c r="N32" s="17" t="n"/>
       <c r="O32" s="23">
-        <f>IF($B32="","",IF($I32="なし","あり",IF($I32="あり",IF(OR($K32="更新の可能性あり",AND($J32&lt;&gt;"",$G32&lt;&gt;"",$J32-$G32+1&gt;62)),"あり","なし"),"")))</f>
+        <f>IF($B32="","",IF($I32="なし","あり",IF($I32&lt;&gt;"あり","",IF($K32="更新の可能性あり","あり",IF(OR($J32="",$G32=""),"なし",IF(OR(NOT(ISNUMBER($G32)),NOT(ISNUMBER($J32)),$G32&gt;80000,$J32&gt;80000),"要確認（日付）",IF($J32&gt;IF(DAY(EDATE($G32,2))&lt;DAY($G32),EOMONTH($G32,2),EDATE($G32,2)-1),"あり","なし"))))))</f>
         <v/>
       </c>
       <c r="P32" s="23">
@@ -4958,7 +5032,7 @@
         <v/>
       </c>
       <c r="X32" s="23">
-        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B32="","",IF(AND($L32&gt;='⓪ 事業所設定'!$C$13*0.75,$M32&gt;='⓪ 事業所設定'!$C$14*0.75,$O32="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L32&gt;=20,$O32="あり",$N32&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S32+$T32)&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
+        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B32="","",IF(AND($L32&gt;='⓪ 事業所設定'!$C$13*0.75,$M32&gt;='⓪ 事業所設定'!$C$14*0.75,$O32="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L32&gt;=20,$O32="あり",$N32&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S32+$T32-N($AW32))&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
         <v/>
       </c>
       <c r="Y32" s="23">
@@ -4966,7 +5040,7 @@
         <v/>
       </c>
       <c r="Z32" s="23">
-        <f>IF($B32="","",IF(AND($L32&gt;=20,$P32="あり",$N32&lt;&gt;"昼間部の学生"),"加入","加入対象外"))</f>
+        <f>IF($B32="","",IF($H32="役員","対象外（兼務役員なら要相談）",IF(AND($L32&gt;=20,$P32="あり",$N32&lt;&gt;"昼間部の学生"),"加入","加入対象外")))</f>
         <v/>
       </c>
       <c r="AA32" s="61" t="n"/>
@@ -4988,13 +5062,16 @@
       <c r="AQ32" s="17" t="n"/>
       <c r="AR32" s="17" t="n"/>
       <c r="AT32">
-        <f>IF($B32="","",IF($B32="",1,0)+IF($C32="",1,0)+IF($D32="",1,0)+IF($E32="",1,0)+IF($G32="",1,0)+IF($H32="",1,0)+IF($I32="",1,0)+IF($L32="",1,0)+IF($M32="",1,0)+IF($N32="",1,0)+IF($Q32="",1,0)+IF($S32="",1,0)+IF($AA32="",1,0)+IF($AC32="",1,0)+IF($AG32="",1,0)+IF($AH32="",1,0)+IF($AI32="",1,0)+IF($AL32="",1,0)+IF($AP32="",1,0)+IF($AQ32="",1,0)+IF(AND($I32="あり",$J32=""),1,0)+IF(AND($I32="あり",$K32=""),1,0)+IF(AND($AA32="",$AB32=""),1,0)+IF(AND($AC32="あり",$AD32=""),1,0)+IF(AND($AC32="あり",OR($AD32="",$AD32="後日提出"),$AE32=""),1,0))</f>
+        <f>IF($B32="","",IF($B32="",1,0)+IF($C32="",1,0)+IF($D32="",1,0)+IF($E32="",1,0)+IF($G32="",1,0)+IF($H32="",1,0)+IF($I32="",1,0)+IF($L32="",1,0)+IF($M32="",1,0)+IF($N32="",1,0)+IF($Q32="",1,0)+IF($S32="",1,0)+IF($AA32="",1,0)+IF($AC32="",1,0)+IF($AG32="",1,0)+IF($AH32="",1,0)+IF($AI32="",1,0)+IF($AL32="",1,0)+IF($AP32="",1,0)+IF($AQ32="",1,0)+IF(AND($I32="あり",$J32=""),1,0)+IF(AND($I32="あり",$K32=""),1,0)+IF(AND($AA32="",$AB32=""),1,0)+IF(AND($AC32="あり",$AD32=""),1,0)+IF(AND($AC32="あり",OR($AD32="",$AD32="後日提出"),$AE32=""),1,0)+IF($AV32="",1,0)+IF(AND($AL32="外国",$AM32=""),1,0)+IF(AND($AL32="外国",$AN32=""),1,0)+IF(AND($AL32="外国",$AO32=""),1,0))</f>
         <v/>
       </c>
       <c r="AU32">
         <f>IF($B32="","",IF(AND($AA32&lt;&gt;"",$AA32&lt;&gt;"後日提出",$AA32&lt;&gt;"別経路提出",LEN($AA32)&lt;&gt;12),1,0)+IF(AND($AB32&lt;&gt;"",$AB32&lt;&gt;"後日提出",LEN($AB32)&lt;&gt;10),1,0)+IF(AND($AD32&lt;&gt;"",$AD32&lt;&gt;"後日提出",LEN($AD32)&lt;&gt;11),1,0)+IF(AND($AG32&lt;&gt;"",LEN(SUBSTITUTE($AG32,"-",""))&lt;&gt;7),1,0))</f>
         <v/>
       </c>
+      <c r="AV32" s="17" t="n"/>
+      <c r="AW32" s="59" t="n"/>
+      <c r="AX32" s="17" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="23">
@@ -5018,7 +5095,7 @@
       <c r="M33" s="17" t="n"/>
       <c r="N33" s="17" t="n"/>
       <c r="O33" s="23">
-        <f>IF($B33="","",IF($I33="なし","あり",IF($I33="あり",IF(OR($K33="更新の可能性あり",AND($J33&lt;&gt;"",$G33&lt;&gt;"",$J33-$G33+1&gt;62)),"あり","なし"),"")))</f>
+        <f>IF($B33="","",IF($I33="なし","あり",IF($I33&lt;&gt;"あり","",IF($K33="更新の可能性あり","あり",IF(OR($J33="",$G33=""),"なし",IF(OR(NOT(ISNUMBER($G33)),NOT(ISNUMBER($J33)),$G33&gt;80000,$J33&gt;80000),"要確認（日付）",IF($J33&gt;IF(DAY(EDATE($G33,2))&lt;DAY($G33),EOMONTH($G33,2),EDATE($G33,2)-1),"あり","なし"))))))</f>
         <v/>
       </c>
       <c r="P33" s="23">
@@ -5036,7 +5113,7 @@
         <v/>
       </c>
       <c r="X33" s="23">
-        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B33="","",IF(AND($L33&gt;='⓪ 事業所設定'!$C$13*0.75,$M33&gt;='⓪ 事業所設定'!$C$14*0.75,$O33="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L33&gt;=20,$O33="あり",$N33&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S33+$T33)&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
+        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B33="","",IF(AND($L33&gt;='⓪ 事業所設定'!$C$13*0.75,$M33&gt;='⓪ 事業所設定'!$C$14*0.75,$O33="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L33&gt;=20,$O33="あり",$N33&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S33+$T33-N($AW33))&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
         <v/>
       </c>
       <c r="Y33" s="23">
@@ -5044,7 +5121,7 @@
         <v/>
       </c>
       <c r="Z33" s="23">
-        <f>IF($B33="","",IF(AND($L33&gt;=20,$P33="あり",$N33&lt;&gt;"昼間部の学生"),"加入","加入対象外"))</f>
+        <f>IF($B33="","",IF($H33="役員","対象外（兼務役員なら要相談）",IF(AND($L33&gt;=20,$P33="あり",$N33&lt;&gt;"昼間部の学生"),"加入","加入対象外")))</f>
         <v/>
       </c>
       <c r="AA33" s="61" t="n"/>
@@ -5066,13 +5143,16 @@
       <c r="AQ33" s="17" t="n"/>
       <c r="AR33" s="17" t="n"/>
       <c r="AT33">
-        <f>IF($B33="","",IF($B33="",1,0)+IF($C33="",1,0)+IF($D33="",1,0)+IF($E33="",1,0)+IF($G33="",1,0)+IF($H33="",1,0)+IF($I33="",1,0)+IF($L33="",1,0)+IF($M33="",1,0)+IF($N33="",1,0)+IF($Q33="",1,0)+IF($S33="",1,0)+IF($AA33="",1,0)+IF($AC33="",1,0)+IF($AG33="",1,0)+IF($AH33="",1,0)+IF($AI33="",1,0)+IF($AL33="",1,0)+IF($AP33="",1,0)+IF($AQ33="",1,0)+IF(AND($I33="あり",$J33=""),1,0)+IF(AND($I33="あり",$K33=""),1,0)+IF(AND($AA33="",$AB33=""),1,0)+IF(AND($AC33="あり",$AD33=""),1,0)+IF(AND($AC33="あり",OR($AD33="",$AD33="後日提出"),$AE33=""),1,0))</f>
+        <f>IF($B33="","",IF($B33="",1,0)+IF($C33="",1,0)+IF($D33="",1,0)+IF($E33="",1,0)+IF($G33="",1,0)+IF($H33="",1,0)+IF($I33="",1,0)+IF($L33="",1,0)+IF($M33="",1,0)+IF($N33="",1,0)+IF($Q33="",1,0)+IF($S33="",1,0)+IF($AA33="",1,0)+IF($AC33="",1,0)+IF($AG33="",1,0)+IF($AH33="",1,0)+IF($AI33="",1,0)+IF($AL33="",1,0)+IF($AP33="",1,0)+IF($AQ33="",1,0)+IF(AND($I33="あり",$J33=""),1,0)+IF(AND($I33="あり",$K33=""),1,0)+IF(AND($AA33="",$AB33=""),1,0)+IF(AND($AC33="あり",$AD33=""),1,0)+IF(AND($AC33="あり",OR($AD33="",$AD33="後日提出"),$AE33=""),1,0)+IF($AV33="",1,0)+IF(AND($AL33="外国",$AM33=""),1,0)+IF(AND($AL33="外国",$AN33=""),1,0)+IF(AND($AL33="外国",$AO33=""),1,0))</f>
         <v/>
       </c>
       <c r="AU33">
         <f>IF($B33="","",IF(AND($AA33&lt;&gt;"",$AA33&lt;&gt;"後日提出",$AA33&lt;&gt;"別経路提出",LEN($AA33)&lt;&gt;12),1,0)+IF(AND($AB33&lt;&gt;"",$AB33&lt;&gt;"後日提出",LEN($AB33)&lt;&gt;10),1,0)+IF(AND($AD33&lt;&gt;"",$AD33&lt;&gt;"後日提出",LEN($AD33)&lt;&gt;11),1,0)+IF(AND($AG33&lt;&gt;"",LEN(SUBSTITUTE($AG33,"-",""))&lt;&gt;7),1,0))</f>
         <v/>
       </c>
+      <c r="AV33" s="17" t="n"/>
+      <c r="AW33" s="59" t="n"/>
+      <c r="AX33" s="17" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="23">
@@ -5096,7 +5176,7 @@
       <c r="M34" s="17" t="n"/>
       <c r="N34" s="17" t="n"/>
       <c r="O34" s="23">
-        <f>IF($B34="","",IF($I34="なし","あり",IF($I34="あり",IF(OR($K34="更新の可能性あり",AND($J34&lt;&gt;"",$G34&lt;&gt;"",$J34-$G34+1&gt;62)),"あり","なし"),"")))</f>
+        <f>IF($B34="","",IF($I34="なし","あり",IF($I34&lt;&gt;"あり","",IF($K34="更新の可能性あり","あり",IF(OR($J34="",$G34=""),"なし",IF(OR(NOT(ISNUMBER($G34)),NOT(ISNUMBER($J34)),$G34&gt;80000,$J34&gt;80000),"要確認（日付）",IF($J34&gt;IF(DAY(EDATE($G34,2))&lt;DAY($G34),EOMONTH($G34,2),EDATE($G34,2)-1),"あり","なし"))))))</f>
         <v/>
       </c>
       <c r="P34" s="23">
@@ -5114,7 +5194,7 @@
         <v/>
       </c>
       <c r="X34" s="23">
-        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B34="","",IF(AND($L34&gt;='⓪ 事業所設定'!$C$13*0.75,$M34&gt;='⓪ 事業所設定'!$C$14*0.75,$O34="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L34&gt;=20,$O34="あり",$N34&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S34+$T34)&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
+        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B34="","",IF(AND($L34&gt;='⓪ 事業所設定'!$C$13*0.75,$M34&gt;='⓪ 事業所設定'!$C$14*0.75,$O34="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L34&gt;=20,$O34="あり",$N34&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S34+$T34-N($AW34))&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
         <v/>
       </c>
       <c r="Y34" s="23">
@@ -5122,7 +5202,7 @@
         <v/>
       </c>
       <c r="Z34" s="23">
-        <f>IF($B34="","",IF(AND($L34&gt;=20,$P34="あり",$N34&lt;&gt;"昼間部の学生"),"加入","加入対象外"))</f>
+        <f>IF($B34="","",IF($H34="役員","対象外（兼務役員なら要相談）",IF(AND($L34&gt;=20,$P34="あり",$N34&lt;&gt;"昼間部の学生"),"加入","加入対象外")))</f>
         <v/>
       </c>
       <c r="AA34" s="61" t="n"/>
@@ -5144,13 +5224,16 @@
       <c r="AQ34" s="17" t="n"/>
       <c r="AR34" s="17" t="n"/>
       <c r="AT34">
-        <f>IF($B34="","",IF($B34="",1,0)+IF($C34="",1,0)+IF($D34="",1,0)+IF($E34="",1,0)+IF($G34="",1,0)+IF($H34="",1,0)+IF($I34="",1,0)+IF($L34="",1,0)+IF($M34="",1,0)+IF($N34="",1,0)+IF($Q34="",1,0)+IF($S34="",1,0)+IF($AA34="",1,0)+IF($AC34="",1,0)+IF($AG34="",1,0)+IF($AH34="",1,0)+IF($AI34="",1,0)+IF($AL34="",1,0)+IF($AP34="",1,0)+IF($AQ34="",1,0)+IF(AND($I34="あり",$J34=""),1,0)+IF(AND($I34="あり",$K34=""),1,0)+IF(AND($AA34="",$AB34=""),1,0)+IF(AND($AC34="あり",$AD34=""),1,0)+IF(AND($AC34="あり",OR($AD34="",$AD34="後日提出"),$AE34=""),1,0))</f>
+        <f>IF($B34="","",IF($B34="",1,0)+IF($C34="",1,0)+IF($D34="",1,0)+IF($E34="",1,0)+IF($G34="",1,0)+IF($H34="",1,0)+IF($I34="",1,0)+IF($L34="",1,0)+IF($M34="",1,0)+IF($N34="",1,0)+IF($Q34="",1,0)+IF($S34="",1,0)+IF($AA34="",1,0)+IF($AC34="",1,0)+IF($AG34="",1,0)+IF($AH34="",1,0)+IF($AI34="",1,0)+IF($AL34="",1,0)+IF($AP34="",1,0)+IF($AQ34="",1,0)+IF(AND($I34="あり",$J34=""),1,0)+IF(AND($I34="あり",$K34=""),1,0)+IF(AND($AA34="",$AB34=""),1,0)+IF(AND($AC34="あり",$AD34=""),1,0)+IF(AND($AC34="あり",OR($AD34="",$AD34="後日提出"),$AE34=""),1,0)+IF($AV34="",1,0)+IF(AND($AL34="外国",$AM34=""),1,0)+IF(AND($AL34="外国",$AN34=""),1,0)+IF(AND($AL34="外国",$AO34=""),1,0))</f>
         <v/>
       </c>
       <c r="AU34">
         <f>IF($B34="","",IF(AND($AA34&lt;&gt;"",$AA34&lt;&gt;"後日提出",$AA34&lt;&gt;"別経路提出",LEN($AA34)&lt;&gt;12),1,0)+IF(AND($AB34&lt;&gt;"",$AB34&lt;&gt;"後日提出",LEN($AB34)&lt;&gt;10),1,0)+IF(AND($AD34&lt;&gt;"",$AD34&lt;&gt;"後日提出",LEN($AD34)&lt;&gt;11),1,0)+IF(AND($AG34&lt;&gt;"",LEN(SUBSTITUTE($AG34,"-",""))&lt;&gt;7),1,0))</f>
         <v/>
       </c>
+      <c r="AV34" s="17" t="n"/>
+      <c r="AW34" s="59" t="n"/>
+      <c r="AX34" s="17" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="23">
@@ -5174,7 +5257,7 @@
       <c r="M35" s="17" t="n"/>
       <c r="N35" s="17" t="n"/>
       <c r="O35" s="23">
-        <f>IF($B35="","",IF($I35="なし","あり",IF($I35="あり",IF(OR($K35="更新の可能性あり",AND($J35&lt;&gt;"",$G35&lt;&gt;"",$J35-$G35+1&gt;62)),"あり","なし"),"")))</f>
+        <f>IF($B35="","",IF($I35="なし","あり",IF($I35&lt;&gt;"あり","",IF($K35="更新の可能性あり","あり",IF(OR($J35="",$G35=""),"なし",IF(OR(NOT(ISNUMBER($G35)),NOT(ISNUMBER($J35)),$G35&gt;80000,$J35&gt;80000),"要確認（日付）",IF($J35&gt;IF(DAY(EDATE($G35,2))&lt;DAY($G35),EOMONTH($G35,2),EDATE($G35,2)-1),"あり","なし"))))))</f>
         <v/>
       </c>
       <c r="P35" s="23">
@@ -5192,7 +5275,7 @@
         <v/>
       </c>
       <c r="X35" s="23">
-        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B35="","",IF(AND($L35&gt;='⓪ 事業所設定'!$C$13*0.75,$M35&gt;='⓪ 事業所設定'!$C$14*0.75,$O35="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L35&gt;=20,$O35="あり",$N35&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S35+$T35)&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
+        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B35="","",IF(AND($L35&gt;='⓪ 事業所設定'!$C$13*0.75,$M35&gt;='⓪ 事業所設定'!$C$14*0.75,$O35="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L35&gt;=20,$O35="あり",$N35&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S35+$T35-N($AW35))&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
         <v/>
       </c>
       <c r="Y35" s="23">
@@ -5200,7 +5283,7 @@
         <v/>
       </c>
       <c r="Z35" s="23">
-        <f>IF($B35="","",IF(AND($L35&gt;=20,$P35="あり",$N35&lt;&gt;"昼間部の学生"),"加入","加入対象外"))</f>
+        <f>IF($B35="","",IF($H35="役員","対象外（兼務役員なら要相談）",IF(AND($L35&gt;=20,$P35="あり",$N35&lt;&gt;"昼間部の学生"),"加入","加入対象外")))</f>
         <v/>
       </c>
       <c r="AA35" s="61" t="n"/>
@@ -5222,13 +5305,16 @@
       <c r="AQ35" s="17" t="n"/>
       <c r="AR35" s="17" t="n"/>
       <c r="AT35">
-        <f>IF($B35="","",IF($B35="",1,0)+IF($C35="",1,0)+IF($D35="",1,0)+IF($E35="",1,0)+IF($G35="",1,0)+IF($H35="",1,0)+IF($I35="",1,0)+IF($L35="",1,0)+IF($M35="",1,0)+IF($N35="",1,0)+IF($Q35="",1,0)+IF($S35="",1,0)+IF($AA35="",1,0)+IF($AC35="",1,0)+IF($AG35="",1,0)+IF($AH35="",1,0)+IF($AI35="",1,0)+IF($AL35="",1,0)+IF($AP35="",1,0)+IF($AQ35="",1,0)+IF(AND($I35="あり",$J35=""),1,0)+IF(AND($I35="あり",$K35=""),1,0)+IF(AND($AA35="",$AB35=""),1,0)+IF(AND($AC35="あり",$AD35=""),1,0)+IF(AND($AC35="あり",OR($AD35="",$AD35="後日提出"),$AE35=""),1,0))</f>
+        <f>IF($B35="","",IF($B35="",1,0)+IF($C35="",1,0)+IF($D35="",1,0)+IF($E35="",1,0)+IF($G35="",1,0)+IF($H35="",1,0)+IF($I35="",1,0)+IF($L35="",1,0)+IF($M35="",1,0)+IF($N35="",1,0)+IF($Q35="",1,0)+IF($S35="",1,0)+IF($AA35="",1,0)+IF($AC35="",1,0)+IF($AG35="",1,0)+IF($AH35="",1,0)+IF($AI35="",1,0)+IF($AL35="",1,0)+IF($AP35="",1,0)+IF($AQ35="",1,0)+IF(AND($I35="あり",$J35=""),1,0)+IF(AND($I35="あり",$K35=""),1,0)+IF(AND($AA35="",$AB35=""),1,0)+IF(AND($AC35="あり",$AD35=""),1,0)+IF(AND($AC35="あり",OR($AD35="",$AD35="後日提出"),$AE35=""),1,0)+IF($AV35="",1,0)+IF(AND($AL35="外国",$AM35=""),1,0)+IF(AND($AL35="外国",$AN35=""),1,0)+IF(AND($AL35="外国",$AO35=""),1,0))</f>
         <v/>
       </c>
       <c r="AU35">
         <f>IF($B35="","",IF(AND($AA35&lt;&gt;"",$AA35&lt;&gt;"後日提出",$AA35&lt;&gt;"別経路提出",LEN($AA35)&lt;&gt;12),1,0)+IF(AND($AB35&lt;&gt;"",$AB35&lt;&gt;"後日提出",LEN($AB35)&lt;&gt;10),1,0)+IF(AND($AD35&lt;&gt;"",$AD35&lt;&gt;"後日提出",LEN($AD35)&lt;&gt;11),1,0)+IF(AND($AG35&lt;&gt;"",LEN(SUBSTITUTE($AG35,"-",""))&lt;&gt;7),1,0))</f>
         <v/>
       </c>
+      <c r="AV35" s="17" t="n"/>
+      <c r="AW35" s="59" t="n"/>
+      <c r="AX35" s="17" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="23">
@@ -5252,7 +5338,7 @@
       <c r="M36" s="17" t="n"/>
       <c r="N36" s="17" t="n"/>
       <c r="O36" s="23">
-        <f>IF($B36="","",IF($I36="なし","あり",IF($I36="あり",IF(OR($K36="更新の可能性あり",AND($J36&lt;&gt;"",$G36&lt;&gt;"",$J36-$G36+1&gt;62)),"あり","なし"),"")))</f>
+        <f>IF($B36="","",IF($I36="なし","あり",IF($I36&lt;&gt;"あり","",IF($K36="更新の可能性あり","あり",IF(OR($J36="",$G36=""),"なし",IF(OR(NOT(ISNUMBER($G36)),NOT(ISNUMBER($J36)),$G36&gt;80000,$J36&gt;80000),"要確認（日付）",IF($J36&gt;IF(DAY(EDATE($G36,2))&lt;DAY($G36),EOMONTH($G36,2),EDATE($G36,2)-1),"あり","なし"))))))</f>
         <v/>
       </c>
       <c r="P36" s="23">
@@ -5270,7 +5356,7 @@
         <v/>
       </c>
       <c r="X36" s="23">
-        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B36="","",IF(AND($L36&gt;='⓪ 事業所設定'!$C$13*0.75,$M36&gt;='⓪ 事業所設定'!$C$14*0.75,$O36="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L36&gt;=20,$O36="あり",$N36&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S36+$T36)&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
+        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B36="","",IF(AND($L36&gt;='⓪ 事業所設定'!$C$13*0.75,$M36&gt;='⓪ 事業所設定'!$C$14*0.75,$O36="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L36&gt;=20,$O36="あり",$N36&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S36+$T36-N($AW36))&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
         <v/>
       </c>
       <c r="Y36" s="23">
@@ -5278,7 +5364,7 @@
         <v/>
       </c>
       <c r="Z36" s="23">
-        <f>IF($B36="","",IF(AND($L36&gt;=20,$P36="あり",$N36&lt;&gt;"昼間部の学生"),"加入","加入対象外"))</f>
+        <f>IF($B36="","",IF($H36="役員","対象外（兼務役員なら要相談）",IF(AND($L36&gt;=20,$P36="あり",$N36&lt;&gt;"昼間部の学生"),"加入","加入対象外")))</f>
         <v/>
       </c>
       <c r="AA36" s="61" t="n"/>
@@ -5300,13 +5386,16 @@
       <c r="AQ36" s="17" t="n"/>
       <c r="AR36" s="17" t="n"/>
       <c r="AT36">
-        <f>IF($B36="","",IF($B36="",1,0)+IF($C36="",1,0)+IF($D36="",1,0)+IF($E36="",1,0)+IF($G36="",1,0)+IF($H36="",1,0)+IF($I36="",1,0)+IF($L36="",1,0)+IF($M36="",1,0)+IF($N36="",1,0)+IF($Q36="",1,0)+IF($S36="",1,0)+IF($AA36="",1,0)+IF($AC36="",1,0)+IF($AG36="",1,0)+IF($AH36="",1,0)+IF($AI36="",1,0)+IF($AL36="",1,0)+IF($AP36="",1,0)+IF($AQ36="",1,0)+IF(AND($I36="あり",$J36=""),1,0)+IF(AND($I36="あり",$K36=""),1,0)+IF(AND($AA36="",$AB36=""),1,0)+IF(AND($AC36="あり",$AD36=""),1,0)+IF(AND($AC36="あり",OR($AD36="",$AD36="後日提出"),$AE36=""),1,0))</f>
+        <f>IF($B36="","",IF($B36="",1,0)+IF($C36="",1,0)+IF($D36="",1,0)+IF($E36="",1,0)+IF($G36="",1,0)+IF($H36="",1,0)+IF($I36="",1,0)+IF($L36="",1,0)+IF($M36="",1,0)+IF($N36="",1,0)+IF($Q36="",1,0)+IF($S36="",1,0)+IF($AA36="",1,0)+IF($AC36="",1,0)+IF($AG36="",1,0)+IF($AH36="",1,0)+IF($AI36="",1,0)+IF($AL36="",1,0)+IF($AP36="",1,0)+IF($AQ36="",1,0)+IF(AND($I36="あり",$J36=""),1,0)+IF(AND($I36="あり",$K36=""),1,0)+IF(AND($AA36="",$AB36=""),1,0)+IF(AND($AC36="あり",$AD36=""),1,0)+IF(AND($AC36="あり",OR($AD36="",$AD36="後日提出"),$AE36=""),1,0)+IF($AV36="",1,0)+IF(AND($AL36="外国",$AM36=""),1,0)+IF(AND($AL36="外国",$AN36=""),1,0)+IF(AND($AL36="外国",$AO36=""),1,0))</f>
         <v/>
       </c>
       <c r="AU36">
         <f>IF($B36="","",IF(AND($AA36&lt;&gt;"",$AA36&lt;&gt;"後日提出",$AA36&lt;&gt;"別経路提出",LEN($AA36)&lt;&gt;12),1,0)+IF(AND($AB36&lt;&gt;"",$AB36&lt;&gt;"後日提出",LEN($AB36)&lt;&gt;10),1,0)+IF(AND($AD36&lt;&gt;"",$AD36&lt;&gt;"後日提出",LEN($AD36)&lt;&gt;11),1,0)+IF(AND($AG36&lt;&gt;"",LEN(SUBSTITUTE($AG36,"-",""))&lt;&gt;7),1,0))</f>
         <v/>
       </c>
+      <c r="AV36" s="17" t="n"/>
+      <c r="AW36" s="59" t="n"/>
+      <c r="AX36" s="17" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="23">
@@ -5330,7 +5419,7 @@
       <c r="M37" s="17" t="n"/>
       <c r="N37" s="17" t="n"/>
       <c r="O37" s="23">
-        <f>IF($B37="","",IF($I37="なし","あり",IF($I37="あり",IF(OR($K37="更新の可能性あり",AND($J37&lt;&gt;"",$G37&lt;&gt;"",$J37-$G37+1&gt;62)),"あり","なし"),"")))</f>
+        <f>IF($B37="","",IF($I37="なし","あり",IF($I37&lt;&gt;"あり","",IF($K37="更新の可能性あり","あり",IF(OR($J37="",$G37=""),"なし",IF(OR(NOT(ISNUMBER($G37)),NOT(ISNUMBER($J37)),$G37&gt;80000,$J37&gt;80000),"要確認（日付）",IF($J37&gt;IF(DAY(EDATE($G37,2))&lt;DAY($G37),EOMONTH($G37,2),EDATE($G37,2)-1),"あり","なし"))))))</f>
         <v/>
       </c>
       <c r="P37" s="23">
@@ -5348,7 +5437,7 @@
         <v/>
       </c>
       <c r="X37" s="23">
-        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B37="","",IF(AND($L37&gt;='⓪ 事業所設定'!$C$13*0.75,$M37&gt;='⓪ 事業所設定'!$C$14*0.75,$O37="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L37&gt;=20,$O37="あり",$N37&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S37+$T37)&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
+        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B37="","",IF(AND($L37&gt;='⓪ 事業所設定'!$C$13*0.75,$M37&gt;='⓪ 事業所設定'!$C$14*0.75,$O37="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L37&gt;=20,$O37="あり",$N37&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S37+$T37-N($AW37))&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
         <v/>
       </c>
       <c r="Y37" s="23">
@@ -5356,7 +5445,7 @@
         <v/>
       </c>
       <c r="Z37" s="23">
-        <f>IF($B37="","",IF(AND($L37&gt;=20,$P37="あり",$N37&lt;&gt;"昼間部の学生"),"加入","加入対象外"))</f>
+        <f>IF($B37="","",IF($H37="役員","対象外（兼務役員なら要相談）",IF(AND($L37&gt;=20,$P37="あり",$N37&lt;&gt;"昼間部の学生"),"加入","加入対象外")))</f>
         <v/>
       </c>
       <c r="AA37" s="61" t="n"/>
@@ -5378,13 +5467,16 @@
       <c r="AQ37" s="17" t="n"/>
       <c r="AR37" s="17" t="n"/>
       <c r="AT37">
-        <f>IF($B37="","",IF($B37="",1,0)+IF($C37="",1,0)+IF($D37="",1,0)+IF($E37="",1,0)+IF($G37="",1,0)+IF($H37="",1,0)+IF($I37="",1,0)+IF($L37="",1,0)+IF($M37="",1,0)+IF($N37="",1,0)+IF($Q37="",1,0)+IF($S37="",1,0)+IF($AA37="",1,0)+IF($AC37="",1,0)+IF($AG37="",1,0)+IF($AH37="",1,0)+IF($AI37="",1,0)+IF($AL37="",1,0)+IF($AP37="",1,0)+IF($AQ37="",1,0)+IF(AND($I37="あり",$J37=""),1,0)+IF(AND($I37="あり",$K37=""),1,0)+IF(AND($AA37="",$AB37=""),1,0)+IF(AND($AC37="あり",$AD37=""),1,0)+IF(AND($AC37="あり",OR($AD37="",$AD37="後日提出"),$AE37=""),1,0))</f>
+        <f>IF($B37="","",IF($B37="",1,0)+IF($C37="",1,0)+IF($D37="",1,0)+IF($E37="",1,0)+IF($G37="",1,0)+IF($H37="",1,0)+IF($I37="",1,0)+IF($L37="",1,0)+IF($M37="",1,0)+IF($N37="",1,0)+IF($Q37="",1,0)+IF($S37="",1,0)+IF($AA37="",1,0)+IF($AC37="",1,0)+IF($AG37="",1,0)+IF($AH37="",1,0)+IF($AI37="",1,0)+IF($AL37="",1,0)+IF($AP37="",1,0)+IF($AQ37="",1,0)+IF(AND($I37="あり",$J37=""),1,0)+IF(AND($I37="あり",$K37=""),1,0)+IF(AND($AA37="",$AB37=""),1,0)+IF(AND($AC37="あり",$AD37=""),1,0)+IF(AND($AC37="あり",OR($AD37="",$AD37="後日提出"),$AE37=""),1,0)+IF($AV37="",1,0)+IF(AND($AL37="外国",$AM37=""),1,0)+IF(AND($AL37="外国",$AN37=""),1,0)+IF(AND($AL37="外国",$AO37=""),1,0))</f>
         <v/>
       </c>
       <c r="AU37">
         <f>IF($B37="","",IF(AND($AA37&lt;&gt;"",$AA37&lt;&gt;"後日提出",$AA37&lt;&gt;"別経路提出",LEN($AA37)&lt;&gt;12),1,0)+IF(AND($AB37&lt;&gt;"",$AB37&lt;&gt;"後日提出",LEN($AB37)&lt;&gt;10),1,0)+IF(AND($AD37&lt;&gt;"",$AD37&lt;&gt;"後日提出",LEN($AD37)&lt;&gt;11),1,0)+IF(AND($AG37&lt;&gt;"",LEN(SUBSTITUTE($AG37,"-",""))&lt;&gt;7),1,0))</f>
         <v/>
       </c>
+      <c r="AV37" s="17" t="n"/>
+      <c r="AW37" s="59" t="n"/>
+      <c r="AX37" s="17" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="23">
@@ -5408,7 +5500,7 @@
       <c r="M38" s="17" t="n"/>
       <c r="N38" s="17" t="n"/>
       <c r="O38" s="23">
-        <f>IF($B38="","",IF($I38="なし","あり",IF($I38="あり",IF(OR($K38="更新の可能性あり",AND($J38&lt;&gt;"",$G38&lt;&gt;"",$J38-$G38+1&gt;62)),"あり","なし"),"")))</f>
+        <f>IF($B38="","",IF($I38="なし","あり",IF($I38&lt;&gt;"あり","",IF($K38="更新の可能性あり","あり",IF(OR($J38="",$G38=""),"なし",IF(OR(NOT(ISNUMBER($G38)),NOT(ISNUMBER($J38)),$G38&gt;80000,$J38&gt;80000),"要確認（日付）",IF($J38&gt;IF(DAY(EDATE($G38,2))&lt;DAY($G38),EOMONTH($G38,2),EDATE($G38,2)-1),"あり","なし"))))))</f>
         <v/>
       </c>
       <c r="P38" s="23">
@@ -5426,7 +5518,7 @@
         <v/>
       </c>
       <c r="X38" s="23">
-        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B38="","",IF(AND($L38&gt;='⓪ 事業所設定'!$C$13*0.75,$M38&gt;='⓪ 事業所設定'!$C$14*0.75,$O38="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L38&gt;=20,$O38="あり",$N38&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S38+$T38)&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
+        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B38="","",IF(AND($L38&gt;='⓪ 事業所設定'!$C$13*0.75,$M38&gt;='⓪ 事業所設定'!$C$14*0.75,$O38="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L38&gt;=20,$O38="あり",$N38&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S38+$T38-N($AW38))&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
         <v/>
       </c>
       <c r="Y38" s="23">
@@ -5434,7 +5526,7 @@
         <v/>
       </c>
       <c r="Z38" s="23">
-        <f>IF($B38="","",IF(AND($L38&gt;=20,$P38="あり",$N38&lt;&gt;"昼間部の学生"),"加入","加入対象外"))</f>
+        <f>IF($B38="","",IF($H38="役員","対象外（兼務役員なら要相談）",IF(AND($L38&gt;=20,$P38="あり",$N38&lt;&gt;"昼間部の学生"),"加入","加入対象外")))</f>
         <v/>
       </c>
       <c r="AA38" s="61" t="n"/>
@@ -5456,13 +5548,16 @@
       <c r="AQ38" s="17" t="n"/>
       <c r="AR38" s="17" t="n"/>
       <c r="AT38">
-        <f>IF($B38="","",IF($B38="",1,0)+IF($C38="",1,0)+IF($D38="",1,0)+IF($E38="",1,0)+IF($G38="",1,0)+IF($H38="",1,0)+IF($I38="",1,0)+IF($L38="",1,0)+IF($M38="",1,0)+IF($N38="",1,0)+IF($Q38="",1,0)+IF($S38="",1,0)+IF($AA38="",1,0)+IF($AC38="",1,0)+IF($AG38="",1,0)+IF($AH38="",1,0)+IF($AI38="",1,0)+IF($AL38="",1,0)+IF($AP38="",1,0)+IF($AQ38="",1,0)+IF(AND($I38="あり",$J38=""),1,0)+IF(AND($I38="あり",$K38=""),1,0)+IF(AND($AA38="",$AB38=""),1,0)+IF(AND($AC38="あり",$AD38=""),1,0)+IF(AND($AC38="あり",OR($AD38="",$AD38="後日提出"),$AE38=""),1,0))</f>
+        <f>IF($B38="","",IF($B38="",1,0)+IF($C38="",1,0)+IF($D38="",1,0)+IF($E38="",1,0)+IF($G38="",1,0)+IF($H38="",1,0)+IF($I38="",1,0)+IF($L38="",1,0)+IF($M38="",1,0)+IF($N38="",1,0)+IF($Q38="",1,0)+IF($S38="",1,0)+IF($AA38="",1,0)+IF($AC38="",1,0)+IF($AG38="",1,0)+IF($AH38="",1,0)+IF($AI38="",1,0)+IF($AL38="",1,0)+IF($AP38="",1,0)+IF($AQ38="",1,0)+IF(AND($I38="あり",$J38=""),1,0)+IF(AND($I38="あり",$K38=""),1,0)+IF(AND($AA38="",$AB38=""),1,0)+IF(AND($AC38="あり",$AD38=""),1,0)+IF(AND($AC38="あり",OR($AD38="",$AD38="後日提出"),$AE38=""),1,0)+IF($AV38="",1,0)+IF(AND($AL38="外国",$AM38=""),1,0)+IF(AND($AL38="外国",$AN38=""),1,0)+IF(AND($AL38="外国",$AO38=""),1,0))</f>
         <v/>
       </c>
       <c r="AU38">
         <f>IF($B38="","",IF(AND($AA38&lt;&gt;"",$AA38&lt;&gt;"後日提出",$AA38&lt;&gt;"別経路提出",LEN($AA38)&lt;&gt;12),1,0)+IF(AND($AB38&lt;&gt;"",$AB38&lt;&gt;"後日提出",LEN($AB38)&lt;&gt;10),1,0)+IF(AND($AD38&lt;&gt;"",$AD38&lt;&gt;"後日提出",LEN($AD38)&lt;&gt;11),1,0)+IF(AND($AG38&lt;&gt;"",LEN(SUBSTITUTE($AG38,"-",""))&lt;&gt;7),1,0))</f>
         <v/>
       </c>
+      <c r="AV38" s="17" t="n"/>
+      <c r="AW38" s="59" t="n"/>
+      <c r="AX38" s="17" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="23">
@@ -5486,7 +5581,7 @@
       <c r="M39" s="17" t="n"/>
       <c r="N39" s="17" t="n"/>
       <c r="O39" s="23">
-        <f>IF($B39="","",IF($I39="なし","あり",IF($I39="あり",IF(OR($K39="更新の可能性あり",AND($J39&lt;&gt;"",$G39&lt;&gt;"",$J39-$G39+1&gt;62)),"あり","なし"),"")))</f>
+        <f>IF($B39="","",IF($I39="なし","あり",IF($I39&lt;&gt;"あり","",IF($K39="更新の可能性あり","あり",IF(OR($J39="",$G39=""),"なし",IF(OR(NOT(ISNUMBER($G39)),NOT(ISNUMBER($J39)),$G39&gt;80000,$J39&gt;80000),"要確認（日付）",IF($J39&gt;IF(DAY(EDATE($G39,2))&lt;DAY($G39),EOMONTH($G39,2),EDATE($G39,2)-1),"あり","なし"))))))</f>
         <v/>
       </c>
       <c r="P39" s="23">
@@ -5504,7 +5599,7 @@
         <v/>
       </c>
       <c r="X39" s="23">
-        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B39="","",IF(AND($L39&gt;='⓪ 事業所設定'!$C$13*0.75,$M39&gt;='⓪ 事業所設定'!$C$14*0.75,$O39="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L39&gt;=20,$O39="あり",$N39&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S39+$T39)&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
+        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B39="","",IF(AND($L39&gt;='⓪ 事業所設定'!$C$13*0.75,$M39&gt;='⓪ 事業所設定'!$C$14*0.75,$O39="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L39&gt;=20,$O39="あり",$N39&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S39+$T39-N($AW39))&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
         <v/>
       </c>
       <c r="Y39" s="23">
@@ -5512,7 +5607,7 @@
         <v/>
       </c>
       <c r="Z39" s="23">
-        <f>IF($B39="","",IF(AND($L39&gt;=20,$P39="あり",$N39&lt;&gt;"昼間部の学生"),"加入","加入対象外"))</f>
+        <f>IF($B39="","",IF($H39="役員","対象外（兼務役員なら要相談）",IF(AND($L39&gt;=20,$P39="あり",$N39&lt;&gt;"昼間部の学生"),"加入","加入対象外")))</f>
         <v/>
       </c>
       <c r="AA39" s="61" t="n"/>
@@ -5534,13 +5629,16 @@
       <c r="AQ39" s="17" t="n"/>
       <c r="AR39" s="17" t="n"/>
       <c r="AT39">
-        <f>IF($B39="","",IF($B39="",1,0)+IF($C39="",1,0)+IF($D39="",1,0)+IF($E39="",1,0)+IF($G39="",1,0)+IF($H39="",1,0)+IF($I39="",1,0)+IF($L39="",1,0)+IF($M39="",1,0)+IF($N39="",1,0)+IF($Q39="",1,0)+IF($S39="",1,0)+IF($AA39="",1,0)+IF($AC39="",1,0)+IF($AG39="",1,0)+IF($AH39="",1,0)+IF($AI39="",1,0)+IF($AL39="",1,0)+IF($AP39="",1,0)+IF($AQ39="",1,0)+IF(AND($I39="あり",$J39=""),1,0)+IF(AND($I39="あり",$K39=""),1,0)+IF(AND($AA39="",$AB39=""),1,0)+IF(AND($AC39="あり",$AD39=""),1,0)+IF(AND($AC39="あり",OR($AD39="",$AD39="後日提出"),$AE39=""),1,0))</f>
+        <f>IF($B39="","",IF($B39="",1,0)+IF($C39="",1,0)+IF($D39="",1,0)+IF($E39="",1,0)+IF($G39="",1,0)+IF($H39="",1,0)+IF($I39="",1,0)+IF($L39="",1,0)+IF($M39="",1,0)+IF($N39="",1,0)+IF($Q39="",1,0)+IF($S39="",1,0)+IF($AA39="",1,0)+IF($AC39="",1,0)+IF($AG39="",1,0)+IF($AH39="",1,0)+IF($AI39="",1,0)+IF($AL39="",1,0)+IF($AP39="",1,0)+IF($AQ39="",1,0)+IF(AND($I39="あり",$J39=""),1,0)+IF(AND($I39="あり",$K39=""),1,0)+IF(AND($AA39="",$AB39=""),1,0)+IF(AND($AC39="あり",$AD39=""),1,0)+IF(AND($AC39="あり",OR($AD39="",$AD39="後日提出"),$AE39=""),1,0)+IF($AV39="",1,0)+IF(AND($AL39="外国",$AM39=""),1,0)+IF(AND($AL39="外国",$AN39=""),1,0)+IF(AND($AL39="外国",$AO39=""),1,0))</f>
         <v/>
       </c>
       <c r="AU39">
         <f>IF($B39="","",IF(AND($AA39&lt;&gt;"",$AA39&lt;&gt;"後日提出",$AA39&lt;&gt;"別経路提出",LEN($AA39)&lt;&gt;12),1,0)+IF(AND($AB39&lt;&gt;"",$AB39&lt;&gt;"後日提出",LEN($AB39)&lt;&gt;10),1,0)+IF(AND($AD39&lt;&gt;"",$AD39&lt;&gt;"後日提出",LEN($AD39)&lt;&gt;11),1,0)+IF(AND($AG39&lt;&gt;"",LEN(SUBSTITUTE($AG39,"-",""))&lt;&gt;7),1,0))</f>
         <v/>
       </c>
+      <c r="AV39" s="17" t="n"/>
+      <c r="AW39" s="59" t="n"/>
+      <c r="AX39" s="17" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="23">
@@ -5564,7 +5662,7 @@
       <c r="M40" s="17" t="n"/>
       <c r="N40" s="17" t="n"/>
       <c r="O40" s="23">
-        <f>IF($B40="","",IF($I40="なし","あり",IF($I40="あり",IF(OR($K40="更新の可能性あり",AND($J40&lt;&gt;"",$G40&lt;&gt;"",$J40-$G40+1&gt;62)),"あり","なし"),"")))</f>
+        <f>IF($B40="","",IF($I40="なし","あり",IF($I40&lt;&gt;"あり","",IF($K40="更新の可能性あり","あり",IF(OR($J40="",$G40=""),"なし",IF(OR(NOT(ISNUMBER($G40)),NOT(ISNUMBER($J40)),$G40&gt;80000,$J40&gt;80000),"要確認（日付）",IF($J40&gt;IF(DAY(EDATE($G40,2))&lt;DAY($G40),EOMONTH($G40,2),EDATE($G40,2)-1),"あり","なし"))))))</f>
         <v/>
       </c>
       <c r="P40" s="23">
@@ -5582,7 +5680,7 @@
         <v/>
       </c>
       <c r="X40" s="23">
-        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B40="","",IF(AND($L40&gt;='⓪ 事業所設定'!$C$13*0.75,$M40&gt;='⓪ 事業所設定'!$C$14*0.75,$O40="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L40&gt;=20,$O40="あり",$N40&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S40+$T40)&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
+        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B40="","",IF(AND($L40&gt;='⓪ 事業所設定'!$C$13*0.75,$M40&gt;='⓪ 事業所設定'!$C$14*0.75,$O40="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L40&gt;=20,$O40="あり",$N40&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S40+$T40-N($AW40))&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
         <v/>
       </c>
       <c r="Y40" s="23">
@@ -5590,7 +5688,7 @@
         <v/>
       </c>
       <c r="Z40" s="23">
-        <f>IF($B40="","",IF(AND($L40&gt;=20,$P40="あり",$N40&lt;&gt;"昼間部の学生"),"加入","加入対象外"))</f>
+        <f>IF($B40="","",IF($H40="役員","対象外（兼務役員なら要相談）",IF(AND($L40&gt;=20,$P40="あり",$N40&lt;&gt;"昼間部の学生"),"加入","加入対象外")))</f>
         <v/>
       </c>
       <c r="AA40" s="61" t="n"/>
@@ -5612,13 +5710,16 @@
       <c r="AQ40" s="17" t="n"/>
       <c r="AR40" s="17" t="n"/>
       <c r="AT40">
-        <f>IF($B40="","",IF($B40="",1,0)+IF($C40="",1,0)+IF($D40="",1,0)+IF($E40="",1,0)+IF($G40="",1,0)+IF($H40="",1,0)+IF($I40="",1,0)+IF($L40="",1,0)+IF($M40="",1,0)+IF($N40="",1,0)+IF($Q40="",1,0)+IF($S40="",1,0)+IF($AA40="",1,0)+IF($AC40="",1,0)+IF($AG40="",1,0)+IF($AH40="",1,0)+IF($AI40="",1,0)+IF($AL40="",1,0)+IF($AP40="",1,0)+IF($AQ40="",1,0)+IF(AND($I40="あり",$J40=""),1,0)+IF(AND($I40="あり",$K40=""),1,0)+IF(AND($AA40="",$AB40=""),1,0)+IF(AND($AC40="あり",$AD40=""),1,0)+IF(AND($AC40="あり",OR($AD40="",$AD40="後日提出"),$AE40=""),1,0))</f>
+        <f>IF($B40="","",IF($B40="",1,0)+IF($C40="",1,0)+IF($D40="",1,0)+IF($E40="",1,0)+IF($G40="",1,0)+IF($H40="",1,0)+IF($I40="",1,0)+IF($L40="",1,0)+IF($M40="",1,0)+IF($N40="",1,0)+IF($Q40="",1,0)+IF($S40="",1,0)+IF($AA40="",1,0)+IF($AC40="",1,0)+IF($AG40="",1,0)+IF($AH40="",1,0)+IF($AI40="",1,0)+IF($AL40="",1,0)+IF($AP40="",1,0)+IF($AQ40="",1,0)+IF(AND($I40="あり",$J40=""),1,0)+IF(AND($I40="あり",$K40=""),1,0)+IF(AND($AA40="",$AB40=""),1,0)+IF(AND($AC40="あり",$AD40=""),1,0)+IF(AND($AC40="あり",OR($AD40="",$AD40="後日提出"),$AE40=""),1,0)+IF($AV40="",1,0)+IF(AND($AL40="外国",$AM40=""),1,0)+IF(AND($AL40="外国",$AN40=""),1,0)+IF(AND($AL40="外国",$AO40=""),1,0))</f>
         <v/>
       </c>
       <c r="AU40">
         <f>IF($B40="","",IF(AND($AA40&lt;&gt;"",$AA40&lt;&gt;"後日提出",$AA40&lt;&gt;"別経路提出",LEN($AA40)&lt;&gt;12),1,0)+IF(AND($AB40&lt;&gt;"",$AB40&lt;&gt;"後日提出",LEN($AB40)&lt;&gt;10),1,0)+IF(AND($AD40&lt;&gt;"",$AD40&lt;&gt;"後日提出",LEN($AD40)&lt;&gt;11),1,0)+IF(AND($AG40&lt;&gt;"",LEN(SUBSTITUTE($AG40,"-",""))&lt;&gt;7),1,0))</f>
         <v/>
       </c>
+      <c r="AV40" s="17" t="n"/>
+      <c r="AW40" s="59" t="n"/>
+      <c r="AX40" s="17" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="23">
@@ -5642,7 +5743,7 @@
       <c r="M41" s="17" t="n"/>
       <c r="N41" s="17" t="n"/>
       <c r="O41" s="23">
-        <f>IF($B41="","",IF($I41="なし","あり",IF($I41="あり",IF(OR($K41="更新の可能性あり",AND($J41&lt;&gt;"",$G41&lt;&gt;"",$J41-$G41+1&gt;62)),"あり","なし"),"")))</f>
+        <f>IF($B41="","",IF($I41="なし","あり",IF($I41&lt;&gt;"あり","",IF($K41="更新の可能性あり","あり",IF(OR($J41="",$G41=""),"なし",IF(OR(NOT(ISNUMBER($G41)),NOT(ISNUMBER($J41)),$G41&gt;80000,$J41&gt;80000),"要確認（日付）",IF($J41&gt;IF(DAY(EDATE($G41,2))&lt;DAY($G41),EOMONTH($G41,2),EDATE($G41,2)-1),"あり","なし"))))))</f>
         <v/>
       </c>
       <c r="P41" s="23">
@@ -5660,7 +5761,7 @@
         <v/>
       </c>
       <c r="X41" s="23">
-        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B41="","",IF(AND($L41&gt;='⓪ 事業所設定'!$C$13*0.75,$M41&gt;='⓪ 事業所設定'!$C$14*0.75,$O41="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L41&gt;=20,$O41="あり",$N41&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S41+$T41)&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
+        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B41="","",IF(AND($L41&gt;='⓪ 事業所設定'!$C$13*0.75,$M41&gt;='⓪ 事業所設定'!$C$14*0.75,$O41="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L41&gt;=20,$O41="あり",$N41&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S41+$T41-N($AW41))&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
         <v/>
       </c>
       <c r="Y41" s="23">
@@ -5668,7 +5769,7 @@
         <v/>
       </c>
       <c r="Z41" s="23">
-        <f>IF($B41="","",IF(AND($L41&gt;=20,$P41="あり",$N41&lt;&gt;"昼間部の学生"),"加入","加入対象外"))</f>
+        <f>IF($B41="","",IF($H41="役員","対象外（兼務役員なら要相談）",IF(AND($L41&gt;=20,$P41="あり",$N41&lt;&gt;"昼間部の学生"),"加入","加入対象外")))</f>
         <v/>
       </c>
       <c r="AA41" s="61" t="n"/>
@@ -5690,13 +5791,16 @@
       <c r="AQ41" s="17" t="n"/>
       <c r="AR41" s="17" t="n"/>
       <c r="AT41">
-        <f>IF($B41="","",IF($B41="",1,0)+IF($C41="",1,0)+IF($D41="",1,0)+IF($E41="",1,0)+IF($G41="",1,0)+IF($H41="",1,0)+IF($I41="",1,0)+IF($L41="",1,0)+IF($M41="",1,0)+IF($N41="",1,0)+IF($Q41="",1,0)+IF($S41="",1,0)+IF($AA41="",1,0)+IF($AC41="",1,0)+IF($AG41="",1,0)+IF($AH41="",1,0)+IF($AI41="",1,0)+IF($AL41="",1,0)+IF($AP41="",1,0)+IF($AQ41="",1,0)+IF(AND($I41="あり",$J41=""),1,0)+IF(AND($I41="あり",$K41=""),1,0)+IF(AND($AA41="",$AB41=""),1,0)+IF(AND($AC41="あり",$AD41=""),1,0)+IF(AND($AC41="あり",OR($AD41="",$AD41="後日提出"),$AE41=""),1,0))</f>
+        <f>IF($B41="","",IF($B41="",1,0)+IF($C41="",1,0)+IF($D41="",1,0)+IF($E41="",1,0)+IF($G41="",1,0)+IF($H41="",1,0)+IF($I41="",1,0)+IF($L41="",1,0)+IF($M41="",1,0)+IF($N41="",1,0)+IF($Q41="",1,0)+IF($S41="",1,0)+IF($AA41="",1,0)+IF($AC41="",1,0)+IF($AG41="",1,0)+IF($AH41="",1,0)+IF($AI41="",1,0)+IF($AL41="",1,0)+IF($AP41="",1,0)+IF($AQ41="",1,0)+IF(AND($I41="あり",$J41=""),1,0)+IF(AND($I41="あり",$K41=""),1,0)+IF(AND($AA41="",$AB41=""),1,0)+IF(AND($AC41="あり",$AD41=""),1,0)+IF(AND($AC41="あり",OR($AD41="",$AD41="後日提出"),$AE41=""),1,0)+IF($AV41="",1,0)+IF(AND($AL41="外国",$AM41=""),1,0)+IF(AND($AL41="外国",$AN41=""),1,0)+IF(AND($AL41="外国",$AO41=""),1,0))</f>
         <v/>
       </c>
       <c r="AU41">
         <f>IF($B41="","",IF(AND($AA41&lt;&gt;"",$AA41&lt;&gt;"後日提出",$AA41&lt;&gt;"別経路提出",LEN($AA41)&lt;&gt;12),1,0)+IF(AND($AB41&lt;&gt;"",$AB41&lt;&gt;"後日提出",LEN($AB41)&lt;&gt;10),1,0)+IF(AND($AD41&lt;&gt;"",$AD41&lt;&gt;"後日提出",LEN($AD41)&lt;&gt;11),1,0)+IF(AND($AG41&lt;&gt;"",LEN(SUBSTITUTE($AG41,"-",""))&lt;&gt;7),1,0))</f>
         <v/>
       </c>
+      <c r="AV41" s="17" t="n"/>
+      <c r="AW41" s="59" t="n"/>
+      <c r="AX41" s="17" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="23">
@@ -5720,7 +5824,7 @@
       <c r="M42" s="17" t="n"/>
       <c r="N42" s="17" t="n"/>
       <c r="O42" s="23">
-        <f>IF($B42="","",IF($I42="なし","あり",IF($I42="あり",IF(OR($K42="更新の可能性あり",AND($J42&lt;&gt;"",$G42&lt;&gt;"",$J42-$G42+1&gt;62)),"あり","なし"),"")))</f>
+        <f>IF($B42="","",IF($I42="なし","あり",IF($I42&lt;&gt;"あり","",IF($K42="更新の可能性あり","あり",IF(OR($J42="",$G42=""),"なし",IF(OR(NOT(ISNUMBER($G42)),NOT(ISNUMBER($J42)),$G42&gt;80000,$J42&gt;80000),"要確認（日付）",IF($J42&gt;IF(DAY(EDATE($G42,2))&lt;DAY($G42),EOMONTH($G42,2),EDATE($G42,2)-1),"あり","なし"))))))</f>
         <v/>
       </c>
       <c r="P42" s="23">
@@ -5738,7 +5842,7 @@
         <v/>
       </c>
       <c r="X42" s="23">
-        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B42="","",IF(AND($L42&gt;='⓪ 事業所設定'!$C$13*0.75,$M42&gt;='⓪ 事業所設定'!$C$14*0.75,$O42="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L42&gt;=20,$O42="あり",$N42&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S42+$T42)&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
+        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B42="","",IF(AND($L42&gt;='⓪ 事業所設定'!$C$13*0.75,$M42&gt;='⓪ 事業所設定'!$C$14*0.75,$O42="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L42&gt;=20,$O42="あり",$N42&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S42+$T42-N($AW42))&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
         <v/>
       </c>
       <c r="Y42" s="23">
@@ -5746,7 +5850,7 @@
         <v/>
       </c>
       <c r="Z42" s="23">
-        <f>IF($B42="","",IF(AND($L42&gt;=20,$P42="あり",$N42&lt;&gt;"昼間部の学生"),"加入","加入対象外"))</f>
+        <f>IF($B42="","",IF($H42="役員","対象外（兼務役員なら要相談）",IF(AND($L42&gt;=20,$P42="あり",$N42&lt;&gt;"昼間部の学生"),"加入","加入対象外")))</f>
         <v/>
       </c>
       <c r="AA42" s="61" t="n"/>
@@ -5768,13 +5872,16 @@
       <c r="AQ42" s="17" t="n"/>
       <c r="AR42" s="17" t="n"/>
       <c r="AT42">
-        <f>IF($B42="","",IF($B42="",1,0)+IF($C42="",1,0)+IF($D42="",1,0)+IF($E42="",1,0)+IF($G42="",1,0)+IF($H42="",1,0)+IF($I42="",1,0)+IF($L42="",1,0)+IF($M42="",1,0)+IF($N42="",1,0)+IF($Q42="",1,0)+IF($S42="",1,0)+IF($AA42="",1,0)+IF($AC42="",1,0)+IF($AG42="",1,0)+IF($AH42="",1,0)+IF($AI42="",1,0)+IF($AL42="",1,0)+IF($AP42="",1,0)+IF($AQ42="",1,0)+IF(AND($I42="あり",$J42=""),1,0)+IF(AND($I42="あり",$K42=""),1,0)+IF(AND($AA42="",$AB42=""),1,0)+IF(AND($AC42="あり",$AD42=""),1,0)+IF(AND($AC42="あり",OR($AD42="",$AD42="後日提出"),$AE42=""),1,0))</f>
+        <f>IF($B42="","",IF($B42="",1,0)+IF($C42="",1,0)+IF($D42="",1,0)+IF($E42="",1,0)+IF($G42="",1,0)+IF($H42="",1,0)+IF($I42="",1,0)+IF($L42="",1,0)+IF($M42="",1,0)+IF($N42="",1,0)+IF($Q42="",1,0)+IF($S42="",1,0)+IF($AA42="",1,0)+IF($AC42="",1,0)+IF($AG42="",1,0)+IF($AH42="",1,0)+IF($AI42="",1,0)+IF($AL42="",1,0)+IF($AP42="",1,0)+IF($AQ42="",1,0)+IF(AND($I42="あり",$J42=""),1,0)+IF(AND($I42="あり",$K42=""),1,0)+IF(AND($AA42="",$AB42=""),1,0)+IF(AND($AC42="あり",$AD42=""),1,0)+IF(AND($AC42="あり",OR($AD42="",$AD42="後日提出"),$AE42=""),1,0)+IF($AV42="",1,0)+IF(AND($AL42="外国",$AM42=""),1,0)+IF(AND($AL42="外国",$AN42=""),1,0)+IF(AND($AL42="外国",$AO42=""),1,0))</f>
         <v/>
       </c>
       <c r="AU42">
         <f>IF($B42="","",IF(AND($AA42&lt;&gt;"",$AA42&lt;&gt;"後日提出",$AA42&lt;&gt;"別経路提出",LEN($AA42)&lt;&gt;12),1,0)+IF(AND($AB42&lt;&gt;"",$AB42&lt;&gt;"後日提出",LEN($AB42)&lt;&gt;10),1,0)+IF(AND($AD42&lt;&gt;"",$AD42&lt;&gt;"後日提出",LEN($AD42)&lt;&gt;11),1,0)+IF(AND($AG42&lt;&gt;"",LEN(SUBSTITUTE($AG42,"-",""))&lt;&gt;7),1,0))</f>
         <v/>
       </c>
+      <c r="AV42" s="17" t="n"/>
+      <c r="AW42" s="59" t="n"/>
+      <c r="AX42" s="17" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="23">
@@ -5798,7 +5905,7 @@
       <c r="M43" s="17" t="n"/>
       <c r="N43" s="17" t="n"/>
       <c r="O43" s="23">
-        <f>IF($B43="","",IF($I43="なし","あり",IF($I43="あり",IF(OR($K43="更新の可能性あり",AND($J43&lt;&gt;"",$G43&lt;&gt;"",$J43-$G43+1&gt;62)),"あり","なし"),"")))</f>
+        <f>IF($B43="","",IF($I43="なし","あり",IF($I43&lt;&gt;"あり","",IF($K43="更新の可能性あり","あり",IF(OR($J43="",$G43=""),"なし",IF(OR(NOT(ISNUMBER($G43)),NOT(ISNUMBER($J43)),$G43&gt;80000,$J43&gt;80000),"要確認（日付）",IF($J43&gt;IF(DAY(EDATE($G43,2))&lt;DAY($G43),EOMONTH($G43,2),EDATE($G43,2)-1),"あり","なし"))))))</f>
         <v/>
       </c>
       <c r="P43" s="23">
@@ -5816,7 +5923,7 @@
         <v/>
       </c>
       <c r="X43" s="23">
-        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B43="","",IF(AND($L43&gt;='⓪ 事業所設定'!$C$13*0.75,$M43&gt;='⓪ 事業所設定'!$C$14*0.75,$O43="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L43&gt;=20,$O43="あり",$N43&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S43+$T43)&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
+        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B43="","",IF(AND($L43&gt;='⓪ 事業所設定'!$C$13*0.75,$M43&gt;='⓪ 事業所設定'!$C$14*0.75,$O43="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L43&gt;=20,$O43="あり",$N43&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S43+$T43-N($AW43))&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
         <v/>
       </c>
       <c r="Y43" s="23">
@@ -5824,7 +5931,7 @@
         <v/>
       </c>
       <c r="Z43" s="23">
-        <f>IF($B43="","",IF(AND($L43&gt;=20,$P43="あり",$N43&lt;&gt;"昼間部の学生"),"加入","加入対象外"))</f>
+        <f>IF($B43="","",IF($H43="役員","対象外（兼務役員なら要相談）",IF(AND($L43&gt;=20,$P43="あり",$N43&lt;&gt;"昼間部の学生"),"加入","加入対象外")))</f>
         <v/>
       </c>
       <c r="AA43" s="61" t="n"/>
@@ -5846,13 +5953,16 @@
       <c r="AQ43" s="17" t="n"/>
       <c r="AR43" s="17" t="n"/>
       <c r="AT43">
-        <f>IF($B43="","",IF($B43="",1,0)+IF($C43="",1,0)+IF($D43="",1,0)+IF($E43="",1,0)+IF($G43="",1,0)+IF($H43="",1,0)+IF($I43="",1,0)+IF($L43="",1,0)+IF($M43="",1,0)+IF($N43="",1,0)+IF($Q43="",1,0)+IF($S43="",1,0)+IF($AA43="",1,0)+IF($AC43="",1,0)+IF($AG43="",1,0)+IF($AH43="",1,0)+IF($AI43="",1,0)+IF($AL43="",1,0)+IF($AP43="",1,0)+IF($AQ43="",1,0)+IF(AND($I43="あり",$J43=""),1,0)+IF(AND($I43="あり",$K43=""),1,0)+IF(AND($AA43="",$AB43=""),1,0)+IF(AND($AC43="あり",$AD43=""),1,0)+IF(AND($AC43="あり",OR($AD43="",$AD43="後日提出"),$AE43=""),1,0))</f>
+        <f>IF($B43="","",IF($B43="",1,0)+IF($C43="",1,0)+IF($D43="",1,0)+IF($E43="",1,0)+IF($G43="",1,0)+IF($H43="",1,0)+IF($I43="",1,0)+IF($L43="",1,0)+IF($M43="",1,0)+IF($N43="",1,0)+IF($Q43="",1,0)+IF($S43="",1,0)+IF($AA43="",1,0)+IF($AC43="",1,0)+IF($AG43="",1,0)+IF($AH43="",1,0)+IF($AI43="",1,0)+IF($AL43="",1,0)+IF($AP43="",1,0)+IF($AQ43="",1,0)+IF(AND($I43="あり",$J43=""),1,0)+IF(AND($I43="あり",$K43=""),1,0)+IF(AND($AA43="",$AB43=""),1,0)+IF(AND($AC43="あり",$AD43=""),1,0)+IF(AND($AC43="あり",OR($AD43="",$AD43="後日提出"),$AE43=""),1,0)+IF($AV43="",1,0)+IF(AND($AL43="外国",$AM43=""),1,0)+IF(AND($AL43="外国",$AN43=""),1,0)+IF(AND($AL43="外国",$AO43=""),1,0))</f>
         <v/>
       </c>
       <c r="AU43">
         <f>IF($B43="","",IF(AND($AA43&lt;&gt;"",$AA43&lt;&gt;"後日提出",$AA43&lt;&gt;"別経路提出",LEN($AA43)&lt;&gt;12),1,0)+IF(AND($AB43&lt;&gt;"",$AB43&lt;&gt;"後日提出",LEN($AB43)&lt;&gt;10),1,0)+IF(AND($AD43&lt;&gt;"",$AD43&lt;&gt;"後日提出",LEN($AD43)&lt;&gt;11),1,0)+IF(AND($AG43&lt;&gt;"",LEN(SUBSTITUTE($AG43,"-",""))&lt;&gt;7),1,0))</f>
         <v/>
       </c>
+      <c r="AV43" s="17" t="n"/>
+      <c r="AW43" s="59" t="n"/>
+      <c r="AX43" s="17" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="23">
@@ -5876,7 +5986,7 @@
       <c r="M44" s="17" t="n"/>
       <c r="N44" s="17" t="n"/>
       <c r="O44" s="23">
-        <f>IF($B44="","",IF($I44="なし","あり",IF($I44="あり",IF(OR($K44="更新の可能性あり",AND($J44&lt;&gt;"",$G44&lt;&gt;"",$J44-$G44+1&gt;62)),"あり","なし"),"")))</f>
+        <f>IF($B44="","",IF($I44="なし","あり",IF($I44&lt;&gt;"あり","",IF($K44="更新の可能性あり","あり",IF(OR($J44="",$G44=""),"なし",IF(OR(NOT(ISNUMBER($G44)),NOT(ISNUMBER($J44)),$G44&gt;80000,$J44&gt;80000),"要確認（日付）",IF($J44&gt;IF(DAY(EDATE($G44,2))&lt;DAY($G44),EOMONTH($G44,2),EDATE($G44,2)-1),"あり","なし"))))))</f>
         <v/>
       </c>
       <c r="P44" s="23">
@@ -5894,7 +6004,7 @@
         <v/>
       </c>
       <c r="X44" s="23">
-        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B44="","",IF(AND($L44&gt;='⓪ 事業所設定'!$C$13*0.75,$M44&gt;='⓪ 事業所設定'!$C$14*0.75,$O44="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L44&gt;=20,$O44="あり",$N44&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S44+$T44)&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
+        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B44="","",IF(AND($L44&gt;='⓪ 事業所設定'!$C$13*0.75,$M44&gt;='⓪ 事業所設定'!$C$14*0.75,$O44="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L44&gt;=20,$O44="あり",$N44&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S44+$T44-N($AW44))&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
         <v/>
       </c>
       <c r="Y44" s="23">
@@ -5902,7 +6012,7 @@
         <v/>
       </c>
       <c r="Z44" s="23">
-        <f>IF($B44="","",IF(AND($L44&gt;=20,$P44="あり",$N44&lt;&gt;"昼間部の学生"),"加入","加入対象外"))</f>
+        <f>IF($B44="","",IF($H44="役員","対象外（兼務役員なら要相談）",IF(AND($L44&gt;=20,$P44="あり",$N44&lt;&gt;"昼間部の学生"),"加入","加入対象外")))</f>
         <v/>
       </c>
       <c r="AA44" s="61" t="n"/>
@@ -5924,13 +6034,16 @@
       <c r="AQ44" s="17" t="n"/>
       <c r="AR44" s="17" t="n"/>
       <c r="AT44">
-        <f>IF($B44="","",IF($B44="",1,0)+IF($C44="",1,0)+IF($D44="",1,0)+IF($E44="",1,0)+IF($G44="",1,0)+IF($H44="",1,0)+IF($I44="",1,0)+IF($L44="",1,0)+IF($M44="",1,0)+IF($N44="",1,0)+IF($Q44="",1,0)+IF($S44="",1,0)+IF($AA44="",1,0)+IF($AC44="",1,0)+IF($AG44="",1,0)+IF($AH44="",1,0)+IF($AI44="",1,0)+IF($AL44="",1,0)+IF($AP44="",1,0)+IF($AQ44="",1,0)+IF(AND($I44="あり",$J44=""),1,0)+IF(AND($I44="あり",$K44=""),1,0)+IF(AND($AA44="",$AB44=""),1,0)+IF(AND($AC44="あり",$AD44=""),1,0)+IF(AND($AC44="あり",OR($AD44="",$AD44="後日提出"),$AE44=""),1,0))</f>
+        <f>IF($B44="","",IF($B44="",1,0)+IF($C44="",1,0)+IF($D44="",1,0)+IF($E44="",1,0)+IF($G44="",1,0)+IF($H44="",1,0)+IF($I44="",1,0)+IF($L44="",1,0)+IF($M44="",1,0)+IF($N44="",1,0)+IF($Q44="",1,0)+IF($S44="",1,0)+IF($AA44="",1,0)+IF($AC44="",1,0)+IF($AG44="",1,0)+IF($AH44="",1,0)+IF($AI44="",1,0)+IF($AL44="",1,0)+IF($AP44="",1,0)+IF($AQ44="",1,0)+IF(AND($I44="あり",$J44=""),1,0)+IF(AND($I44="あり",$K44=""),1,0)+IF(AND($AA44="",$AB44=""),1,0)+IF(AND($AC44="あり",$AD44=""),1,0)+IF(AND($AC44="あり",OR($AD44="",$AD44="後日提出"),$AE44=""),1,0)+IF($AV44="",1,0)+IF(AND($AL44="外国",$AM44=""),1,0)+IF(AND($AL44="外国",$AN44=""),1,0)+IF(AND($AL44="外国",$AO44=""),1,0))</f>
         <v/>
       </c>
       <c r="AU44">
         <f>IF($B44="","",IF(AND($AA44&lt;&gt;"",$AA44&lt;&gt;"後日提出",$AA44&lt;&gt;"別経路提出",LEN($AA44)&lt;&gt;12),1,0)+IF(AND($AB44&lt;&gt;"",$AB44&lt;&gt;"後日提出",LEN($AB44)&lt;&gt;10),1,0)+IF(AND($AD44&lt;&gt;"",$AD44&lt;&gt;"後日提出",LEN($AD44)&lt;&gt;11),1,0)+IF(AND($AG44&lt;&gt;"",LEN(SUBSTITUTE($AG44,"-",""))&lt;&gt;7),1,0))</f>
         <v/>
       </c>
+      <c r="AV44" s="17" t="n"/>
+      <c r="AW44" s="59" t="n"/>
+      <c r="AX44" s="17" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="23">
@@ -5954,7 +6067,7 @@
       <c r="M45" s="17" t="n"/>
       <c r="N45" s="17" t="n"/>
       <c r="O45" s="23">
-        <f>IF($B45="","",IF($I45="なし","あり",IF($I45="あり",IF(OR($K45="更新の可能性あり",AND($J45&lt;&gt;"",$G45&lt;&gt;"",$J45-$G45+1&gt;62)),"あり","なし"),"")))</f>
+        <f>IF($B45="","",IF($I45="なし","あり",IF($I45&lt;&gt;"あり","",IF($K45="更新の可能性あり","あり",IF(OR($J45="",$G45=""),"なし",IF(OR(NOT(ISNUMBER($G45)),NOT(ISNUMBER($J45)),$G45&gt;80000,$J45&gt;80000),"要確認（日付）",IF($J45&gt;IF(DAY(EDATE($G45,2))&lt;DAY($G45),EOMONTH($G45,2),EDATE($G45,2)-1),"あり","なし"))))))</f>
         <v/>
       </c>
       <c r="P45" s="23">
@@ -5972,7 +6085,7 @@
         <v/>
       </c>
       <c r="X45" s="23">
-        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B45="","",IF(AND($L45&gt;='⓪ 事業所設定'!$C$13*0.75,$M45&gt;='⓪ 事業所設定'!$C$14*0.75,$O45="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L45&gt;=20,$O45="あり",$N45&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S45+$T45)&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
+        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B45="","",IF(AND($L45&gt;='⓪ 事業所設定'!$C$13*0.75,$M45&gt;='⓪ 事業所設定'!$C$14*0.75,$O45="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L45&gt;=20,$O45="あり",$N45&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S45+$T45-N($AW45))&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
         <v/>
       </c>
       <c r="Y45" s="23">
@@ -5980,7 +6093,7 @@
         <v/>
       </c>
       <c r="Z45" s="23">
-        <f>IF($B45="","",IF(AND($L45&gt;=20,$P45="あり",$N45&lt;&gt;"昼間部の学生"),"加入","加入対象外"))</f>
+        <f>IF($B45="","",IF($H45="役員","対象外（兼務役員なら要相談）",IF(AND($L45&gt;=20,$P45="あり",$N45&lt;&gt;"昼間部の学生"),"加入","加入対象外")))</f>
         <v/>
       </c>
       <c r="AA45" s="61" t="n"/>
@@ -6002,13 +6115,16 @@
       <c r="AQ45" s="17" t="n"/>
       <c r="AR45" s="17" t="n"/>
       <c r="AT45">
-        <f>IF($B45="","",IF($B45="",1,0)+IF($C45="",1,0)+IF($D45="",1,0)+IF($E45="",1,0)+IF($G45="",1,0)+IF($H45="",1,0)+IF($I45="",1,0)+IF($L45="",1,0)+IF($M45="",1,0)+IF($N45="",1,0)+IF($Q45="",1,0)+IF($S45="",1,0)+IF($AA45="",1,0)+IF($AC45="",1,0)+IF($AG45="",1,0)+IF($AH45="",1,0)+IF($AI45="",1,0)+IF($AL45="",1,0)+IF($AP45="",1,0)+IF($AQ45="",1,0)+IF(AND($I45="あり",$J45=""),1,0)+IF(AND($I45="あり",$K45=""),1,0)+IF(AND($AA45="",$AB45=""),1,0)+IF(AND($AC45="あり",$AD45=""),1,0)+IF(AND($AC45="あり",OR($AD45="",$AD45="後日提出"),$AE45=""),1,0))</f>
+        <f>IF($B45="","",IF($B45="",1,0)+IF($C45="",1,0)+IF($D45="",1,0)+IF($E45="",1,0)+IF($G45="",1,0)+IF($H45="",1,0)+IF($I45="",1,0)+IF($L45="",1,0)+IF($M45="",1,0)+IF($N45="",1,0)+IF($Q45="",1,0)+IF($S45="",1,0)+IF($AA45="",1,0)+IF($AC45="",1,0)+IF($AG45="",1,0)+IF($AH45="",1,0)+IF($AI45="",1,0)+IF($AL45="",1,0)+IF($AP45="",1,0)+IF($AQ45="",1,0)+IF(AND($I45="あり",$J45=""),1,0)+IF(AND($I45="あり",$K45=""),1,0)+IF(AND($AA45="",$AB45=""),1,0)+IF(AND($AC45="あり",$AD45=""),1,0)+IF(AND($AC45="あり",OR($AD45="",$AD45="後日提出"),$AE45=""),1,0)+IF($AV45="",1,0)+IF(AND($AL45="外国",$AM45=""),1,0)+IF(AND($AL45="外国",$AN45=""),1,0)+IF(AND($AL45="外国",$AO45=""),1,0))</f>
         <v/>
       </c>
       <c r="AU45">
         <f>IF($B45="","",IF(AND($AA45&lt;&gt;"",$AA45&lt;&gt;"後日提出",$AA45&lt;&gt;"別経路提出",LEN($AA45)&lt;&gt;12),1,0)+IF(AND($AB45&lt;&gt;"",$AB45&lt;&gt;"後日提出",LEN($AB45)&lt;&gt;10),1,0)+IF(AND($AD45&lt;&gt;"",$AD45&lt;&gt;"後日提出",LEN($AD45)&lt;&gt;11),1,0)+IF(AND($AG45&lt;&gt;"",LEN(SUBSTITUTE($AG45,"-",""))&lt;&gt;7),1,0))</f>
         <v/>
       </c>
+      <c r="AV45" s="17" t="n"/>
+      <c r="AW45" s="59" t="n"/>
+      <c r="AX45" s="17" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="23">
@@ -6032,7 +6148,7 @@
       <c r="M46" s="17" t="n"/>
       <c r="N46" s="17" t="n"/>
       <c r="O46" s="23">
-        <f>IF($B46="","",IF($I46="なし","あり",IF($I46="あり",IF(OR($K46="更新の可能性あり",AND($J46&lt;&gt;"",$G46&lt;&gt;"",$J46-$G46+1&gt;62)),"あり","なし"),"")))</f>
+        <f>IF($B46="","",IF($I46="なし","あり",IF($I46&lt;&gt;"あり","",IF($K46="更新の可能性あり","あり",IF(OR($J46="",$G46=""),"なし",IF(OR(NOT(ISNUMBER($G46)),NOT(ISNUMBER($J46)),$G46&gt;80000,$J46&gt;80000),"要確認（日付）",IF($J46&gt;IF(DAY(EDATE($G46,2))&lt;DAY($G46),EOMONTH($G46,2),EDATE($G46,2)-1),"あり","なし"))))))</f>
         <v/>
       </c>
       <c r="P46" s="23">
@@ -6050,7 +6166,7 @@
         <v/>
       </c>
       <c r="X46" s="23">
-        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B46="","",IF(AND($L46&gt;='⓪ 事業所設定'!$C$13*0.75,$M46&gt;='⓪ 事業所設定'!$C$14*0.75,$O46="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L46&gt;=20,$O46="あり",$N46&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S46+$T46)&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
+        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B46="","",IF(AND($L46&gt;='⓪ 事業所設定'!$C$13*0.75,$M46&gt;='⓪ 事業所設定'!$C$14*0.75,$O46="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L46&gt;=20,$O46="あり",$N46&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S46+$T46-N($AW46))&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
         <v/>
       </c>
       <c r="Y46" s="23">
@@ -6058,7 +6174,7 @@
         <v/>
       </c>
       <c r="Z46" s="23">
-        <f>IF($B46="","",IF(AND($L46&gt;=20,$P46="あり",$N46&lt;&gt;"昼間部の学生"),"加入","加入対象外"))</f>
+        <f>IF($B46="","",IF($H46="役員","対象外（兼務役員なら要相談）",IF(AND($L46&gt;=20,$P46="あり",$N46&lt;&gt;"昼間部の学生"),"加入","加入対象外")))</f>
         <v/>
       </c>
       <c r="AA46" s="61" t="n"/>
@@ -6080,13 +6196,16 @@
       <c r="AQ46" s="17" t="n"/>
       <c r="AR46" s="17" t="n"/>
       <c r="AT46">
-        <f>IF($B46="","",IF($B46="",1,0)+IF($C46="",1,0)+IF($D46="",1,0)+IF($E46="",1,0)+IF($G46="",1,0)+IF($H46="",1,0)+IF($I46="",1,0)+IF($L46="",1,0)+IF($M46="",1,0)+IF($N46="",1,0)+IF($Q46="",1,0)+IF($S46="",1,0)+IF($AA46="",1,0)+IF($AC46="",1,0)+IF($AG46="",1,0)+IF($AH46="",1,0)+IF($AI46="",1,0)+IF($AL46="",1,0)+IF($AP46="",1,0)+IF($AQ46="",1,0)+IF(AND($I46="あり",$J46=""),1,0)+IF(AND($I46="あり",$K46=""),1,0)+IF(AND($AA46="",$AB46=""),1,0)+IF(AND($AC46="あり",$AD46=""),1,0)+IF(AND($AC46="あり",OR($AD46="",$AD46="後日提出"),$AE46=""),1,0))</f>
+        <f>IF($B46="","",IF($B46="",1,0)+IF($C46="",1,0)+IF($D46="",1,0)+IF($E46="",1,0)+IF($G46="",1,0)+IF($H46="",1,0)+IF($I46="",1,0)+IF($L46="",1,0)+IF($M46="",1,0)+IF($N46="",1,0)+IF($Q46="",1,0)+IF($S46="",1,0)+IF($AA46="",1,0)+IF($AC46="",1,0)+IF($AG46="",1,0)+IF($AH46="",1,0)+IF($AI46="",1,0)+IF($AL46="",1,0)+IF($AP46="",1,0)+IF($AQ46="",1,0)+IF(AND($I46="あり",$J46=""),1,0)+IF(AND($I46="あり",$K46=""),1,0)+IF(AND($AA46="",$AB46=""),1,0)+IF(AND($AC46="あり",$AD46=""),1,0)+IF(AND($AC46="あり",OR($AD46="",$AD46="後日提出"),$AE46=""),1,0)+IF($AV46="",1,0)+IF(AND($AL46="外国",$AM46=""),1,0)+IF(AND($AL46="外国",$AN46=""),1,0)+IF(AND($AL46="外国",$AO46=""),1,0))</f>
         <v/>
       </c>
       <c r="AU46">
         <f>IF($B46="","",IF(AND($AA46&lt;&gt;"",$AA46&lt;&gt;"後日提出",$AA46&lt;&gt;"別経路提出",LEN($AA46)&lt;&gt;12),1,0)+IF(AND($AB46&lt;&gt;"",$AB46&lt;&gt;"後日提出",LEN($AB46)&lt;&gt;10),1,0)+IF(AND($AD46&lt;&gt;"",$AD46&lt;&gt;"後日提出",LEN($AD46)&lt;&gt;11),1,0)+IF(AND($AG46&lt;&gt;"",LEN(SUBSTITUTE($AG46,"-",""))&lt;&gt;7),1,0))</f>
         <v/>
       </c>
+      <c r="AV46" s="17" t="n"/>
+      <c r="AW46" s="59" t="n"/>
+      <c r="AX46" s="17" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="23">
@@ -6110,7 +6229,7 @@
       <c r="M47" s="17" t="n"/>
       <c r="N47" s="17" t="n"/>
       <c r="O47" s="23">
-        <f>IF($B47="","",IF($I47="なし","あり",IF($I47="あり",IF(OR($K47="更新の可能性あり",AND($J47&lt;&gt;"",$G47&lt;&gt;"",$J47-$G47+1&gt;62)),"あり","なし"),"")))</f>
+        <f>IF($B47="","",IF($I47="なし","あり",IF($I47&lt;&gt;"あり","",IF($K47="更新の可能性あり","あり",IF(OR($J47="",$G47=""),"なし",IF(OR(NOT(ISNUMBER($G47)),NOT(ISNUMBER($J47)),$G47&gt;80000,$J47&gt;80000),"要確認（日付）",IF($J47&gt;IF(DAY(EDATE($G47,2))&lt;DAY($G47),EOMONTH($G47,2),EDATE($G47,2)-1),"あり","なし"))))))</f>
         <v/>
       </c>
       <c r="P47" s="23">
@@ -6128,7 +6247,7 @@
         <v/>
       </c>
       <c r="X47" s="23">
-        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B47="","",IF(AND($L47&gt;='⓪ 事業所設定'!$C$13*0.75,$M47&gt;='⓪ 事業所設定'!$C$14*0.75,$O47="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L47&gt;=20,$O47="あり",$N47&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S47+$T47)&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
+        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B47="","",IF(AND($L47&gt;='⓪ 事業所設定'!$C$13*0.75,$M47&gt;='⓪ 事業所設定'!$C$14*0.75,$O47="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L47&gt;=20,$O47="あり",$N47&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S47+$T47-N($AW47))&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
         <v/>
       </c>
       <c r="Y47" s="23">
@@ -6136,7 +6255,7 @@
         <v/>
       </c>
       <c r="Z47" s="23">
-        <f>IF($B47="","",IF(AND($L47&gt;=20,$P47="あり",$N47&lt;&gt;"昼間部の学生"),"加入","加入対象外"))</f>
+        <f>IF($B47="","",IF($H47="役員","対象外（兼務役員なら要相談）",IF(AND($L47&gt;=20,$P47="あり",$N47&lt;&gt;"昼間部の学生"),"加入","加入対象外")))</f>
         <v/>
       </c>
       <c r="AA47" s="61" t="n"/>
@@ -6158,13 +6277,16 @@
       <c r="AQ47" s="17" t="n"/>
       <c r="AR47" s="17" t="n"/>
       <c r="AT47">
-        <f>IF($B47="","",IF($B47="",1,0)+IF($C47="",1,0)+IF($D47="",1,0)+IF($E47="",1,0)+IF($G47="",1,0)+IF($H47="",1,0)+IF($I47="",1,0)+IF($L47="",1,0)+IF($M47="",1,0)+IF($N47="",1,0)+IF($Q47="",1,0)+IF($S47="",1,0)+IF($AA47="",1,0)+IF($AC47="",1,0)+IF($AG47="",1,0)+IF($AH47="",1,0)+IF($AI47="",1,0)+IF($AL47="",1,0)+IF($AP47="",1,0)+IF($AQ47="",1,0)+IF(AND($I47="あり",$J47=""),1,0)+IF(AND($I47="あり",$K47=""),1,0)+IF(AND($AA47="",$AB47=""),1,0)+IF(AND($AC47="あり",$AD47=""),1,0)+IF(AND($AC47="あり",OR($AD47="",$AD47="後日提出"),$AE47=""),1,0))</f>
+        <f>IF($B47="","",IF($B47="",1,0)+IF($C47="",1,0)+IF($D47="",1,0)+IF($E47="",1,0)+IF($G47="",1,0)+IF($H47="",1,0)+IF($I47="",1,0)+IF($L47="",1,0)+IF($M47="",1,0)+IF($N47="",1,0)+IF($Q47="",1,0)+IF($S47="",1,0)+IF($AA47="",1,0)+IF($AC47="",1,0)+IF($AG47="",1,0)+IF($AH47="",1,0)+IF($AI47="",1,0)+IF($AL47="",1,0)+IF($AP47="",1,0)+IF($AQ47="",1,0)+IF(AND($I47="あり",$J47=""),1,0)+IF(AND($I47="あり",$K47=""),1,0)+IF(AND($AA47="",$AB47=""),1,0)+IF(AND($AC47="あり",$AD47=""),1,0)+IF(AND($AC47="あり",OR($AD47="",$AD47="後日提出"),$AE47=""),1,0)+IF($AV47="",1,0)+IF(AND($AL47="外国",$AM47=""),1,0)+IF(AND($AL47="外国",$AN47=""),1,0)+IF(AND($AL47="外国",$AO47=""),1,0))</f>
         <v/>
       </c>
       <c r="AU47">
         <f>IF($B47="","",IF(AND($AA47&lt;&gt;"",$AA47&lt;&gt;"後日提出",$AA47&lt;&gt;"別経路提出",LEN($AA47)&lt;&gt;12),1,0)+IF(AND($AB47&lt;&gt;"",$AB47&lt;&gt;"後日提出",LEN($AB47)&lt;&gt;10),1,0)+IF(AND($AD47&lt;&gt;"",$AD47&lt;&gt;"後日提出",LEN($AD47)&lt;&gt;11),1,0)+IF(AND($AG47&lt;&gt;"",LEN(SUBSTITUTE($AG47,"-",""))&lt;&gt;7),1,0))</f>
         <v/>
       </c>
+      <c r="AV47" s="17" t="n"/>
+      <c r="AW47" s="59" t="n"/>
+      <c r="AX47" s="17" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="23">
@@ -6188,7 +6310,7 @@
       <c r="M48" s="17" t="n"/>
       <c r="N48" s="17" t="n"/>
       <c r="O48" s="23">
-        <f>IF($B48="","",IF($I48="なし","あり",IF($I48="あり",IF(OR($K48="更新の可能性あり",AND($J48&lt;&gt;"",$G48&lt;&gt;"",$J48-$G48+1&gt;62)),"あり","なし"),"")))</f>
+        <f>IF($B48="","",IF($I48="なし","あり",IF($I48&lt;&gt;"あり","",IF($K48="更新の可能性あり","あり",IF(OR($J48="",$G48=""),"なし",IF(OR(NOT(ISNUMBER($G48)),NOT(ISNUMBER($J48)),$G48&gt;80000,$J48&gt;80000),"要確認（日付）",IF($J48&gt;IF(DAY(EDATE($G48,2))&lt;DAY($G48),EOMONTH($G48,2),EDATE($G48,2)-1),"あり","なし"))))))</f>
         <v/>
       </c>
       <c r="P48" s="23">
@@ -6206,7 +6328,7 @@
         <v/>
       </c>
       <c r="X48" s="23">
-        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B48="","",IF(AND($L48&gt;='⓪ 事業所設定'!$C$13*0.75,$M48&gt;='⓪ 事業所設定'!$C$14*0.75,$O48="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L48&gt;=20,$O48="あり",$N48&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S48+$T48)&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
+        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B48="","",IF(AND($L48&gt;='⓪ 事業所設定'!$C$13*0.75,$M48&gt;='⓪ 事業所設定'!$C$14*0.75,$O48="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L48&gt;=20,$O48="あり",$N48&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S48+$T48-N($AW48))&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
         <v/>
       </c>
       <c r="Y48" s="23">
@@ -6214,7 +6336,7 @@
         <v/>
       </c>
       <c r="Z48" s="23">
-        <f>IF($B48="","",IF(AND($L48&gt;=20,$P48="あり",$N48&lt;&gt;"昼間部の学生"),"加入","加入対象外"))</f>
+        <f>IF($B48="","",IF($H48="役員","対象外（兼務役員なら要相談）",IF(AND($L48&gt;=20,$P48="あり",$N48&lt;&gt;"昼間部の学生"),"加入","加入対象外")))</f>
         <v/>
       </c>
       <c r="AA48" s="61" t="n"/>
@@ -6236,13 +6358,16 @@
       <c r="AQ48" s="17" t="n"/>
       <c r="AR48" s="17" t="n"/>
       <c r="AT48">
-        <f>IF($B48="","",IF($B48="",1,0)+IF($C48="",1,0)+IF($D48="",1,0)+IF($E48="",1,0)+IF($G48="",1,0)+IF($H48="",1,0)+IF($I48="",1,0)+IF($L48="",1,0)+IF($M48="",1,0)+IF($N48="",1,0)+IF($Q48="",1,0)+IF($S48="",1,0)+IF($AA48="",1,0)+IF($AC48="",1,0)+IF($AG48="",1,0)+IF($AH48="",1,0)+IF($AI48="",1,0)+IF($AL48="",1,0)+IF($AP48="",1,0)+IF($AQ48="",1,0)+IF(AND($I48="あり",$J48=""),1,0)+IF(AND($I48="あり",$K48=""),1,0)+IF(AND($AA48="",$AB48=""),1,0)+IF(AND($AC48="あり",$AD48=""),1,0)+IF(AND($AC48="あり",OR($AD48="",$AD48="後日提出"),$AE48=""),1,0))</f>
+        <f>IF($B48="","",IF($B48="",1,0)+IF($C48="",1,0)+IF($D48="",1,0)+IF($E48="",1,0)+IF($G48="",1,0)+IF($H48="",1,0)+IF($I48="",1,0)+IF($L48="",1,0)+IF($M48="",1,0)+IF($N48="",1,0)+IF($Q48="",1,0)+IF($S48="",1,0)+IF($AA48="",1,0)+IF($AC48="",1,0)+IF($AG48="",1,0)+IF($AH48="",1,0)+IF($AI48="",1,0)+IF($AL48="",1,0)+IF($AP48="",1,0)+IF($AQ48="",1,0)+IF(AND($I48="あり",$J48=""),1,0)+IF(AND($I48="あり",$K48=""),1,0)+IF(AND($AA48="",$AB48=""),1,0)+IF(AND($AC48="あり",$AD48=""),1,0)+IF(AND($AC48="あり",OR($AD48="",$AD48="後日提出"),$AE48=""),1,0)+IF($AV48="",1,0)+IF(AND($AL48="外国",$AM48=""),1,0)+IF(AND($AL48="外国",$AN48=""),1,0)+IF(AND($AL48="外国",$AO48=""),1,0))</f>
         <v/>
       </c>
       <c r="AU48">
         <f>IF($B48="","",IF(AND($AA48&lt;&gt;"",$AA48&lt;&gt;"後日提出",$AA48&lt;&gt;"別経路提出",LEN($AA48)&lt;&gt;12),1,0)+IF(AND($AB48&lt;&gt;"",$AB48&lt;&gt;"後日提出",LEN($AB48)&lt;&gt;10),1,0)+IF(AND($AD48&lt;&gt;"",$AD48&lt;&gt;"後日提出",LEN($AD48)&lt;&gt;11),1,0)+IF(AND($AG48&lt;&gt;"",LEN(SUBSTITUTE($AG48,"-",""))&lt;&gt;7),1,0))</f>
         <v/>
       </c>
+      <c r="AV48" s="17" t="n"/>
+      <c r="AW48" s="59" t="n"/>
+      <c r="AX48" s="17" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="23">
@@ -6266,7 +6391,7 @@
       <c r="M49" s="17" t="n"/>
       <c r="N49" s="17" t="n"/>
       <c r="O49" s="23">
-        <f>IF($B49="","",IF($I49="なし","あり",IF($I49="あり",IF(OR($K49="更新の可能性あり",AND($J49&lt;&gt;"",$G49&lt;&gt;"",$J49-$G49+1&gt;62)),"あり","なし"),"")))</f>
+        <f>IF($B49="","",IF($I49="なし","あり",IF($I49&lt;&gt;"あり","",IF($K49="更新の可能性あり","あり",IF(OR($J49="",$G49=""),"なし",IF(OR(NOT(ISNUMBER($G49)),NOT(ISNUMBER($J49)),$G49&gt;80000,$J49&gt;80000),"要確認（日付）",IF($J49&gt;IF(DAY(EDATE($G49,2))&lt;DAY($G49),EOMONTH($G49,2),EDATE($G49,2)-1),"あり","なし"))))))</f>
         <v/>
       </c>
       <c r="P49" s="23">
@@ -6284,7 +6409,7 @@
         <v/>
       </c>
       <c r="X49" s="23">
-        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B49="","",IF(AND($L49&gt;='⓪ 事業所設定'!$C$13*0.75,$M49&gt;='⓪ 事業所設定'!$C$14*0.75,$O49="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L49&gt;=20,$O49="あり",$N49&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S49+$T49)&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
+        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B49="","",IF(AND($L49&gt;='⓪ 事業所設定'!$C$13*0.75,$M49&gt;='⓪ 事業所設定'!$C$14*0.75,$O49="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L49&gt;=20,$O49="あり",$N49&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S49+$T49-N($AW49))&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
         <v/>
       </c>
       <c r="Y49" s="23">
@@ -6292,7 +6417,7 @@
         <v/>
       </c>
       <c r="Z49" s="23">
-        <f>IF($B49="","",IF(AND($L49&gt;=20,$P49="あり",$N49&lt;&gt;"昼間部の学生"),"加入","加入対象外"))</f>
+        <f>IF($B49="","",IF($H49="役員","対象外（兼務役員なら要相談）",IF(AND($L49&gt;=20,$P49="あり",$N49&lt;&gt;"昼間部の学生"),"加入","加入対象外")))</f>
         <v/>
       </c>
       <c r="AA49" s="61" t="n"/>
@@ -6314,13 +6439,16 @@
       <c r="AQ49" s="17" t="n"/>
       <c r="AR49" s="17" t="n"/>
       <c r="AT49">
-        <f>IF($B49="","",IF($B49="",1,0)+IF($C49="",1,0)+IF($D49="",1,0)+IF($E49="",1,0)+IF($G49="",1,0)+IF($H49="",1,0)+IF($I49="",1,0)+IF($L49="",1,0)+IF($M49="",1,0)+IF($N49="",1,0)+IF($Q49="",1,0)+IF($S49="",1,0)+IF($AA49="",1,0)+IF($AC49="",1,0)+IF($AG49="",1,0)+IF($AH49="",1,0)+IF($AI49="",1,0)+IF($AL49="",1,0)+IF($AP49="",1,0)+IF($AQ49="",1,0)+IF(AND($I49="あり",$J49=""),1,0)+IF(AND($I49="あり",$K49=""),1,0)+IF(AND($AA49="",$AB49=""),1,0)+IF(AND($AC49="あり",$AD49=""),1,0)+IF(AND($AC49="あり",OR($AD49="",$AD49="後日提出"),$AE49=""),1,0))</f>
+        <f>IF($B49="","",IF($B49="",1,0)+IF($C49="",1,0)+IF($D49="",1,0)+IF($E49="",1,0)+IF($G49="",1,0)+IF($H49="",1,0)+IF($I49="",1,0)+IF($L49="",1,0)+IF($M49="",1,0)+IF($N49="",1,0)+IF($Q49="",1,0)+IF($S49="",1,0)+IF($AA49="",1,0)+IF($AC49="",1,0)+IF($AG49="",1,0)+IF($AH49="",1,0)+IF($AI49="",1,0)+IF($AL49="",1,0)+IF($AP49="",1,0)+IF($AQ49="",1,0)+IF(AND($I49="あり",$J49=""),1,0)+IF(AND($I49="あり",$K49=""),1,0)+IF(AND($AA49="",$AB49=""),1,0)+IF(AND($AC49="あり",$AD49=""),1,0)+IF(AND($AC49="あり",OR($AD49="",$AD49="後日提出"),$AE49=""),1,0)+IF($AV49="",1,0)+IF(AND($AL49="外国",$AM49=""),1,0)+IF(AND($AL49="外国",$AN49=""),1,0)+IF(AND($AL49="外国",$AO49=""),1,0))</f>
         <v/>
       </c>
       <c r="AU49">
         <f>IF($B49="","",IF(AND($AA49&lt;&gt;"",$AA49&lt;&gt;"後日提出",$AA49&lt;&gt;"別経路提出",LEN($AA49)&lt;&gt;12),1,0)+IF(AND($AB49&lt;&gt;"",$AB49&lt;&gt;"後日提出",LEN($AB49)&lt;&gt;10),1,0)+IF(AND($AD49&lt;&gt;"",$AD49&lt;&gt;"後日提出",LEN($AD49)&lt;&gt;11),1,0)+IF(AND($AG49&lt;&gt;"",LEN(SUBSTITUTE($AG49,"-",""))&lt;&gt;7),1,0))</f>
         <v/>
       </c>
+      <c r="AV49" s="17" t="n"/>
+      <c r="AW49" s="59" t="n"/>
+      <c r="AX49" s="17" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="23">
@@ -6344,7 +6472,7 @@
       <c r="M50" s="17" t="n"/>
       <c r="N50" s="17" t="n"/>
       <c r="O50" s="23">
-        <f>IF($B50="","",IF($I50="なし","あり",IF($I50="あり",IF(OR($K50="更新の可能性あり",AND($J50&lt;&gt;"",$G50&lt;&gt;"",$J50-$G50+1&gt;62)),"あり","なし"),"")))</f>
+        <f>IF($B50="","",IF($I50="なし","あり",IF($I50&lt;&gt;"あり","",IF($K50="更新の可能性あり","あり",IF(OR($J50="",$G50=""),"なし",IF(OR(NOT(ISNUMBER($G50)),NOT(ISNUMBER($J50)),$G50&gt;80000,$J50&gt;80000),"要確認（日付）",IF($J50&gt;IF(DAY(EDATE($G50,2))&lt;DAY($G50),EOMONTH($G50,2),EDATE($G50,2)-1),"あり","なし"))))))</f>
         <v/>
       </c>
       <c r="P50" s="23">
@@ -6362,7 +6490,7 @@
         <v/>
       </c>
       <c r="X50" s="23">
-        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B50="","",IF(AND($L50&gt;='⓪ 事業所設定'!$C$13*0.75,$M50&gt;='⓪ 事業所設定'!$C$14*0.75,$O50="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L50&gt;=20,$O50="あり",$N50&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S50+$T50)&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
+        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B50="","",IF(AND($L50&gt;='⓪ 事業所設定'!$C$13*0.75,$M50&gt;='⓪ 事業所設定'!$C$14*0.75,$O50="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L50&gt;=20,$O50="あり",$N50&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S50+$T50-N($AW50))&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
         <v/>
       </c>
       <c r="Y50" s="23">
@@ -6370,7 +6498,7 @@
         <v/>
       </c>
       <c r="Z50" s="23">
-        <f>IF($B50="","",IF(AND($L50&gt;=20,$P50="あり",$N50&lt;&gt;"昼間部の学生"),"加入","加入対象外"))</f>
+        <f>IF($B50="","",IF($H50="役員","対象外（兼務役員なら要相談）",IF(AND($L50&gt;=20,$P50="あり",$N50&lt;&gt;"昼間部の学生"),"加入","加入対象外")))</f>
         <v/>
       </c>
       <c r="AA50" s="61" t="n"/>
@@ -6392,13 +6520,16 @@
       <c r="AQ50" s="17" t="n"/>
       <c r="AR50" s="17" t="n"/>
       <c r="AT50">
-        <f>IF($B50="","",IF($B50="",1,0)+IF($C50="",1,0)+IF($D50="",1,0)+IF($E50="",1,0)+IF($G50="",1,0)+IF($H50="",1,0)+IF($I50="",1,0)+IF($L50="",1,0)+IF($M50="",1,0)+IF($N50="",1,0)+IF($Q50="",1,0)+IF($S50="",1,0)+IF($AA50="",1,0)+IF($AC50="",1,0)+IF($AG50="",1,0)+IF($AH50="",1,0)+IF($AI50="",1,0)+IF($AL50="",1,0)+IF($AP50="",1,0)+IF($AQ50="",1,0)+IF(AND($I50="あり",$J50=""),1,0)+IF(AND($I50="あり",$K50=""),1,0)+IF(AND($AA50="",$AB50=""),1,0)+IF(AND($AC50="あり",$AD50=""),1,0)+IF(AND($AC50="あり",OR($AD50="",$AD50="後日提出"),$AE50=""),1,0))</f>
+        <f>IF($B50="","",IF($B50="",1,0)+IF($C50="",1,0)+IF($D50="",1,0)+IF($E50="",1,0)+IF($G50="",1,0)+IF($H50="",1,0)+IF($I50="",1,0)+IF($L50="",1,0)+IF($M50="",1,0)+IF($N50="",1,0)+IF($Q50="",1,0)+IF($S50="",1,0)+IF($AA50="",1,0)+IF($AC50="",1,0)+IF($AG50="",1,0)+IF($AH50="",1,0)+IF($AI50="",1,0)+IF($AL50="",1,0)+IF($AP50="",1,0)+IF($AQ50="",1,0)+IF(AND($I50="あり",$J50=""),1,0)+IF(AND($I50="あり",$K50=""),1,0)+IF(AND($AA50="",$AB50=""),1,0)+IF(AND($AC50="あり",$AD50=""),1,0)+IF(AND($AC50="あり",OR($AD50="",$AD50="後日提出"),$AE50=""),1,0)+IF($AV50="",1,0)+IF(AND($AL50="外国",$AM50=""),1,0)+IF(AND($AL50="外国",$AN50=""),1,0)+IF(AND($AL50="外国",$AO50=""),1,0))</f>
         <v/>
       </c>
       <c r="AU50">
         <f>IF($B50="","",IF(AND($AA50&lt;&gt;"",$AA50&lt;&gt;"後日提出",$AA50&lt;&gt;"別経路提出",LEN($AA50)&lt;&gt;12),1,0)+IF(AND($AB50&lt;&gt;"",$AB50&lt;&gt;"後日提出",LEN($AB50)&lt;&gt;10),1,0)+IF(AND($AD50&lt;&gt;"",$AD50&lt;&gt;"後日提出",LEN($AD50)&lt;&gt;11),1,0)+IF(AND($AG50&lt;&gt;"",LEN(SUBSTITUTE($AG50,"-",""))&lt;&gt;7),1,0))</f>
         <v/>
       </c>
+      <c r="AV50" s="17" t="n"/>
+      <c r="AW50" s="59" t="n"/>
+      <c r="AX50" s="17" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="23">
@@ -6422,7 +6553,7 @@
       <c r="M51" s="17" t="n"/>
       <c r="N51" s="17" t="n"/>
       <c r="O51" s="23">
-        <f>IF($B51="","",IF($I51="なし","あり",IF($I51="あり",IF(OR($K51="更新の可能性あり",AND($J51&lt;&gt;"",$G51&lt;&gt;"",$J51-$G51+1&gt;62)),"あり","なし"),"")))</f>
+        <f>IF($B51="","",IF($I51="なし","あり",IF($I51&lt;&gt;"あり","",IF($K51="更新の可能性あり","あり",IF(OR($J51="",$G51=""),"なし",IF(OR(NOT(ISNUMBER($G51)),NOT(ISNUMBER($J51)),$G51&gt;80000,$J51&gt;80000),"要確認（日付）",IF($J51&gt;IF(DAY(EDATE($G51,2))&lt;DAY($G51),EOMONTH($G51,2),EDATE($G51,2)-1),"あり","なし"))))))</f>
         <v/>
       </c>
       <c r="P51" s="23">
@@ -6440,7 +6571,7 @@
         <v/>
       </c>
       <c r="X51" s="23">
-        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B51="","",IF(AND($L51&gt;='⓪ 事業所設定'!$C$13*0.75,$M51&gt;='⓪ 事業所設定'!$C$14*0.75,$O51="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L51&gt;=20,$O51="あり",$N51&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S51+$T51)&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
+        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B51="","",IF(AND($L51&gt;='⓪ 事業所設定'!$C$13*0.75,$M51&gt;='⓪ 事業所設定'!$C$14*0.75,$O51="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L51&gt;=20,$O51="あり",$N51&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S51+$T51-N($AW51))&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
         <v/>
       </c>
       <c r="Y51" s="23">
@@ -6448,7 +6579,7 @@
         <v/>
       </c>
       <c r="Z51" s="23">
-        <f>IF($B51="","",IF(AND($L51&gt;=20,$P51="あり",$N51&lt;&gt;"昼間部の学生"),"加入","加入対象外"))</f>
+        <f>IF($B51="","",IF($H51="役員","対象外（兼務役員なら要相談）",IF(AND($L51&gt;=20,$P51="あり",$N51&lt;&gt;"昼間部の学生"),"加入","加入対象外")))</f>
         <v/>
       </c>
       <c r="AA51" s="61" t="n"/>
@@ -6470,13 +6601,16 @@
       <c r="AQ51" s="17" t="n"/>
       <c r="AR51" s="17" t="n"/>
       <c r="AT51">
-        <f>IF($B51="","",IF($B51="",1,0)+IF($C51="",1,0)+IF($D51="",1,0)+IF($E51="",1,0)+IF($G51="",1,0)+IF($H51="",1,0)+IF($I51="",1,0)+IF($L51="",1,0)+IF($M51="",1,0)+IF($N51="",1,0)+IF($Q51="",1,0)+IF($S51="",1,0)+IF($AA51="",1,0)+IF($AC51="",1,0)+IF($AG51="",1,0)+IF($AH51="",1,0)+IF($AI51="",1,0)+IF($AL51="",1,0)+IF($AP51="",1,0)+IF($AQ51="",1,0)+IF(AND($I51="あり",$J51=""),1,0)+IF(AND($I51="あり",$K51=""),1,0)+IF(AND($AA51="",$AB51=""),1,0)+IF(AND($AC51="あり",$AD51=""),1,0)+IF(AND($AC51="あり",OR($AD51="",$AD51="後日提出"),$AE51=""),1,0))</f>
+        <f>IF($B51="","",IF($B51="",1,0)+IF($C51="",1,0)+IF($D51="",1,0)+IF($E51="",1,0)+IF($G51="",1,0)+IF($H51="",1,0)+IF($I51="",1,0)+IF($L51="",1,0)+IF($M51="",1,0)+IF($N51="",1,0)+IF($Q51="",1,0)+IF($S51="",1,0)+IF($AA51="",1,0)+IF($AC51="",1,0)+IF($AG51="",1,0)+IF($AH51="",1,0)+IF($AI51="",1,0)+IF($AL51="",1,0)+IF($AP51="",1,0)+IF($AQ51="",1,0)+IF(AND($I51="あり",$J51=""),1,0)+IF(AND($I51="あり",$K51=""),1,0)+IF(AND($AA51="",$AB51=""),1,0)+IF(AND($AC51="あり",$AD51=""),1,0)+IF(AND($AC51="あり",OR($AD51="",$AD51="後日提出"),$AE51=""),1,0)+IF($AV51="",1,0)+IF(AND($AL51="外国",$AM51=""),1,0)+IF(AND($AL51="外国",$AN51=""),1,0)+IF(AND($AL51="外国",$AO51=""),1,0))</f>
         <v/>
       </c>
       <c r="AU51">
         <f>IF($B51="","",IF(AND($AA51&lt;&gt;"",$AA51&lt;&gt;"後日提出",$AA51&lt;&gt;"別経路提出",LEN($AA51)&lt;&gt;12),1,0)+IF(AND($AB51&lt;&gt;"",$AB51&lt;&gt;"後日提出",LEN($AB51)&lt;&gt;10),1,0)+IF(AND($AD51&lt;&gt;"",$AD51&lt;&gt;"後日提出",LEN($AD51)&lt;&gt;11),1,0)+IF(AND($AG51&lt;&gt;"",LEN(SUBSTITUTE($AG51,"-",""))&lt;&gt;7),1,0))</f>
         <v/>
       </c>
+      <c r="AV51" s="17" t="n"/>
+      <c r="AW51" s="59" t="n"/>
+      <c r="AX51" s="17" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="23">
@@ -6500,7 +6634,7 @@
       <c r="M52" s="17" t="n"/>
       <c r="N52" s="17" t="n"/>
       <c r="O52" s="23">
-        <f>IF($B52="","",IF($I52="なし","あり",IF($I52="あり",IF(OR($K52="更新の可能性あり",AND($J52&lt;&gt;"",$G52&lt;&gt;"",$J52-$G52+1&gt;62)),"あり","なし"),"")))</f>
+        <f>IF($B52="","",IF($I52="なし","あり",IF($I52&lt;&gt;"あり","",IF($K52="更新の可能性あり","あり",IF(OR($J52="",$G52=""),"なし",IF(OR(NOT(ISNUMBER($G52)),NOT(ISNUMBER($J52)),$G52&gt;80000,$J52&gt;80000),"要確認（日付）",IF($J52&gt;IF(DAY(EDATE($G52,2))&lt;DAY($G52),EOMONTH($G52,2),EDATE($G52,2)-1),"あり","なし"))))))</f>
         <v/>
       </c>
       <c r="P52" s="23">
@@ -6518,7 +6652,7 @@
         <v/>
       </c>
       <c r="X52" s="23">
-        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B52="","",IF(AND($L52&gt;='⓪ 事業所設定'!$C$13*0.75,$M52&gt;='⓪ 事業所設定'!$C$14*0.75,$O52="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L52&gt;=20,$O52="あり",$N52&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S52+$T52)&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
+        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B52="","",IF(AND($L52&gt;='⓪ 事業所設定'!$C$13*0.75,$M52&gt;='⓪ 事業所設定'!$C$14*0.75,$O52="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L52&gt;=20,$O52="あり",$N52&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S52+$T52-N($AW52))&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
         <v/>
       </c>
       <c r="Y52" s="23">
@@ -6526,7 +6660,7 @@
         <v/>
       </c>
       <c r="Z52" s="23">
-        <f>IF($B52="","",IF(AND($L52&gt;=20,$P52="あり",$N52&lt;&gt;"昼間部の学生"),"加入","加入対象外"))</f>
+        <f>IF($B52="","",IF($H52="役員","対象外（兼務役員なら要相談）",IF(AND($L52&gt;=20,$P52="あり",$N52&lt;&gt;"昼間部の学生"),"加入","加入対象外")))</f>
         <v/>
       </c>
       <c r="AA52" s="61" t="n"/>
@@ -6548,13 +6682,16 @@
       <c r="AQ52" s="17" t="n"/>
       <c r="AR52" s="17" t="n"/>
       <c r="AT52">
-        <f>IF($B52="","",IF($B52="",1,0)+IF($C52="",1,0)+IF($D52="",1,0)+IF($E52="",1,0)+IF($G52="",1,0)+IF($H52="",1,0)+IF($I52="",1,0)+IF($L52="",1,0)+IF($M52="",1,0)+IF($N52="",1,0)+IF($Q52="",1,0)+IF($S52="",1,0)+IF($AA52="",1,0)+IF($AC52="",1,0)+IF($AG52="",1,0)+IF($AH52="",1,0)+IF($AI52="",1,0)+IF($AL52="",1,0)+IF($AP52="",1,0)+IF($AQ52="",1,0)+IF(AND($I52="あり",$J52=""),1,0)+IF(AND($I52="あり",$K52=""),1,0)+IF(AND($AA52="",$AB52=""),1,0)+IF(AND($AC52="あり",$AD52=""),1,0)+IF(AND($AC52="あり",OR($AD52="",$AD52="後日提出"),$AE52=""),1,0))</f>
+        <f>IF($B52="","",IF($B52="",1,0)+IF($C52="",1,0)+IF($D52="",1,0)+IF($E52="",1,0)+IF($G52="",1,0)+IF($H52="",1,0)+IF($I52="",1,0)+IF($L52="",1,0)+IF($M52="",1,0)+IF($N52="",1,0)+IF($Q52="",1,0)+IF($S52="",1,0)+IF($AA52="",1,0)+IF($AC52="",1,0)+IF($AG52="",1,0)+IF($AH52="",1,0)+IF($AI52="",1,0)+IF($AL52="",1,0)+IF($AP52="",1,0)+IF($AQ52="",1,0)+IF(AND($I52="あり",$J52=""),1,0)+IF(AND($I52="あり",$K52=""),1,0)+IF(AND($AA52="",$AB52=""),1,0)+IF(AND($AC52="あり",$AD52=""),1,0)+IF(AND($AC52="あり",OR($AD52="",$AD52="後日提出"),$AE52=""),1,0)+IF($AV52="",1,0)+IF(AND($AL52="外国",$AM52=""),1,0)+IF(AND($AL52="外国",$AN52=""),1,0)+IF(AND($AL52="外国",$AO52=""),1,0))</f>
         <v/>
       </c>
       <c r="AU52">
         <f>IF($B52="","",IF(AND($AA52&lt;&gt;"",$AA52&lt;&gt;"後日提出",$AA52&lt;&gt;"別経路提出",LEN($AA52)&lt;&gt;12),1,0)+IF(AND($AB52&lt;&gt;"",$AB52&lt;&gt;"後日提出",LEN($AB52)&lt;&gt;10),1,0)+IF(AND($AD52&lt;&gt;"",$AD52&lt;&gt;"後日提出",LEN($AD52)&lt;&gt;11),1,0)+IF(AND($AG52&lt;&gt;"",LEN(SUBSTITUTE($AG52,"-",""))&lt;&gt;7),1,0))</f>
         <v/>
       </c>
+      <c r="AV52" s="17" t="n"/>
+      <c r="AW52" s="59" t="n"/>
+      <c r="AX52" s="17" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="23">
@@ -6578,7 +6715,7 @@
       <c r="M53" s="17" t="n"/>
       <c r="N53" s="17" t="n"/>
       <c r="O53" s="23">
-        <f>IF($B53="","",IF($I53="なし","あり",IF($I53="あり",IF(OR($K53="更新の可能性あり",AND($J53&lt;&gt;"",$G53&lt;&gt;"",$J53-$G53+1&gt;62)),"あり","なし"),"")))</f>
+        <f>IF($B53="","",IF($I53="なし","あり",IF($I53&lt;&gt;"あり","",IF($K53="更新の可能性あり","あり",IF(OR($J53="",$G53=""),"なし",IF(OR(NOT(ISNUMBER($G53)),NOT(ISNUMBER($J53)),$G53&gt;80000,$J53&gt;80000),"要確認（日付）",IF($J53&gt;IF(DAY(EDATE($G53,2))&lt;DAY($G53),EOMONTH($G53,2),EDATE($G53,2)-1),"あり","なし"))))))</f>
         <v/>
       </c>
       <c r="P53" s="23">
@@ -6596,7 +6733,7 @@
         <v/>
       </c>
       <c r="X53" s="23">
-        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B53="","",IF(AND($L53&gt;='⓪ 事業所設定'!$C$13*0.75,$M53&gt;='⓪ 事業所設定'!$C$14*0.75,$O53="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L53&gt;=20,$O53="あり",$N53&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S53+$T53)&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
+        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B53="","",IF(AND($L53&gt;='⓪ 事業所設定'!$C$13*0.75,$M53&gt;='⓪ 事業所設定'!$C$14*0.75,$O53="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L53&gt;=20,$O53="あり",$N53&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S53+$T53-N($AW53))&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
         <v/>
       </c>
       <c r="Y53" s="23">
@@ -6604,7 +6741,7 @@
         <v/>
       </c>
       <c r="Z53" s="23">
-        <f>IF($B53="","",IF(AND($L53&gt;=20,$P53="あり",$N53&lt;&gt;"昼間部の学生"),"加入","加入対象外"))</f>
+        <f>IF($B53="","",IF($H53="役員","対象外（兼務役員なら要相談）",IF(AND($L53&gt;=20,$P53="あり",$N53&lt;&gt;"昼間部の学生"),"加入","加入対象外")))</f>
         <v/>
       </c>
       <c r="AA53" s="61" t="n"/>
@@ -6626,13 +6763,16 @@
       <c r="AQ53" s="17" t="n"/>
       <c r="AR53" s="17" t="n"/>
       <c r="AT53">
-        <f>IF($B53="","",IF($B53="",1,0)+IF($C53="",1,0)+IF($D53="",1,0)+IF($E53="",1,0)+IF($G53="",1,0)+IF($H53="",1,0)+IF($I53="",1,0)+IF($L53="",1,0)+IF($M53="",1,0)+IF($N53="",1,0)+IF($Q53="",1,0)+IF($S53="",1,0)+IF($AA53="",1,0)+IF($AC53="",1,0)+IF($AG53="",1,0)+IF($AH53="",1,0)+IF($AI53="",1,0)+IF($AL53="",1,0)+IF($AP53="",1,0)+IF($AQ53="",1,0)+IF(AND($I53="あり",$J53=""),1,0)+IF(AND($I53="あり",$K53=""),1,0)+IF(AND($AA53="",$AB53=""),1,0)+IF(AND($AC53="あり",$AD53=""),1,0)+IF(AND($AC53="あり",OR($AD53="",$AD53="後日提出"),$AE53=""),1,0))</f>
+        <f>IF($B53="","",IF($B53="",1,0)+IF($C53="",1,0)+IF($D53="",1,0)+IF($E53="",1,0)+IF($G53="",1,0)+IF($H53="",1,0)+IF($I53="",1,0)+IF($L53="",1,0)+IF($M53="",1,0)+IF($N53="",1,0)+IF($Q53="",1,0)+IF($S53="",1,0)+IF($AA53="",1,0)+IF($AC53="",1,0)+IF($AG53="",1,0)+IF($AH53="",1,0)+IF($AI53="",1,0)+IF($AL53="",1,0)+IF($AP53="",1,0)+IF($AQ53="",1,0)+IF(AND($I53="あり",$J53=""),1,0)+IF(AND($I53="あり",$K53=""),1,0)+IF(AND($AA53="",$AB53=""),1,0)+IF(AND($AC53="あり",$AD53=""),1,0)+IF(AND($AC53="あり",OR($AD53="",$AD53="後日提出"),$AE53=""),1,0)+IF($AV53="",1,0)+IF(AND($AL53="外国",$AM53=""),1,0)+IF(AND($AL53="外国",$AN53=""),1,0)+IF(AND($AL53="外国",$AO53=""),1,0))</f>
         <v/>
       </c>
       <c r="AU53">
         <f>IF($B53="","",IF(AND($AA53&lt;&gt;"",$AA53&lt;&gt;"後日提出",$AA53&lt;&gt;"別経路提出",LEN($AA53)&lt;&gt;12),1,0)+IF(AND($AB53&lt;&gt;"",$AB53&lt;&gt;"後日提出",LEN($AB53)&lt;&gt;10),1,0)+IF(AND($AD53&lt;&gt;"",$AD53&lt;&gt;"後日提出",LEN($AD53)&lt;&gt;11),1,0)+IF(AND($AG53&lt;&gt;"",LEN(SUBSTITUTE($AG53,"-",""))&lt;&gt;7),1,0))</f>
         <v/>
       </c>
+      <c r="AV53" s="17" t="n"/>
+      <c r="AW53" s="59" t="n"/>
+      <c r="AX53" s="17" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="23">
@@ -6656,7 +6796,7 @@
       <c r="M54" s="17" t="n"/>
       <c r="N54" s="17" t="n"/>
       <c r="O54" s="23">
-        <f>IF($B54="","",IF($I54="なし","あり",IF($I54="あり",IF(OR($K54="更新の可能性あり",AND($J54&lt;&gt;"",$G54&lt;&gt;"",$J54-$G54+1&gt;62)),"あり","なし"),"")))</f>
+        <f>IF($B54="","",IF($I54="なし","あり",IF($I54&lt;&gt;"あり","",IF($K54="更新の可能性あり","あり",IF(OR($J54="",$G54=""),"なし",IF(OR(NOT(ISNUMBER($G54)),NOT(ISNUMBER($J54)),$G54&gt;80000,$J54&gt;80000),"要確認（日付）",IF($J54&gt;IF(DAY(EDATE($G54,2))&lt;DAY($G54),EOMONTH($G54,2),EDATE($G54,2)-1),"あり","なし"))))))</f>
         <v/>
       </c>
       <c r="P54" s="23">
@@ -6674,7 +6814,7 @@
         <v/>
       </c>
       <c r="X54" s="23">
-        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B54="","",IF(AND($L54&gt;='⓪ 事業所設定'!$C$13*0.75,$M54&gt;='⓪ 事業所設定'!$C$14*0.75,$O54="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L54&gt;=20,$O54="あり",$N54&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S54+$T54)&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
+        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B54="","",IF(AND($L54&gt;='⓪ 事業所設定'!$C$13*0.75,$M54&gt;='⓪ 事業所設定'!$C$14*0.75,$O54="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L54&gt;=20,$O54="あり",$N54&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S54+$T54-N($AW54))&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
         <v/>
       </c>
       <c r="Y54" s="23">
@@ -6682,7 +6822,7 @@
         <v/>
       </c>
       <c r="Z54" s="23">
-        <f>IF($B54="","",IF(AND($L54&gt;=20,$P54="あり",$N54&lt;&gt;"昼間部の学生"),"加入","加入対象外"))</f>
+        <f>IF($B54="","",IF($H54="役員","対象外（兼務役員なら要相談）",IF(AND($L54&gt;=20,$P54="あり",$N54&lt;&gt;"昼間部の学生"),"加入","加入対象外")))</f>
         <v/>
       </c>
       <c r="AA54" s="61" t="n"/>
@@ -6704,13 +6844,16 @@
       <c r="AQ54" s="17" t="n"/>
       <c r="AR54" s="17" t="n"/>
       <c r="AT54">
-        <f>IF($B54="","",IF($B54="",1,0)+IF($C54="",1,0)+IF($D54="",1,0)+IF($E54="",1,0)+IF($G54="",1,0)+IF($H54="",1,0)+IF($I54="",1,0)+IF($L54="",1,0)+IF($M54="",1,0)+IF($N54="",1,0)+IF($Q54="",1,0)+IF($S54="",1,0)+IF($AA54="",1,0)+IF($AC54="",1,0)+IF($AG54="",1,0)+IF($AH54="",1,0)+IF($AI54="",1,0)+IF($AL54="",1,0)+IF($AP54="",1,0)+IF($AQ54="",1,0)+IF(AND($I54="あり",$J54=""),1,0)+IF(AND($I54="あり",$K54=""),1,0)+IF(AND($AA54="",$AB54=""),1,0)+IF(AND($AC54="あり",$AD54=""),1,0)+IF(AND($AC54="あり",OR($AD54="",$AD54="後日提出"),$AE54=""),1,0))</f>
+        <f>IF($B54="","",IF($B54="",1,0)+IF($C54="",1,0)+IF($D54="",1,0)+IF($E54="",1,0)+IF($G54="",1,0)+IF($H54="",1,0)+IF($I54="",1,0)+IF($L54="",1,0)+IF($M54="",1,0)+IF($N54="",1,0)+IF($Q54="",1,0)+IF($S54="",1,0)+IF($AA54="",1,0)+IF($AC54="",1,0)+IF($AG54="",1,0)+IF($AH54="",1,0)+IF($AI54="",1,0)+IF($AL54="",1,0)+IF($AP54="",1,0)+IF($AQ54="",1,0)+IF(AND($I54="あり",$J54=""),1,0)+IF(AND($I54="あり",$K54=""),1,0)+IF(AND($AA54="",$AB54=""),1,0)+IF(AND($AC54="あり",$AD54=""),1,0)+IF(AND($AC54="あり",OR($AD54="",$AD54="後日提出"),$AE54=""),1,0)+IF($AV54="",1,0)+IF(AND($AL54="外国",$AM54=""),1,0)+IF(AND($AL54="外国",$AN54=""),1,0)+IF(AND($AL54="外国",$AO54=""),1,0))</f>
         <v/>
       </c>
       <c r="AU54">
         <f>IF($B54="","",IF(AND($AA54&lt;&gt;"",$AA54&lt;&gt;"後日提出",$AA54&lt;&gt;"別経路提出",LEN($AA54)&lt;&gt;12),1,0)+IF(AND($AB54&lt;&gt;"",$AB54&lt;&gt;"後日提出",LEN($AB54)&lt;&gt;10),1,0)+IF(AND($AD54&lt;&gt;"",$AD54&lt;&gt;"後日提出",LEN($AD54)&lt;&gt;11),1,0)+IF(AND($AG54&lt;&gt;"",LEN(SUBSTITUTE($AG54,"-",""))&lt;&gt;7),1,0))</f>
         <v/>
       </c>
+      <c r="AV54" s="17" t="n"/>
+      <c r="AW54" s="59" t="n"/>
+      <c r="AX54" s="17" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="23">
@@ -6734,7 +6877,7 @@
       <c r="M55" s="17" t="n"/>
       <c r="N55" s="17" t="n"/>
       <c r="O55" s="23">
-        <f>IF($B55="","",IF($I55="なし","あり",IF($I55="あり",IF(OR($K55="更新の可能性あり",AND($J55&lt;&gt;"",$G55&lt;&gt;"",$J55-$G55+1&gt;62)),"あり","なし"),"")))</f>
+        <f>IF($B55="","",IF($I55="なし","あり",IF($I55&lt;&gt;"あり","",IF($K55="更新の可能性あり","あり",IF(OR($J55="",$G55=""),"なし",IF(OR(NOT(ISNUMBER($G55)),NOT(ISNUMBER($J55)),$G55&gt;80000,$J55&gt;80000),"要確認（日付）",IF($J55&gt;IF(DAY(EDATE($G55,2))&lt;DAY($G55),EOMONTH($G55,2),EDATE($G55,2)-1),"あり","なし"))))))</f>
         <v/>
       </c>
       <c r="P55" s="23">
@@ -6752,7 +6895,7 @@
         <v/>
       </c>
       <c r="X55" s="23">
-        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B55="","",IF(AND($L55&gt;='⓪ 事業所設定'!$C$13*0.75,$M55&gt;='⓪ 事業所設定'!$C$14*0.75,$O55="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L55&gt;=20,$O55="あり",$N55&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S55+$T55)&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
+        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B55="","",IF(AND($L55&gt;='⓪ 事業所設定'!$C$13*0.75,$M55&gt;='⓪ 事業所設定'!$C$14*0.75,$O55="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L55&gt;=20,$O55="あり",$N55&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S55+$T55-N($AW55))&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
         <v/>
       </c>
       <c r="Y55" s="23">
@@ -6760,7 +6903,7 @@
         <v/>
       </c>
       <c r="Z55" s="23">
-        <f>IF($B55="","",IF(AND($L55&gt;=20,$P55="あり",$N55&lt;&gt;"昼間部の学生"),"加入","加入対象外"))</f>
+        <f>IF($B55="","",IF($H55="役員","対象外（兼務役員なら要相談）",IF(AND($L55&gt;=20,$P55="あり",$N55&lt;&gt;"昼間部の学生"),"加入","加入対象外")))</f>
         <v/>
       </c>
       <c r="AA55" s="61" t="n"/>
@@ -6782,13 +6925,16 @@
       <c r="AQ55" s="17" t="n"/>
       <c r="AR55" s="17" t="n"/>
       <c r="AT55">
-        <f>IF($B55="","",IF($B55="",1,0)+IF($C55="",1,0)+IF($D55="",1,0)+IF($E55="",1,0)+IF($G55="",1,0)+IF($H55="",1,0)+IF($I55="",1,0)+IF($L55="",1,0)+IF($M55="",1,0)+IF($N55="",1,0)+IF($Q55="",1,0)+IF($S55="",1,0)+IF($AA55="",1,0)+IF($AC55="",1,0)+IF($AG55="",1,0)+IF($AH55="",1,0)+IF($AI55="",1,0)+IF($AL55="",1,0)+IF($AP55="",1,0)+IF($AQ55="",1,0)+IF(AND($I55="あり",$J55=""),1,0)+IF(AND($I55="あり",$K55=""),1,0)+IF(AND($AA55="",$AB55=""),1,0)+IF(AND($AC55="あり",$AD55=""),1,0)+IF(AND($AC55="あり",OR($AD55="",$AD55="後日提出"),$AE55=""),1,0))</f>
+        <f>IF($B55="","",IF($B55="",1,0)+IF($C55="",1,0)+IF($D55="",1,0)+IF($E55="",1,0)+IF($G55="",1,0)+IF($H55="",1,0)+IF($I55="",1,0)+IF($L55="",1,0)+IF($M55="",1,0)+IF($N55="",1,0)+IF($Q55="",1,0)+IF($S55="",1,0)+IF($AA55="",1,0)+IF($AC55="",1,0)+IF($AG55="",1,0)+IF($AH55="",1,0)+IF($AI55="",1,0)+IF($AL55="",1,0)+IF($AP55="",1,0)+IF($AQ55="",1,0)+IF(AND($I55="あり",$J55=""),1,0)+IF(AND($I55="あり",$K55=""),1,0)+IF(AND($AA55="",$AB55=""),1,0)+IF(AND($AC55="あり",$AD55=""),1,0)+IF(AND($AC55="あり",OR($AD55="",$AD55="後日提出"),$AE55=""),1,0)+IF($AV55="",1,0)+IF(AND($AL55="外国",$AM55=""),1,0)+IF(AND($AL55="外国",$AN55=""),1,0)+IF(AND($AL55="外国",$AO55=""),1,0))</f>
         <v/>
       </c>
       <c r="AU55">
         <f>IF($B55="","",IF(AND($AA55&lt;&gt;"",$AA55&lt;&gt;"後日提出",$AA55&lt;&gt;"別経路提出",LEN($AA55)&lt;&gt;12),1,0)+IF(AND($AB55&lt;&gt;"",$AB55&lt;&gt;"後日提出",LEN($AB55)&lt;&gt;10),1,0)+IF(AND($AD55&lt;&gt;"",$AD55&lt;&gt;"後日提出",LEN($AD55)&lt;&gt;11),1,0)+IF(AND($AG55&lt;&gt;"",LEN(SUBSTITUTE($AG55,"-",""))&lt;&gt;7),1,0))</f>
         <v/>
       </c>
+      <c r="AV55" s="17" t="n"/>
+      <c r="AW55" s="59" t="n"/>
+      <c r="AX55" s="17" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="23">
@@ -6812,7 +6958,7 @@
       <c r="M56" s="17" t="n"/>
       <c r="N56" s="17" t="n"/>
       <c r="O56" s="23">
-        <f>IF($B56="","",IF($I56="なし","あり",IF($I56="あり",IF(OR($K56="更新の可能性あり",AND($J56&lt;&gt;"",$G56&lt;&gt;"",$J56-$G56+1&gt;62)),"あり","なし"),"")))</f>
+        <f>IF($B56="","",IF($I56="なし","あり",IF($I56&lt;&gt;"あり","",IF($K56="更新の可能性あり","あり",IF(OR($J56="",$G56=""),"なし",IF(OR(NOT(ISNUMBER($G56)),NOT(ISNUMBER($J56)),$G56&gt;80000,$J56&gt;80000),"要確認（日付）",IF($J56&gt;IF(DAY(EDATE($G56,2))&lt;DAY($G56),EOMONTH($G56,2),EDATE($G56,2)-1),"あり","なし"))))))</f>
         <v/>
       </c>
       <c r="P56" s="23">
@@ -6830,7 +6976,7 @@
         <v/>
       </c>
       <c r="X56" s="23">
-        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B56="","",IF(AND($L56&gt;='⓪ 事業所設定'!$C$13*0.75,$M56&gt;='⓪ 事業所設定'!$C$14*0.75,$O56="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L56&gt;=20,$O56="あり",$N56&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S56+$T56)&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
+        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B56="","",IF(AND($L56&gt;='⓪ 事業所設定'!$C$13*0.75,$M56&gt;='⓪ 事業所設定'!$C$14*0.75,$O56="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L56&gt;=20,$O56="あり",$N56&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S56+$T56-N($AW56))&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
         <v/>
       </c>
       <c r="Y56" s="23">
@@ -6838,7 +6984,7 @@
         <v/>
       </c>
       <c r="Z56" s="23">
-        <f>IF($B56="","",IF(AND($L56&gt;=20,$P56="あり",$N56&lt;&gt;"昼間部の学生"),"加入","加入対象外"))</f>
+        <f>IF($B56="","",IF($H56="役員","対象外（兼務役員なら要相談）",IF(AND($L56&gt;=20,$P56="あり",$N56&lt;&gt;"昼間部の学生"),"加入","加入対象外")))</f>
         <v/>
       </c>
       <c r="AA56" s="61" t="n"/>
@@ -6860,13 +7006,16 @@
       <c r="AQ56" s="17" t="n"/>
       <c r="AR56" s="17" t="n"/>
       <c r="AT56">
-        <f>IF($B56="","",IF($B56="",1,0)+IF($C56="",1,0)+IF($D56="",1,0)+IF($E56="",1,0)+IF($G56="",1,0)+IF($H56="",1,0)+IF($I56="",1,0)+IF($L56="",1,0)+IF($M56="",1,0)+IF($N56="",1,0)+IF($Q56="",1,0)+IF($S56="",1,0)+IF($AA56="",1,0)+IF($AC56="",1,0)+IF($AG56="",1,0)+IF($AH56="",1,0)+IF($AI56="",1,0)+IF($AL56="",1,0)+IF($AP56="",1,0)+IF($AQ56="",1,0)+IF(AND($I56="あり",$J56=""),1,0)+IF(AND($I56="あり",$K56=""),1,0)+IF(AND($AA56="",$AB56=""),1,0)+IF(AND($AC56="あり",$AD56=""),1,0)+IF(AND($AC56="あり",OR($AD56="",$AD56="後日提出"),$AE56=""),1,0))</f>
+        <f>IF($B56="","",IF($B56="",1,0)+IF($C56="",1,0)+IF($D56="",1,0)+IF($E56="",1,0)+IF($G56="",1,0)+IF($H56="",1,0)+IF($I56="",1,0)+IF($L56="",1,0)+IF($M56="",1,0)+IF($N56="",1,0)+IF($Q56="",1,0)+IF($S56="",1,0)+IF($AA56="",1,0)+IF($AC56="",1,0)+IF($AG56="",1,0)+IF($AH56="",1,0)+IF($AI56="",1,0)+IF($AL56="",1,0)+IF($AP56="",1,0)+IF($AQ56="",1,0)+IF(AND($I56="あり",$J56=""),1,0)+IF(AND($I56="あり",$K56=""),1,0)+IF(AND($AA56="",$AB56=""),1,0)+IF(AND($AC56="あり",$AD56=""),1,0)+IF(AND($AC56="あり",OR($AD56="",$AD56="後日提出"),$AE56=""),1,0)+IF($AV56="",1,0)+IF(AND($AL56="外国",$AM56=""),1,0)+IF(AND($AL56="外国",$AN56=""),1,0)+IF(AND($AL56="外国",$AO56=""),1,0))</f>
         <v/>
       </c>
       <c r="AU56">
         <f>IF($B56="","",IF(AND($AA56&lt;&gt;"",$AA56&lt;&gt;"後日提出",$AA56&lt;&gt;"別経路提出",LEN($AA56)&lt;&gt;12),1,0)+IF(AND($AB56&lt;&gt;"",$AB56&lt;&gt;"後日提出",LEN($AB56)&lt;&gt;10),1,0)+IF(AND($AD56&lt;&gt;"",$AD56&lt;&gt;"後日提出",LEN($AD56)&lt;&gt;11),1,0)+IF(AND($AG56&lt;&gt;"",LEN(SUBSTITUTE($AG56,"-",""))&lt;&gt;7),1,0))</f>
         <v/>
       </c>
+      <c r="AV56" s="17" t="n"/>
+      <c r="AW56" s="59" t="n"/>
+      <c r="AX56" s="17" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="23">
@@ -6890,7 +7039,7 @@
       <c r="M57" s="17" t="n"/>
       <c r="N57" s="17" t="n"/>
       <c r="O57" s="23">
-        <f>IF($B57="","",IF($I57="なし","あり",IF($I57="あり",IF(OR($K57="更新の可能性あり",AND($J57&lt;&gt;"",$G57&lt;&gt;"",$J57-$G57+1&gt;62)),"あり","なし"),"")))</f>
+        <f>IF($B57="","",IF($I57="なし","あり",IF($I57&lt;&gt;"あり","",IF($K57="更新の可能性あり","あり",IF(OR($J57="",$G57=""),"なし",IF(OR(NOT(ISNUMBER($G57)),NOT(ISNUMBER($J57)),$G57&gt;80000,$J57&gt;80000),"要確認（日付）",IF($J57&gt;IF(DAY(EDATE($G57,2))&lt;DAY($G57),EOMONTH($G57,2),EDATE($G57,2)-1),"あり","なし"))))))</f>
         <v/>
       </c>
       <c r="P57" s="23">
@@ -6908,7 +7057,7 @@
         <v/>
       </c>
       <c r="X57" s="23">
-        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B57="","",IF(AND($L57&gt;='⓪ 事業所設定'!$C$13*0.75,$M57&gt;='⓪ 事業所設定'!$C$14*0.75,$O57="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L57&gt;=20,$O57="あり",$N57&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S57+$T57)&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
+        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B57="","",IF(AND($L57&gt;='⓪ 事業所設定'!$C$13*0.75,$M57&gt;='⓪ 事業所設定'!$C$14*0.75,$O57="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L57&gt;=20,$O57="あり",$N57&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S57+$T57-N($AW57))&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
         <v/>
       </c>
       <c r="Y57" s="23">
@@ -6916,7 +7065,7 @@
         <v/>
       </c>
       <c r="Z57" s="23">
-        <f>IF($B57="","",IF(AND($L57&gt;=20,$P57="あり",$N57&lt;&gt;"昼間部の学生"),"加入","加入対象外"))</f>
+        <f>IF($B57="","",IF($H57="役員","対象外（兼務役員なら要相談）",IF(AND($L57&gt;=20,$P57="あり",$N57&lt;&gt;"昼間部の学生"),"加入","加入対象外")))</f>
         <v/>
       </c>
       <c r="AA57" s="61" t="n"/>
@@ -6938,13 +7087,16 @@
       <c r="AQ57" s="17" t="n"/>
       <c r="AR57" s="17" t="n"/>
       <c r="AT57">
-        <f>IF($B57="","",IF($B57="",1,0)+IF($C57="",1,0)+IF($D57="",1,0)+IF($E57="",1,0)+IF($G57="",1,0)+IF($H57="",1,0)+IF($I57="",1,0)+IF($L57="",1,0)+IF($M57="",1,0)+IF($N57="",1,0)+IF($Q57="",1,0)+IF($S57="",1,0)+IF($AA57="",1,0)+IF($AC57="",1,0)+IF($AG57="",1,0)+IF($AH57="",1,0)+IF($AI57="",1,0)+IF($AL57="",1,0)+IF($AP57="",1,0)+IF($AQ57="",1,0)+IF(AND($I57="あり",$J57=""),1,0)+IF(AND($I57="あり",$K57=""),1,0)+IF(AND($AA57="",$AB57=""),1,0)+IF(AND($AC57="あり",$AD57=""),1,0)+IF(AND($AC57="あり",OR($AD57="",$AD57="後日提出"),$AE57=""),1,0))</f>
+        <f>IF($B57="","",IF($B57="",1,0)+IF($C57="",1,0)+IF($D57="",1,0)+IF($E57="",1,0)+IF($G57="",1,0)+IF($H57="",1,0)+IF($I57="",1,0)+IF($L57="",1,0)+IF($M57="",1,0)+IF($N57="",1,0)+IF($Q57="",1,0)+IF($S57="",1,0)+IF($AA57="",1,0)+IF($AC57="",1,0)+IF($AG57="",1,0)+IF($AH57="",1,0)+IF($AI57="",1,0)+IF($AL57="",1,0)+IF($AP57="",1,0)+IF($AQ57="",1,0)+IF(AND($I57="あり",$J57=""),1,0)+IF(AND($I57="あり",$K57=""),1,0)+IF(AND($AA57="",$AB57=""),1,0)+IF(AND($AC57="あり",$AD57=""),1,0)+IF(AND($AC57="あり",OR($AD57="",$AD57="後日提出"),$AE57=""),1,0)+IF($AV57="",1,0)+IF(AND($AL57="外国",$AM57=""),1,0)+IF(AND($AL57="外国",$AN57=""),1,0)+IF(AND($AL57="外国",$AO57=""),1,0))</f>
         <v/>
       </c>
       <c r="AU57">
         <f>IF($B57="","",IF(AND($AA57&lt;&gt;"",$AA57&lt;&gt;"後日提出",$AA57&lt;&gt;"別経路提出",LEN($AA57)&lt;&gt;12),1,0)+IF(AND($AB57&lt;&gt;"",$AB57&lt;&gt;"後日提出",LEN($AB57)&lt;&gt;10),1,0)+IF(AND($AD57&lt;&gt;"",$AD57&lt;&gt;"後日提出",LEN($AD57)&lt;&gt;11),1,0)+IF(AND($AG57&lt;&gt;"",LEN(SUBSTITUTE($AG57,"-",""))&lt;&gt;7),1,0))</f>
         <v/>
       </c>
+      <c r="AV57" s="17" t="n"/>
+      <c r="AW57" s="59" t="n"/>
+      <c r="AX57" s="17" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="23">
@@ -6968,7 +7120,7 @@
       <c r="M58" s="17" t="n"/>
       <c r="N58" s="17" t="n"/>
       <c r="O58" s="23">
-        <f>IF($B58="","",IF($I58="なし","あり",IF($I58="あり",IF(OR($K58="更新の可能性あり",AND($J58&lt;&gt;"",$G58&lt;&gt;"",$J58-$G58+1&gt;62)),"あり","なし"),"")))</f>
+        <f>IF($B58="","",IF($I58="なし","あり",IF($I58&lt;&gt;"あり","",IF($K58="更新の可能性あり","あり",IF(OR($J58="",$G58=""),"なし",IF(OR(NOT(ISNUMBER($G58)),NOT(ISNUMBER($J58)),$G58&gt;80000,$J58&gt;80000),"要確認（日付）",IF($J58&gt;IF(DAY(EDATE($G58,2))&lt;DAY($G58),EOMONTH($G58,2),EDATE($G58,2)-1),"あり","なし"))))))</f>
         <v/>
       </c>
       <c r="P58" s="23">
@@ -6986,7 +7138,7 @@
         <v/>
       </c>
       <c r="X58" s="23">
-        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B58="","",IF(AND($L58&gt;='⓪ 事業所設定'!$C$13*0.75,$M58&gt;='⓪ 事業所設定'!$C$14*0.75,$O58="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L58&gt;=20,$O58="あり",$N58&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S58+$T58)&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
+        <f>IF(OR('⓪ 事業所設定'!$C$9="",'⓪ 事業所設定'!$C$13="",'⓪ 事業所設定'!$C$14="",'⓪ 事業所設定'!$C$17=""),"事業所設定が未入力です",IF($B58="","",IF(AND($L58&gt;='⓪ 事業所設定'!$C$13*0.75,$M58&gt;='⓪ 事業所設定'!$C$14*0.75,$O58="あり"),"加入（一般被保険者）",IF(AND('⓪ 事業所設定'!$C$12="適用あり",$L58&gt;=20,$O58="あり",$N58&lt;&gt;"昼間部の学生",OR('⓪ 事業所設定'!$C$17&gt;=DATE(2026,10,1),($S58+$T58-N($AW58))&gt;=88000)),"加入（短時間労働者）","加入対象外"))))</f>
         <v/>
       </c>
       <c r="Y58" s="23">
@@ -6994,7 +7146,7 @@
         <v/>
       </c>
       <c r="Z58" s="23">
-        <f>IF($B58="","",IF(AND($L58&gt;=20,$P58="あり",$N58&lt;&gt;"昼間部の学生"),"加入","加入対象外"))</f>
+        <f>IF($B58="","",IF($H58="役員","対象外（兼務役員なら要相談）",IF(AND($L58&gt;=20,$P58="あり",$N58&lt;&gt;"昼間部の学生"),"加入","加入対象外")))</f>
         <v/>
       </c>
       <c r="AA58" s="61" t="n"/>
@@ -7016,16 +7168,19 @@
       <c r="AQ58" s="17" t="n"/>
       <c r="AR58" s="17" t="n"/>
       <c r="AT58">
-        <f>IF($B58="","",IF($B58="",1,0)+IF($C58="",1,0)+IF($D58="",1,0)+IF($E58="",1,0)+IF($G58="",1,0)+IF($H58="",1,0)+IF($I58="",1,0)+IF($L58="",1,0)+IF($M58="",1,0)+IF($N58="",1,0)+IF($Q58="",1,0)+IF($S58="",1,0)+IF($AA58="",1,0)+IF($AC58="",1,0)+IF($AG58="",1,0)+IF($AH58="",1,0)+IF($AI58="",1,0)+IF($AL58="",1,0)+IF($AP58="",1,0)+IF($AQ58="",1,0)+IF(AND($I58="あり",$J58=""),1,0)+IF(AND($I58="あり",$K58=""),1,0)+IF(AND($AA58="",$AB58=""),1,0)+IF(AND($AC58="あり",$AD58=""),1,0)+IF(AND($AC58="あり",OR($AD58="",$AD58="後日提出"),$AE58=""),1,0))</f>
+        <f>IF($B58="","",IF($B58="",1,0)+IF($C58="",1,0)+IF($D58="",1,0)+IF($E58="",1,0)+IF($G58="",1,0)+IF($H58="",1,0)+IF($I58="",1,0)+IF($L58="",1,0)+IF($M58="",1,0)+IF($N58="",1,0)+IF($Q58="",1,0)+IF($S58="",1,0)+IF($AA58="",1,0)+IF($AC58="",1,0)+IF($AG58="",1,0)+IF($AH58="",1,0)+IF($AI58="",1,0)+IF($AL58="",1,0)+IF($AP58="",1,0)+IF($AQ58="",1,0)+IF(AND($I58="あり",$J58=""),1,0)+IF(AND($I58="あり",$K58=""),1,0)+IF(AND($AA58="",$AB58=""),1,0)+IF(AND($AC58="あり",$AD58=""),1,0)+IF(AND($AC58="あり",OR($AD58="",$AD58="後日提出"),$AE58=""),1,0)+IF($AV58="",1,0)+IF(AND($AL58="外国",$AM58=""),1,0)+IF(AND($AL58="外国",$AN58=""),1,0)+IF(AND($AL58="外国",$AO58=""),1,0))</f>
         <v/>
       </c>
       <c r="AU58">
         <f>IF($B58="","",IF(AND($AA58&lt;&gt;"",$AA58&lt;&gt;"後日提出",$AA58&lt;&gt;"別経路提出",LEN($AA58)&lt;&gt;12),1,0)+IF(AND($AB58&lt;&gt;"",$AB58&lt;&gt;"後日提出",LEN($AB58)&lt;&gt;10),1,0)+IF(AND($AD58&lt;&gt;"",$AD58&lt;&gt;"後日提出",LEN($AD58)&lt;&gt;11),1,0)+IF(AND($AG58&lt;&gt;"",LEN(SUBSTITUTE($AG58,"-",""))&lt;&gt;7),1,0))</f>
         <v/>
       </c>
+      <c r="AV58" s="17" t="n"/>
+      <c r="AW58" s="59" t="n"/>
+      <c r="AX58" s="17" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="22">
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="F3:G3"/>
@@ -7034,6 +7189,7 @@
     <mergeCell ref="AP6:AR6"/>
     <mergeCell ref="AG6:AK6"/>
     <mergeCell ref="AL6:AO6"/>
+    <mergeCell ref="AV6:AX6"/>
     <mergeCell ref="I3:J3"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="L4:M4"/>
@@ -7042,9 +7198,9 @@
     <mergeCell ref="G6:P6"/>
     <mergeCell ref="I4:J4"/>
     <mergeCell ref="B4:C4"/>
-    <mergeCell ref="K1:AR1"/>
     <mergeCell ref="B5:L5"/>
     <mergeCell ref="A6:F6"/>
+    <mergeCell ref="K1:AX1"/>
     <mergeCell ref="Q6:W6"/>
     <mergeCell ref="AA6:AF6"/>
   </mergeCells>
@@ -7234,6 +7390,9 @@
     <cfRule type="expression" priority="41" dxfId="1" stopIfTrue="1">
       <formula>AND(ISNUMBER(AN9),AN9&gt;80000)</formula>
     </cfRule>
+    <cfRule type="expression" priority="50" dxfId="2" stopIfTrue="1">
+      <formula>AND($AL9="外国",AN9="")</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X8:X58">
     <cfRule type="expression" priority="42" dxfId="0" stopIfTrue="1">
@@ -7259,7 +7418,22 @@
       <formula>AND($B8&lt;&gt;"",Y8="")</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="27">
+  <conditionalFormatting sqref="AV9:AV58">
+    <cfRule type="expression" priority="48" dxfId="2" stopIfTrue="1">
+      <formula>AND($B9&lt;&gt;"",AV9="")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AM9:AM58">
+    <cfRule type="expression" priority="49" dxfId="2" stopIfTrue="1">
+      <formula>AND($AL9="外国",AM9="")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AO9:AO58">
+    <cfRule type="expression" priority="51" dxfId="2" stopIfTrue="1">
+      <formula>AND($AL9="外国",AO9="")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="30">
     <dataValidation sqref="D8:D58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="入力エラー" error="一覧から選択してください。" type="list" errorStyle="stop">
       <formula1>m_性別</formula1>
     </dataValidation>
@@ -7354,6 +7528,16 @@
     <dataValidation sqref="AQ8:AQ58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="入力エラー" error="一覧から選択してください。" promptTitle="入力のヒント" prompt="「あり」を選んだ方は、シート②被扶養者情報も併せてご記入ください。" type="list" errorStyle="stop">
       <formula1>m_ありなし</formula1>
     </dataValidation>
+    <dataValidation sqref="AV8:AV58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="入力エラー" error="一覧から選択してください。" promptTitle="入力のヒント" prompt="雇用保険 資格取得届の職種欄に対応します。近いものを選んでください。分からないときは『分からない』で構いません。〔区分名は提出前に現行様式で照合します〕" type="list" errorStyle="stop">
+      <formula1>m_職種</formula1>
+    </dataValidation>
+    <dataValidation sqref="AW8:AW58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="入力エラー" error="0以上の整数（円）で入力してください。" promptTitle="入力のヒント" prompt="左の『固定手当』に含めた家族手当・精皆勤手当の月額（円）。8.8万円要件（短時間労働者の賃金要件）の判定から差し引きます。無ければ空欄で構いません（0として扱います）。" type="whole" errorStyle="warning" operator="between">
+      <formula1>0</formula1>
+      <formula2>100000000</formula2>
+    </dataValidation>
+    <dataValidation sqref="AX8:AX58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="入力エラー" error="一覧から選択してください。" promptTitle="入力のヒント" prompt="他社でも社会保険（健康保険・厚生年金）に加入していますか。『はい』のときは二以上事業所勤務届が別途必要になります（当事務所からご案内します）。" type="list" errorStyle="stop">
+      <formula1>"いいえ,はい,分からない"</formula1>
+    </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7368,7 +7552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O67"/>
+  <dimension ref="A1:P67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -7386,6 +7570,7 @@
     <col width="24" customWidth="1" min="13" max="13"/>
     <col hidden="1" width="13" customWidth="1" min="14" max="14"/>
     <col hidden="1" width="13" customWidth="1" min="15" max="15"/>
+    <col width="30" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -7509,7 +7694,8 @@
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>年間収入見込(円)
+          <t>年間収入見込（円）
+※万円ではありません
 【必】</t>
         </is>
       </c>
@@ -7535,6 +7721,12 @@
         <is>
           <t>備考
 【任】</t>
+        </is>
+      </c>
+      <c r="P6" s="7" t="inlineStr">
+        <is>
+          <t>ご住所（別居のとき）
+【条件必須】別居のとき</t>
         </is>
       </c>
     </row>
@@ -7576,11 +7768,11 @@
         </is>
       </c>
       <c r="I7" s="78" t="n">
-        <v>0</v>
+        <v>1030000</v>
       </c>
       <c r="J7" s="54" t="inlineStr">
         <is>
-          <t>無職</t>
+          <t>パート勤務</t>
         </is>
       </c>
       <c r="K7" s="77" t="n">
@@ -7593,7 +7785,12 @@
       </c>
       <c r="M7" s="54" t="inlineStr">
         <is>
-          <t>← この行は記入例です（編集不可）</t>
+          <t>← この行は記入例です。8行目からご記入ください（消しても構いません）</t>
+        </is>
+      </c>
+      <c r="P7" s="54" t="inlineStr">
+        <is>
+          <t>（同居のため記入不要）</t>
         </is>
       </c>
     </row>
@@ -7612,9 +7809,10 @@
       <c r="L8" s="17" t="n"/>
       <c r="M8" s="17" t="n"/>
       <c r="O8">
-        <f>IF($B8="","",IF($A8="",1,0)+IF($B8="",1,0)+IF($C8="",1,0)+IF($D8="",1,0)+IF($E8="",1,0)+IF($F8="",1,0)+IF($G8="",1,0)+IF($H8="",1,0)+IF($I8="",1,0)+IF($K8="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B8="","",IF($A8="",1,0)+IF($B8="",1,0)+IF($C8="",1,0)+IF($D8="",1,0)+IF($E8="",1,0)+IF($F8="",1,0)+IF($G8="",1,0)+IF($H8="",1,0)+IF($I8="",1,0)+IF($K8="",1,0)+IF(AND($H8="別居",$P8=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P8" s="17" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="17" t="n"/>
@@ -7631,9 +7829,10 @@
       <c r="L9" s="17" t="n"/>
       <c r="M9" s="17" t="n"/>
       <c r="O9">
-        <f>IF($B9="","",IF($A9="",1,0)+IF($B9="",1,0)+IF($C9="",1,0)+IF($D9="",1,0)+IF($E9="",1,0)+IF($F9="",1,0)+IF($G9="",1,0)+IF($H9="",1,0)+IF($I9="",1,0)+IF($K9="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B9="","",IF($A9="",1,0)+IF($B9="",1,0)+IF($C9="",1,0)+IF($D9="",1,0)+IF($E9="",1,0)+IF($F9="",1,0)+IF($G9="",1,0)+IF($H9="",1,0)+IF($I9="",1,0)+IF($K9="",1,0)+IF(AND($H9="別居",$P9=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P9" s="17" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="17" t="n"/>
@@ -7650,9 +7849,10 @@
       <c r="L10" s="17" t="n"/>
       <c r="M10" s="17" t="n"/>
       <c r="O10">
-        <f>IF($B10="","",IF($A10="",1,0)+IF($B10="",1,0)+IF($C10="",1,0)+IF($D10="",1,0)+IF($E10="",1,0)+IF($F10="",1,0)+IF($G10="",1,0)+IF($H10="",1,0)+IF($I10="",1,0)+IF($K10="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B10="","",IF($A10="",1,0)+IF($B10="",1,0)+IF($C10="",1,0)+IF($D10="",1,0)+IF($E10="",1,0)+IF($F10="",1,0)+IF($G10="",1,0)+IF($H10="",1,0)+IF($I10="",1,0)+IF($K10="",1,0)+IF(AND($H10="別居",$P10=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P10" s="17" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="17" t="n"/>
@@ -7669,9 +7869,10 @@
       <c r="L11" s="17" t="n"/>
       <c r="M11" s="17" t="n"/>
       <c r="O11">
-        <f>IF($B11="","",IF($A11="",1,0)+IF($B11="",1,0)+IF($C11="",1,0)+IF($D11="",1,0)+IF($E11="",1,0)+IF($F11="",1,0)+IF($G11="",1,0)+IF($H11="",1,0)+IF($I11="",1,0)+IF($K11="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B11="","",IF($A11="",1,0)+IF($B11="",1,0)+IF($C11="",1,0)+IF($D11="",1,0)+IF($E11="",1,0)+IF($F11="",1,0)+IF($G11="",1,0)+IF($H11="",1,0)+IF($I11="",1,0)+IF($K11="",1,0)+IF(AND($H11="別居",$P11=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P11" s="17" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="17" t="n"/>
@@ -7688,9 +7889,10 @@
       <c r="L12" s="17" t="n"/>
       <c r="M12" s="17" t="n"/>
       <c r="O12">
-        <f>IF($B12="","",IF($A12="",1,0)+IF($B12="",1,0)+IF($C12="",1,0)+IF($D12="",1,0)+IF($E12="",1,0)+IF($F12="",1,0)+IF($G12="",1,0)+IF($H12="",1,0)+IF($I12="",1,0)+IF($K12="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B12="","",IF($A12="",1,0)+IF($B12="",1,0)+IF($C12="",1,0)+IF($D12="",1,0)+IF($E12="",1,0)+IF($F12="",1,0)+IF($G12="",1,0)+IF($H12="",1,0)+IF($I12="",1,0)+IF($K12="",1,0)+IF(AND($H12="別居",$P12=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P12" s="17" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="17" t="n"/>
@@ -7707,9 +7909,10 @@
       <c r="L13" s="17" t="n"/>
       <c r="M13" s="17" t="n"/>
       <c r="O13">
-        <f>IF($B13="","",IF($A13="",1,0)+IF($B13="",1,0)+IF($C13="",1,0)+IF($D13="",1,0)+IF($E13="",1,0)+IF($F13="",1,0)+IF($G13="",1,0)+IF($H13="",1,0)+IF($I13="",1,0)+IF($K13="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B13="","",IF($A13="",1,0)+IF($B13="",1,0)+IF($C13="",1,0)+IF($D13="",1,0)+IF($E13="",1,0)+IF($F13="",1,0)+IF($G13="",1,0)+IF($H13="",1,0)+IF($I13="",1,0)+IF($K13="",1,0)+IF(AND($H13="別居",$P13=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P13" s="17" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="17" t="n"/>
@@ -7726,9 +7929,10 @@
       <c r="L14" s="17" t="n"/>
       <c r="M14" s="17" t="n"/>
       <c r="O14">
-        <f>IF($B14="","",IF($A14="",1,0)+IF($B14="",1,0)+IF($C14="",1,0)+IF($D14="",1,0)+IF($E14="",1,0)+IF($F14="",1,0)+IF($G14="",1,0)+IF($H14="",1,0)+IF($I14="",1,0)+IF($K14="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B14="","",IF($A14="",1,0)+IF($B14="",1,0)+IF($C14="",1,0)+IF($D14="",1,0)+IF($E14="",1,0)+IF($F14="",1,0)+IF($G14="",1,0)+IF($H14="",1,0)+IF($I14="",1,0)+IF($K14="",1,0)+IF(AND($H14="別居",$P14=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P14" s="17" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="17" t="n"/>
@@ -7745,9 +7949,10 @@
       <c r="L15" s="17" t="n"/>
       <c r="M15" s="17" t="n"/>
       <c r="O15">
-        <f>IF($B15="","",IF($A15="",1,0)+IF($B15="",1,0)+IF($C15="",1,0)+IF($D15="",1,0)+IF($E15="",1,0)+IF($F15="",1,0)+IF($G15="",1,0)+IF($H15="",1,0)+IF($I15="",1,0)+IF($K15="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B15="","",IF($A15="",1,0)+IF($B15="",1,0)+IF($C15="",1,0)+IF($D15="",1,0)+IF($E15="",1,0)+IF($F15="",1,0)+IF($G15="",1,0)+IF($H15="",1,0)+IF($I15="",1,0)+IF($K15="",1,0)+IF(AND($H15="別居",$P15=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P15" s="17" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="17" t="n"/>
@@ -7764,9 +7969,10 @@
       <c r="L16" s="17" t="n"/>
       <c r="M16" s="17" t="n"/>
       <c r="O16">
-        <f>IF($B16="","",IF($A16="",1,0)+IF($B16="",1,0)+IF($C16="",1,0)+IF($D16="",1,0)+IF($E16="",1,0)+IF($F16="",1,0)+IF($G16="",1,0)+IF($H16="",1,0)+IF($I16="",1,0)+IF($K16="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B16="","",IF($A16="",1,0)+IF($B16="",1,0)+IF($C16="",1,0)+IF($D16="",1,0)+IF($E16="",1,0)+IF($F16="",1,0)+IF($G16="",1,0)+IF($H16="",1,0)+IF($I16="",1,0)+IF($K16="",1,0)+IF(AND($H16="別居",$P16=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P16" s="17" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="17" t="n"/>
@@ -7783,9 +7989,10 @@
       <c r="L17" s="17" t="n"/>
       <c r="M17" s="17" t="n"/>
       <c r="O17">
-        <f>IF($B17="","",IF($A17="",1,0)+IF($B17="",1,0)+IF($C17="",1,0)+IF($D17="",1,0)+IF($E17="",1,0)+IF($F17="",1,0)+IF($G17="",1,0)+IF($H17="",1,0)+IF($I17="",1,0)+IF($K17="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B17="","",IF($A17="",1,0)+IF($B17="",1,0)+IF($C17="",1,0)+IF($D17="",1,0)+IF($E17="",1,0)+IF($F17="",1,0)+IF($G17="",1,0)+IF($H17="",1,0)+IF($I17="",1,0)+IF($K17="",1,0)+IF(AND($H17="別居",$P17=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P17" s="17" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="17" t="n"/>
@@ -7802,9 +8009,10 @@
       <c r="L18" s="17" t="n"/>
       <c r="M18" s="17" t="n"/>
       <c r="O18">
-        <f>IF($B18="","",IF($A18="",1,0)+IF($B18="",1,0)+IF($C18="",1,0)+IF($D18="",1,0)+IF($E18="",1,0)+IF($F18="",1,0)+IF($G18="",1,0)+IF($H18="",1,0)+IF($I18="",1,0)+IF($K18="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B18="","",IF($A18="",1,0)+IF($B18="",1,0)+IF($C18="",1,0)+IF($D18="",1,0)+IF($E18="",1,0)+IF($F18="",1,0)+IF($G18="",1,0)+IF($H18="",1,0)+IF($I18="",1,0)+IF($K18="",1,0)+IF(AND($H18="別居",$P18=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P18" s="17" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="17" t="n"/>
@@ -7821,9 +8029,10 @@
       <c r="L19" s="17" t="n"/>
       <c r="M19" s="17" t="n"/>
       <c r="O19">
-        <f>IF($B19="","",IF($A19="",1,0)+IF($B19="",1,0)+IF($C19="",1,0)+IF($D19="",1,0)+IF($E19="",1,0)+IF($F19="",1,0)+IF($G19="",1,0)+IF($H19="",1,0)+IF($I19="",1,0)+IF($K19="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B19="","",IF($A19="",1,0)+IF($B19="",1,0)+IF($C19="",1,0)+IF($D19="",1,0)+IF($E19="",1,0)+IF($F19="",1,0)+IF($G19="",1,0)+IF($H19="",1,0)+IF($I19="",1,0)+IF($K19="",1,0)+IF(AND($H19="別居",$P19=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P19" s="17" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="17" t="n"/>
@@ -7840,9 +8049,10 @@
       <c r="L20" s="17" t="n"/>
       <c r="M20" s="17" t="n"/>
       <c r="O20">
-        <f>IF($B20="","",IF($A20="",1,0)+IF($B20="",1,0)+IF($C20="",1,0)+IF($D20="",1,0)+IF($E20="",1,0)+IF($F20="",1,0)+IF($G20="",1,0)+IF($H20="",1,0)+IF($I20="",1,0)+IF($K20="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B20="","",IF($A20="",1,0)+IF($B20="",1,0)+IF($C20="",1,0)+IF($D20="",1,0)+IF($E20="",1,0)+IF($F20="",1,0)+IF($G20="",1,0)+IF($H20="",1,0)+IF($I20="",1,0)+IF($K20="",1,0)+IF(AND($H20="別居",$P20=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P20" s="17" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="17" t="n"/>
@@ -7859,9 +8069,10 @@
       <c r="L21" s="17" t="n"/>
       <c r="M21" s="17" t="n"/>
       <c r="O21">
-        <f>IF($B21="","",IF($A21="",1,0)+IF($B21="",1,0)+IF($C21="",1,0)+IF($D21="",1,0)+IF($E21="",1,0)+IF($F21="",1,0)+IF($G21="",1,0)+IF($H21="",1,0)+IF($I21="",1,0)+IF($K21="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B21="","",IF($A21="",1,0)+IF($B21="",1,0)+IF($C21="",1,0)+IF($D21="",1,0)+IF($E21="",1,0)+IF($F21="",1,0)+IF($G21="",1,0)+IF($H21="",1,0)+IF($I21="",1,0)+IF($K21="",1,0)+IF(AND($H21="別居",$P21=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P21" s="17" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="17" t="n"/>
@@ -7878,9 +8089,10 @@
       <c r="L22" s="17" t="n"/>
       <c r="M22" s="17" t="n"/>
       <c r="O22">
-        <f>IF($B22="","",IF($A22="",1,0)+IF($B22="",1,0)+IF($C22="",1,0)+IF($D22="",1,0)+IF($E22="",1,0)+IF($F22="",1,0)+IF($G22="",1,0)+IF($H22="",1,0)+IF($I22="",1,0)+IF($K22="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B22="","",IF($A22="",1,0)+IF($B22="",1,0)+IF($C22="",1,0)+IF($D22="",1,0)+IF($E22="",1,0)+IF($F22="",1,0)+IF($G22="",1,0)+IF($H22="",1,0)+IF($I22="",1,0)+IF($K22="",1,0)+IF(AND($H22="別居",$P22=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P22" s="17" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="17" t="n"/>
@@ -7897,9 +8109,10 @@
       <c r="L23" s="17" t="n"/>
       <c r="M23" s="17" t="n"/>
       <c r="O23">
-        <f>IF($B23="","",IF($A23="",1,0)+IF($B23="",1,0)+IF($C23="",1,0)+IF($D23="",1,0)+IF($E23="",1,0)+IF($F23="",1,0)+IF($G23="",1,0)+IF($H23="",1,0)+IF($I23="",1,0)+IF($K23="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B23="","",IF($A23="",1,0)+IF($B23="",1,0)+IF($C23="",1,0)+IF($D23="",1,0)+IF($E23="",1,0)+IF($F23="",1,0)+IF($G23="",1,0)+IF($H23="",1,0)+IF($I23="",1,0)+IF($K23="",1,0)+IF(AND($H23="別居",$P23=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P23" s="17" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="17" t="n"/>
@@ -7916,9 +8129,10 @@
       <c r="L24" s="17" t="n"/>
       <c r="M24" s="17" t="n"/>
       <c r="O24">
-        <f>IF($B24="","",IF($A24="",1,0)+IF($B24="",1,0)+IF($C24="",1,0)+IF($D24="",1,0)+IF($E24="",1,0)+IF($F24="",1,0)+IF($G24="",1,0)+IF($H24="",1,0)+IF($I24="",1,0)+IF($K24="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B24="","",IF($A24="",1,0)+IF($B24="",1,0)+IF($C24="",1,0)+IF($D24="",1,0)+IF($E24="",1,0)+IF($F24="",1,0)+IF($G24="",1,0)+IF($H24="",1,0)+IF($I24="",1,0)+IF($K24="",1,0)+IF(AND($H24="別居",$P24=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P24" s="17" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="17" t="n"/>
@@ -7935,9 +8149,10 @@
       <c r="L25" s="17" t="n"/>
       <c r="M25" s="17" t="n"/>
       <c r="O25">
-        <f>IF($B25="","",IF($A25="",1,0)+IF($B25="",1,0)+IF($C25="",1,0)+IF($D25="",1,0)+IF($E25="",1,0)+IF($F25="",1,0)+IF($G25="",1,0)+IF($H25="",1,0)+IF($I25="",1,0)+IF($K25="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B25="","",IF($A25="",1,0)+IF($B25="",1,0)+IF($C25="",1,0)+IF($D25="",1,0)+IF($E25="",1,0)+IF($F25="",1,0)+IF($G25="",1,0)+IF($H25="",1,0)+IF($I25="",1,0)+IF($K25="",1,0)+IF(AND($H25="別居",$P25=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P25" s="17" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="17" t="n"/>
@@ -7954,9 +8169,10 @@
       <c r="L26" s="17" t="n"/>
       <c r="M26" s="17" t="n"/>
       <c r="O26">
-        <f>IF($B26="","",IF($A26="",1,0)+IF($B26="",1,0)+IF($C26="",1,0)+IF($D26="",1,0)+IF($E26="",1,0)+IF($F26="",1,0)+IF($G26="",1,0)+IF($H26="",1,0)+IF($I26="",1,0)+IF($K26="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B26="","",IF($A26="",1,0)+IF($B26="",1,0)+IF($C26="",1,0)+IF($D26="",1,0)+IF($E26="",1,0)+IF($F26="",1,0)+IF($G26="",1,0)+IF($H26="",1,0)+IF($I26="",1,0)+IF($K26="",1,0)+IF(AND($H26="別居",$P26=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P26" s="17" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="17" t="n"/>
@@ -7973,9 +8189,10 @@
       <c r="L27" s="17" t="n"/>
       <c r="M27" s="17" t="n"/>
       <c r="O27">
-        <f>IF($B27="","",IF($A27="",1,0)+IF($B27="",1,0)+IF($C27="",1,0)+IF($D27="",1,0)+IF($E27="",1,0)+IF($F27="",1,0)+IF($G27="",1,0)+IF($H27="",1,0)+IF($I27="",1,0)+IF($K27="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B27="","",IF($A27="",1,0)+IF($B27="",1,0)+IF($C27="",1,0)+IF($D27="",1,0)+IF($E27="",1,0)+IF($F27="",1,0)+IF($G27="",1,0)+IF($H27="",1,0)+IF($I27="",1,0)+IF($K27="",1,0)+IF(AND($H27="別居",$P27=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P27" s="17" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="17" t="n"/>
@@ -7992,9 +8209,10 @@
       <c r="L28" s="17" t="n"/>
       <c r="M28" s="17" t="n"/>
       <c r="O28">
-        <f>IF($B28="","",IF($A28="",1,0)+IF($B28="",1,0)+IF($C28="",1,0)+IF($D28="",1,0)+IF($E28="",1,0)+IF($F28="",1,0)+IF($G28="",1,0)+IF($H28="",1,0)+IF($I28="",1,0)+IF($K28="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B28="","",IF($A28="",1,0)+IF($B28="",1,0)+IF($C28="",1,0)+IF($D28="",1,0)+IF($E28="",1,0)+IF($F28="",1,0)+IF($G28="",1,0)+IF($H28="",1,0)+IF($I28="",1,0)+IF($K28="",1,0)+IF(AND($H28="別居",$P28=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P28" s="17" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="17" t="n"/>
@@ -8011,9 +8229,10 @@
       <c r="L29" s="17" t="n"/>
       <c r="M29" s="17" t="n"/>
       <c r="O29">
-        <f>IF($B29="","",IF($A29="",1,0)+IF($B29="",1,0)+IF($C29="",1,0)+IF($D29="",1,0)+IF($E29="",1,0)+IF($F29="",1,0)+IF($G29="",1,0)+IF($H29="",1,0)+IF($I29="",1,0)+IF($K29="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B29="","",IF($A29="",1,0)+IF($B29="",1,0)+IF($C29="",1,0)+IF($D29="",1,0)+IF($E29="",1,0)+IF($F29="",1,0)+IF($G29="",1,0)+IF($H29="",1,0)+IF($I29="",1,0)+IF($K29="",1,0)+IF(AND($H29="別居",$P29=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P29" s="17" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="17" t="n"/>
@@ -8030,9 +8249,10 @@
       <c r="L30" s="17" t="n"/>
       <c r="M30" s="17" t="n"/>
       <c r="O30">
-        <f>IF($B30="","",IF($A30="",1,0)+IF($B30="",1,0)+IF($C30="",1,0)+IF($D30="",1,0)+IF($E30="",1,0)+IF($F30="",1,0)+IF($G30="",1,0)+IF($H30="",1,0)+IF($I30="",1,0)+IF($K30="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B30="","",IF($A30="",1,0)+IF($B30="",1,0)+IF($C30="",1,0)+IF($D30="",1,0)+IF($E30="",1,0)+IF($F30="",1,0)+IF($G30="",1,0)+IF($H30="",1,0)+IF($I30="",1,0)+IF($K30="",1,0)+IF(AND($H30="別居",$P30=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P30" s="17" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="17" t="n"/>
@@ -8049,9 +8269,10 @@
       <c r="L31" s="17" t="n"/>
       <c r="M31" s="17" t="n"/>
       <c r="O31">
-        <f>IF($B31="","",IF($A31="",1,0)+IF($B31="",1,0)+IF($C31="",1,0)+IF($D31="",1,0)+IF($E31="",1,0)+IF($F31="",1,0)+IF($G31="",1,0)+IF($H31="",1,0)+IF($I31="",1,0)+IF($K31="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B31="","",IF($A31="",1,0)+IF($B31="",1,0)+IF($C31="",1,0)+IF($D31="",1,0)+IF($E31="",1,0)+IF($F31="",1,0)+IF($G31="",1,0)+IF($H31="",1,0)+IF($I31="",1,0)+IF($K31="",1,0)+IF(AND($H31="別居",$P31=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P31" s="17" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="17" t="n"/>
@@ -8068,9 +8289,10 @@
       <c r="L32" s="17" t="n"/>
       <c r="M32" s="17" t="n"/>
       <c r="O32">
-        <f>IF($B32="","",IF($A32="",1,0)+IF($B32="",1,0)+IF($C32="",1,0)+IF($D32="",1,0)+IF($E32="",1,0)+IF($F32="",1,0)+IF($G32="",1,0)+IF($H32="",1,0)+IF($I32="",1,0)+IF($K32="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B32="","",IF($A32="",1,0)+IF($B32="",1,0)+IF($C32="",1,0)+IF($D32="",1,0)+IF($E32="",1,0)+IF($F32="",1,0)+IF($G32="",1,0)+IF($H32="",1,0)+IF($I32="",1,0)+IF($K32="",1,0)+IF(AND($H32="別居",$P32=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P32" s="17" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="17" t="n"/>
@@ -8087,9 +8309,10 @@
       <c r="L33" s="17" t="n"/>
       <c r="M33" s="17" t="n"/>
       <c r="O33">
-        <f>IF($B33="","",IF($A33="",1,0)+IF($B33="",1,0)+IF($C33="",1,0)+IF($D33="",1,0)+IF($E33="",1,0)+IF($F33="",1,0)+IF($G33="",1,0)+IF($H33="",1,0)+IF($I33="",1,0)+IF($K33="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B33="","",IF($A33="",1,0)+IF($B33="",1,0)+IF($C33="",1,0)+IF($D33="",1,0)+IF($E33="",1,0)+IF($F33="",1,0)+IF($G33="",1,0)+IF($H33="",1,0)+IF($I33="",1,0)+IF($K33="",1,0)+IF(AND($H33="別居",$P33=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P33" s="17" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="17" t="n"/>
@@ -8106,9 +8329,10 @@
       <c r="L34" s="17" t="n"/>
       <c r="M34" s="17" t="n"/>
       <c r="O34">
-        <f>IF($B34="","",IF($A34="",1,0)+IF($B34="",1,0)+IF($C34="",1,0)+IF($D34="",1,0)+IF($E34="",1,0)+IF($F34="",1,0)+IF($G34="",1,0)+IF($H34="",1,0)+IF($I34="",1,0)+IF($K34="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B34="","",IF($A34="",1,0)+IF($B34="",1,0)+IF($C34="",1,0)+IF($D34="",1,0)+IF($E34="",1,0)+IF($F34="",1,0)+IF($G34="",1,0)+IF($H34="",1,0)+IF($I34="",1,0)+IF($K34="",1,0)+IF(AND($H34="別居",$P34=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P34" s="17" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="17" t="n"/>
@@ -8125,9 +8349,10 @@
       <c r="L35" s="17" t="n"/>
       <c r="M35" s="17" t="n"/>
       <c r="O35">
-        <f>IF($B35="","",IF($A35="",1,0)+IF($B35="",1,0)+IF($C35="",1,0)+IF($D35="",1,0)+IF($E35="",1,0)+IF($F35="",1,0)+IF($G35="",1,0)+IF($H35="",1,0)+IF($I35="",1,0)+IF($K35="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B35="","",IF($A35="",1,0)+IF($B35="",1,0)+IF($C35="",1,0)+IF($D35="",1,0)+IF($E35="",1,0)+IF($F35="",1,0)+IF($G35="",1,0)+IF($H35="",1,0)+IF($I35="",1,0)+IF($K35="",1,0)+IF(AND($H35="別居",$P35=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P35" s="17" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="17" t="n"/>
@@ -8144,9 +8369,10 @@
       <c r="L36" s="17" t="n"/>
       <c r="M36" s="17" t="n"/>
       <c r="O36">
-        <f>IF($B36="","",IF($A36="",1,0)+IF($B36="",1,0)+IF($C36="",1,0)+IF($D36="",1,0)+IF($E36="",1,0)+IF($F36="",1,0)+IF($G36="",1,0)+IF($H36="",1,0)+IF($I36="",1,0)+IF($K36="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B36="","",IF($A36="",1,0)+IF($B36="",1,0)+IF($C36="",1,0)+IF($D36="",1,0)+IF($E36="",1,0)+IF($F36="",1,0)+IF($G36="",1,0)+IF($H36="",1,0)+IF($I36="",1,0)+IF($K36="",1,0)+IF(AND($H36="別居",$P36=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P36" s="17" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="17" t="n"/>
@@ -8163,9 +8389,10 @@
       <c r="L37" s="17" t="n"/>
       <c r="M37" s="17" t="n"/>
       <c r="O37">
-        <f>IF($B37="","",IF($A37="",1,0)+IF($B37="",1,0)+IF($C37="",1,0)+IF($D37="",1,0)+IF($E37="",1,0)+IF($F37="",1,0)+IF($G37="",1,0)+IF($H37="",1,0)+IF($I37="",1,0)+IF($K37="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B37="","",IF($A37="",1,0)+IF($B37="",1,0)+IF($C37="",1,0)+IF($D37="",1,0)+IF($E37="",1,0)+IF($F37="",1,0)+IF($G37="",1,0)+IF($H37="",1,0)+IF($I37="",1,0)+IF($K37="",1,0)+IF(AND($H37="別居",$P37=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P37" s="17" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="17" t="n"/>
@@ -8182,9 +8409,10 @@
       <c r="L38" s="17" t="n"/>
       <c r="M38" s="17" t="n"/>
       <c r="O38">
-        <f>IF($B38="","",IF($A38="",1,0)+IF($B38="",1,0)+IF($C38="",1,0)+IF($D38="",1,0)+IF($E38="",1,0)+IF($F38="",1,0)+IF($G38="",1,0)+IF($H38="",1,0)+IF($I38="",1,0)+IF($K38="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B38="","",IF($A38="",1,0)+IF($B38="",1,0)+IF($C38="",1,0)+IF($D38="",1,0)+IF($E38="",1,0)+IF($F38="",1,0)+IF($G38="",1,0)+IF($H38="",1,0)+IF($I38="",1,0)+IF($K38="",1,0)+IF(AND($H38="別居",$P38=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P38" s="17" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="17" t="n"/>
@@ -8201,9 +8429,10 @@
       <c r="L39" s="17" t="n"/>
       <c r="M39" s="17" t="n"/>
       <c r="O39">
-        <f>IF($B39="","",IF($A39="",1,0)+IF($B39="",1,0)+IF($C39="",1,0)+IF($D39="",1,0)+IF($E39="",1,0)+IF($F39="",1,0)+IF($G39="",1,0)+IF($H39="",1,0)+IF($I39="",1,0)+IF($K39="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B39="","",IF($A39="",1,0)+IF($B39="",1,0)+IF($C39="",1,0)+IF($D39="",1,0)+IF($E39="",1,0)+IF($F39="",1,0)+IF($G39="",1,0)+IF($H39="",1,0)+IF($I39="",1,0)+IF($K39="",1,0)+IF(AND($H39="別居",$P39=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P39" s="17" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="17" t="n"/>
@@ -8220,9 +8449,10 @@
       <c r="L40" s="17" t="n"/>
       <c r="M40" s="17" t="n"/>
       <c r="O40">
-        <f>IF($B40="","",IF($A40="",1,0)+IF($B40="",1,0)+IF($C40="",1,0)+IF($D40="",1,0)+IF($E40="",1,0)+IF($F40="",1,0)+IF($G40="",1,0)+IF($H40="",1,0)+IF($I40="",1,0)+IF($K40="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B40="","",IF($A40="",1,0)+IF($B40="",1,0)+IF($C40="",1,0)+IF($D40="",1,0)+IF($E40="",1,0)+IF($F40="",1,0)+IF($G40="",1,0)+IF($H40="",1,0)+IF($I40="",1,0)+IF($K40="",1,0)+IF(AND($H40="別居",$P40=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P40" s="17" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="17" t="n"/>
@@ -8239,9 +8469,10 @@
       <c r="L41" s="17" t="n"/>
       <c r="M41" s="17" t="n"/>
       <c r="O41">
-        <f>IF($B41="","",IF($A41="",1,0)+IF($B41="",1,0)+IF($C41="",1,0)+IF($D41="",1,0)+IF($E41="",1,0)+IF($F41="",1,0)+IF($G41="",1,0)+IF($H41="",1,0)+IF($I41="",1,0)+IF($K41="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B41="","",IF($A41="",1,0)+IF($B41="",1,0)+IF($C41="",1,0)+IF($D41="",1,0)+IF($E41="",1,0)+IF($F41="",1,0)+IF($G41="",1,0)+IF($H41="",1,0)+IF($I41="",1,0)+IF($K41="",1,0)+IF(AND($H41="別居",$P41=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P41" s="17" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="17" t="n"/>
@@ -8258,9 +8489,10 @@
       <c r="L42" s="17" t="n"/>
       <c r="M42" s="17" t="n"/>
       <c r="O42">
-        <f>IF($B42="","",IF($A42="",1,0)+IF($B42="",1,0)+IF($C42="",1,0)+IF($D42="",1,0)+IF($E42="",1,0)+IF($F42="",1,0)+IF($G42="",1,0)+IF($H42="",1,0)+IF($I42="",1,0)+IF($K42="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B42="","",IF($A42="",1,0)+IF($B42="",1,0)+IF($C42="",1,0)+IF($D42="",1,0)+IF($E42="",1,0)+IF($F42="",1,0)+IF($G42="",1,0)+IF($H42="",1,0)+IF($I42="",1,0)+IF($K42="",1,0)+IF(AND($H42="別居",$P42=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P42" s="17" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="17" t="n"/>
@@ -8277,9 +8509,10 @@
       <c r="L43" s="17" t="n"/>
       <c r="M43" s="17" t="n"/>
       <c r="O43">
-        <f>IF($B43="","",IF($A43="",1,0)+IF($B43="",1,0)+IF($C43="",1,0)+IF($D43="",1,0)+IF($E43="",1,0)+IF($F43="",1,0)+IF($G43="",1,0)+IF($H43="",1,0)+IF($I43="",1,0)+IF($K43="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B43="","",IF($A43="",1,0)+IF($B43="",1,0)+IF($C43="",1,0)+IF($D43="",1,0)+IF($E43="",1,0)+IF($F43="",1,0)+IF($G43="",1,0)+IF($H43="",1,0)+IF($I43="",1,0)+IF($K43="",1,0)+IF(AND($H43="別居",$P43=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P43" s="17" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="17" t="n"/>
@@ -8296,9 +8529,10 @@
       <c r="L44" s="17" t="n"/>
       <c r="M44" s="17" t="n"/>
       <c r="O44">
-        <f>IF($B44="","",IF($A44="",1,0)+IF($B44="",1,0)+IF($C44="",1,0)+IF($D44="",1,0)+IF($E44="",1,0)+IF($F44="",1,0)+IF($G44="",1,0)+IF($H44="",1,0)+IF($I44="",1,0)+IF($K44="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B44="","",IF($A44="",1,0)+IF($B44="",1,0)+IF($C44="",1,0)+IF($D44="",1,0)+IF($E44="",1,0)+IF($F44="",1,0)+IF($G44="",1,0)+IF($H44="",1,0)+IF($I44="",1,0)+IF($K44="",1,0)+IF(AND($H44="別居",$P44=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P44" s="17" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="17" t="n"/>
@@ -8315,9 +8549,10 @@
       <c r="L45" s="17" t="n"/>
       <c r="M45" s="17" t="n"/>
       <c r="O45">
-        <f>IF($B45="","",IF($A45="",1,0)+IF($B45="",1,0)+IF($C45="",1,0)+IF($D45="",1,0)+IF($E45="",1,0)+IF($F45="",1,0)+IF($G45="",1,0)+IF($H45="",1,0)+IF($I45="",1,0)+IF($K45="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B45="","",IF($A45="",1,0)+IF($B45="",1,0)+IF($C45="",1,0)+IF($D45="",1,0)+IF($E45="",1,0)+IF($F45="",1,0)+IF($G45="",1,0)+IF($H45="",1,0)+IF($I45="",1,0)+IF($K45="",1,0)+IF(AND($H45="別居",$P45=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P45" s="17" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="17" t="n"/>
@@ -8334,9 +8569,10 @@
       <c r="L46" s="17" t="n"/>
       <c r="M46" s="17" t="n"/>
       <c r="O46">
-        <f>IF($B46="","",IF($A46="",1,0)+IF($B46="",1,0)+IF($C46="",1,0)+IF($D46="",1,0)+IF($E46="",1,0)+IF($F46="",1,0)+IF($G46="",1,0)+IF($H46="",1,0)+IF($I46="",1,0)+IF($K46="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B46="","",IF($A46="",1,0)+IF($B46="",1,0)+IF($C46="",1,0)+IF($D46="",1,0)+IF($E46="",1,0)+IF($F46="",1,0)+IF($G46="",1,0)+IF($H46="",1,0)+IF($I46="",1,0)+IF($K46="",1,0)+IF(AND($H46="別居",$P46=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P46" s="17" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="17" t="n"/>
@@ -8353,9 +8589,10 @@
       <c r="L47" s="17" t="n"/>
       <c r="M47" s="17" t="n"/>
       <c r="O47">
-        <f>IF($B47="","",IF($A47="",1,0)+IF($B47="",1,0)+IF($C47="",1,0)+IF($D47="",1,0)+IF($E47="",1,0)+IF($F47="",1,0)+IF($G47="",1,0)+IF($H47="",1,0)+IF($I47="",1,0)+IF($K47="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B47="","",IF($A47="",1,0)+IF($B47="",1,0)+IF($C47="",1,0)+IF($D47="",1,0)+IF($E47="",1,0)+IF($F47="",1,0)+IF($G47="",1,0)+IF($H47="",1,0)+IF($I47="",1,0)+IF($K47="",1,0)+IF(AND($H47="別居",$P47=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P47" s="17" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="17" t="n"/>
@@ -8372,9 +8609,10 @@
       <c r="L48" s="17" t="n"/>
       <c r="M48" s="17" t="n"/>
       <c r="O48">
-        <f>IF($B48="","",IF($A48="",1,0)+IF($B48="",1,0)+IF($C48="",1,0)+IF($D48="",1,0)+IF($E48="",1,0)+IF($F48="",1,0)+IF($G48="",1,0)+IF($H48="",1,0)+IF($I48="",1,0)+IF($K48="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B48="","",IF($A48="",1,0)+IF($B48="",1,0)+IF($C48="",1,0)+IF($D48="",1,0)+IF($E48="",1,0)+IF($F48="",1,0)+IF($G48="",1,0)+IF($H48="",1,0)+IF($I48="",1,0)+IF($K48="",1,0)+IF(AND($H48="別居",$P48=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P48" s="17" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="17" t="n"/>
@@ -8391,9 +8629,10 @@
       <c r="L49" s="17" t="n"/>
       <c r="M49" s="17" t="n"/>
       <c r="O49">
-        <f>IF($B49="","",IF($A49="",1,0)+IF($B49="",1,0)+IF($C49="",1,0)+IF($D49="",1,0)+IF($E49="",1,0)+IF($F49="",1,0)+IF($G49="",1,0)+IF($H49="",1,0)+IF($I49="",1,0)+IF($K49="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B49="","",IF($A49="",1,0)+IF($B49="",1,0)+IF($C49="",1,0)+IF($D49="",1,0)+IF($E49="",1,0)+IF($F49="",1,0)+IF($G49="",1,0)+IF($H49="",1,0)+IF($I49="",1,0)+IF($K49="",1,0)+IF(AND($H49="別居",$P49=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P49" s="17" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="17" t="n"/>
@@ -8410,9 +8649,10 @@
       <c r="L50" s="17" t="n"/>
       <c r="M50" s="17" t="n"/>
       <c r="O50">
-        <f>IF($B50="","",IF($A50="",1,0)+IF($B50="",1,0)+IF($C50="",1,0)+IF($D50="",1,0)+IF($E50="",1,0)+IF($F50="",1,0)+IF($G50="",1,0)+IF($H50="",1,0)+IF($I50="",1,0)+IF($K50="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B50="","",IF($A50="",1,0)+IF($B50="",1,0)+IF($C50="",1,0)+IF($D50="",1,0)+IF($E50="",1,0)+IF($F50="",1,0)+IF($G50="",1,0)+IF($H50="",1,0)+IF($I50="",1,0)+IF($K50="",1,0)+IF(AND($H50="別居",$P50=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P50" s="17" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="17" t="n"/>
@@ -8429,9 +8669,10 @@
       <c r="L51" s="17" t="n"/>
       <c r="M51" s="17" t="n"/>
       <c r="O51">
-        <f>IF($B51="","",IF($A51="",1,0)+IF($B51="",1,0)+IF($C51="",1,0)+IF($D51="",1,0)+IF($E51="",1,0)+IF($F51="",1,0)+IF($G51="",1,0)+IF($H51="",1,0)+IF($I51="",1,0)+IF($K51="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B51="","",IF($A51="",1,0)+IF($B51="",1,0)+IF($C51="",1,0)+IF($D51="",1,0)+IF($E51="",1,0)+IF($F51="",1,0)+IF($G51="",1,0)+IF($H51="",1,0)+IF($I51="",1,0)+IF($K51="",1,0)+IF(AND($H51="別居",$P51=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P51" s="17" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="17" t="n"/>
@@ -8448,9 +8689,10 @@
       <c r="L52" s="17" t="n"/>
       <c r="M52" s="17" t="n"/>
       <c r="O52">
-        <f>IF($B52="","",IF($A52="",1,0)+IF($B52="",1,0)+IF($C52="",1,0)+IF($D52="",1,0)+IF($E52="",1,0)+IF($F52="",1,0)+IF($G52="",1,0)+IF($H52="",1,0)+IF($I52="",1,0)+IF($K52="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B52="","",IF($A52="",1,0)+IF($B52="",1,0)+IF($C52="",1,0)+IF($D52="",1,0)+IF($E52="",1,0)+IF($F52="",1,0)+IF($G52="",1,0)+IF($H52="",1,0)+IF($I52="",1,0)+IF($K52="",1,0)+IF(AND($H52="別居",$P52=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P52" s="17" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="17" t="n"/>
@@ -8467,9 +8709,10 @@
       <c r="L53" s="17" t="n"/>
       <c r="M53" s="17" t="n"/>
       <c r="O53">
-        <f>IF($B53="","",IF($A53="",1,0)+IF($B53="",1,0)+IF($C53="",1,0)+IF($D53="",1,0)+IF($E53="",1,0)+IF($F53="",1,0)+IF($G53="",1,0)+IF($H53="",1,0)+IF($I53="",1,0)+IF($K53="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B53="","",IF($A53="",1,0)+IF($B53="",1,0)+IF($C53="",1,0)+IF($D53="",1,0)+IF($E53="",1,0)+IF($F53="",1,0)+IF($G53="",1,0)+IF($H53="",1,0)+IF($I53="",1,0)+IF($K53="",1,0)+IF(AND($H53="別居",$P53=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P53" s="17" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="17" t="n"/>
@@ -8486,9 +8729,10 @@
       <c r="L54" s="17" t="n"/>
       <c r="M54" s="17" t="n"/>
       <c r="O54">
-        <f>IF($B54="","",IF($A54="",1,0)+IF($B54="",1,0)+IF($C54="",1,0)+IF($D54="",1,0)+IF($E54="",1,0)+IF($F54="",1,0)+IF($G54="",1,0)+IF($H54="",1,0)+IF($I54="",1,0)+IF($K54="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B54="","",IF($A54="",1,0)+IF($B54="",1,0)+IF($C54="",1,0)+IF($D54="",1,0)+IF($E54="",1,0)+IF($F54="",1,0)+IF($G54="",1,0)+IF($H54="",1,0)+IF($I54="",1,0)+IF($K54="",1,0)+IF(AND($H54="別居",$P54=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P54" s="17" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="17" t="n"/>
@@ -8505,9 +8749,10 @@
       <c r="L55" s="17" t="n"/>
       <c r="M55" s="17" t="n"/>
       <c r="O55">
-        <f>IF($B55="","",IF($A55="",1,0)+IF($B55="",1,0)+IF($C55="",1,0)+IF($D55="",1,0)+IF($E55="",1,0)+IF($F55="",1,0)+IF($G55="",1,0)+IF($H55="",1,0)+IF($I55="",1,0)+IF($K55="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B55="","",IF($A55="",1,0)+IF($B55="",1,0)+IF($C55="",1,0)+IF($D55="",1,0)+IF($E55="",1,0)+IF($F55="",1,0)+IF($G55="",1,0)+IF($H55="",1,0)+IF($I55="",1,0)+IF($K55="",1,0)+IF(AND($H55="別居",$P55=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P55" s="17" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="17" t="n"/>
@@ -8524,9 +8769,10 @@
       <c r="L56" s="17" t="n"/>
       <c r="M56" s="17" t="n"/>
       <c r="O56">
-        <f>IF($B56="","",IF($A56="",1,0)+IF($B56="",1,0)+IF($C56="",1,0)+IF($D56="",1,0)+IF($E56="",1,0)+IF($F56="",1,0)+IF($G56="",1,0)+IF($H56="",1,0)+IF($I56="",1,0)+IF($K56="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B56="","",IF($A56="",1,0)+IF($B56="",1,0)+IF($C56="",1,0)+IF($D56="",1,0)+IF($E56="",1,0)+IF($F56="",1,0)+IF($G56="",1,0)+IF($H56="",1,0)+IF($I56="",1,0)+IF($K56="",1,0)+IF(AND($H56="別居",$P56=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P56" s="17" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="17" t="n"/>
@@ -8543,9 +8789,10 @@
       <c r="L57" s="17" t="n"/>
       <c r="M57" s="17" t="n"/>
       <c r="O57">
-        <f>IF($B57="","",IF($A57="",1,0)+IF($B57="",1,0)+IF($C57="",1,0)+IF($D57="",1,0)+IF($E57="",1,0)+IF($F57="",1,0)+IF($G57="",1,0)+IF($H57="",1,0)+IF($I57="",1,0)+IF($K57="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B57="","",IF($A57="",1,0)+IF($B57="",1,0)+IF($C57="",1,0)+IF($D57="",1,0)+IF($E57="",1,0)+IF($F57="",1,0)+IF($G57="",1,0)+IF($H57="",1,0)+IF($I57="",1,0)+IF($K57="",1,0)+IF(AND($H57="別居",$P57=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P57" s="17" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="17" t="n"/>
@@ -8562,9 +8809,10 @@
       <c r="L58" s="17" t="n"/>
       <c r="M58" s="17" t="n"/>
       <c r="O58">
-        <f>IF($B58="","",IF($A58="",1,0)+IF($B58="",1,0)+IF($C58="",1,0)+IF($D58="",1,0)+IF($E58="",1,0)+IF($F58="",1,0)+IF($G58="",1,0)+IF($H58="",1,0)+IF($I58="",1,0)+IF($K58="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B58="","",IF($A58="",1,0)+IF($B58="",1,0)+IF($C58="",1,0)+IF($D58="",1,0)+IF($E58="",1,0)+IF($F58="",1,0)+IF($G58="",1,0)+IF($H58="",1,0)+IF($I58="",1,0)+IF($K58="",1,0)+IF(AND($H58="別居",$P58=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P58" s="17" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="17" t="n"/>
@@ -8581,9 +8829,10 @@
       <c r="L59" s="17" t="n"/>
       <c r="M59" s="17" t="n"/>
       <c r="O59">
-        <f>IF($B59="","",IF($A59="",1,0)+IF($B59="",1,0)+IF($C59="",1,0)+IF($D59="",1,0)+IF($E59="",1,0)+IF($F59="",1,0)+IF($G59="",1,0)+IF($H59="",1,0)+IF($I59="",1,0)+IF($K59="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B59="","",IF($A59="",1,0)+IF($B59="",1,0)+IF($C59="",1,0)+IF($D59="",1,0)+IF($E59="",1,0)+IF($F59="",1,0)+IF($G59="",1,0)+IF($H59="",1,0)+IF($I59="",1,0)+IF($K59="",1,0)+IF(AND($H59="別居",$P59=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P59" s="17" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="17" t="n"/>
@@ -8600,9 +8849,10 @@
       <c r="L60" s="17" t="n"/>
       <c r="M60" s="17" t="n"/>
       <c r="O60">
-        <f>IF($B60="","",IF($A60="",1,0)+IF($B60="",1,0)+IF($C60="",1,0)+IF($D60="",1,0)+IF($E60="",1,0)+IF($F60="",1,0)+IF($G60="",1,0)+IF($H60="",1,0)+IF($I60="",1,0)+IF($K60="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B60="","",IF($A60="",1,0)+IF($B60="",1,0)+IF($C60="",1,0)+IF($D60="",1,0)+IF($E60="",1,0)+IF($F60="",1,0)+IF($G60="",1,0)+IF($H60="",1,0)+IF($I60="",1,0)+IF($K60="",1,0)+IF(AND($H60="別居",$P60=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P60" s="17" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="17" t="n"/>
@@ -8619,9 +8869,10 @@
       <c r="L61" s="17" t="n"/>
       <c r="M61" s="17" t="n"/>
       <c r="O61">
-        <f>IF($B61="","",IF($A61="",1,0)+IF($B61="",1,0)+IF($C61="",1,0)+IF($D61="",1,0)+IF($E61="",1,0)+IF($F61="",1,0)+IF($G61="",1,0)+IF($H61="",1,0)+IF($I61="",1,0)+IF($K61="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B61="","",IF($A61="",1,0)+IF($B61="",1,0)+IF($C61="",1,0)+IF($D61="",1,0)+IF($E61="",1,0)+IF($F61="",1,0)+IF($G61="",1,0)+IF($H61="",1,0)+IF($I61="",1,0)+IF($K61="",1,0)+IF(AND($H61="別居",$P61=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P61" s="17" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="17" t="n"/>
@@ -8638,9 +8889,10 @@
       <c r="L62" s="17" t="n"/>
       <c r="M62" s="17" t="n"/>
       <c r="O62">
-        <f>IF($B62="","",IF($A62="",1,0)+IF($B62="",1,0)+IF($C62="",1,0)+IF($D62="",1,0)+IF($E62="",1,0)+IF($F62="",1,0)+IF($G62="",1,0)+IF($H62="",1,0)+IF($I62="",1,0)+IF($K62="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B62="","",IF($A62="",1,0)+IF($B62="",1,0)+IF($C62="",1,0)+IF($D62="",1,0)+IF($E62="",1,0)+IF($F62="",1,0)+IF($G62="",1,0)+IF($H62="",1,0)+IF($I62="",1,0)+IF($K62="",1,0)+IF(AND($H62="別居",$P62=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P62" s="17" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="17" t="n"/>
@@ -8657,9 +8909,10 @@
       <c r="L63" s="17" t="n"/>
       <c r="M63" s="17" t="n"/>
       <c r="O63">
-        <f>IF($B63="","",IF($A63="",1,0)+IF($B63="",1,0)+IF($C63="",1,0)+IF($D63="",1,0)+IF($E63="",1,0)+IF($F63="",1,0)+IF($G63="",1,0)+IF($H63="",1,0)+IF($I63="",1,0)+IF($K63="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B63="","",IF($A63="",1,0)+IF($B63="",1,0)+IF($C63="",1,0)+IF($D63="",1,0)+IF($E63="",1,0)+IF($F63="",1,0)+IF($G63="",1,0)+IF($H63="",1,0)+IF($I63="",1,0)+IF($K63="",1,0)+IF(AND($H63="別居",$P63=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P63" s="17" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="17" t="n"/>
@@ -8676,9 +8929,10 @@
       <c r="L64" s="17" t="n"/>
       <c r="M64" s="17" t="n"/>
       <c r="O64">
-        <f>IF($B64="","",IF($A64="",1,0)+IF($B64="",1,0)+IF($C64="",1,0)+IF($D64="",1,0)+IF($E64="",1,0)+IF($F64="",1,0)+IF($G64="",1,0)+IF($H64="",1,0)+IF($I64="",1,0)+IF($K64="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B64="","",IF($A64="",1,0)+IF($B64="",1,0)+IF($C64="",1,0)+IF($D64="",1,0)+IF($E64="",1,0)+IF($F64="",1,0)+IF($G64="",1,0)+IF($H64="",1,0)+IF($I64="",1,0)+IF($K64="",1,0)+IF(AND($H64="別居",$P64=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P64" s="17" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="17" t="n"/>
@@ -8695,9 +8949,10 @@
       <c r="L65" s="17" t="n"/>
       <c r="M65" s="17" t="n"/>
       <c r="O65">
-        <f>IF($B65="","",IF($A65="",1,0)+IF($B65="",1,0)+IF($C65="",1,0)+IF($D65="",1,0)+IF($E65="",1,0)+IF($F65="",1,0)+IF($G65="",1,0)+IF($H65="",1,0)+IF($I65="",1,0)+IF($K65="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B65="","",IF($A65="",1,0)+IF($B65="",1,0)+IF($C65="",1,0)+IF($D65="",1,0)+IF($E65="",1,0)+IF($F65="",1,0)+IF($G65="",1,0)+IF($H65="",1,0)+IF($I65="",1,0)+IF($K65="",1,0)+IF(AND($H65="別居",$P65=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P65" s="17" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="17" t="n"/>
@@ -8714,9 +8969,10 @@
       <c r="L66" s="17" t="n"/>
       <c r="M66" s="17" t="n"/>
       <c r="O66">
-        <f>IF($B66="","",IF($A66="",1,0)+IF($B66="",1,0)+IF($C66="",1,0)+IF($D66="",1,0)+IF($E66="",1,0)+IF($F66="",1,0)+IF($G66="",1,0)+IF($H66="",1,0)+IF($I66="",1,0)+IF($K66="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B66="","",IF($A66="",1,0)+IF($B66="",1,0)+IF($C66="",1,0)+IF($D66="",1,0)+IF($E66="",1,0)+IF($F66="",1,0)+IF($G66="",1,0)+IF($H66="",1,0)+IF($I66="",1,0)+IF($K66="",1,0)+IF(AND($H66="別居",$P66=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P66" s="17" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="17" t="n"/>
@@ -8733,16 +8989,17 @@
       <c r="L67" s="17" t="n"/>
       <c r="M67" s="17" t="n"/>
       <c r="O67">
-        <f>IF($B67="","",IF($A67="",1,0)+IF($B67="",1,0)+IF($C67="",1,0)+IF($D67="",1,0)+IF($E67="",1,0)+IF($F67="",1,0)+IF($G67="",1,0)+IF($H67="",1,0)+IF($I67="",1,0)+IF($K67="",1,0))</f>
-        <v/>
-      </c>
+        <f>IF($B67="","",IF($A67="",1,0)+IF($B67="",1,0)+IF($C67="",1,0)+IF($D67="",1,0)+IF($E67="",1,0)+IF($F67="",1,0)+IF($G67="",1,0)+IF($H67="",1,0)+IF($I67="",1,0)+IF($K67="",1,0)+IF(AND($H67="別居",$P67=""),1,0))</f>
+        <v/>
+      </c>
+      <c r="P67" s="17" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="E4:F4"/>
-    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A1:P1"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="G3:H3"/>
@@ -8832,7 +9089,12 @@
       <formula>AND(B8&lt;&gt;"",ISERROR(FIND("　",B8)),ISERROR(FIND(" ",B8)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="9">
+  <conditionalFormatting sqref="P8:P67">
+    <cfRule type="expression" priority="19" dxfId="2" stopIfTrue="1">
+      <formula>AND($H8="別居",P8="")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="10">
     <dataValidation sqref="A7:A67" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="入力エラー" error="整数で入力してください。" promptTitle="入力のヒント" prompt="シート①の『フォーム内No.』（左端の番号）を入力。どの従業員の被扶養者かを紐付けます。" type="whole" errorStyle="stop" operator="between">
       <formula1>1</formula1>
       <formula2>9999</formula2>
@@ -8864,6 +9126,7 @@
     <dataValidation sqref="G7:G67" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="入力のヒント" prompt="12桁の数字。ハイフン無し。会社所定の安全な経路で別提出する場合は、ドロップダウンから『別経路提出』を選んでください。入社時点で未回収なら『後日提出』を選択します。" type="list">
       <formula1>m_番号提出状態</formula1>
     </dataValidation>
+    <dataValidation sqref="P7:P67" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="入力のヒント" prompt="同居・別居が『別居』のときにご記入ください（郵便番号・都道府県から）。"/>
   </dataValidations>
   <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8879,7 +9142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R48"/>
+  <dimension ref="A1:S48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8900,6 +9163,7 @@
     <col width="16" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="24" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="20.5" customHeight="1">
@@ -8993,6 +9257,11 @@
           <t>都道府県</t>
         </is>
       </c>
+      <c r="S1" s="65" t="inlineStr">
+        <is>
+          <t>職種</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="66" t="inlineStr">
@@ -9085,6 +9354,11 @@
           <t>北海道</t>
         </is>
       </c>
+      <c r="S2" s="66" t="inlineStr">
+        <is>
+          <t>専門的・技術的職業</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="66" t="inlineStr">
@@ -9172,6 +9446,11 @@
           <t>青森県</t>
         </is>
       </c>
+      <c r="S3" s="66" t="inlineStr">
+        <is>
+          <t>管理的職業</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="B4" s="66" t="inlineStr">
@@ -9214,6 +9493,11 @@
           <t>岩手県</t>
         </is>
       </c>
+      <c r="S4" s="66" t="inlineStr">
+        <is>
+          <t>事務的職業</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="B5" s="66" t="inlineStr">
@@ -9236,6 +9520,11 @@
           <t>宮城県</t>
         </is>
       </c>
+      <c r="S5" s="66" t="inlineStr">
+        <is>
+          <t>販売の職業</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="B6" s="66" t="inlineStr">
@@ -9258,6 +9547,11 @@
           <t>秋田県</t>
         </is>
       </c>
+      <c r="S6" s="66" t="inlineStr">
+        <is>
+          <t>サービスの職業</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="B7" s="66" t="inlineStr">
@@ -9275,6 +9569,11 @@
           <t>山形県</t>
         </is>
       </c>
+      <c r="S7" s="66" t="inlineStr">
+        <is>
+          <t>保安の職業</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="N8" s="66" t="inlineStr">
@@ -9287,6 +9586,11 @@
           <t>福島県</t>
         </is>
       </c>
+      <c r="S8" s="66" t="inlineStr">
+        <is>
+          <t>農林漁業の職業</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="R9" s="66" t="inlineStr">
@@ -9294,6 +9598,11 @@
           <t>茨城県</t>
         </is>
       </c>
+      <c r="S9" s="66" t="inlineStr">
+        <is>
+          <t>生産工程の職業</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="R10" s="66" t="inlineStr">
@@ -9301,6 +9610,11 @@
           <t>栃木県</t>
         </is>
       </c>
+      <c r="S10" s="66" t="inlineStr">
+        <is>
+          <t>輸送・機械運転の職業</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="R11" s="66" t="inlineStr">
@@ -9308,6 +9622,11 @@
           <t>群馬県</t>
         </is>
       </c>
+      <c r="S11" s="66" t="inlineStr">
+        <is>
+          <t>建設・採掘の職業</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="R12" s="66" t="inlineStr">
@@ -9315,11 +9634,21 @@
           <t>埼玉県</t>
         </is>
       </c>
+      <c r="S12" s="66" t="inlineStr">
+        <is>
+          <t>運搬・清掃・包装等の職業</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="R13" s="66" t="inlineStr">
         <is>
           <t>千葉県</t>
+        </is>
+      </c>
+      <c r="S13" s="66" t="inlineStr">
+        <is>
+          <t>分からない</t>
         </is>
       </c>
     </row>

--- a/go/xlsx/nyusha-juryo-form.xlsx
+++ b/go/xlsx/nyusha-juryo-form.xlsx
@@ -41,6 +41,7 @@
     <definedName name="正社員月所定">'⓪ 事業所設定'!$C$14</definedName>
     <definedName name="判定基準日">'⓪ 事業所設定'!$C$17</definedName>
     <definedName name="m_職種">'_マスタ（非表示）'!$S$2:$S$13</definedName>
+    <definedName name="m_現物給与種類">'_マスタ（非表示）'!$T$2:$T$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'⓪ 事業所設定'!$1:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'① 従業員情報（本人）'!$1:$7</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'② 被扶養者情報'!$1:$6</definedName>
@@ -718,6 +719,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>社労士フォーム</author>
+    <author>点検</author>
   </authors>
   <commentList>
     <comment ref="A7" authorId="0" shapeId="0">
@@ -953,6 +955,11 @@
     <comment ref="AX7" authorId="0" shapeId="0">
       <text>
         <t>用途：他社でも社会保険（健康保険・厚生年金）に加入しているか。『はい』のときは二以上事業所勤務届が別途必要です。</t>
+      </text>
+    </comment>
+    <comment ref="AY7" authorId="1" shapeId="0">
+      <text>
+        <t>用途：報酬月額に算入する現物給与の種類。都道府県別の標準価額で算定するのが原則〔健保法46条・厚年法25条ほか、要確認〕なので、種類が分からないと金額を検算できません。</t>
       </text>
     </comment>
   </commentList>
@@ -1875,7 +1882,7 @@
         </is>
       </c>
       <c r="C12" s="23">
-        <f>IF('① 従業員情報（本人）'!B4=0,"未入力（対象者なし）",IF(AND('① 従業員情報（本人）'!F4=0,'① 従業員情報（本人）'!D4&lt;&gt;'① 従業員情報（本人）'!B4),"確認が必要：式の入っていない行があります（行を挿入せず9〜58行にご記入ください）",IF(COUNTBLANK('⓪ 事業所設定'!$C$6)+COUNTBLANK('⓪ 事業所設定'!$C$8)+COUNTBLANK('⓪ 事業所設定'!$C$9)+COUNTBLANK('⓪ 事業所設定'!$C$11)+COUNTBLANK('⓪ 事業所設定'!$C$13)+COUNTBLANK('⓪ 事業所設定'!$C$14)+COUNTBLANK('⓪ 事業所設定'!$C$17)&gt;0,"未入力あり：⓪事業所設定をご記入ください",IF('① 従業員情報（本人）'!F4&gt;0,"未入力あり：本体シートの薄赤セル・行ステータスをご確認ください",IF('② 被扶養者情報'!E4&gt;0,"未入力あり：②被扶養者情報をご確認ください",IF(ISNUMBER(SEARCH("未入力",$C$13)),"未入力あり：被扶養者ありの方の②をご記入ください","提出可（必須の未入力なし）"))))))</f>
+        <f>IF('① 従業員情報（本人）'!B4=0,"未入力（対象者なし）",IF(AND('① 従業員情報（本人）'!F4=0,'① 従業員情報（本人）'!D4&lt;&gt;'① 従業員情報（本人）'!B4),"確認が必要：式の入っていない行があります（行を挿入せず9〜58行にご記入ください）",IF(COUNTBLANK('⓪ 事業所設定'!$C$6)+COUNTBLANK('⓪ 事業所設定'!$C$8)+COUNTBLANK('⓪ 事業所設定'!$C$9)+COUNTBLANK('⓪ 事業所設定'!$C$11)+COUNTBLANK('⓪ 事業所設定'!$C$13)+COUNTBLANK('⓪ 事業所設定'!$C$14)+COUNTBLANK('⓪ 事業所設定'!$C$17)+COUNTBLANK('⓪ 事業所設定'!$C$19)+COUNTBLANK('⓪ 事業所設定'!$C$20)+COUNTBLANK('⓪ 事業所設定'!$C$21)&gt;0,"未入力あり：⓪事業所設定をご記入ください",IF('① 従業員情報（本人）'!F4&gt;0,"未入力あり：本体シートの薄赤セル・行ステータスをご確認ください",IF('② 被扶養者情報'!E4&gt;0,"未入力あり：②被扶養者情報をご確認ください",IF(ISNUMBER(SEARCH("未入力",$C$13)),"未入力あり：被扶養者ありの方の②をご記入ください","提出可（必須の未入力なし）"))))))</f>
         <v/>
       </c>
       <c r="D12" s="18" t="inlineStr">
@@ -2121,7 +2128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:D18"/>
+  <dimension ref="B1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2339,6 +2346,45 @@
       <c r="D18" s="33" t="inlineStr">
         <is>
           <t>任意。参考情報として保持。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="38" customHeight="1">
+      <c r="B19" s="31" t="inlineStr">
+        <is>
+          <t>【必】 健康保険・厚生年金の事業所整理記号</t>
+        </is>
+      </c>
+      <c r="C19" s="35" t="n"/>
+      <c r="D19" s="33" t="inlineStr">
+        <is>
+          <t>毎月20日ごろ年金事務所から届く「保険料納入告知額・領収済額通知書」に載っています。口座振替の会社は別名の紙で届きます。例）12-アイウ</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="38" customHeight="1">
+      <c r="B20" s="31" t="inlineStr">
+        <is>
+          <t>【必】 同 事業所番号</t>
+        </is>
+      </c>
+      <c r="C20" s="35" t="n"/>
+      <c r="D20" s="33" t="inlineStr">
+        <is>
+          <t>同じ紙の、整理記号の隣にある番号です。5桁。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="38" customHeight="1">
+      <c r="B21" s="31" t="inlineStr">
+        <is>
+          <t>【必】 雇用保険の事業所番号</t>
+        </is>
+      </c>
+      <c r="C21" s="35" t="n"/>
+      <c r="D21" s="33" t="inlineStr">
+        <is>
+          <t>「雇用保険適用事業所設置届 事業主控」または資格取得等確認通知書に載っています。4桁-6桁-1桁。例）1610-123456-7</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2428,7 @@
       <formula>C17=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="8">
+  <dataValidations count="11">
     <dataValidation sqref="C7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="入力エラー" error="13桁で入力してください。" promptTitle="入力のヒント" prompt="13桁の法人番号（任意）。" type="textLength" errorStyle="warning" operator="equal">
       <formula1>13</formula1>
     </dataValidation>
@@ -2412,6 +2458,18 @@
       <formula1>0</formula1>
       <formula2>100000</formula2>
     </dataValidation>
+    <dataValidation sqref="C19" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="ご記入のお願い" prompt="資格取得届の事業所整理記号欄。初めて社会保険に加入する会社は「新規適用の申請中」とご記入ください。" type="textLength" operator="between">
+      <formula1>1</formula1>
+      <formula2>30</formula2>
+    </dataValidation>
+    <dataValidation sqref="C20" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="ご記入のお願い" prompt="資格取得届の事業所番号欄。" type="textLength" operator="between">
+      <formula1>1</formula1>
+      <formula2>30</formula2>
+    </dataValidation>
+    <dataValidation sqref="C21" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="ご記入のお願い" prompt="雇用保険 資格取得届の事業所番号欄。初めて雇用保険に加入する会社は「新規適用の申請中」とご記入ください。" type="textLength" operator="between">
+      <formula1>1</formula1>
+      <formula2>30</formula2>
+    </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2425,7 +2483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AX58"/>
+  <dimension ref="A1:AY58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2478,6 +2536,7 @@
     <col width="22" customWidth="1" min="48" max="48"/>
     <col width="22" customWidth="1" min="49" max="49"/>
     <col width="22" customWidth="1" min="50" max="50"/>
+    <col width="22" customWidth="1" min="51" max="51"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -2671,6 +2730,7 @@
       </c>
       <c r="AW6" s="76" t="n"/>
       <c r="AX6" s="74" t="n"/>
+      <c r="AY6" s="74" t="n"/>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
@@ -2954,6 +3014,12 @@
         <is>
           <t>他社でも社会保険に加入
 【任】</t>
+        </is>
+      </c>
+      <c r="AY7" s="6" t="inlineStr">
+        <is>
+          <t>現物給与の種類
+【条件必須】現物給与があるとき</t>
         </is>
       </c>
     </row>
@@ -3126,6 +3192,11 @@
       <c r="AX8" s="54" t="inlineStr">
         <is>
           <t>いいえ</t>
+        </is>
+      </c>
+      <c r="AY8" s="54" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -3209,6 +3280,7 @@
       <c r="AV9" s="17" t="n"/>
       <c r="AW9" s="59" t="n"/>
       <c r="AX9" s="17" t="n"/>
+      <c r="AY9" s="17" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="23">
@@ -3290,6 +3362,7 @@
       <c r="AV10" s="17" t="n"/>
       <c r="AW10" s="59" t="n"/>
       <c r="AX10" s="17" t="n"/>
+      <c r="AY10" s="17" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="23">
@@ -3371,6 +3444,7 @@
       <c r="AV11" s="17" t="n"/>
       <c r="AW11" s="59" t="n"/>
       <c r="AX11" s="17" t="n"/>
+      <c r="AY11" s="17" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="23">
@@ -3452,6 +3526,7 @@
       <c r="AV12" s="17" t="n"/>
       <c r="AW12" s="59" t="n"/>
       <c r="AX12" s="17" t="n"/>
+      <c r="AY12" s="17" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="23">
@@ -3533,6 +3608,7 @@
       <c r="AV13" s="17" t="n"/>
       <c r="AW13" s="59" t="n"/>
       <c r="AX13" s="17" t="n"/>
+      <c r="AY13" s="17" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="23">
@@ -3614,6 +3690,7 @@
       <c r="AV14" s="17" t="n"/>
       <c r="AW14" s="59" t="n"/>
       <c r="AX14" s="17" t="n"/>
+      <c r="AY14" s="17" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="23">
@@ -3695,6 +3772,7 @@
       <c r="AV15" s="17" t="n"/>
       <c r="AW15" s="59" t="n"/>
       <c r="AX15" s="17" t="n"/>
+      <c r="AY15" s="17" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="23">
@@ -3776,6 +3854,7 @@
       <c r="AV16" s="17" t="n"/>
       <c r="AW16" s="59" t="n"/>
       <c r="AX16" s="17" t="n"/>
+      <c r="AY16" s="17" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="23">
@@ -3857,6 +3936,7 @@
       <c r="AV17" s="17" t="n"/>
       <c r="AW17" s="59" t="n"/>
       <c r="AX17" s="17" t="n"/>
+      <c r="AY17" s="17" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="23">
@@ -3938,6 +4018,7 @@
       <c r="AV18" s="17" t="n"/>
       <c r="AW18" s="59" t="n"/>
       <c r="AX18" s="17" t="n"/>
+      <c r="AY18" s="17" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="23">
@@ -4019,6 +4100,7 @@
       <c r="AV19" s="17" t="n"/>
       <c r="AW19" s="59" t="n"/>
       <c r="AX19" s="17" t="n"/>
+      <c r="AY19" s="17" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="23">
@@ -4100,6 +4182,7 @@
       <c r="AV20" s="17" t="n"/>
       <c r="AW20" s="59" t="n"/>
       <c r="AX20" s="17" t="n"/>
+      <c r="AY20" s="17" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="23">
@@ -4181,6 +4264,7 @@
       <c r="AV21" s="17" t="n"/>
       <c r="AW21" s="59" t="n"/>
       <c r="AX21" s="17" t="n"/>
+      <c r="AY21" s="17" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="23">
@@ -4262,6 +4346,7 @@
       <c r="AV22" s="17" t="n"/>
       <c r="AW22" s="59" t="n"/>
       <c r="AX22" s="17" t="n"/>
+      <c r="AY22" s="17" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="23">
@@ -4343,6 +4428,7 @@
       <c r="AV23" s="17" t="n"/>
       <c r="AW23" s="59" t="n"/>
       <c r="AX23" s="17" t="n"/>
+      <c r="AY23" s="17" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="23">
@@ -4424,6 +4510,7 @@
       <c r="AV24" s="17" t="n"/>
       <c r="AW24" s="59" t="n"/>
       <c r="AX24" s="17" t="n"/>
+      <c r="AY24" s="17" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="23">
@@ -4505,6 +4592,7 @@
       <c r="AV25" s="17" t="n"/>
       <c r="AW25" s="59" t="n"/>
       <c r="AX25" s="17" t="n"/>
+      <c r="AY25" s="17" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="23">
@@ -4586,6 +4674,7 @@
       <c r="AV26" s="17" t="n"/>
       <c r="AW26" s="59" t="n"/>
       <c r="AX26" s="17" t="n"/>
+      <c r="AY26" s="17" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="23">
@@ -4667,6 +4756,7 @@
       <c r="AV27" s="17" t="n"/>
       <c r="AW27" s="59" t="n"/>
       <c r="AX27" s="17" t="n"/>
+      <c r="AY27" s="17" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="23">
@@ -4748,6 +4838,7 @@
       <c r="AV28" s="17" t="n"/>
       <c r="AW28" s="59" t="n"/>
       <c r="AX28" s="17" t="n"/>
+      <c r="AY28" s="17" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="23">
@@ -4829,6 +4920,7 @@
       <c r="AV29" s="17" t="n"/>
       <c r="AW29" s="59" t="n"/>
       <c r="AX29" s="17" t="n"/>
+      <c r="AY29" s="17" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="23">
@@ -4910,6 +5002,7 @@
       <c r="AV30" s="17" t="n"/>
       <c r="AW30" s="59" t="n"/>
       <c r="AX30" s="17" t="n"/>
+      <c r="AY30" s="17" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="23">
@@ -4991,6 +5084,7 @@
       <c r="AV31" s="17" t="n"/>
       <c r="AW31" s="59" t="n"/>
       <c r="AX31" s="17" t="n"/>
+      <c r="AY31" s="17" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="23">
@@ -5072,6 +5166,7 @@
       <c r="AV32" s="17" t="n"/>
       <c r="AW32" s="59" t="n"/>
       <c r="AX32" s="17" t="n"/>
+      <c r="AY32" s="17" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="23">
@@ -5153,6 +5248,7 @@
       <c r="AV33" s="17" t="n"/>
       <c r="AW33" s="59" t="n"/>
       <c r="AX33" s="17" t="n"/>
+      <c r="AY33" s="17" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="23">
@@ -5234,6 +5330,7 @@
       <c r="AV34" s="17" t="n"/>
       <c r="AW34" s="59" t="n"/>
       <c r="AX34" s="17" t="n"/>
+      <c r="AY34" s="17" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="23">
@@ -5315,6 +5412,7 @@
       <c r="AV35" s="17" t="n"/>
       <c r="AW35" s="59" t="n"/>
       <c r="AX35" s="17" t="n"/>
+      <c r="AY35" s="17" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="23">
@@ -5396,6 +5494,7 @@
       <c r="AV36" s="17" t="n"/>
       <c r="AW36" s="59" t="n"/>
       <c r="AX36" s="17" t="n"/>
+      <c r="AY36" s="17" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="23">
@@ -5477,6 +5576,7 @@
       <c r="AV37" s="17" t="n"/>
       <c r="AW37" s="59" t="n"/>
       <c r="AX37" s="17" t="n"/>
+      <c r="AY37" s="17" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="23">
@@ -5558,6 +5658,7 @@
       <c r="AV38" s="17" t="n"/>
       <c r="AW38" s="59" t="n"/>
       <c r="AX38" s="17" t="n"/>
+      <c r="AY38" s="17" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="23">
@@ -5639,6 +5740,7 @@
       <c r="AV39" s="17" t="n"/>
       <c r="AW39" s="59" t="n"/>
       <c r="AX39" s="17" t="n"/>
+      <c r="AY39" s="17" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="23">
@@ -5720,6 +5822,7 @@
       <c r="AV40" s="17" t="n"/>
       <c r="AW40" s="59" t="n"/>
       <c r="AX40" s="17" t="n"/>
+      <c r="AY40" s="17" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="23">
@@ -5801,6 +5904,7 @@
       <c r="AV41" s="17" t="n"/>
       <c r="AW41" s="59" t="n"/>
       <c r="AX41" s="17" t="n"/>
+      <c r="AY41" s="17" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="23">
@@ -5882,6 +5986,7 @@
       <c r="AV42" s="17" t="n"/>
       <c r="AW42" s="59" t="n"/>
       <c r="AX42" s="17" t="n"/>
+      <c r="AY42" s="17" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="23">
@@ -5963,6 +6068,7 @@
       <c r="AV43" s="17" t="n"/>
       <c r="AW43" s="59" t="n"/>
       <c r="AX43" s="17" t="n"/>
+      <c r="AY43" s="17" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="23">
@@ -6044,6 +6150,7 @@
       <c r="AV44" s="17" t="n"/>
       <c r="AW44" s="59" t="n"/>
       <c r="AX44" s="17" t="n"/>
+      <c r="AY44" s="17" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="23">
@@ -6125,6 +6232,7 @@
       <c r="AV45" s="17" t="n"/>
       <c r="AW45" s="59" t="n"/>
       <c r="AX45" s="17" t="n"/>
+      <c r="AY45" s="17" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="23">
@@ -6206,6 +6314,7 @@
       <c r="AV46" s="17" t="n"/>
       <c r="AW46" s="59" t="n"/>
       <c r="AX46" s="17" t="n"/>
+      <c r="AY46" s="17" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="23">
@@ -6287,6 +6396,7 @@
       <c r="AV47" s="17" t="n"/>
       <c r="AW47" s="59" t="n"/>
       <c r="AX47" s="17" t="n"/>
+      <c r="AY47" s="17" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="23">
@@ -6368,6 +6478,7 @@
       <c r="AV48" s="17" t="n"/>
       <c r="AW48" s="59" t="n"/>
       <c r="AX48" s="17" t="n"/>
+      <c r="AY48" s="17" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="23">
@@ -6449,6 +6560,7 @@
       <c r="AV49" s="17" t="n"/>
       <c r="AW49" s="59" t="n"/>
       <c r="AX49" s="17" t="n"/>
+      <c r="AY49" s="17" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="23">
@@ -6530,6 +6642,7 @@
       <c r="AV50" s="17" t="n"/>
       <c r="AW50" s="59" t="n"/>
       <c r="AX50" s="17" t="n"/>
+      <c r="AY50" s="17" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="23">
@@ -6611,6 +6724,7 @@
       <c r="AV51" s="17" t="n"/>
       <c r="AW51" s="59" t="n"/>
       <c r="AX51" s="17" t="n"/>
+      <c r="AY51" s="17" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="23">
@@ -6692,6 +6806,7 @@
       <c r="AV52" s="17" t="n"/>
       <c r="AW52" s="59" t="n"/>
       <c r="AX52" s="17" t="n"/>
+      <c r="AY52" s="17" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="23">
@@ -6773,6 +6888,7 @@
       <c r="AV53" s="17" t="n"/>
       <c r="AW53" s="59" t="n"/>
       <c r="AX53" s="17" t="n"/>
+      <c r="AY53" s="17" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="23">
@@ -6854,6 +6970,7 @@
       <c r="AV54" s="17" t="n"/>
       <c r="AW54" s="59" t="n"/>
       <c r="AX54" s="17" t="n"/>
+      <c r="AY54" s="17" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="23">
@@ -6935,6 +7052,7 @@
       <c r="AV55" s="17" t="n"/>
       <c r="AW55" s="59" t="n"/>
       <c r="AX55" s="17" t="n"/>
+      <c r="AY55" s="17" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="23">
@@ -7016,6 +7134,7 @@
       <c r="AV56" s="17" t="n"/>
       <c r="AW56" s="59" t="n"/>
       <c r="AX56" s="17" t="n"/>
+      <c r="AY56" s="17" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="23">
@@ -7097,6 +7216,7 @@
       <c r="AV57" s="17" t="n"/>
       <c r="AW57" s="59" t="n"/>
       <c r="AX57" s="17" t="n"/>
+      <c r="AY57" s="17" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="23">
@@ -7178,6 +7298,7 @@
       <c r="AV58" s="17" t="n"/>
       <c r="AW58" s="59" t="n"/>
       <c r="AX58" s="17" t="n"/>
+      <c r="AY58" s="17" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="22">
@@ -7433,7 +7554,12 @@
       <formula>AND($AL9="外国",AO9="")</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="30">
+  <conditionalFormatting sqref="AY9:AY58">
+    <cfRule type="expression" priority="52" dxfId="2" stopIfTrue="1">
+      <formula>AND($V9&lt;&gt;"",$V9&lt;&gt;0,AY9="")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="31">
     <dataValidation sqref="D8:D58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="入力エラー" error="一覧から選択してください。" type="list" errorStyle="stop">
       <formula1>m_性別</formula1>
     </dataValidation>
@@ -7537,6 +7663,9 @@
     </dataValidation>
     <dataValidation sqref="AX8:AX58" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="入力エラー" error="一覧から選択してください。" promptTitle="入力のヒント" prompt="他社でも社会保険（健康保険・厚生年金）に加入していますか。『はい』のときは二以上事業所勤務届が別途必要になります（当事務所からご案内します）。" type="list" errorStyle="stop">
       <formula1>"いいえ,はい,分からない"</formula1>
+    </dataValidation>
+    <dataValidation sqref="AY9:AY58" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="現物給与の種類" prompt="V列に金額を入れたときはご記入ください。社宅・食事・定期券など。複数あればその他を選び、備考に内訳を。" type="list">
+      <formula1>=m_現物給与種類</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="0"/>
@@ -9142,7 +9271,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S48"/>
+  <dimension ref="A1:T48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9262,6 +9391,11 @@
           <t>職種</t>
         </is>
       </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>現物給与の種類</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="66" t="inlineStr">
@@ -9359,6 +9493,11 @@
           <t>専門的・技術的職業</t>
         </is>
       </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>社宅・寮</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="66" t="inlineStr">
@@ -9451,6 +9590,11 @@
           <t>管理的職業</t>
         </is>
       </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>食事</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="B4" s="66" t="inlineStr">
@@ -9498,6 +9642,11 @@
           <t>事務的職業</t>
         </is>
       </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>定期券・通勤定期</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="B5" s="66" t="inlineStr">
@@ -9525,6 +9674,11 @@
           <t>販売の職業</t>
         </is>
       </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>制服以外の被服</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="B6" s="66" t="inlineStr">
@@ -9550,6 +9704,11 @@
       <c r="S6" s="66" t="inlineStr">
         <is>
           <t>サービスの職業</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>その他</t>
         </is>
       </c>
     </row>

--- a/go/xlsx/nyusha-juryo-form.xlsx
+++ b/go/xlsx/nyusha-juryo-form.xlsx
@@ -2358,7 +2358,7 @@
       <c r="C19" s="35" t="n"/>
       <c r="D19" s="33" t="inlineStr">
         <is>
-          <t>毎月20日ごろ年金事務所から届く「保険料納入告知額・領収済額通知書」に載っています。口座振替の会社は別名の紙で届きます。例）12-アイウ</t>
+          <t>毎月20日ごろ年金事務所から届く「保険料納入告知額・領収済額通知書」に載っています。口座振替の会社は別名の紙で届きます。例）12-アイウ　2回目以降のご注文で、前回お知らせいただいていれば「前回と同じ」とご記入ください。</t>
         </is>
       </c>
     </row>
@@ -2371,7 +2371,7 @@
       <c r="C20" s="35" t="n"/>
       <c r="D20" s="33" t="inlineStr">
         <is>
-          <t>同じ紙の、整理記号の隣にある番号です。5桁。</t>
+          <t>同じ紙の、整理記号の隣にある番号です。5桁。　2回目以降のご注文で、前回お知らせいただいていれば「前回と同じ」とご記入ください。</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
       <c r="C21" s="35" t="n"/>
       <c r="D21" s="33" t="inlineStr">
         <is>
-          <t>「雇用保険適用事業所設置届 事業主控」または資格取得等確認通知書に載っています。4桁-6桁-1桁。例）1610-123456-7</t>
+          <t>「雇用保険適用事業所設置届 事業主控」または資格取得等確認通知書に載っています。4桁-6桁-1桁。例）1610-123456-7　2回目以降のご注文で、前回お知らせいただいていれば「前回と同じ」とご記入ください。</t>
         </is>
       </c>
     </row>
@@ -2458,15 +2458,15 @@
       <formula1>0</formula1>
       <formula2>100000</formula2>
     </dataValidation>
-    <dataValidation sqref="C19" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="ご記入のお願い" prompt="資格取得届の事業所整理記号欄。初めて社会保険に加入する会社は「新規適用の申請中」とご記入ください。" type="textLength" operator="between">
+    <dataValidation sqref="C19" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="ご記入のお願い" prompt="資格取得届の事業所整理記号欄。初めて社会保険に加入する会社は「新規適用の申請中」とご記入ください。2回目以降のご注文で、前回お知らせいただいていれば「前回と同じ」とご記入ください。" type="textLength" operator="between">
       <formula1>1</formula1>
       <formula2>30</formula2>
     </dataValidation>
-    <dataValidation sqref="C20" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="ご記入のお願い" prompt="資格取得届の事業所番号欄。" type="textLength" operator="between">
+    <dataValidation sqref="C20" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="ご記入のお願い" prompt="資格取得届の事業所番号欄。2回目以降のご注文で、前回お知らせいただいていれば「前回と同じ」とご記入ください。" type="textLength" operator="between">
       <formula1>1</formula1>
       <formula2>30</formula2>
     </dataValidation>
-    <dataValidation sqref="C21" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="ご記入のお願い" prompt="雇用保険 資格取得届の事業所番号欄。初めて雇用保険に加入する会社は「新規適用の申請中」とご記入ください。" type="textLength" operator="between">
+    <dataValidation sqref="C21" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="ご記入のお願い" prompt="雇用保険 資格取得届の事業所番号欄。初めて雇用保険に加入する会社は「新規適用の申請中」とご記入ください。2回目以降のご注文で、前回お知らせいただいていれば「前回と同じ」とご記入ください。" type="textLength" operator="between">
       <formula1>1</formula1>
       <formula2>30</formula2>
     </dataValidation>

--- a/go/xlsx/nyusha-juryo-form.xlsx
+++ b/go/xlsx/nyusha-juryo-form.xlsx
@@ -1429,7 +1429,7 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>シート『⓪ 事業所設定』を最初に一度だけ設定します（会社全体の情報。2回目以降は不要）。</t>
+          <t>シート『⓪ 事業所設定』をご記入ください（会社全体の情報。事業所の番号は届出に必ず要ります。2回目以降は「前回と同じ」で結構です）。</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>シート『① 従業員情報（本人）』に、入社者を1行＝1名で入力します。複数名まとめて入力できます。</t>
+          <t>シート『① 従業員情報（本人）』の9行目から、1行に1名ずつご記入ください（58行目まで・50名分）。行の挿入はしないでください。挿入した行には自動計算の式が入らず、未入力を見逃したまま「提出可」と表示されます。</t>
         </is>
       </c>
     </row>
@@ -1460,12 +1460,12 @@
     <row r="16" ht="34" customHeight="1">
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>ヒント</t>
+          <t>STEP 4</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>上部の『進捗ブロック』で、未入力の残件数・完了率が自動表示されます。100%を目指してご記入ください。</t>
+          <t>シート『提出チェック・添付・返送』の提出可否が「提出可」になったら、受任メールのリンクから案件ページを開き、このファイルをそのまま送ってください。</t>
         </is>
       </c>
     </row>

--- a/go/xlsx/nyusha-juryo-form.xlsx
+++ b/go/xlsx/nyusha-juryo-form.xlsx
@@ -1417,7 +1417,7 @@
     <row r="12" ht="22" customHeight="1">
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>入力の流れ（所要時間の目安：1名あたり 5〜10分）</t>
+          <t>入力の流れ（所要時間の目安：1名あたり 5 分ほど）</t>
         </is>
       </c>
     </row>

--- a/go/xlsx/nyusha-juryo-form.xlsx
+++ b/go/xlsx/nyusha-juryo-form.xlsx
@@ -1335,7 +1335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:C44"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1357,6 +1357,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="22" customHeight="1">
       <c r="B4" s="3" t="inlineStr">
         <is>
@@ -1400,6 +1401,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9" ht="22" customHeight="1">
       <c r="B9" s="3" t="inlineStr">
         <is>
@@ -1414,6 +1416,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12" ht="22" customHeight="1">
       <c r="B12" s="3" t="inlineStr">
         <is>
@@ -1469,6 +1472,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18" ht="22" customHeight="1">
       <c r="B18" s="3" t="inlineStr">
         <is>
@@ -1584,6 +1588,7 @@
         </is>
       </c>
     </row>
+    <row r="28"/>
     <row r="29" ht="22" customHeight="1">
       <c r="B29" s="3" t="inlineStr">
         <is>
@@ -1598,6 +1603,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32" ht="22" customHeight="1">
       <c r="B32" s="3" t="inlineStr">
         <is>
@@ -1641,6 +1647,7 @@
         </is>
       </c>
     </row>
+    <row r="36"/>
     <row r="37" ht="22" customHeight="1">
       <c r="B37" s="3" t="inlineStr">
         <is>
@@ -1745,7 +1752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:D33"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1768,6 +1775,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="24" customHeight="1">
       <c r="B4" s="3" t="inlineStr">
         <is>
@@ -2026,6 +2034,7 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
     <row r="25" ht="24" customHeight="1">
       <c r="B25" s="3" t="inlineStr">
         <is>
@@ -2058,6 +2067,7 @@
       <c r="C30" s="69" t="n"/>
       <c r="D30" s="70" t="n"/>
     </row>
+    <row r="31"/>
     <row r="32" ht="24" customHeight="1">
       <c r="B32" s="3" t="inlineStr">
         <is>
@@ -2128,7 +2138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:D21"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2165,6 +2175,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="38" customHeight="1">
       <c r="B6" s="31" t="inlineStr">
         <is>
@@ -3078,7 +3089,7 @@
         </is>
       </c>
       <c r="O8" s="54">
-        <f>IF($B8="","",IF($I8="なし","あり",IF($I8&lt;&gt;"あり","",IF($K8="更新の可能性あり","あり",IF(OR($J8="",$G8=""),"なし",IF(OR(NOT(ISNUMBER($G8)),NOT(ISNUMBER($J8)),$G8&gt;80000,$J8&gt;80000),"要確認（日付）",IF($J8&gt;IF(DAY(EDATE($G8,2))&lt;DAY($G8),EOMONTH($G8,2),EDATE($G8,2)-1),"あり","なし"))))))</f>
+        <f>IF($B8="","",IF($I8="なし","あり",IF($I8&lt;&gt;"あり","",IF($K8="更新の可能性あり","あり",IF(OR($J8="",$G8=""),"なし",IF(OR(NOT(ISNUMBER($G8)),NOT(ISNUMBER($J8)),$G8&gt;80000,$J8&gt;80000),"要確認（日付）",IF($J8&gt;IF(DAY(EDATE($G8,2))&lt;DAY($G8),EOMONTH($G8,2),EDATE($G8,2)-1),"あり","なし")))))))</f>
         <v/>
       </c>
       <c r="P8" s="54">
@@ -3222,7 +3233,7 @@
       <c r="M9" s="17" t="n"/>
       <c r="N9" s="17" t="n"/>
       <c r="O9" s="23">
-        <f>IF($B9="","",IF($I9="なし","あり",IF($I9&lt;&gt;"あり","",IF($K9="更新の可能性あり","あり",IF(OR($J9="",$G9=""),"なし",IF(OR(NOT(ISNUMBER($G9)),NOT(ISNUMBER($J9)),$G9&gt;80000,$J9&gt;80000),"要確認（日付）",IF($J9&gt;IF(DAY(EDATE($G9,2))&lt;DAY($G9),EOMONTH($G9,2),EDATE($G9,2)-1),"あり","なし"))))))</f>
+        <f>IF($B9="","",IF($I9="なし","あり",IF($I9&lt;&gt;"あり","",IF($K9="更新の可能性あり","あり",IF(OR($J9="",$G9=""),"なし",IF(OR(NOT(ISNUMBER($G9)),NOT(ISNUMBER($J9)),$G9&gt;80000,$J9&gt;80000),"要確認（日付）",IF($J9&gt;IF(DAY(EDATE($G9,2))&lt;DAY($G9),EOMONTH($G9,2),EDATE($G9,2)-1),"あり","なし")))))))</f>
         <v/>
       </c>
       <c r="P9" s="23">
@@ -3304,7 +3315,7 @@
       <c r="M10" s="17" t="n"/>
       <c r="N10" s="17" t="n"/>
       <c r="O10" s="23">
-        <f>IF($B10="","",IF($I10="なし","あり",IF($I10&lt;&gt;"あり","",IF($K10="更新の可能性あり","あり",IF(OR($J10="",$G10=""),"なし",IF(OR(NOT(ISNUMBER($G10)),NOT(ISNUMBER($J10)),$G10&gt;80000,$J10&gt;80000),"要確認（日付）",IF($J10&gt;IF(DAY(EDATE($G10,2))&lt;DAY($G10),EOMONTH($G10,2),EDATE($G10,2)-1),"あり","なし"))))))</f>
+        <f>IF($B10="","",IF($I10="なし","あり",IF($I10&lt;&gt;"あり","",IF($K10="更新の可能性あり","あり",IF(OR($J10="",$G10=""),"なし",IF(OR(NOT(ISNUMBER($G10)),NOT(ISNUMBER($J10)),$G10&gt;80000,$J10&gt;80000),"要確認（日付）",IF($J10&gt;IF(DAY(EDATE($G10,2))&lt;DAY($G10),EOMONTH($G10,2),EDATE($G10,2)-1),"あり","なし")))))))</f>
         <v/>
       </c>
       <c r="P10" s="23">
@@ -3386,7 +3397,7 @@
       <c r="M11" s="17" t="n"/>
       <c r="N11" s="17" t="n"/>
       <c r="O11" s="23">
-        <f>IF($B11="","",IF($I11="なし","あり",IF($I11&lt;&gt;"あり","",IF($K11="更新の可能性あり","あり",IF(OR($J11="",$G11=""),"なし",IF(OR(NOT(ISNUMBER($G11)),NOT(ISNUMBER($J11)),$G11&gt;80000,$J11&gt;80000),"要確認（日付）",IF($J11&gt;IF(DAY(EDATE($G11,2))&lt;DAY($G11),EOMONTH($G11,2),EDATE($G11,2)-1),"あり","なし"))))))</f>
+        <f>IF($B11="","",IF($I11="なし","あり",IF($I11&lt;&gt;"あり","",IF($K11="更新の可能性あり","あり",IF(OR($J11="",$G11=""),"なし",IF(OR(NOT(ISNUMBER($G11)),NOT(ISNUMBER($J11)),$G11&gt;80000,$J11&gt;80000),"要確認（日付）",IF($J11&gt;IF(DAY(EDATE($G11,2))&lt;DAY($G11),EOMONTH($G11,2),EDATE($G11,2)-1),"あり","なし")))))))</f>
         <v/>
       </c>
       <c r="P11" s="23">
@@ -3468,7 +3479,7 @@
       <c r="M12" s="17" t="n"/>
       <c r="N12" s="17" t="n"/>
       <c r="O12" s="23">
-        <f>IF($B12="","",IF($I12="なし","あり",IF($I12&lt;&gt;"あり","",IF($K12="更新の可能性あり","あり",IF(OR($J12="",$G12=""),"なし",IF(OR(NOT(ISNUMBER($G12)),NOT(ISNUMBER($J12)),$G12&gt;80000,$J12&gt;80000),"要確認（日付）",IF($J12&gt;IF(DAY(EDATE($G12,2))&lt;DAY($G12),EOMONTH($G12,2),EDATE($G12,2)-1),"あり","なし"))))))</f>
+        <f>IF($B12="","",IF($I12="なし","あり",IF($I12&lt;&gt;"あり","",IF($K12="更新の可能性あり","あり",IF(OR($J12="",$G12=""),"なし",IF(OR(NOT(ISNUMBER($G12)),NOT(ISNUMBER($J12)),$G12&gt;80000,$J12&gt;80000),"要確認（日付）",IF($J12&gt;IF(DAY(EDATE($G12,2))&lt;DAY($G12),EOMONTH($G12,2),EDATE($G12,2)-1),"あり","なし")))))))</f>
         <v/>
       </c>
       <c r="P12" s="23">
@@ -3550,7 +3561,7 @@
       <c r="M13" s="17" t="n"/>
       <c r="N13" s="17" t="n"/>
       <c r="O13" s="23">
-        <f>IF($B13="","",IF($I13="なし","あり",IF($I13&lt;&gt;"あり","",IF($K13="更新の可能性あり","あり",IF(OR($J13="",$G13=""),"なし",IF(OR(NOT(ISNUMBER($G13)),NOT(ISNUMBER($J13)),$G13&gt;80000,$J13&gt;80000),"要確認（日付）",IF($J13&gt;IF(DAY(EDATE($G13,2))&lt;DAY($G13),EOMONTH($G13,2),EDATE($G13,2)-1),"あり","なし"))))))</f>
+        <f>IF($B13="","",IF($I13="なし","あり",IF($I13&lt;&gt;"あり","",IF($K13="更新の可能性あり","あり",IF(OR($J13="",$G13=""),"なし",IF(OR(NOT(ISNUMBER($G13)),NOT(ISNUMBER($J13)),$G13&gt;80000,$J13&gt;80000),"要確認（日付）",IF($J13&gt;IF(DAY(EDATE($G13,2))&lt;DAY($G13),EOMONTH($G13,2),EDATE($G13,2)-1),"あり","なし")))))))</f>
         <v/>
       </c>
       <c r="P13" s="23">
@@ -3632,7 +3643,7 @@
       <c r="M14" s="17" t="n"/>
       <c r="N14" s="17" t="n"/>
       <c r="O14" s="23">
-        <f>IF($B14="","",IF($I14="なし","あり",IF($I14&lt;&gt;"あり","",IF($K14="更新の可能性あり","あり",IF(OR($J14="",$G14=""),"なし",IF(OR(NOT(ISNUMBER($G14)),NOT(ISNUMBER($J14)),$G14&gt;80000,$J14&gt;80000),"要確認（日付）",IF($J14&gt;IF(DAY(EDATE($G14,2))&lt;DAY($G14),EOMONTH($G14,2),EDATE($G14,2)-1),"あり","なし"))))))</f>
+        <f>IF($B14="","",IF($I14="なし","あり",IF($I14&lt;&gt;"あり","",IF($K14="更新の可能性あり","あり",IF(OR($J14="",$G14=""),"なし",IF(OR(NOT(ISNUMBER($G14)),NOT(ISNUMBER($J14)),$G14&gt;80000,$J14&gt;80000),"要確認（日付）",IF($J14&gt;IF(DAY(EDATE($G14,2))&lt;DAY($G14),EOMONTH($G14,2),EDATE($G14,2)-1),"あり","なし")))))))</f>
         <v/>
       </c>
       <c r="P14" s="23">
@@ -3714,7 +3725,7 @@
       <c r="M15" s="17" t="n"/>
       <c r="N15" s="17" t="n"/>
       <c r="O15" s="23">
-        <f>IF($B15="","",IF($I15="なし","あり",IF($I15&lt;&gt;"あり","",IF($K15="更新の可能性あり","あり",IF(OR($J15="",$G15=""),"なし",IF(OR(NOT(ISNUMBER($G15)),NOT(ISNUMBER($J15)),$G15&gt;80000,$J15&gt;80000),"要確認（日付）",IF($J15&gt;IF(DAY(EDATE($G15,2))&lt;DAY($G15),EOMONTH($G15,2),EDATE($G15,2)-1),"あり","なし"))))))</f>
+        <f>IF($B15="","",IF($I15="なし","あり",IF($I15&lt;&gt;"あり","",IF($K15="更新の可能性あり","あり",IF(OR($J15="",$G15=""),"なし",IF(OR(NOT(ISNUMBER($G15)),NOT(ISNUMBER($J15)),$G15&gt;80000,$J15&gt;80000),"要確認（日付）",IF($J15&gt;IF(DAY(EDATE($G15,2))&lt;DAY($G15),EOMONTH($G15,2),EDATE($G15,2)-1),"あり","なし")))))))</f>
         <v/>
       </c>
       <c r="P15" s="23">
@@ -3796,7 +3807,7 @@
       <c r="M16" s="17" t="n"/>
       <c r="N16" s="17" t="n"/>
       <c r="O16" s="23">
-        <f>IF($B16="","",IF($I16="なし","あり",IF($I16&lt;&gt;"あり","",IF($K16="更新の可能性あり","あり",IF(OR($J16="",$G16=""),"なし",IF(OR(NOT(ISNUMBER($G16)),NOT(ISNUMBER($J16)),$G16&gt;80000,$J16&gt;80000),"要確認（日付）",IF($J16&gt;IF(DAY(EDATE($G16,2))&lt;DAY($G16),EOMONTH($G16,2),EDATE($G16,2)-1),"あり","なし"))))))</f>
+        <f>IF($B16="","",IF($I16="なし","あり",IF($I16&lt;&gt;"あり","",IF($K16="更新の可能性あり","あり",IF(OR($J16="",$G16=""),"なし",IF(OR(NOT(ISNUMBER($G16)),NOT(ISNUMBER($J16)),$G16&gt;80000,$J16&gt;80000),"要確認（日付）",IF($J16&gt;IF(DAY(EDATE($G16,2))&lt;DAY($G16),EOMONTH($G16,2),EDATE($G16,2)-1),"あり","なし")))))))</f>
         <v/>
       </c>
       <c r="P16" s="23">
@@ -3878,7 +3889,7 @@
       <c r="M17" s="17" t="n"/>
       <c r="N17" s="17" t="n"/>
       <c r="O17" s="23">
-        <f>IF($B17="","",IF($I17="なし","あり",IF($I17&lt;&gt;"あり","",IF($K17="更新の可能性あり","あり",IF(OR($J17="",$G17=""),"なし",IF(OR(NOT(ISNUMBER($G17)),NOT(ISNUMBER($J17)),$G17&gt;80000,$J17&gt;80000),"要確認（日付）",IF($J17&gt;IF(DAY(EDATE($G17,2))&lt;DAY($G17),EOMONTH($G17,2),EDATE($G17,2)-1),"あり","なし"))))))</f>
+        <f>IF($B17="","",IF($I17="なし","あり",IF($I17&lt;&gt;"あり","",IF($K17="更新の可能性あり","あり",IF(OR($J17="",$G17=""),"なし",IF(OR(NOT(ISNUMBER($G17)),NOT(ISNUMBER($J17)),$G17&gt;80000,$J17&gt;80000),"要確認（日付）",IF($J17&gt;IF(DAY(EDATE($G17,2))&lt;DAY($G17),EOMONTH($G17,2),EDATE($G17,2)-1),"あり","なし")))))))</f>
         <v/>
       </c>
       <c r="P17" s="23">
@@ -3960,7 +3971,7 @@
       <c r="M18" s="17" t="n"/>
       <c r="N18" s="17" t="n"/>
       <c r="O18" s="23">
-        <f>IF($B18="","",IF($I18="なし","あり",IF($I18&lt;&gt;"あり","",IF($K18="更新の可能性あり","あり",IF(OR($J18="",$G18=""),"なし",IF(OR(NOT(ISNUMBER($G18)),NOT(ISNUMBER($J18)),$G18&gt;80000,$J18&gt;80000),"要確認（日付）",IF($J18&gt;IF(DAY(EDATE($G18,2))&lt;DAY($G18),EOMONTH($G18,2),EDATE($G18,2)-1),"あり","なし"))))))</f>
+        <f>IF($B18="","",IF($I18="なし","あり",IF($I18&lt;&gt;"あり","",IF($K18="更新の可能性あり","あり",IF(OR($J18="",$G18=""),"なし",IF(OR(NOT(ISNUMBER($G18)),NOT(ISNUMBER($J18)),$G18&gt;80000,$J18&gt;80000),"要確認（日付）",IF($J18&gt;IF(DAY(EDATE($G18,2))&lt;DAY($G18),EOMONTH($G18,2),EDATE($G18,2)-1),"あり","なし")))))))</f>
         <v/>
       </c>
       <c r="P18" s="23">
@@ -4042,7 +4053,7 @@
       <c r="M19" s="17" t="n"/>
       <c r="N19" s="17" t="n"/>
       <c r="O19" s="23">
-        <f>IF($B19="","",IF($I19="なし","あり",IF($I19&lt;&gt;"あり","",IF($K19="更新の可能性あり","あり",IF(OR($J19="",$G19=""),"なし",IF(OR(NOT(ISNUMBER($G19)),NOT(ISNUMBER($J19)),$G19&gt;80000,$J19&gt;80000),"要確認（日付）",IF($J19&gt;IF(DAY(EDATE($G19,2))&lt;DAY($G19),EOMONTH($G19,2),EDATE($G19,2)-1),"あり","なし"))))))</f>
+        <f>IF($B19="","",IF($I19="なし","あり",IF($I19&lt;&gt;"あり","",IF($K19="更新の可能性あり","あり",IF(OR($J19="",$G19=""),"なし",IF(OR(NOT(ISNUMBER($G19)),NOT(ISNUMBER($J19)),$G19&gt;80000,$J19&gt;80000),"要確認（日付）",IF($J19&gt;IF(DAY(EDATE($G19,2))&lt;DAY($G19),EOMONTH($G19,2),EDATE($G19,2)-1),"あり","なし")))))))</f>
         <v/>
       </c>
       <c r="P19" s="23">
@@ -4124,7 +4135,7 @@
       <c r="M20" s="17" t="n"/>
       <c r="N20" s="17" t="n"/>
       <c r="O20" s="23">
-        <f>IF($B20="","",IF($I20="なし","あり",IF($I20&lt;&gt;"あり","",IF($K20="更新の可能性あり","あり",IF(OR($J20="",$G20=""),"なし",IF(OR(NOT(ISNUMBER($G20)),NOT(ISNUMBER($J20)),$G20&gt;80000,$J20&gt;80000),"要確認（日付）",IF($J20&gt;IF(DAY(EDATE($G20,2))&lt;DAY($G20),EOMONTH($G20,2),EDATE($G20,2)-1),"あり","なし"))))))</f>
+        <f>IF($B20="","",IF($I20="なし","あり",IF($I20&lt;&gt;"あり","",IF($K20="更新の可能性あり","あり",IF(OR($J20="",$G20=""),"なし",IF(OR(NOT(ISNUMBER($G20)),NOT(ISNUMBER($J20)),$G20&gt;80000,$J20&gt;80000),"要確認（日付）",IF($J20&gt;IF(DAY(EDATE($G20,2))&lt;DAY($G20),EOMONTH($G20,2),EDATE($G20,2)-1),"あり","なし")))))))</f>
         <v/>
       </c>
       <c r="P20" s="23">
@@ -4206,7 +4217,7 @@
       <c r="M21" s="17" t="n"/>
       <c r="N21" s="17" t="n"/>
       <c r="O21" s="23">
-        <f>IF($B21="","",IF($I21="なし","あり",IF($I21&lt;&gt;"あり","",IF($K21="更新の可能性あり","あり",IF(OR($J21="",$G21=""),"なし",IF(OR(NOT(ISNUMBER($G21)),NOT(ISNUMBER($J21)),$G21&gt;80000,$J21&gt;80000),"要確認（日付）",IF($J21&gt;IF(DAY(EDATE($G21,2))&lt;DAY($G21),EOMONTH($G21,2),EDATE($G21,2)-1),"あり","なし"))))))</f>
+        <f>IF($B21="","",IF($I21="なし","あり",IF($I21&lt;&gt;"あり","",IF($K21="更新の可能性あり","あり",IF(OR($J21="",$G21=""),"なし",IF(OR(NOT(ISNUMBER($G21)),NOT(ISNUMBER($J21)),$G21&gt;80000,$J21&gt;80000),"要確認（日付）",IF($J21&gt;IF(DAY(EDATE($G21,2))&lt;DAY($G21),EOMONTH($G21,2),EDATE($G21,2)-1),"あり","なし")))))))</f>
         <v/>
       </c>
       <c r="P21" s="23">
@@ -4288,7 +4299,7 @@
       <c r="M22" s="17" t="n"/>
       <c r="N22" s="17" t="n"/>
       <c r="O22" s="23">
-        <f>IF($B22="","",IF($I22="なし","あり",IF($I22&lt;&gt;"あり","",IF($K22="更新の可能性あり","あり",IF(OR($J22="",$G22=""),"なし",IF(OR(NOT(ISNUMBER($G22)),NOT(ISNUMBER($J22)),$G22&gt;80000,$J22&gt;80000),"要確認（日付）",IF($J22&gt;IF(DAY(EDATE($G22,2))&lt;DAY($G22),EOMONTH($G22,2),EDATE($G22,2)-1),"あり","なし"))))))</f>
+        <f>IF($B22="","",IF($I22="なし","あり",IF($I22&lt;&gt;"あり","",IF($K22="更新の可能性あり","あり",IF(OR($J22="",$G22=""),"なし",IF(OR(NOT(ISNUMBER($G22)),NOT(ISNUMBER($J22)),$G22&gt;80000,$J22&gt;80000),"要確認（日付）",IF($J22&gt;IF(DAY(EDATE($G22,2))&lt;DAY($G22),EOMONTH($G22,2),EDATE($G22,2)-1),"あり","なし")))))))</f>
         <v/>
       </c>
       <c r="P22" s="23">
@@ -4370,7 +4381,7 @@
       <c r="M23" s="17" t="n"/>
       <c r="N23" s="17" t="n"/>
       <c r="O23" s="23">
-        <f>IF($B23="","",IF($I23="なし","あり",IF($I23&lt;&gt;"あり","",IF($K23="更新の可能性あり","あり",IF(OR($J23="",$G23=""),"なし",IF(OR(NOT(ISNUMBER($G23)),NOT(ISNUMBER($J23)),$G23&gt;80000,$J23&gt;80000),"要確認（日付）",IF($J23&gt;IF(DAY(EDATE($G23,2))&lt;DAY($G23),EOMONTH($G23,2),EDATE($G23,2)-1),"あり","なし"))))))</f>
+        <f>IF($B23="","",IF($I23="なし","あり",IF($I23&lt;&gt;"あり","",IF($K23="更新の可能性あり","あり",IF(OR($J23="",$G23=""),"なし",IF(OR(NOT(ISNUMBER($G23)),NOT(ISNUMBER($J23)),$G23&gt;80000,$J23&gt;80000),"要確認（日付）",IF($J23&gt;IF(DAY(EDATE($G23,2))&lt;DAY($G23),EOMONTH($G23,2),EDATE($G23,2)-1),"あり","なし")))))))</f>
         <v/>
       </c>
       <c r="P23" s="23">
@@ -4452,7 +4463,7 @@
       <c r="M24" s="17" t="n"/>
       <c r="N24" s="17" t="n"/>
       <c r="O24" s="23">
-        <f>IF($B24="","",IF($I24="なし","あり",IF($I24&lt;&gt;"あり","",IF($K24="更新の可能性あり","あり",IF(OR($J24="",$G24=""),"なし",IF(OR(NOT(ISNUMBER($G24)),NOT(ISNUMBER($J24)),$G24&gt;80000,$J24&gt;80000),"要確認（日付）",IF($J24&gt;IF(DAY(EDATE($G24,2))&lt;DAY($G24),EOMONTH($G24,2),EDATE($G24,2)-1),"あり","なし"))))))</f>
+        <f>IF($B24="","",IF($I24="なし","あり",IF($I24&lt;&gt;"あり","",IF($K24="更新の可能性あり","あり",IF(OR($J24="",$G24=""),"なし",IF(OR(NOT(ISNUMBER($G24)),NOT(ISNUMBER($J24)),$G24&gt;80000,$J24&gt;80000),"要確認（日付）",IF($J24&gt;IF(DAY(EDATE($G24,2))&lt;DAY($G24),EOMONTH($G24,2),EDATE($G24,2)-1),"あり","なし")))))))</f>
         <v/>
       </c>
       <c r="P24" s="23">
@@ -4534,7 +4545,7 @@
       <c r="M25" s="17" t="n"/>
       <c r="N25" s="17" t="n"/>
       <c r="O25" s="23">
-        <f>IF($B25="","",IF($I25="なし","あり",IF($I25&lt;&gt;"あり","",IF($K25="更新の可能性あり","あり",IF(OR($J25="",$G25=""),"なし",IF(OR(NOT(ISNUMBER($G25)),NOT(ISNUMBER($J25)),$G25&gt;80000,$J25&gt;80000),"要確認（日付）",IF($J25&gt;IF(DAY(EDATE($G25,2))&lt;DAY($G25),EOMONTH($G25,2),EDATE($G25,2)-1),"あり","なし"))))))</f>
+        <f>IF($B25="","",IF($I25="なし","あり",IF($I25&lt;&gt;"あり","",IF($K25="更新の可能性あり","あり",IF(OR($J25="",$G25=""),"なし",IF(OR(NOT(ISNUMBER($G25)),NOT(ISNUMBER($J25)),$G25&gt;80000,$J25&gt;80000),"要確認（日付）",IF($J25&gt;IF(DAY(EDATE($G25,2))&lt;DAY($G25),EOMONTH($G25,2),EDATE($G25,2)-1),"あり","なし")))))))</f>
         <v/>
       </c>
       <c r="P25" s="23">
@@ -4616,7 +4627,7 @@
       <c r="M26" s="17" t="n"/>
       <c r="N26" s="17" t="n"/>
       <c r="O26" s="23">
-        <f>IF($B26="","",IF($I26="なし","あり",IF($I26&lt;&gt;"あり","",IF($K26="更新の可能性あり","あり",IF(OR($J26="",$G26=""),"なし",IF(OR(NOT(ISNUMBER($G26)),NOT(ISNUMBER($J26)),$G26&gt;80000,$J26&gt;80000),"要確認（日付）",IF($J26&gt;IF(DAY(EDATE($G26,2))&lt;DAY($G26),EOMONTH($G26,2),EDATE($G26,2)-1),"あり","なし"))))))</f>
+        <f>IF($B26="","",IF($I26="なし","あり",IF($I26&lt;&gt;"あり","",IF($K26="更新の可能性あり","あり",IF(OR($J26="",$G26=""),"なし",IF(OR(NOT(ISNUMBER($G26)),NOT(ISNUMBER($J26)),$G26&gt;80000,$J26&gt;80000),"要確認（日付）",IF($J26&gt;IF(DAY(EDATE($G26,2))&lt;DAY($G26),EOMONTH($G26,2),EDATE($G26,2)-1),"あり","なし")))))))</f>
         <v/>
       </c>
       <c r="P26" s="23">
@@ -4698,7 +4709,7 @@
       <c r="M27" s="17" t="n"/>
       <c r="N27" s="17" t="n"/>
       <c r="O27" s="23">
-        <f>IF($B27="","",IF($I27="なし","あり",IF($I27&lt;&gt;"あり","",IF($K27="更新の可能性あり","あり",IF(OR($J27="",$G27=""),"なし",IF(OR(NOT(ISNUMBER($G27)),NOT(ISNUMBER($J27)),$G27&gt;80000,$J27&gt;80000),"要確認（日付）",IF($J27&gt;IF(DAY(EDATE($G27,2))&lt;DAY($G27),EOMONTH($G27,2),EDATE($G27,2)-1),"あり","なし"))))))</f>
+        <f>IF($B27="","",IF($I27="なし","あり",IF($I27&lt;&gt;"あり","",IF($K27="更新の可能性あり","あり",IF(OR($J27="",$G27=""),"なし",IF(OR(NOT(ISNUMBER($G27)),NOT(ISNUMBER($J27)),$G27&gt;80000,$J27&gt;80000),"要確認（日付）",IF($J27&gt;IF(DAY(EDATE($G27,2))&lt;DAY($G27),EOMONTH($G27,2),EDATE($G27,2)-1),"あり","なし")))))))</f>
         <v/>
       </c>
       <c r="P27" s="23">
@@ -4780,7 +4791,7 @@
       <c r="M28" s="17" t="n"/>
       <c r="N28" s="17" t="n"/>
       <c r="O28" s="23">
-        <f>IF($B28="","",IF($I28="なし","あり",IF($I28&lt;&gt;"あり","",IF($K28="更新の可能性あり","あり",IF(OR($J28="",$G28=""),"なし",IF(OR(NOT(ISNUMBER($G28)),NOT(ISNUMBER($J28)),$G28&gt;80000,$J28&gt;80000),"要確認（日付）",IF($J28&gt;IF(DAY(EDATE($G28,2))&lt;DAY($G28),EOMONTH($G28,2),EDATE($G28,2)-1),"あり","なし"))))))</f>
+        <f>IF($B28="","",IF($I28="なし","あり",IF($I28&lt;&gt;"あり","",IF($K28="更新の可能性あり","あり",IF(OR($J28="",$G28=""),"なし",IF(OR(NOT(ISNUMBER($G28)),NOT(ISNUMBER($J28)),$G28&gt;80000,$J28&gt;80000),"要確認（日付）",IF($J28&gt;IF(DAY(EDATE($G28,2))&lt;DAY($G28),EOMONTH($G28,2),EDATE($G28,2)-1),"あり","なし")))))))</f>
         <v/>
       </c>
       <c r="P28" s="23">
@@ -4862,7 +4873,7 @@
       <c r="M29" s="17" t="n"/>
       <c r="N29" s="17" t="n"/>
       <c r="O29" s="23">
-        <f>IF($B29="","",IF($I29="なし","あり",IF($I29&lt;&gt;"あり","",IF($K29="更新の可能性あり","あり",IF(OR($J29="",$G29=""),"なし",IF(OR(NOT(ISNUMBER($G29)),NOT(ISNUMBER($J29)),$G29&gt;80000,$J29&gt;80000),"要確認（日付）",IF($J29&gt;IF(DAY(EDATE($G29,2))&lt;DAY($G29),EOMONTH($G29,2),EDATE($G29,2)-1),"あり","なし"))))))</f>
+        <f>IF($B29="","",IF($I29="なし","あり",IF($I29&lt;&gt;"あり","",IF($K29="更新の可能性あり","あり",IF(OR($J29="",$G29=""),"なし",IF(OR(NOT(ISNUMBER($G29)),NOT(ISNUMBER($J29)),$G29&gt;80000,$J29&gt;80000),"要確認（日付）",IF($J29&gt;IF(DAY(EDATE($G29,2))&lt;DAY($G29),EOMONTH($G29,2),EDATE($G29,2)-1),"あり","なし")))))))</f>
         <v/>
       </c>
       <c r="P29" s="23">
@@ -4944,7 +4955,7 @@
       <c r="M30" s="17" t="n"/>
       <c r="N30" s="17" t="n"/>
       <c r="O30" s="23">
-        <f>IF($B30="","",IF($I30="なし","あり",IF($I30&lt;&gt;"あり","",IF($K30="更新の可能性あり","あり",IF(OR($J30="",$G30=""),"なし",IF(OR(NOT(ISNUMBER($G30)),NOT(ISNUMBER($J30)),$G30&gt;80000,$J30&gt;80000),"要確認（日付）",IF($J30&gt;IF(DAY(EDATE($G30,2))&lt;DAY($G30),EOMONTH($G30,2),EDATE($G30,2)-1),"あり","なし"))))))</f>
+        <f>IF($B30="","",IF($I30="なし","あり",IF($I30&lt;&gt;"あり","",IF($K30="更新の可能性あり","あり",IF(OR($J30="",$G30=""),"なし",IF(OR(NOT(ISNUMBER($G30)),NOT(ISNUMBER($J30)),$G30&gt;80000,$J30&gt;80000),"要確認（日付）",IF($J30&gt;IF(DAY(EDATE($G30,2))&lt;DAY($G30),EOMONTH($G30,2),EDATE($G30,2)-1),"あり","なし")))))))</f>
         <v/>
       </c>
       <c r="P30" s="23">
@@ -5026,7 +5037,7 @@
       <c r="M31" s="17" t="n"/>
       <c r="N31" s="17" t="n"/>
       <c r="O31" s="23">
-        <f>IF($B31="","",IF($I31="なし","あり",IF($I31&lt;&gt;"あり","",IF($K31="更新の可能性あり","あり",IF(OR($J31="",$G31=""),"なし",IF(OR(NOT(ISNUMBER($G31)),NOT(ISNUMBER($J31)),$G31&gt;80000,$J31&gt;80000),"要確認（日付）",IF($J31&gt;IF(DAY(EDATE($G31,2))&lt;DAY($G31),EOMONTH($G31,2),EDATE($G31,2)-1),"あり","なし"))))))</f>
+        <f>IF($B31="","",IF($I31="なし","あり",IF($I31&lt;&gt;"あり","",IF($K31="更新の可能性あり","あり",IF(OR($J31="",$G31=""),"なし",IF(OR(NOT(ISNUMBER($G31)),NOT(ISNUMBER($J31)),$G31&gt;80000,$J31&gt;80000),"要確認（日付）",IF($J31&gt;IF(DAY(EDATE($G31,2))&lt;DAY($G31),EOMONTH($G31,2),EDATE($G31,2)-1),"あり","なし")))))))</f>
         <v/>
       </c>
       <c r="P31" s="23">
@@ -5108,7 +5119,7 @@
       <c r="M32" s="17" t="n"/>
       <c r="N32" s="17" t="n"/>
       <c r="O32" s="23">
-        <f>IF($B32="","",IF($I32="なし","あり",IF($I32&lt;&gt;"あり","",IF($K32="更新の可能性あり","あり",IF(OR($J32="",$G32=""),"なし",IF(OR(NOT(ISNUMBER($G32)),NOT(ISNUMBER($J32)),$G32&gt;80000,$J32&gt;80000),"要確認（日付）",IF($J32&gt;IF(DAY(EDATE($G32,2))&lt;DAY($G32),EOMONTH($G32,2),EDATE($G32,2)-1),"あり","なし"))))))</f>
+        <f>IF($B32="","",IF($I32="なし","あり",IF($I32&lt;&gt;"あり","",IF($K32="更新の可能性あり","あり",IF(OR($J32="",$G32=""),"なし",IF(OR(NOT(ISNUMBER($G32)),NOT(ISNUMBER($J32)),$G32&gt;80000,$J32&gt;80000),"要確認（日付）",IF($J32&gt;IF(DAY(EDATE($G32,2))&lt;DAY($G32),EOMONTH($G32,2),EDATE($G32,2)-1),"あり","なし")))))))</f>
         <v/>
       </c>
       <c r="P32" s="23">
@@ -5190,7 +5201,7 @@
       <c r="M33" s="17" t="n"/>
       <c r="N33" s="17" t="n"/>
       <c r="O33" s="23">
-        <f>IF($B33="","",IF($I33="なし","あり",IF($I33&lt;&gt;"あり","",IF($K33="更新の可能性あり","あり",IF(OR($J33="",$G33=""),"なし",IF(OR(NOT(ISNUMBER($G33)),NOT(ISNUMBER($J33)),$G33&gt;80000,$J33&gt;80000),"要確認（日付）",IF($J33&gt;IF(DAY(EDATE($G33,2))&lt;DAY($G33),EOMONTH($G33,2),EDATE($G33,2)-1),"あり","なし"))))))</f>
+        <f>IF($B33="","",IF($I33="なし","あり",IF($I33&lt;&gt;"あり","",IF($K33="更新の可能性あり","あり",IF(OR($J33="",$G33=""),"なし",IF(OR(NOT(ISNUMBER($G33)),NOT(ISNUMBER($J33)),$G33&gt;80000,$J33&gt;80000),"要確認（日付）",IF($J33&gt;IF(DAY(EDATE($G33,2))&lt;DAY($G33),EOMONTH($G33,2),EDATE($G33,2)-1),"あり","なし")))))))</f>
         <v/>
       </c>
       <c r="P33" s="23">
@@ -5272,7 +5283,7 @@
       <c r="M34" s="17" t="n"/>
       <c r="N34" s="17" t="n"/>
       <c r="O34" s="23">
-        <f>IF($B34="","",IF($I34="なし","あり",IF($I34&lt;&gt;"あり","",IF($K34="更新の可能性あり","あり",IF(OR($J34="",$G34=""),"なし",IF(OR(NOT(ISNUMBER($G34)),NOT(ISNUMBER($J34)),$G34&gt;80000,$J34&gt;80000),"要確認（日付）",IF($J34&gt;IF(DAY(EDATE($G34,2))&lt;DAY($G34),EOMONTH($G34,2),EDATE($G34,2)-1),"あり","なし"))))))</f>
+        <f>IF($B34="","",IF($I34="なし","あり",IF($I34&lt;&gt;"あり","",IF($K34="更新の可能性あり","あり",IF(OR($J34="",$G34=""),"なし",IF(OR(NOT(ISNUMBER($G34)),NOT(ISNUMBER($J34)),$G34&gt;80000,$J34&gt;80000),"要確認（日付）",IF($J34&gt;IF(DAY(EDATE($G34,2))&lt;DAY($G34),EOMONTH($G34,2),EDATE($G34,2)-1),"あり","なし")))))))</f>
         <v/>
       </c>
       <c r="P34" s="23">
@@ -5354,7 +5365,7 @@
       <c r="M35" s="17" t="n"/>
       <c r="N35" s="17" t="n"/>
       <c r="O35" s="23">
-        <f>IF($B35="","",IF($I35="なし","あり",IF($I35&lt;&gt;"あり","",IF($K35="更新の可能性あり","あり",IF(OR($J35="",$G35=""),"なし",IF(OR(NOT(ISNUMBER($G35)),NOT(ISNUMBER($J35)),$G35&gt;80000,$J35&gt;80000),"要確認（日付）",IF($J35&gt;IF(DAY(EDATE($G35,2))&lt;DAY($G35),EOMONTH($G35,2),EDATE($G35,2)-1),"あり","なし"))))))</f>
+        <f>IF($B35="","",IF($I35="なし","あり",IF($I35&lt;&gt;"あり","",IF($K35="更新の可能性あり","あり",IF(OR($J35="",$G35=""),"なし",IF(OR(NOT(ISNUMBER($G35)),NOT(ISNUMBER($J35)),$G35&gt;80000,$J35&gt;80000),"要確認（日付）",IF($J35&gt;IF(DAY(EDATE($G35,2))&lt;DAY($G35),EOMONTH($G35,2),EDATE($G35,2)-1),"あり","なし")))))))</f>
         <v/>
       </c>
       <c r="P35" s="23">
@@ -5436,7 +5447,7 @@
       <c r="M36" s="17" t="n"/>
       <c r="N36" s="17" t="n"/>
       <c r="O36" s="23">
-        <f>IF($B36="","",IF($I36="なし","あり",IF($I36&lt;&gt;"あり","",IF($K36="更新の可能性あり","あり",IF(OR($J36="",$G36=""),"なし",IF(OR(NOT(ISNUMBER($G36)),NOT(ISNUMBER($J36)),$G36&gt;80000,$J36&gt;80000),"要確認（日付）",IF($J36&gt;IF(DAY(EDATE($G36,2))&lt;DAY($G36),EOMONTH($G36,2),EDATE($G36,2)-1),"あり","なし"))))))</f>
+        <f>IF($B36="","",IF($I36="なし","あり",IF($I36&lt;&gt;"あり","",IF($K36="更新の可能性あり","あり",IF(OR($J36="",$G36=""),"なし",IF(OR(NOT(ISNUMBER($G36)),NOT(ISNUMBER($J36)),$G36&gt;80000,$J36&gt;80000),"要確認（日付）",IF($J36&gt;IF(DAY(EDATE($G36,2))&lt;DAY($G36),EOMONTH($G36,2),EDATE($G36,2)-1),"あり","なし")))))))</f>
         <v/>
       </c>
       <c r="P36" s="23">
@@ -5518,7 +5529,7 @@
       <c r="M37" s="17" t="n"/>
       <c r="N37" s="17" t="n"/>
       <c r="O37" s="23">
-        <f>IF($B37="","",IF($I37="なし","あり",IF($I37&lt;&gt;"あり","",IF($K37="更新の可能性あり","あり",IF(OR($J37="",$G37=""),"なし",IF(OR(NOT(ISNUMBER($G37)),NOT(ISNUMBER($J37)),$G37&gt;80000,$J37&gt;80000),"要確認（日付）",IF($J37&gt;IF(DAY(EDATE($G37,2))&lt;DAY($G37),EOMONTH($G37,2),EDATE($G37,2)-1),"あり","なし"))))))</f>
+        <f>IF($B37="","",IF($I37="なし","あり",IF($I37&lt;&gt;"あり","",IF($K37="更新の可能性あり","あり",IF(OR($J37="",$G37=""),"なし",IF(OR(NOT(ISNUMBER($G37)),NOT(ISNUMBER($J37)),$G37&gt;80000,$J37&gt;80000),"要確認（日付）",IF($J37&gt;IF(DAY(EDATE($G37,2))&lt;DAY($G37),EOMONTH($G37,2),EDATE($G37,2)-1),"あり","なし")))))))</f>
         <v/>
       </c>
       <c r="P37" s="23">
@@ -5600,7 +5611,7 @@
       <c r="M38" s="17" t="n"/>
       <c r="N38" s="17" t="n"/>
       <c r="O38" s="23">
-        <f>IF($B38="","",IF($I38="なし","あり",IF($I38&lt;&gt;"あり","",IF($K38="更新の可能性あり","あり",IF(OR($J38="",$G38=""),"なし",IF(OR(NOT(ISNUMBER($G38)),NOT(ISNUMBER($J38)),$G38&gt;80000,$J38&gt;80000),"要確認（日付）",IF($J38&gt;IF(DAY(EDATE($G38,2))&lt;DAY($G38),EOMONTH($G38,2),EDATE($G38,2)-1),"あり","なし"))))))</f>
+        <f>IF($B38="","",IF($I38="なし","あり",IF($I38&lt;&gt;"あり","",IF($K38="更新の可能性あり","あり",IF(OR($J38="",$G38=""),"なし",IF(OR(NOT(ISNUMBER($G38)),NOT(ISNUMBER($J38)),$G38&gt;80000,$J38&gt;80000),"要確認（日付）",IF($J38&gt;IF(DAY(EDATE($G38,2))&lt;DAY($G38),EOMONTH($G38,2),EDATE($G38,2)-1),"あり","なし")))))))</f>
         <v/>
       </c>
       <c r="P38" s="23">
@@ -5682,7 +5693,7 @@
       <c r="M39" s="17" t="n"/>
       <c r="N39" s="17" t="n"/>
       <c r="O39" s="23">
-        <f>IF($B39="","",IF($I39="なし","あり",IF($I39&lt;&gt;"あり","",IF($K39="更新の可能性あり","あり",IF(OR($J39="",$G39=""),"なし",IF(OR(NOT(ISNUMBER($G39)),NOT(ISNUMBER($J39)),$G39&gt;80000,$J39&gt;80000),"要確認（日付）",IF($J39&gt;IF(DAY(EDATE($G39,2))&lt;DAY($G39),EOMONTH($G39,2),EDATE($G39,2)-1),"あり","なし"))))))</f>
+        <f>IF($B39="","",IF($I39="なし","あり",IF($I39&lt;&gt;"あり","",IF($K39="更新の可能性あり","あり",IF(OR($J39="",$G39=""),"なし",IF(OR(NOT(ISNUMBER($G39)),NOT(ISNUMBER($J39)),$G39&gt;80000,$J39&gt;80000),"要確認（日付）",IF($J39&gt;IF(DAY(EDATE($G39,2))&lt;DAY($G39),EOMONTH($G39,2),EDATE($G39,2)-1),"あり","なし")))))))</f>
         <v/>
       </c>
       <c r="P39" s="23">
@@ -5764,7 +5775,7 @@
       <c r="M40" s="17" t="n"/>
       <c r="N40" s="17" t="n"/>
       <c r="O40" s="23">
-        <f>IF($B40="","",IF($I40="なし","あり",IF($I40&lt;&gt;"あり","",IF($K40="更新の可能性あり","あり",IF(OR($J40="",$G40=""),"なし",IF(OR(NOT(ISNUMBER($G40)),NOT(ISNUMBER($J40)),$G40&gt;80000,$J40&gt;80000),"要確認（日付）",IF($J40&gt;IF(DAY(EDATE($G40,2))&lt;DAY($G40),EOMONTH($G40,2),EDATE($G40,2)-1),"あり","なし"))))))</f>
+        <f>IF($B40="","",IF($I40="なし","あり",IF($I40&lt;&gt;"あり","",IF($K40="更新の可能性あり","あり",IF(OR($J40="",$G40=""),"なし",IF(OR(NOT(ISNUMBER($G40)),NOT(ISNUMBER($J40)),$G40&gt;80000,$J40&gt;80000),"要確認（日付）",IF($J40&gt;IF(DAY(EDATE($G40,2))&lt;DAY($G40),EOMONTH($G40,2),EDATE($G40,2)-1),"あり","なし")))))))</f>
         <v/>
       </c>
       <c r="P40" s="23">
@@ -5846,7 +5857,7 @@
       <c r="M41" s="17" t="n"/>
       <c r="N41" s="17" t="n"/>
       <c r="O41" s="23">
-        <f>IF($B41="","",IF($I41="なし","あり",IF($I41&lt;&gt;"あり","",IF($K41="更新の可能性あり","あり",IF(OR($J41="",$G41=""),"なし",IF(OR(NOT(ISNUMBER($G41)),NOT(ISNUMBER($J41)),$G41&gt;80000,$J41&gt;80000),"要確認（日付）",IF($J41&gt;IF(DAY(EDATE($G41,2))&lt;DAY($G41),EOMONTH($G41,2),EDATE($G41,2)-1),"あり","なし"))))))</f>
+        <f>IF($B41="","",IF($I41="なし","あり",IF($I41&lt;&gt;"あり","",IF($K41="更新の可能性あり","あり",IF(OR($J41="",$G41=""),"なし",IF(OR(NOT(ISNUMBER($G41)),NOT(ISNUMBER($J41)),$G41&gt;80000,$J41&gt;80000),"要確認（日付）",IF($J41&gt;IF(DAY(EDATE($G41,2))&lt;DAY($G41),EOMONTH($G41,2),EDATE($G41,2)-1),"あり","なし")))))))</f>
         <v/>
       </c>
       <c r="P41" s="23">
@@ -5928,7 +5939,7 @@
       <c r="M42" s="17" t="n"/>
       <c r="N42" s="17" t="n"/>
       <c r="O42" s="23">
-        <f>IF($B42="","",IF($I42="なし","あり",IF($I42&lt;&gt;"あり","",IF($K42="更新の可能性あり","あり",IF(OR($J42="",$G42=""),"なし",IF(OR(NOT(ISNUMBER($G42)),NOT(ISNUMBER($J42)),$G42&gt;80000,$J42&gt;80000),"要確認（日付）",IF($J42&gt;IF(DAY(EDATE($G42,2))&lt;DAY($G42),EOMONTH($G42,2),EDATE($G42,2)-1),"あり","なし"))))))</f>
+        <f>IF($B42="","",IF($I42="なし","あり",IF($I42&lt;&gt;"あり","",IF($K42="更新の可能性あり","あり",IF(OR($J42="",$G42=""),"なし",IF(OR(NOT(ISNUMBER($G42)),NOT(ISNUMBER($J42)),$G42&gt;80000,$J42&gt;80000),"要確認（日付）",IF($J42&gt;IF(DAY(EDATE($G42,2))&lt;DAY($G42),EOMONTH($G42,2),EDATE($G42,2)-1),"あり","なし")))))))</f>
         <v/>
       </c>
       <c r="P42" s="23">
@@ -6010,7 +6021,7 @@
       <c r="M43" s="17" t="n"/>
       <c r="N43" s="17" t="n"/>
       <c r="O43" s="23">
-        <f>IF($B43="","",IF($I43="なし","あり",IF($I43&lt;&gt;"あり","",IF($K43="更新の可能性あり","あり",IF(OR($J43="",$G43=""),"なし",IF(OR(NOT(ISNUMBER($G43)),NOT(ISNUMBER($J43)),$G43&gt;80000,$J43&gt;80000),"要確認（日付）",IF($J43&gt;IF(DAY(EDATE($G43,2))&lt;DAY($G43),EOMONTH($G43,2),EDATE($G43,2)-1),"あり","なし"))))))</f>
+        <f>IF($B43="","",IF($I43="なし","あり",IF($I43&lt;&gt;"あり","",IF($K43="更新の可能性あり","あり",IF(OR($J43="",$G43=""),"なし",IF(OR(NOT(ISNUMBER($G43)),NOT(ISNUMBER($J43)),$G43&gt;80000,$J43&gt;80000),"要確認（日付）",IF($J43&gt;IF(DAY(EDATE($G43,2))&lt;DAY($G43),EOMONTH($G43,2),EDATE($G43,2)-1),"あり","なし")))))))</f>
         <v/>
       </c>
       <c r="P43" s="23">
@@ -6092,7 +6103,7 @@
       <c r="M44" s="17" t="n"/>
       <c r="N44" s="17" t="n"/>
       <c r="O44" s="23">
-        <f>IF($B44="","",IF($I44="なし","あり",IF($I44&lt;&gt;"あり","",IF($K44="更新の可能性あり","あり",IF(OR($J44="",$G44=""),"なし",IF(OR(NOT(ISNUMBER($G44)),NOT(ISNUMBER($J44)),$G44&gt;80000,$J44&gt;80000),"要確認（日付）",IF($J44&gt;IF(DAY(EDATE($G44,2))&lt;DAY($G44),EOMONTH($G44,2),EDATE($G44,2)-1),"あり","なし"))))))</f>
+        <f>IF($B44="","",IF($I44="なし","あり",IF($I44&lt;&gt;"あり","",IF($K44="更新の可能性あり","あり",IF(OR($J44="",$G44=""),"なし",IF(OR(NOT(ISNUMBER($G44)),NOT(ISNUMBER($J44)),$G44&gt;80000,$J44&gt;80000),"要確認（日付）",IF($J44&gt;IF(DAY(EDATE($G44,2))&lt;DAY($G44),EOMONTH($G44,2),EDATE($G44,2)-1),"あり","なし")))))))</f>
         <v/>
       </c>
       <c r="P44" s="23">
@@ -6174,7 +6185,7 @@
       <c r="M45" s="17" t="n"/>
       <c r="N45" s="17" t="n"/>
       <c r="O45" s="23">
-        <f>IF($B45="","",IF($I45="なし","あり",IF($I45&lt;&gt;"あり","",IF($K45="更新の可能性あり","あり",IF(OR($J45="",$G45=""),"なし",IF(OR(NOT(ISNUMBER($G45)),NOT(ISNUMBER($J45)),$G45&gt;80000,$J45&gt;80000),"要確認（日付）",IF($J45&gt;IF(DAY(EDATE($G45,2))&lt;DAY($G45),EOMONTH($G45,2),EDATE($G45,2)-1),"あり","なし"))))))</f>
+        <f>IF($B45="","",IF($I45="なし","あり",IF($I45&lt;&gt;"あり","",IF($K45="更新の可能性あり","あり",IF(OR($J45="",$G45=""),"なし",IF(OR(NOT(ISNUMBER($G45)),NOT(ISNUMBER($J45)),$G45&gt;80000,$J45&gt;80000),"要確認（日付）",IF($J45&gt;IF(DAY(EDATE($G45,2))&lt;DAY($G45),EOMONTH($G45,2),EDATE($G45,2)-1),"あり","なし")))))))</f>
         <v/>
       </c>
       <c r="P45" s="23">
@@ -6256,7 +6267,7 @@
       <c r="M46" s="17" t="n"/>
       <c r="N46" s="17" t="n"/>
       <c r="O46" s="23">
-        <f>IF($B46="","",IF($I46="なし","あり",IF($I46&lt;&gt;"あり","",IF($K46="更新の可能性あり","あり",IF(OR($J46="",$G46=""),"なし",IF(OR(NOT(ISNUMBER($G46)),NOT(ISNUMBER($J46)),$G46&gt;80000,$J46&gt;80000),"要確認（日付）",IF($J46&gt;IF(DAY(EDATE($G46,2))&lt;DAY($G46),EOMONTH($G46,2),EDATE($G46,2)-1),"あり","なし"))))))</f>
+        <f>IF($B46="","",IF($I46="なし","あり",IF($I46&lt;&gt;"あり","",IF($K46="更新の可能性あり","あり",IF(OR($J46="",$G46=""),"なし",IF(OR(NOT(ISNUMBER($G46)),NOT(ISNUMBER($J46)),$G46&gt;80000,$J46&gt;80000),"要確認（日付）",IF($J46&gt;IF(DAY(EDATE($G46,2))&lt;DAY($G46),EOMONTH($G46,2),EDATE($G46,2)-1),"あり","なし")))))))</f>
         <v/>
       </c>
       <c r="P46" s="23">
@@ -6338,7 +6349,7 @@
       <c r="M47" s="17" t="n"/>
       <c r="N47" s="17" t="n"/>
       <c r="O47" s="23">
-        <f>IF($B47="","",IF($I47="なし","あり",IF($I47&lt;&gt;"あり","",IF($K47="更新の可能性あり","あり",IF(OR($J47="",$G47=""),"なし",IF(OR(NOT(ISNUMBER($G47)),NOT(ISNUMBER($J47)),$G47&gt;80000,$J47&gt;80000),"要確認（日付）",IF($J47&gt;IF(DAY(EDATE($G47,2))&lt;DAY($G47),EOMONTH($G47,2),EDATE($G47,2)-1),"あり","なし"))))))</f>
+        <f>IF($B47="","",IF($I47="なし","あり",IF($I47&lt;&gt;"あり","",IF($K47="更新の可能性あり","あり",IF(OR($J47="",$G47=""),"なし",IF(OR(NOT(ISNUMBER($G47)),NOT(ISNUMBER($J47)),$G47&gt;80000,$J47&gt;80000),"要確認（日付）",IF($J47&gt;IF(DAY(EDATE($G47,2))&lt;DAY($G47),EOMONTH($G47,2),EDATE($G47,2)-1),"あり","なし")))))))</f>
         <v/>
       </c>
       <c r="P47" s="23">
@@ -6420,7 +6431,7 @@
       <c r="M48" s="17" t="n"/>
       <c r="N48" s="17" t="n"/>
       <c r="O48" s="23">
-        <f>IF($B48="","",IF($I48="なし","あり",IF($I48&lt;&gt;"あり","",IF($K48="更新の可能性あり","あり",IF(OR($J48="",$G48=""),"なし",IF(OR(NOT(ISNUMBER($G48)),NOT(ISNUMBER($J48)),$G48&gt;80000,$J48&gt;80000),"要確認（日付）",IF($J48&gt;IF(DAY(EDATE($G48,2))&lt;DAY($G48),EOMONTH($G48,2),EDATE($G48,2)-1),"あり","なし"))))))</f>
+        <f>IF($B48="","",IF($I48="なし","あり",IF($I48&lt;&gt;"あり","",IF($K48="更新の可能性あり","あり",IF(OR($J48="",$G48=""),"なし",IF(OR(NOT(ISNUMBER($G48)),NOT(ISNUMBER($J48)),$G48&gt;80000,$J48&gt;80000),"要確認（日付）",IF($J48&gt;IF(DAY(EDATE($G48,2))&lt;DAY($G48),EOMONTH($G48,2),EDATE($G48,2)-1),"あり","なし")))))))</f>
         <v/>
       </c>
       <c r="P48" s="23">
@@ -6502,7 +6513,7 @@
       <c r="M49" s="17" t="n"/>
       <c r="N49" s="17" t="n"/>
       <c r="O49" s="23">
-        <f>IF($B49="","",IF($I49="なし","あり",IF($I49&lt;&gt;"あり","",IF($K49="更新の可能性あり","あり",IF(OR($J49="",$G49=""),"なし",IF(OR(NOT(ISNUMBER($G49)),NOT(ISNUMBER($J49)),$G49&gt;80000,$J49&gt;80000),"要確認（日付）",IF($J49&gt;IF(DAY(EDATE($G49,2))&lt;DAY($G49),EOMONTH($G49,2),EDATE($G49,2)-1),"あり","なし"))))))</f>
+        <f>IF($B49="","",IF($I49="なし","あり",IF($I49&lt;&gt;"あり","",IF($K49="更新の可能性あり","あり",IF(OR($J49="",$G49=""),"なし",IF(OR(NOT(ISNUMBER($G49)),NOT(ISNUMBER($J49)),$G49&gt;80000,$J49&gt;80000),"要確認（日付）",IF($J49&gt;IF(DAY(EDATE($G49,2))&lt;DAY($G49),EOMONTH($G49,2),EDATE($G49,2)-1),"あり","なし")))))))</f>
         <v/>
       </c>
       <c r="P49" s="23">
@@ -6584,7 +6595,7 @@
       <c r="M50" s="17" t="n"/>
       <c r="N50" s="17" t="n"/>
       <c r="O50" s="23">
-        <f>IF($B50="","",IF($I50="なし","あり",IF($I50&lt;&gt;"あり","",IF($K50="更新の可能性あり","あり",IF(OR($J50="",$G50=""),"なし",IF(OR(NOT(ISNUMBER($G50)),NOT(ISNUMBER($J50)),$G50&gt;80000,$J50&gt;80000),"要確認（日付）",IF($J50&gt;IF(DAY(EDATE($G50,2))&lt;DAY($G50),EOMONTH($G50,2),EDATE($G50,2)-1),"あり","なし"))))))</f>
+        <f>IF($B50="","",IF($I50="なし","あり",IF($I50&lt;&gt;"あり","",IF($K50="更新の可能性あり","あり",IF(OR($J50="",$G50=""),"なし",IF(OR(NOT(ISNUMBER($G50)),NOT(ISNUMBER($J50)),$G50&gt;80000,$J50&gt;80000),"要確認（日付）",IF($J50&gt;IF(DAY(EDATE($G50,2))&lt;DAY($G50),EOMONTH($G50,2),EDATE($G50,2)-1),"あり","なし")))))))</f>
         <v/>
       </c>
       <c r="P50" s="23">
@@ -6666,7 +6677,7 @@
       <c r="M51" s="17" t="n"/>
       <c r="N51" s="17" t="n"/>
       <c r="O51" s="23">
-        <f>IF($B51="","",IF($I51="なし","あり",IF($I51&lt;&gt;"あり","",IF($K51="更新の可能性あり","あり",IF(OR($J51="",$G51=""),"なし",IF(OR(NOT(ISNUMBER($G51)),NOT(ISNUMBER($J51)),$G51&gt;80000,$J51&gt;80000),"要確認（日付）",IF($J51&gt;IF(DAY(EDATE($G51,2))&lt;DAY($G51),EOMONTH($G51,2),EDATE($G51,2)-1),"あり","なし"))))))</f>
+        <f>IF($B51="","",IF($I51="なし","あり",IF($I51&lt;&gt;"あり","",IF($K51="更新の可能性あり","あり",IF(OR($J51="",$G51=""),"なし",IF(OR(NOT(ISNUMBER($G51)),NOT(ISNUMBER($J51)),$G51&gt;80000,$J51&gt;80000),"要確認（日付）",IF($J51&gt;IF(DAY(EDATE($G51,2))&lt;DAY($G51),EOMONTH($G51,2),EDATE($G51,2)-1),"あり","なし")))))))</f>
         <v/>
       </c>
       <c r="P51" s="23">
@@ -6748,7 +6759,7 @@
       <c r="M52" s="17" t="n"/>
       <c r="N52" s="17" t="n"/>
       <c r="O52" s="23">
-        <f>IF($B52="","",IF($I52="なし","あり",IF($I52&lt;&gt;"あり","",IF($K52="更新の可能性あり","あり",IF(OR($J52="",$G52=""),"なし",IF(OR(NOT(ISNUMBER($G52)),NOT(ISNUMBER($J52)),$G52&gt;80000,$J52&gt;80000),"要確認（日付）",IF($J52&gt;IF(DAY(EDATE($G52,2))&lt;DAY($G52),EOMONTH($G52,2),EDATE($G52,2)-1),"あり","なし"))))))</f>
+        <f>IF($B52="","",IF($I52="なし","あり",IF($I52&lt;&gt;"あり","",IF($K52="更新の可能性あり","あり",IF(OR($J52="",$G52=""),"なし",IF(OR(NOT(ISNUMBER($G52)),NOT(ISNUMBER($J52)),$G52&gt;80000,$J52&gt;80000),"要確認（日付）",IF($J52&gt;IF(DAY(EDATE($G52,2))&lt;DAY($G52),EOMONTH($G52,2),EDATE($G52,2)-1),"あり","なし")))))))</f>
         <v/>
       </c>
       <c r="P52" s="23">
@@ -6830,7 +6841,7 @@
       <c r="M53" s="17" t="n"/>
       <c r="N53" s="17" t="n"/>
       <c r="O53" s="23">
-        <f>IF($B53="","",IF($I53="なし","あり",IF($I53&lt;&gt;"あり","",IF($K53="更新の可能性あり","あり",IF(OR($J53="",$G53=""),"なし",IF(OR(NOT(ISNUMBER($G53)),NOT(ISNUMBER($J53)),$G53&gt;80000,$J53&gt;80000),"要確認（日付）",IF($J53&gt;IF(DAY(EDATE($G53,2))&lt;DAY($G53),EOMONTH($G53,2),EDATE($G53,2)-1),"あり","なし"))))))</f>
+        <f>IF($B53="","",IF($I53="なし","あり",IF($I53&lt;&gt;"あり","",IF($K53="更新の可能性あり","あり",IF(OR($J53="",$G53=""),"なし",IF(OR(NOT(ISNUMBER($G53)),NOT(ISNUMBER($J53)),$G53&gt;80000,$J53&gt;80000),"要確認（日付）",IF($J53&gt;IF(DAY(EDATE($G53,2))&lt;DAY($G53),EOMONTH($G53,2),EDATE($G53,2)-1),"あり","なし")))))))</f>
         <v/>
       </c>
       <c r="P53" s="23">
@@ -6912,7 +6923,7 @@
       <c r="M54" s="17" t="n"/>
       <c r="N54" s="17" t="n"/>
       <c r="O54" s="23">
-        <f>IF($B54="","",IF($I54="なし","あり",IF($I54&lt;&gt;"あり","",IF($K54="更新の可能性あり","あり",IF(OR($J54="",$G54=""),"なし",IF(OR(NOT(ISNUMBER($G54)),NOT(ISNUMBER($J54)),$G54&gt;80000,$J54&gt;80000),"要確認（日付）",IF($J54&gt;IF(DAY(EDATE($G54,2))&lt;DAY($G54),EOMONTH($G54,2),EDATE($G54,2)-1),"あり","なし"))))))</f>
+        <f>IF($B54="","",IF($I54="なし","あり",IF($I54&lt;&gt;"あり","",IF($K54="更新の可能性あり","あり",IF(OR($J54="",$G54=""),"なし",IF(OR(NOT(ISNUMBER($G54)),NOT(ISNUMBER($J54)),$G54&gt;80000,$J54&gt;80000),"要確認（日付）",IF($J54&gt;IF(DAY(EDATE($G54,2))&lt;DAY($G54),EOMONTH($G54,2),EDATE($G54,2)-1),"あり","なし")))))))</f>
         <v/>
       </c>
       <c r="P54" s="23">
@@ -6994,7 +7005,7 @@
       <c r="M55" s="17" t="n"/>
       <c r="N55" s="17" t="n"/>
       <c r="O55" s="23">
-        <f>IF($B55="","",IF($I55="なし","あり",IF($I55&lt;&gt;"あり","",IF($K55="更新の可能性あり","あり",IF(OR($J55="",$G55=""),"なし",IF(OR(NOT(ISNUMBER($G55)),NOT(ISNUMBER($J55)),$G55&gt;80000,$J55&gt;80000),"要確認（日付）",IF($J55&gt;IF(DAY(EDATE($G55,2))&lt;DAY($G55),EOMONTH($G55,2),EDATE($G55,2)-1),"あり","なし"))))))</f>
+        <f>IF($B55="","",IF($I55="なし","あり",IF($I55&lt;&gt;"あり","",IF($K55="更新の可能性あり","あり",IF(OR($J55="",$G55=""),"なし",IF(OR(NOT(ISNUMBER($G55)),NOT(ISNUMBER($J55)),$G55&gt;80000,$J55&gt;80000),"要確認（日付）",IF($J55&gt;IF(DAY(EDATE($G55,2))&lt;DAY($G55),EOMONTH($G55,2),EDATE($G55,2)-1),"あり","なし")))))))</f>
         <v/>
       </c>
       <c r="P55" s="23">
@@ -7076,7 +7087,7 @@
       <c r="M56" s="17" t="n"/>
       <c r="N56" s="17" t="n"/>
       <c r="O56" s="23">
-        <f>IF($B56="","",IF($I56="なし","あり",IF($I56&lt;&gt;"あり","",IF($K56="更新の可能性あり","あり",IF(OR($J56="",$G56=""),"なし",IF(OR(NOT(ISNUMBER($G56)),NOT(ISNUMBER($J56)),$G56&gt;80000,$J56&gt;80000),"要確認（日付）",IF($J56&gt;IF(DAY(EDATE($G56,2))&lt;DAY($G56),EOMONTH($G56,2),EDATE($G56,2)-1),"あり","なし"))))))</f>
+        <f>IF($B56="","",IF($I56="なし","あり",IF($I56&lt;&gt;"あり","",IF($K56="更新の可能性あり","あり",IF(OR($J56="",$G56=""),"なし",IF(OR(NOT(ISNUMBER($G56)),NOT(ISNUMBER($J56)),$G56&gt;80000,$J56&gt;80000),"要確認（日付）",IF($J56&gt;IF(DAY(EDATE($G56,2))&lt;DAY($G56),EOMONTH($G56,2),EDATE($G56,2)-1),"あり","なし")))))))</f>
         <v/>
       </c>
       <c r="P56" s="23">
@@ -7158,7 +7169,7 @@
       <c r="M57" s="17" t="n"/>
       <c r="N57" s="17" t="n"/>
       <c r="O57" s="23">
-        <f>IF($B57="","",IF($I57="なし","あり",IF($I57&lt;&gt;"あり","",IF($K57="更新の可能性あり","あり",IF(OR($J57="",$G57=""),"なし",IF(OR(NOT(ISNUMBER($G57)),NOT(ISNUMBER($J57)),$G57&gt;80000,$J57&gt;80000),"要確認（日付）",IF($J57&gt;IF(DAY(EDATE($G57,2))&lt;DAY($G57),EOMONTH($G57,2),EDATE($G57,2)-1),"あり","なし"))))))</f>
+        <f>IF($B57="","",IF($I57="なし","あり",IF($I57&lt;&gt;"あり","",IF($K57="更新の可能性あり","あり",IF(OR($J57="",$G57=""),"なし",IF(OR(NOT(ISNUMBER($G57)),NOT(ISNUMBER($J57)),$G57&gt;80000,$J57&gt;80000),"要確認（日付）",IF($J57&gt;IF(DAY(EDATE($G57,2))&lt;DAY($G57),EOMONTH($G57,2),EDATE($G57,2)-1),"あり","なし")))))))</f>
         <v/>
       </c>
       <c r="P57" s="23">
@@ -7240,7 +7251,7 @@
       <c r="M58" s="17" t="n"/>
       <c r="N58" s="17" t="n"/>
       <c r="O58" s="23">
-        <f>IF($B58="","",IF($I58="なし","あり",IF($I58&lt;&gt;"あり","",IF($K58="更新の可能性あり","あり",IF(OR($J58="",$G58=""),"なし",IF(OR(NOT(ISNUMBER($G58)),NOT(ISNUMBER($J58)),$G58&gt;80000,$J58&gt;80000),"要確認（日付）",IF($J58&gt;IF(DAY(EDATE($G58,2))&lt;DAY($G58),EOMONTH($G58,2),EDATE($G58,2)-1),"あり","なし"))))))</f>
+        <f>IF($B58="","",IF($I58="なし","あり",IF($I58&lt;&gt;"あり","",IF($K58="更新の可能性あり","あり",IF(OR($J58="",$G58=""),"なし",IF(OR(NOT(ISNUMBER($G58)),NOT(ISNUMBER($J58)),$G58&gt;80000,$J58&gt;80000),"要確認（日付）",IF($J58&gt;IF(DAY(EDATE($G58,2))&lt;DAY($G58),EOMONTH($G58,2),EDATE($G58,2)-1),"あり","なし")))))))</f>
         <v/>
       </c>
       <c r="P58" s="23">
